--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>4</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,10 +2085,10 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="2">
-                  <v>91</v>
+                  <v>92</v>
                 </pt>
                 <pt idx="3">
                   <v>10</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>51</v>
+                  <v>52</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>Belden Inc</v>
+                </pt>
+                <pt idx="7">
                   <v>Hitachi</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>Merck</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>Schneider Electric</v>
-                </pt>
-                <pt idx="9">
-                  <v>UVM Health Network</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>20</v>
+                  <v>22</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>26</v>
+                  <v>27</v>
                 </pt>
                 <pt idx="1">
                   <v>31</v>
@@ -3005,7 +3005,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z104" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z106" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z104"/>
+  <dimension ref="A1:Z106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14705,6 +14705,230 @@
         </is>
       </c>
       <c r="Z104" s="37" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B105" s="37" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C105" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D105" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E105" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="33" t="inlineStr">
+        <is>
+          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
+        </is>
+      </c>
+      <c r="G105" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H105" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I105" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J105" s="33" t="inlineStr">
+        <is>
+          <t>Visibility</t>
+        </is>
+      </c>
+      <c r="K105" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L105" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M105" s="33" t="inlineStr">
+        <is>
+          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces for review is detected rather than discovered by a customer</t>
+        </is>
+      </c>
+      <c r="N105" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O105" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for TSMC's 28nm production capacity reduction. The customer states the cut is directly impacting their supply chain and that visibility around June could have avoided the current allocation situation. Cause established as a portal fault: the news was captured by the vendor sources but never surfaced on the analyst portal, so no coverage was ever created.</t>
+        </is>
+      </c>
+      <c r="P105" s="33" t="n"/>
+      <c r="Q105" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R105" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S105" s="39" t="n"/>
+      <c r="T105" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U105" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V105" s="33" t="inlineStr">
+        <is>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+      <c r="W105" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X105" s="33" t="inlineStr">
+        <is>
+          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue.</t>
+        </is>
+      </c>
+      <c r="Y105" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z105" s="37" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B106" s="37" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C106" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D106" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E106" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="33" t="inlineStr">
+        <is>
+          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
+        </is>
+      </c>
+      <c r="G106" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H106" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I106" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J106" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K106" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L106" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M106" s="33" t="inlineStr">
+        <is>
+          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
+        </is>
+      </c>
+      <c r="N106" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O106" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
+        </is>
+      </c>
+      <c r="P106" s="33" t="n"/>
+      <c r="Q106" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R106" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S106" s="39" t="n"/>
+      <c r="T106" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U106" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V106" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W106" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X106" s="33" t="inlineStr">
+        <is>
+          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
+        </is>
+      </c>
+      <c r="Y106" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z106" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -16462,7 +16686,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35555555555555557</v>
+        <v>0.34782608695652173</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -16503,7 +16727,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13333333333333333</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -16545,7 +16769,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.07608695652173914</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -16587,7 +16811,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.044444444444444446</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -16629,7 +16853,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.044444444444444446</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -16671,7 +16895,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03260869565217391</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -16706,14 +16930,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -16748,14 +16972,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -16790,14 +17014,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -16832,14 +17056,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17146,13 +17370,13 @@
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K87" s="76" t="n">
         <v>3</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -17266,13 +17490,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>13</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>24</v>
+                  <v>27</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="L84" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M84" s="33" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L85" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M85" s="33" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="L102" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M102" s="33" t="inlineStr">
@@ -14470,7 +14470,11 @@
           <t>EAO-35/EAO-36</t>
         </is>
       </c>
-      <c r="X102" s="33" t="n"/>
+      <c r="X102" s="33" t="inlineStr">
+        <is>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+        </is>
+      </c>
       <c r="Y102" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1774,10 +1774,10 @@
                   <v>27</v>
                 </pt>
                 <pt idx="2">
-                  <v>17</v>
+                  <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="L31" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M31" s="33" t="inlineStr">
@@ -6900,7 +6900,11 @@
           <t>CAN-3298</t>
         </is>
       </c>
-      <c r="X31" s="33" t="n"/>
+      <c r="X31" s="33" t="inlineStr">
+        <is>
+          <t>No RCA was issued. An RCA was requested on this record, but the case was closed out with a clarification to Harman rather than a root cause analysis, and no root cause was documented at the time. Recorded as it happened rather than reconstructed after the fact.</t>
+        </is>
+      </c>
       <c r="Y31" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>6</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,10 +2085,10 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="2">
-                  <v>92</v>
+                  <v>93</v>
                 </pt>
                 <pt idx="3">
                   <v>10</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>52</v>
+                  <v>54</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
                   <v>12</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>22</v>
+                  <v>23</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z106" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z108" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z106"/>
+  <dimension ref="A1:Z108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14937,6 +14937,222 @@
         </is>
       </c>
       <c r="Z106" s="37" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B107" s="37" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C107" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D107" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E107" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="33" t="inlineStr">
+        <is>
+          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
+        </is>
+      </c>
+      <c r="G107" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H107" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I107" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J107" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K107" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L107" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M107" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
+        </is>
+      </c>
+      <c r="N107" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O107" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
+        </is>
+      </c>
+      <c r="P107" s="33" t="n"/>
+      <c r="Q107" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R107" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S107" s="39" t="n"/>
+      <c r="T107" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U107" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V107" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W107" s="33" t="inlineStr">
+        <is>
+          <t>EAO-40</t>
+        </is>
+      </c>
+      <c r="X107" s="33" t="n"/>
+      <c r="Y107" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z107" s="37" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B108" s="37" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C108" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D108" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil</t>
+        </is>
+      </c>
+      <c r="E108" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="33" t="inlineStr">
+        <is>
+          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
+        </is>
+      </c>
+      <c r="G108" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H108" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I108" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J108" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K108" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L108" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M108" s="33" t="inlineStr">
+        <is>
+          <t>Coverage of specialist insolvency publications and court filing registries, so a CCAA or equivalent restructuring filing is captured at source rather than from mainstream news</t>
+        </is>
+      </c>
+      <c r="N108" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O108" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-41 (Open). Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca.</t>
+        </is>
+      </c>
+      <c r="P108" s="33" t="n"/>
+      <c r="Q108" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R108" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S108" s="39" t="n"/>
+      <c r="T108" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U108" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V108" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W108" s="33" t="inlineStr">
+        <is>
+          <t>EAO-41</t>
+        </is>
+      </c>
+      <c r="X108" s="33" t="n"/>
+      <c r="Y108" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z108" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -16690,11 +16906,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.34782608695652173</v>
+        <v>0.35106382978723405</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -16716,13 +16932,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -16735,7 +16951,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13043478260869565</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -16777,7 +16993,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07608695652173914</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -16819,7 +17035,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -16861,7 +17077,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -16903,7 +17119,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03260869565217391</v>
+        <v>0.031914893617021274</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -16945,7 +17161,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -16987,7 +17203,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17029,7 +17245,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17052,13 +17268,13 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K75" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
@@ -17071,7 +17287,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17498,13 +17714,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>13</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,7 +2085,7 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="2">
                   <v>93</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>54</v>
+                  <v>55</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2666,7 +2666,7 @@
                   <v>33</v>
                 </pt>
                 <pt idx="1">
-                  <v>12</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z108" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z109" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z108"/>
+  <dimension ref="A1:Z109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15153,6 +15153,118 @@
         </is>
       </c>
       <c r="Z108" s="37" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B109" s="37" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C109" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D109" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E109" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="33" t="inlineStr">
+        <is>
+          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
+        </is>
+      </c>
+      <c r="G109" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H109" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I109" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J109" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K109" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L109" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M109" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring of national insolvency registries and regional business press - KSV1870 and ORF both carried this filing - so an Austrian or EU restructuring proceeding is captured at the registry rather than after a customer finds it</t>
+        </is>
+      </c>
+      <c r="N109" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O109" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-42 (Open). Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. The customer notes similar detection concerns have been escalated before and has asked for an RCA plus corrective and preventive actions.</t>
+        </is>
+      </c>
+      <c r="P109" s="33" t="inlineStr">
+        <is>
+          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
+        </is>
+      </c>
+      <c r="Q109" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R109" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S109" s="39" t="n"/>
+      <c r="T109" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U109" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V109" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W109" s="33" t="inlineStr">
+        <is>
+          <t>EAO-42</t>
+        </is>
+      </c>
+      <c r="X109" s="33" t="n"/>
+      <c r="Y109" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z109" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -16910,7 +17022,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35106382978723405</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -16932,13 +17044,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -16948,10 +17060,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.1368421052631579</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -16993,7 +17105,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07446808510638298</v>
+        <v>0.07368421052631578</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17035,7 +17147,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17077,7 +17189,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17119,7 +17231,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031914893617021274</v>
+        <v>0.031578947368421054</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17161,7 +17273,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17203,7 +17315,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17245,7 +17357,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17287,7 +17399,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17714,13 +17826,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>13</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>9</v>
+                  <v>11</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1771,7 +1771,7 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>27</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
@@ -2085,13 +2085,13 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>93</v>
+                  <v>94</v>
                 </pt>
                 <pt idx="3">
-                  <v>10</v>
+                  <v>11</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>57</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2663,10 +2663,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="1">
-                  <v>13</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="5">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z109" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z112" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z109"/>
+  <dimension ref="A1:Z112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15038,7 +15038,11 @@
           <t>EAO-40</t>
         </is>
       </c>
-      <c r="X107" s="33" t="n"/>
+      <c r="X107" s="33" t="inlineStr">
+        <is>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. On 24-Sep-2026 Engineering further confirmed to the customer that the vendor being onboarded next quarter already carries that source, so the same event would have been captured under the incoming network. The RCA is being revised to state that and re-shared.</t>
+        </is>
+      </c>
       <c r="Y107" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -15088,7 +15092,7 @@
       </c>
       <c r="J108" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K108" s="33" t="inlineStr">
@@ -15098,12 +15102,12 @@
       </c>
       <c r="L108" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M108" s="33" t="inlineStr">
         <is>
-          <t>Coverage of specialist insolvency publications and court filing registries, so a CCAA or equivalent restructuring filing is captured at source rather than from mainstream news</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
@@ -15113,7 +15117,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-41 (Open). Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca.</t>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15146,13 +15150,19 @@
           <t>EAO-41</t>
         </is>
       </c>
-      <c r="X108" s="33" t="n"/>
+      <c r="X108" s="33" t="inlineStr">
+        <is>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+        </is>
+      </c>
       <c r="Y108" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z108" s="37" t="n"/>
+      <c r="Z108" s="37" t="n">
+        <v>46288</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="35" t="n">
@@ -15196,7 +15206,7 @@
       </c>
       <c r="J109" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K109" s="33" t="inlineStr">
@@ -15206,12 +15216,12 @@
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M109" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of national insolvency registries and regional business press - KSV1870 and ORF both carried this filing - so an Austrian or EU restructuring proceeding is captured at the registry rather than after a customer finds it</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N109" s="33" t="inlineStr">
@@ -15221,7 +15231,7 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-42 (Open). Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. The customer notes similar detection concerns have been escalated before and has asked for an RCA plus corrective and preventive actions.</t>
+          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
         </is>
       </c>
       <c r="P109" s="33" t="inlineStr">
@@ -15258,13 +15268,353 @@
           <t>EAO-42</t>
         </is>
       </c>
-      <c r="X109" s="33" t="n"/>
+      <c r="X109" s="33" t="inlineStr">
+        <is>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+        </is>
+      </c>
       <c r="Y109" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z109" s="37" t="n"/>
+      <c r="Z109" s="37" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B110" s="37" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C110" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E110" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="33" t="inlineStr">
+        <is>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+        </is>
+      </c>
+      <c r="G110" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H110" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring Strategy RFI</t>
+        </is>
+      </c>
+      <c r="I110" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J110" s="33" t="inlineStr">
+        <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="K110" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L110" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M110" s="33" t="inlineStr">
+        <is>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+        </is>
+      </c>
+      <c r="N110" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O110" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P110" s="33" t="n"/>
+      <c r="Q110" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R110" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S110" s="39" t="n"/>
+      <c r="T110" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U110" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V110" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W110" s="33" t="inlineStr">
+        <is>
+          <t>EAO-43</t>
+        </is>
+      </c>
+      <c r="X110" s="33" t="inlineStr">
+        <is>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+        </is>
+      </c>
+      <c r="Y110" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z110" s="37" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B111" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C111" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E111" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="33" t="inlineStr">
+        <is>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+        </is>
+      </c>
+      <c r="G111" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H111" s="33" t="inlineStr">
+        <is>
+          <t>Wrong Relevancy</t>
+        </is>
+      </c>
+      <c r="I111" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J111" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K111" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L111" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M111" s="33" t="inlineStr">
+        <is>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+        </is>
+      </c>
+      <c r="N111" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O111" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+        </is>
+      </c>
+      <c r="P111" s="33" t="n"/>
+      <c r="Q111" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R111" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S111" s="39" t="n"/>
+      <c r="T111" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U111" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V111" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W111" s="33" t="inlineStr">
+        <is>
+          <t>EAO-44</t>
+        </is>
+      </c>
+      <c r="X111" s="33" t="n"/>
+      <c r="Y111" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z111" s="37" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B112" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C112" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E112" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+        </is>
+      </c>
+      <c r="G112" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H112" s="33" t="inlineStr">
+        <is>
+          <t>Delayed Event</t>
+        </is>
+      </c>
+      <c r="I112" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J112" s="33" t="inlineStr">
+        <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="K112" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L112" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M112" s="33" t="inlineStr">
+        <is>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+        </is>
+      </c>
+      <c r="N112" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O112" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
+      <c r="Q112" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R112" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S112" s="39" t="n">
+        <v>252</v>
+      </c>
+      <c r="T112" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U112" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V112" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W112" s="33" t="inlineStr">
+        <is>
+          <t>EAO-45</t>
+        </is>
+      </c>
+      <c r="X112" s="33" t="n"/>
+      <c r="Y112" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z112" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17018,11 +17368,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3473684210526316</v>
+        <v>0.35051546391752575</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17044,13 +17394,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -17060,10 +17410,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.14432989690721648</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17105,7 +17455,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07368421052631578</v>
+        <v>0.07216494845360824</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17147,7 +17497,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17189,7 +17539,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17231,7 +17581,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031578947368421054</v>
+        <v>0.030927835051546393</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17273,7 +17623,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17315,7 +17665,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17357,7 +17707,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17380,13 +17730,13 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
@@ -17399,7 +17749,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17589,10 +17939,10 @@
         <v>3</v>
       </c>
       <c r="K82" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
@@ -17826,13 +18176,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -2085,10 +2085,10 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>94</v>
+                  <v>96</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z112" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z113" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z112"/>
+  <dimension ref="A1:Z113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14781,7 +14781,7 @@
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for TSMC's 28nm production capacity reduction. The customer states the cut is directly impacting their supply chain and that visibility around June could have avoided the current allocation situation. Cause established as a portal fault: the news was captured by the vendor sources but never surfaced on the analyst portal, so no coverage was ever created.</t>
+          <t>EAO-39: Belden reported receiving no EventWatch notification and seeing no related news for TSMC's 28nm production capacity reduction, stating the cut was directly impacting their supply chain. Cause established as a portal fault: the news was captured by the vendor sources but never surfaced on the analyst portal, so no coverage was ever created. On 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs. No customer notification was therefore owed. The portal fault stands on its own, so Missed_Flag remains Yes on the coverage sense of the term, and Severity is reduced from High to Medium now that no supply exposure sits behind the record.</t>
         </is>
       </c>
       <c r="P105" s="33" t="n"/>
@@ -14801,7 +14801,7 @@
       </c>
       <c r="U105" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V105" s="33" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue.</t>
+          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue. Separately, the customer's exposure claim did not hold: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities, and the near-identical name is what led the customer to believe they were covered.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
@@ -15399,16 +15399,16 @@
         <v>46266</v>
       </c>
       <c r="B111" s="37" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E111" s="39" t="n">
@@ -15416,27 +15416,27 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>TSMC 28nm Capacity Reduction – News Authenticity and Verification Criteria Queried (Belden)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>An evidence-grade label carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and a later company denial or correction updates that grade rather than arriving as a separate query</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+          <t>EAO-39: Belden cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked three questions: how EventWatch screens real from fake news, what criteria establish that an event notification is not fake, and whether the TSMC 28nm capacity reduction is real or fake. A written assessment was issued covering the source hierarchy, the five evidence grades and the specific TSMC timeline. Separately, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15486,18 +15486,22 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
-        </is>
-      </c>
-      <c r="X111" s="33" t="n"/>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X111" s="33" t="inlineStr">
+        <is>
+          <t>Not a defect. Assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A. Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000, customer migration toward 12nm and reallocation toward silicon-interposer production; Economic Daily News (May 2026) reported Fab 15A converting from 22nm/28nm toward 4nm; TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged. The two views are not contradictory: an unchanged mature-node strategy is compatible with selective conversion at one fab. The specific 25 percent reduction was attributed to supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
+        </is>
+      </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -15511,12 +15515,12 @@
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15524,7 +15528,7 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
@@ -15534,7 +15538,7 @@
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
@@ -15544,7 +15548,7 @@
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15559,35 +15563,29 @@
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
-        </is>
-      </c>
-      <c r="P112" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="n"/>
       <c r="Q112" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R112" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S112" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S112" s="39" t="n"/>
       <c r="T112" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15595,17 +15593,17 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X112" s="33" t="n"/>
@@ -15615,6 +15613,120 @@
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B113" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C113" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+        </is>
+      </c>
+      <c r="G113" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr">
+        <is>
+          <t>Delayed Event</t>
+        </is>
+      </c>
+      <c r="I113" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J113" s="33" t="inlineStr">
+        <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="K113" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L113" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M113" s="33" t="inlineStr">
+        <is>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+        </is>
+      </c>
+      <c r="N113" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O113" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
+      <c r="Q113" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R113" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" s="39" t="n">
+        <v>252</v>
+      </c>
+      <c r="T113" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U113" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V113" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W113" s="33" t="inlineStr">
+        <is>
+          <t>EAO-45</t>
+        </is>
+      </c>
+      <c r="X113" s="33" t="n"/>
+      <c r="Y113" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z113" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18059,10 +18171,10 @@
         <v>5</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -18179,10 +18291,10 @@
         <v>97</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>11</v>
+                  <v>10</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>3</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,10 +2085,10 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="2">
-                  <v>96</v>
+                  <v>98</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>57</v>
+                  <v>56</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
-                  <v>Belden Inc</v>
+                  <v>Hitachi</v>
                 </pt>
                 <pt idx="7">
-                  <v>Hitachi</v>
+                  <v>Merck</v>
                 </pt>
                 <pt idx="8">
-                  <v>Merck</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="9">
-                  <v>Schneider Electric</v>
+                  <v>UVM Health Network</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>23</v>
+                  <v>22</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3005,7 +3005,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
+                  <v>7</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z113" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z114" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z113"/>
+  <dimension ref="A1:Z114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14741,12 +14741,12 @@
       </c>
       <c r="G105" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H105" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="J105" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K105" s="33" t="inlineStr">
@@ -14781,13 +14781,13 @@
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden reported receiving no EventWatch notification and seeing no related news for TSMC's 28nm production capacity reduction, stating the cut was directly impacting their supply chain. Cause established as a portal fault: the news was captured by the vendor sources but never surfaced on the analyst portal, so no coverage was ever created. On 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs. No customer notification was therefore owed. The portal fault stands on its own, so Missed_Flag remains Yes on the coverage sense of the term, and Severity is reduced from High to Medium now that no supply exposure sits behind the record.</t>
+          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. On 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage. The Engineering investigation recorded in RCA Details found the article was captured by the vendor sources and never surfaced on the analyst portal. The missing partner mapping is logged as its own record.</t>
         </is>
       </c>
       <c r="P105" s="33" t="n"/>
       <c r="Q105" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R105" s="39" t="n">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="V105" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W105" s="33" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="X107" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. On 24-Sep-2026 Engineering further confirmed to the customer that the vendor being onboarded next quarter already carries that source, so the same event would have been captured under the incoming network. The RCA is being revised to state that and re-shared.</t>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
         </is>
       </c>
       <c r="Y107" s="33" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="U109" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V109" s="33" t="inlineStr">
@@ -15511,16 +15511,16 @@
         <v>46266</v>
       </c>
       <c r="B112" s="37" t="n">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>TSMC Not Mapped as a Partner in Belden's BOM – Supplier Mapping Gap (Belden)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
@@ -15558,12 +15558,12 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>Name-collision detection across the supplier mapping surface, so a customer who maps Taiwan Semiconductor Co., Ltd. while expecting coverage of Taiwan Semiconductor Manufacturing Company is warned at mapping time rather than finding out through a missed-event complaint</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+          <t>EAO-39: Established while investigating the TSMC 28nm query. Belden confirmed on 22-Sep-2026 that TSMC is not mapped as a partner in their BOM - they source the wafer through Broadcom - and that the Taiwan Semiconductor entity they had mapped is a different company covering resistors and MOSFETs. The missing partner mapping is why no notification was applicable to their org, independent of the portal fault logged on the coverage record. Explained to the customer; no RCA requested.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
@@ -15603,13 +15603,17 @@
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
-        </is>
-      </c>
-      <c r="X112" s="33" t="n"/>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X112" s="33" t="inlineStr">
+        <is>
+          <t>Not an EventWatch defect. TSMC was absent from the customer's mapped supply network, so no customer-specific notification or WarRoom was applicable regardless of coverage. The customer had mapped Taiwan Semiconductor Co., Ltd., a discrete components supplier covering resistors and MOSFETs, and read it as Taiwan Semiconductor Manufacturing Company; the two are different suppliers in different commodities and the near-identical name is what led to the expectation of coverage. Nothing in the mapping surface flags that collision.</t>
+        </is>
+      </c>
       <c r="Y112" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
@@ -15623,12 +15627,12 @@
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E113" s="39" t="n">
@@ -15636,7 +15640,7 @@
       </c>
       <c r="F113" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G113" s="33" t="inlineStr">
@@ -15646,7 +15650,7 @@
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I113" s="33" t="inlineStr">
@@ -15656,7 +15660,7 @@
       </c>
       <c r="J113" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K113" s="33" t="inlineStr">
@@ -15671,35 +15675,29 @@
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
-        </is>
-      </c>
-      <c r="P113" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="n"/>
       <c r="Q113" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R113" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S113" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S113" s="39" t="n"/>
       <c r="T113" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15707,17 +15705,17 @@
       </c>
       <c r="U113" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V113" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W113" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X113" s="33" t="n"/>
@@ -15727,6 +15725,120 @@
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B114" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C114" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E114" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="33" t="inlineStr">
+        <is>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+        </is>
+      </c>
+      <c r="G114" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr">
+        <is>
+          <t>Delayed Event</t>
+        </is>
+      </c>
+      <c r="I114" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J114" s="33" t="inlineStr">
+        <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="K114" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L114" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M114" s="33" t="inlineStr">
+        <is>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+        </is>
+      </c>
+      <c r="N114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O114" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
+      <c r="Q114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R114" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S114" s="39" t="n">
+        <v>252</v>
+      </c>
+      <c r="T114" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U114" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V114" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W114" s="33" t="inlineStr">
+        <is>
+          <t>EAO-45</t>
+        </is>
+      </c>
+      <c r="X114" s="33" t="n"/>
+      <c r="Y114" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z114" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17484,7 +17596,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35051546391752575</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17525,7 +17637,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.14432989690721648</v>
+        <v>0.14583333333333334</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17567,7 +17679,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07216494845360824</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17609,7 +17721,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17651,7 +17763,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17693,7 +17805,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030927835051546393</v>
+        <v>0.03125</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17728,14 +17840,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17770,14 +17882,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17812,14 +17924,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17854,14 +17966,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>UVM Health Network</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18168,13 +18280,13 @@
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -18288,13 +18400,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>10</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>5</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>29</v>
+                  <v>28</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>56</v>
+                  <v>53</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2663,10 +2663,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>34</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
-                  <v>14</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>22</v>
+                  <v>21</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>35</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>8</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="5">
                   <v>5</v>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="G108" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H108" s="33" t="inlineStr">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding.</t>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="G113" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H113" s="33" t="inlineStr">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="L113" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M113" s="33" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (Open). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. No investigation comments on the ticket yet.</t>
+          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="G114" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H114" s="33" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-45 (Open). Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. Logged as an Inquiry on review. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026; the rest of the delay is still under investigation.</t>
         </is>
       </c>
       <c r="P114" s="33" t="inlineStr">
@@ -15832,7 +15832,11 @@
           <t>EAO-45</t>
         </is>
       </c>
-      <c r="X114" s="33" t="n"/>
+      <c r="X114" s="33" t="inlineStr">
+        <is>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+        </is>
+      </c>
       <c r="Y114" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -17592,11 +17596,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3541666666666667</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17618,10 +17622,10 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K67" s="75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="75" t="n">
         <v>13</v>
@@ -17634,10 +17638,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.14583333333333334</v>
+        <v>0.13978494623655913</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17679,7 +17683,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17721,7 +17725,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17763,7 +17767,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17805,7 +17809,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03125</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17847,7 +17851,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17889,7 +17893,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17931,7 +17935,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17954,10 +17958,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -17973,7 +17977,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18400,10 +18404,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>113</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>9</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>1</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>27</v>
+                  <v>28</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,13 +2085,13 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="2">
-                  <v>93</v>
+                  <v>98</v>
                 </pt>
                 <pt idx="3">
-                  <v>10</v>
+                  <v>11</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>53</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
-                  <v>Belden Inc</v>
+                  <v>Hitachi</v>
                 </pt>
                 <pt idx="7">
-                  <v>Hitachi</v>
+                  <v>Merck</v>
                 </pt>
                 <pt idx="8">
-                  <v>Merck</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="9">
-                  <v>Schneider Electric</v>
+                  <v>UVM Health Network</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>23</v>
+                  <v>21</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -3005,7 +3005,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
+                  <v>7</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z109" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z114" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z109"/>
+  <dimension ref="A1:Z114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14741,12 +14741,12 @@
       </c>
       <c r="G105" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H105" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="J105" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K105" s="33" t="inlineStr">
@@ -14781,13 +14781,13 @@
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for TSMC's 28nm production capacity reduction. The customer states the cut is directly impacting their supply chain and that visibility around June could have avoided the current allocation situation. Cause established as a portal fault: the news was captured by the vendor sources but never surfaced on the analyst portal, so no coverage was ever created.</t>
+          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. On 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage. The Engineering investigation recorded in RCA Details found the article was captured by the vendor sources and never surfaced on the analyst portal. The missing partner mapping is logged as its own record.</t>
         </is>
       </c>
       <c r="P105" s="33" t="n"/>
       <c r="Q105" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R105" s="39" t="n">
@@ -14801,12 +14801,12 @@
       </c>
       <c r="U105" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V105" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W105" s="33" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue.</t>
+          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue. Separately, the customer's exposure claim did not hold: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities, and the near-identical name is what led the customer to believe they were covered.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
@@ -15038,7 +15038,11 @@
           <t>EAO-40</t>
         </is>
       </c>
-      <c r="X107" s="33" t="n"/>
+      <c r="X107" s="33" t="inlineStr">
+        <is>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
+        </is>
+      </c>
       <c r="Y107" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -15073,7 +15077,7 @@
       </c>
       <c r="G108" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H108" s="33" t="inlineStr">
@@ -15088,7 +15092,7 @@
       </c>
       <c r="J108" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K108" s="33" t="inlineStr">
@@ -15098,12 +15102,12 @@
       </c>
       <c r="L108" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M108" s="33" t="inlineStr">
         <is>
-          <t>Coverage of specialist insolvency publications and court filing registries, so a CCAA or equivalent restructuring filing is captured at source rather than from mainstream news</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
@@ -15113,7 +15117,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-41 (Open). Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca.</t>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15146,13 +15150,19 @@
           <t>EAO-41</t>
         </is>
       </c>
-      <c r="X108" s="33" t="n"/>
+      <c r="X108" s="33" t="inlineStr">
+        <is>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+        </is>
+      </c>
       <c r="Y108" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z108" s="37" t="n"/>
+      <c r="Z108" s="37" t="n">
+        <v>46288</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="35" t="n">
@@ -15196,7 +15206,7 @@
       </c>
       <c r="J109" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K109" s="33" t="inlineStr">
@@ -15206,12 +15216,12 @@
       </c>
       <c r="L109" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M109" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of national insolvency registries and regional business press - KSV1870 and ORF both carried this filing - so an Austrian or EU restructuring proceeding is captured at the registry rather than after a customer finds it</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N109" s="33" t="inlineStr">
@@ -15221,7 +15231,7 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-42 (Open). Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. The customer notes similar detection concerns have been escalated before and has asked for an RCA plus corrective and preventive actions.</t>
+          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
         </is>
       </c>
       <c r="P109" s="33" t="inlineStr">
@@ -15245,26 +15255,594 @@
       </c>
       <c r="U109" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V109" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W109" s="33" t="inlineStr">
+        <is>
+          <t>EAO-42</t>
+        </is>
+      </c>
+      <c r="X109" s="33" t="inlineStr">
+        <is>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+        </is>
+      </c>
+      <c r="Y109" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z109" s="37" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B110" s="37" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C110" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D110" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E110" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="33" t="inlineStr">
+        <is>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+        </is>
+      </c>
+      <c r="G110" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H110" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring Strategy RFI</t>
+        </is>
+      </c>
+      <c r="I110" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J110" s="33" t="inlineStr">
+        <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="K110" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L110" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M110" s="33" t="inlineStr">
+        <is>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+        </is>
+      </c>
+      <c r="N110" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O110" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P110" s="33" t="n"/>
+      <c r="Q110" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R110" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S110" s="39" t="n"/>
+      <c r="T110" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U110" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V110" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W110" s="33" t="inlineStr">
+        <is>
+          <t>EAO-43</t>
+        </is>
+      </c>
+      <c r="X110" s="33" t="inlineStr">
+        <is>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+        </is>
+      </c>
+      <c r="Y110" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z110" s="37" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B111" s="37" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C111" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D111" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E111" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="33" t="inlineStr">
+        <is>
+          <t>TSMC 28nm Capacity Reduction – News Authenticity and Verification Criteria Queried (Belden)</t>
+        </is>
+      </c>
+      <c r="G111" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H111" s="33" t="inlineStr">
+        <is>
+          <t>Customer Requested Verification</t>
+        </is>
+      </c>
+      <c r="I111" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J111" s="33" t="inlineStr">
+        <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="K111" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L111" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M111" s="33" t="inlineStr">
+        <is>
+          <t>An evidence-grade label carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and a later company denial or correction updates that grade rather than arriving as a separate query</t>
+        </is>
+      </c>
+      <c r="N111" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O111" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39: Belden cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked three questions: how EventWatch screens real from fake news, what criteria establish that an event notification is not fake, and whether the TSMC 28nm capacity reduction is real or fake. A written assessment was issued covering the source hierarchy, the five evidence grades and the specific TSMC timeline. Separately, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs.</t>
+        </is>
+      </c>
+      <c r="P111" s="33" t="n"/>
+      <c r="Q111" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R111" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S111" s="39" t="n"/>
+      <c r="T111" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U111" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V111" s="33" t="inlineStr">
+        <is>
+          <t>Other Control Automation</t>
+        </is>
+      </c>
+      <c r="W111" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X111" s="33" t="inlineStr">
+        <is>
+          <t>Not a defect. Assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A. Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000, customer migration toward 12nm and reallocation toward silicon-interposer production; Economic Daily News (May 2026) reported Fab 15A converting from 22nm/28nm toward 4nm; TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged. The two views are not contradictory: an unchanged mature-node strategy is compatible with selective conversion at one fab. The specific 25 percent reduction was attributed to supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
+        </is>
+      </c>
+      <c r="Y111" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z111" s="37" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B112" s="37" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C112" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D112" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E112" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="33" t="inlineStr">
+        <is>
+          <t>TSMC Not Mapped as a Partner in Belden's BOM – Supplier Mapping Gap (Belden)</t>
+        </is>
+      </c>
+      <c r="G112" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H112" s="33" t="inlineStr">
+        <is>
+          <t>Supplier Impact Mapping Clarification</t>
+        </is>
+      </c>
+      <c r="I112" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J112" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K112" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L112" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M112" s="33" t="inlineStr">
+        <is>
+          <t>Name-collision detection across the supplier mapping surface, so a customer who maps Taiwan Semiconductor Co., Ltd. while expecting coverage of Taiwan Semiconductor Manufacturing Company is warned at mapping time rather than finding out through a missed-event complaint</t>
+        </is>
+      </c>
+      <c r="N112" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O112" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39: Established while investigating the TSMC 28nm query. Belden confirmed on 22-Sep-2026 that TSMC is not mapped as a partner in their BOM - they source the wafer through Broadcom - and that the Taiwan Semiconductor entity they had mapped is a different company covering resistors and MOSFETs. The missing partner mapping is why no notification was applicable to their org, independent of the portal fault logged on the coverage record. Explained to the customer; no RCA requested.</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="n"/>
+      <c r="Q112" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R112" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S112" s="39" t="n"/>
+      <c r="T112" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U112" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V112" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W112" s="33" t="inlineStr">
+        <is>
+          <t>EAO-39</t>
+        </is>
+      </c>
+      <c r="X112" s="33" t="inlineStr">
+        <is>
+          <t>Not an EventWatch defect. TSMC was absent from the customer's mapped supply network, so no customer-specific notification or WarRoom was applicable regardless of coverage. The customer had mapped Taiwan Semiconductor Co., Ltd., a discrete components supplier covering resistors and MOSFETs, and read it as Taiwan Semiconductor Manufacturing Company; the two are different suppliers in different commodities and the near-identical name is what led to the expectation of coverage. Nothing in the mapping surface flags that collision.</t>
+        </is>
+      </c>
+      <c r="Y112" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z112" s="37" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B113" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C113" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+        </is>
+      </c>
+      <c r="G113" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr">
+        <is>
+          <t>Wrong Relevancy</t>
+        </is>
+      </c>
+      <c r="I113" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J113" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K113" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L113" s="33" t="inlineStr">
+        <is>
+          <t>Clarification Provided</t>
+        </is>
+      </c>
+      <c r="M113" s="33" t="inlineStr">
+        <is>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+        </is>
+      </c>
+      <c r="N113" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O113" s="33" t="inlineStr">
+        <is>
+          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="n"/>
+      <c r="Q113" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R113" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" s="39" t="n"/>
+      <c r="T113" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U113" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V113" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W113" s="33" t="inlineStr">
+        <is>
+          <t>EAO-44</t>
+        </is>
+      </c>
+      <c r="X113" s="33" t="n"/>
+      <c r="Y113" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z113" s="37" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B114" s="37" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C114" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E114" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="33" t="inlineStr">
+        <is>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+        </is>
+      </c>
+      <c r="G114" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr">
+        <is>
+          <t>Delayed Event</t>
+        </is>
+      </c>
+      <c r="I114" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J114" s="33" t="inlineStr">
+        <is>
+          <t>Captured Late</t>
+        </is>
+      </c>
+      <c r="K114" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L114" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M114" s="33" t="inlineStr">
+        <is>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+        </is>
+      </c>
+      <c r="N114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O114" s="33" t="inlineStr">
+        <is>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. Logged as an Inquiry on review. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026; the rest of the delay is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
+      <c r="Q114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R114" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S114" s="39" t="n">
+        <v>252</v>
+      </c>
+      <c r="T114" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U114" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V109" s="33" t="inlineStr">
+      <c r="V114" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W109" s="33" t="inlineStr">
-        <is>
-          <t>EAO-42</t>
-        </is>
-      </c>
-      <c r="X109" s="33" t="n"/>
-      <c r="Y109" s="33" t="inlineStr">
+      <c r="W114" s="33" t="inlineStr">
+        <is>
+          <t>EAO-45</t>
+        </is>
+      </c>
+      <c r="X114" s="33" t="inlineStr">
+        <is>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+        </is>
+      </c>
+      <c r="Y114" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z109" s="37" t="n"/>
+      <c r="Z114" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17022,7 +17600,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3473684210526316</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17044,13 +17622,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K67" s="75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -17063,7 +17641,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.13978494623655913</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17105,7 +17683,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07368421052631578</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17147,7 +17725,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17189,7 +17767,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17231,7 +17809,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031578947368421054</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17266,14 +17844,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17308,14 +17886,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17350,14 +17928,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17383,23 +17961,23 @@
         <v>13</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>UVM Health Network</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17589,10 +18167,10 @@
         <v>3</v>
       </c>
       <c r="K82" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
@@ -17706,13 +18284,13 @@
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -17826,13 +18404,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>8</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -2088,7 +2088,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="2">
-                  <v>98</v>
+                  <v>96</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z114" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z112" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z114"/>
+  <dimension ref="A1:Z112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -14766,12 +14766,12 @@
       </c>
       <c r="L105" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M105" s="33" t="inlineStr">
         <is>
-          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces for review is detected rather than discovered by a customer</t>
+          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
         </is>
       </c>
       <c r="N105" s="33" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. On 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage. The Engineering investigation recorded in RCA Details found the article was captured by the vendor sources and never surfaced on the analyst portal. The missing partner mapping is logged as its own record.</t>
+          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. The query ran on through two follow-ups, both part of the same contact rather than separate records. First, on 18-Sep-2026 the customer cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked how EventWatch separates real reporting from fake, what criteria establish that a notification is not fake, and whether the 28nm reduction is real; a written assessment was issued covering the source hierarchy, the five evidence grades and the TSMC timeline. Second, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage.</t>
         </is>
       </c>
       <c r="P105" s="33" t="n"/>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created. The failure sits between ingestion and the analyst queue. Separately, the customer's exposure claim did not hold: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities, and the near-identical name is what led the customer to believe they were covered.</t>
+          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
@@ -15399,16 +15399,16 @@
         <v>46266</v>
       </c>
       <c r="B111" s="37" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E111" s="39" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>TSMC 28nm Capacity Reduction – News Authenticity and Verification Criteria Queried (Belden)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
@@ -15426,17 +15426,17 @@
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>An evidence-grade label carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and a later company denial or correction updates that grade rather than arriving as a separate query</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked three questions: how EventWatch screens real from fake news, what criteria establish that an event notification is not fake, and whether the TSMC 28nm capacity reduction is real or fake. A written assessment was issued covering the source hierarchy, the five evidence grades and the specific TSMC timeline. Separately, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs.</t>
+          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15486,22 +15486,18 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
         <is>
-          <t>EAO-39</t>
-        </is>
-      </c>
-      <c r="X111" s="33" t="inlineStr">
-        <is>
-          <t>Not a defect. Assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A. Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000, customer migration toward 12nm and reallocation toward silicon-interposer production; Economic Daily News (May 2026) reported Fab 15A converting from 22nm/28nm toward 4nm; TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged. The two views are not contradictory: an unchanged mature-node strategy is compatible with selective conversion at one fab. The specific 25 percent reduction was attributed to supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
-        </is>
-      </c>
+          <t>EAO-44</t>
+        </is>
+      </c>
+      <c r="X111" s="33" t="n"/>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -15511,16 +15507,16 @@
         <v>46266</v>
       </c>
       <c r="B112" s="37" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15528,7 +15524,7 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>TSMC Not Mapped as a Partner in Belden's BOM – Supplier Mapping Gap (Belden)</t>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
@@ -15538,17 +15534,17 @@
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15558,34 +15554,40 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Name-collision detection across the supplier mapping surface, so a customer who maps Taiwan Semiconductor Co., Ltd. while expecting coverage of Taiwan Semiconductor Manufacturing Company is warned at mapping time rather than finding out through a missed-event complaint</t>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Established while investigating the TSMC 28nm query. Belden confirmed on 22-Sep-2026 that TSMC is not mapped as a partner in their BOM - they source the wafer through Broadcom - and that the Taiwan Semiconductor entity they had mapped is a different company covering resistors and MOSFETs. The missing partner mapping is why no notification was applicable to their org, independent of the portal fault logged on the coverage record. Explained to the customer; no RCA requested.</t>
-        </is>
-      </c>
-      <c r="P112" s="33" t="n"/>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. Logged as an Inquiry on review. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026; the rest of the delay is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R112" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S112" s="39" t="n"/>
+      <c r="S112" s="39" t="n">
+        <v>252</v>
+      </c>
       <c r="T112" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15593,256 +15595,30 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-39</t>
+          <t>EAO-45</t>
         </is>
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Not an EventWatch defect. TSMC was absent from the customer's mapped supply network, so no customer-specific notification or WarRoom was applicable regardless of coverage. The customer had mapped Taiwan Semiconductor Co., Ltd., a discrete components supplier covering resistors and MOSFETs, and read it as Taiwan Semiconductor Manufacturing Company; the two are different suppliers in different commodities and the near-identical name is what led to the expectation of coverage. Nothing in the mapping surface flags that collision.</t>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="35" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B113" s="37" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C113" s="33" t="inlineStr">
-        <is>
-          <t>Bankruptcy</t>
-        </is>
-      </c>
-      <c r="D113" s="33" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="E113" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="33" t="inlineStr">
-        <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
-        </is>
-      </c>
-      <c r="G113" s="33" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H113" s="33" t="inlineStr">
-        <is>
-          <t>Wrong Relevancy</t>
-        </is>
-      </c>
-      <c r="I113" s="33" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J113" s="33" t="inlineStr">
-        <is>
-          <t>Mapping</t>
-        </is>
-      </c>
-      <c r="K113" s="33" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L113" s="33" t="inlineStr">
-        <is>
-          <t>Clarification Provided</t>
-        </is>
-      </c>
-      <c r="M113" s="33" t="inlineStr">
-        <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
-        </is>
-      </c>
-      <c r="N113" s="33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O113" s="33" t="inlineStr">
-        <is>
-          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
-        </is>
-      </c>
-      <c r="P113" s="33" t="n"/>
-      <c r="Q113" s="33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R113" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="S113" s="39" t="n"/>
-      <c r="T113" s="35" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="U113" s="33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V113" s="33" t="inlineStr">
-        <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="W113" s="33" t="inlineStr">
-        <is>
-          <t>EAO-44</t>
-        </is>
-      </c>
-      <c r="X113" s="33" t="n"/>
-      <c r="Y113" s="33" t="inlineStr">
-        <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z113" s="37" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="35" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B114" s="37" t="n">
-        <v>46289</v>
-      </c>
-      <c r="C114" s="33" t="inlineStr">
-        <is>
-          <t>Factory Fire</t>
-        </is>
-      </c>
-      <c r="D114" s="33" t="inlineStr">
-        <is>
-          <t>Ford</t>
-        </is>
-      </c>
-      <c r="E114" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="33" t="inlineStr">
-        <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
-        </is>
-      </c>
-      <c r="G114" s="33" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="H114" s="33" t="inlineStr">
-        <is>
-          <t>Delayed Event</t>
-        </is>
-      </c>
-      <c r="I114" s="33" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="J114" s="33" t="inlineStr">
-        <is>
-          <t>Captured Late</t>
-        </is>
-      </c>
-      <c r="K114" s="33" t="inlineStr">
-        <is>
-          <t>Improvement</t>
-        </is>
-      </c>
-      <c r="L114" s="33" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M114" s="33" t="inlineStr">
-        <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
-        </is>
-      </c>
-      <c r="N114" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O114" s="33" t="inlineStr">
-        <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. Logged as an Inquiry on review. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026; the rest of the delay is still under investigation.</t>
-        </is>
-      </c>
-      <c r="P114" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
-      <c r="Q114" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R114" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="S114" s="39" t="n">
-        <v>252</v>
-      </c>
-      <c r="T114" s="35" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="U114" s="33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="V114" s="33" t="inlineStr">
-        <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W114" s="33" t="inlineStr">
-        <is>
-          <t>EAO-45</t>
-        </is>
-      </c>
-      <c r="X114" s="33" t="inlineStr">
-        <is>
-          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
-        </is>
-      </c>
-      <c r="Y114" s="33" t="inlineStr">
-        <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z114" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18287,10 +18063,10 @@
         <v>4</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -18407,10 +18183,10 @@
         <v>93</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1768,10 +1768,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>45</v>
+                  <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>28</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="L22" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M22" s="33" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O22" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3278 (Closed). Danaher received the notification email for the Massachusetts Level 3 Critical Drought WarRoom, but the WarRoom was empty across Suppliers, Sites, Parts and Products and was absent from the WarRoom listing page more than three hours after creation. CS recorded it as reproducible and as a likely regression of CAN-2921.</t>
+          <t>From Jira CAN-3278 (Closed). Danaher received the notification email for the Massachusetts Level 3 Critical Drought WarRoom, but the WarRoom was empty across Suppliers, Sites, Parts and Products and was absent from the WarRoom listing page more than three hours after creation. CS recorded it as reproducible and as a likely regression of CAN-2921. Cause established by Engineering as a production defect in Resilinc Analytics, fixed and verified in late March, and conveyed to the customer.</t>
         </is>
       </c>
       <c r="P22" s="33" t="n"/>
@@ -5965,7 +5965,11 @@
           <t>CAN-3278</t>
         </is>
       </c>
-      <c r="X22" s="33" t="n"/>
+      <c r="X22" s="33" t="inlineStr">
+        <is>
+          <t>Production fault in Resilinc Analytics, established on the ticket by Engineering (Sagar Date). Two faults sat in the same window. First, Customer Impact notifications were failing in production and analysts were manually re-triggering the affected events; twelve events over the preceding month were affected, including 'Authorities Declare Level 3 Critical Drought for Parts of Massachusetts, USA', the event behind this record. That fix was deployed to production on 21-Mar-2026 with no recurrence since. Second, the API that asynchronously populates event site summary data was sitting in its queue for over five hours because the required configuration was missing and the service fell back to a default queue size of 8; the execution pool was raised to a core size of 16, a maximum of 50 and a queue capacity of 2000, and database connections from 16 initial to 48 maximum. Those configurations were deployed on 27-Mar-2026, the what-if event flow was re-verified with Rohit Sawant on 31-Mar-2026, and backend checks confirmed event data being created in near real time. This was not an EventWatch analyst or process failure: the cause was an engineering configuration and notification defect, which is why the record routes to Product &amp; Platform.</t>
+        </is>
+      </c>
       <c r="Y22" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1287,10 +1287,10 @@
                   <v>9</v>
                 </pt>
                 <pt idx="6">
-                  <v>7</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="7">
-                  <v>15</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="8">
                   <v>7</v>
@@ -1409,10 +1409,10 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="7">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="8">
                   <v>6</v>
@@ -1771,7 +1771,7 @@
                   <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>29</v>
+                  <v>26</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>53</v>
+                  <v>50</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2663,10 +2663,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>13</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2999,7 +2999,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="6">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K22" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L22" s="33" t="inlineStr">
@@ -10988,7 +10988,11 @@
           <t>EAO-5</t>
         </is>
       </c>
-      <c r="X70" s="33" t="n"/>
+      <c r="X70" s="33" t="inlineStr">
+        <is>
+          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
+        </is>
+      </c>
       <c r="Y70" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -12239,7 +12243,7 @@
       </c>
       <c r="G82" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H82" s="33" t="inlineStr">
@@ -12264,7 +12268,7 @@
       </c>
       <c r="L82" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M82" s="33" t="inlineStr">
@@ -12274,7 +12278,7 @@
       </c>
       <c r="N82" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O82" s="33" t="inlineStr">
@@ -12284,7 +12288,7 @@
       </c>
       <c r="Q82" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R82" s="39" t="n">
@@ -12308,7 +12312,11 @@
           <t>EAO-22</t>
         </is>
       </c>
-      <c r="X82" s="33" t="n"/>
+      <c r="X82" s="33" t="inlineStr">
+        <is>
+          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
+        </is>
+      </c>
       <c r="Y82" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -12345,7 +12353,7 @@
       </c>
       <c r="G83" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H83" s="33" t="inlineStr">
@@ -12370,7 +12378,7 @@
       </c>
       <c r="L83" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M83" s="33" t="inlineStr">
@@ -12380,7 +12388,7 @@
       </c>
       <c r="N83" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O83" s="33" t="inlineStr">
@@ -12391,7 +12399,7 @@
       <c r="P83" s="33" t="n"/>
       <c r="Q83" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R83" s="39" t="n">
@@ -12416,7 +12424,11 @@
           <t>EAO-24</t>
         </is>
       </c>
-      <c r="X83" s="33" t="n"/>
+      <c r="X83" s="33" t="inlineStr">
+        <is>
+          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
+        </is>
+      </c>
       <c r="Y83" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -13223,7 +13235,7 @@
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
@@ -13248,7 +13260,7 @@
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M91" s="33" t="inlineStr">
@@ -13258,7 +13270,7 @@
       </c>
       <c r="N91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O91" s="33" t="inlineStr">
@@ -13294,7 +13306,11 @@
           <t>EAO-29</t>
         </is>
       </c>
-      <c r="X91" s="33" t="n"/>
+      <c r="X91" s="33" t="inlineStr">
+        <is>
+          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
+        </is>
+      </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -17376,11 +17392,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3548387096774194</v>
+        <v>0.34444444444444444</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17418,10 +17434,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13978494623655913</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17463,7 +17479,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07526881720430108</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17505,7 +17521,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17528,10 +17544,10 @@
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K70" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="76" t="n">
         <v>14</v>
@@ -17547,7 +17563,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17589,7 +17605,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17631,7 +17647,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17673,7 +17689,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17715,7 +17731,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17738,10 +17754,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -17757,7 +17773,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17848,10 +17864,10 @@
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="76" t="n">
         <v>2</v>
@@ -18184,10 +18200,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>111</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2996,10 +2996,10 @@
                   <v>7</v>
                 </pt>
                 <pt idx="5">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="6">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="V70" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W70" s="33" t="inlineStr">
@@ -12248,17 +12248,17 @@
       </c>
       <c r="H82" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I82" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J82" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K82" s="33" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="M82" s="33" t="inlineStr">
         <is>
-          <t>Government/public-sector cyberattack source coverage expansion (regional-language sources)</t>
+          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
         </is>
       </c>
       <c r="N82" s="33" t="inlineStr">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="V82" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W82" s="33" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="Y82" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z82" s="37" t="n">
@@ -12358,17 +12358,17 @@
       </c>
       <c r="H83" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I83" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="M83" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
         </is>
       </c>
       <c r="N83" s="33" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="V83" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W83" s="33" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="Y83" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z83" s="37" t="n">
@@ -13240,17 +13240,17 @@
       </c>
       <c r="H91" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I91" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity Validation</t>
+          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
         </is>
       </c>
       <c r="N91" s="33" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="V91" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W91" s="33" t="inlineStr">
@@ -13313,7 +13313,7 @@
       </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z91" s="37" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1287,10 +1287,10 @@
                   <v>9</v>
                 </pt>
                 <pt idx="6">
-                  <v>7</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="7">
-                  <v>15</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="8">
                   <v>7</v>
@@ -1409,10 +1409,10 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="7">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="8">
                   <v>6</v>
@@ -1768,10 +1768,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>45</v>
+                  <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>28</v>
+                  <v>26</v>
                 </pt>
                 <pt idx="2">
                   <v>18</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>53</v>
+                  <v>50</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2663,10 +2663,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>13</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2996,7 +2996,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="5">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="6">
                   <v>2</v>
@@ -5912,12 +5912,12 @@
       </c>
       <c r="K22" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L22" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M22" s="33" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O22" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3278 (Closed). Danaher received the notification email for the Massachusetts Level 3 Critical Drought WarRoom, but the WarRoom was empty across Suppliers, Sites, Parts and Products and was absent from the WarRoom listing page more than three hours after creation. CS recorded it as reproducible and as a likely regression of CAN-2921.</t>
+          <t>From Jira CAN-3278 (Closed). Danaher received the notification email for the Massachusetts Level 3 Critical Drought WarRoom, but the WarRoom was empty across Suppliers, Sites, Parts and Products and was absent from the WarRoom listing page more than three hours after creation. CS recorded it as reproducible and as a likely regression of CAN-2921. Cause established by Engineering as a production defect in Resilinc Analytics, fixed and verified in late March, and conveyed to the customer.</t>
         </is>
       </c>
       <c r="P22" s="33" t="n"/>
@@ -5965,7 +5965,11 @@
           <t>CAN-3278</t>
         </is>
       </c>
-      <c r="X22" s="33" t="n"/>
+      <c r="X22" s="33" t="inlineStr">
+        <is>
+          <t>Production fault in Resilinc Analytics, established on the ticket by Engineering (Sagar Date). Two faults sat in the same window. First, Customer Impact notifications were failing in production and analysts were manually re-triggering the affected events; twelve events over the preceding month were affected, including 'Authorities Declare Level 3 Critical Drought for Parts of Massachusetts, USA', the event behind this record. That fix was deployed to production on 21-Mar-2026 with no recurrence since. Second, the API that asynchronously populates event site summary data was sitting in its queue for over five hours because the required configuration was missing and the service fell back to a default queue size of 8; the execution pool was raised to a core size of 16, a maximum of 50 and a queue capacity of 2000, and database connections from 16 initial to 48 maximum. Those configurations were deployed on 27-Mar-2026, the what-if event flow was re-verified with Rohit Sawant on 31-Mar-2026, and backend checks confirmed event data being created in near real time. This was not an EventWatch analyst or process failure: the cause was an engineering configuration and notification defect, which is why the record routes to Product &amp; Platform.</t>
+        </is>
+      </c>
       <c r="Y22" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -10976,7 +10980,7 @@
       </c>
       <c r="V70" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W70" s="33" t="inlineStr">
@@ -10984,7 +10988,11 @@
           <t>EAO-5</t>
         </is>
       </c>
-      <c r="X70" s="33" t="n"/>
+      <c r="X70" s="33" t="inlineStr">
+        <is>
+          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
+        </is>
+      </c>
       <c r="Y70" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -12235,22 +12243,22 @@
       </c>
       <c r="G82" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H82" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I82" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J82" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K82" s="33" t="inlineStr">
@@ -12260,17 +12268,17 @@
       </c>
       <c r="L82" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M82" s="33" t="inlineStr">
         <is>
-          <t>Government/public-sector cyberattack source coverage expansion (regional-language sources)</t>
+          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
         </is>
       </c>
       <c r="N82" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O82" s="33" t="inlineStr">
@@ -12280,7 +12288,7 @@
       </c>
       <c r="Q82" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R82" s="39" t="n">
@@ -12296,7 +12304,7 @@
       </c>
       <c r="V82" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W82" s="33" t="inlineStr">
@@ -12304,10 +12312,14 @@
           <t>EAO-22</t>
         </is>
       </c>
-      <c r="X82" s="33" t="n"/>
+      <c r="X82" s="33" t="inlineStr">
+        <is>
+          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
+        </is>
+      </c>
       <c r="Y82" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z82" s="37" t="n">
@@ -12341,22 +12353,22 @@
       </c>
       <c r="G83" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H83" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I83" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12366,17 +12378,17 @@
       </c>
       <c r="L83" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M83" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
         </is>
       </c>
       <c r="N83" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O83" s="33" t="inlineStr">
@@ -12387,7 +12399,7 @@
       <c r="P83" s="33" t="n"/>
       <c r="Q83" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R83" s="39" t="n">
@@ -12404,7 +12416,7 @@
       </c>
       <c r="V83" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W83" s="33" t="inlineStr">
@@ -12412,10 +12424,14 @@
           <t>EAO-24</t>
         </is>
       </c>
-      <c r="X83" s="33" t="n"/>
+      <c r="X83" s="33" t="inlineStr">
+        <is>
+          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
+        </is>
+      </c>
       <c r="Y83" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z83" s="37" t="n">
@@ -13219,22 +13235,22 @@
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I91" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13244,17 +13260,17 @@
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity Validation</t>
+          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
         </is>
       </c>
       <c r="N91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O91" s="33" t="inlineStr">
@@ -13282,7 +13298,7 @@
       </c>
       <c r="V91" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W91" s="33" t="inlineStr">
@@ -13290,10 +13306,14 @@
           <t>EAO-29</t>
         </is>
       </c>
-      <c r="X91" s="33" t="n"/>
+      <c r="X91" s="33" t="inlineStr">
+        <is>
+          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
+        </is>
+      </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z91" s="37" t="n">
@@ -17372,11 +17392,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3548387096774194</v>
+        <v>0.34444444444444444</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17414,10 +17434,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13978494623655913</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17459,7 +17479,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07526881720430108</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17501,7 +17521,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17524,10 +17544,10 @@
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K70" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="76" t="n">
         <v>14</v>
@@ -17543,7 +17563,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17585,7 +17605,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17627,7 +17647,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17669,7 +17689,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17711,7 +17731,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17734,10 +17754,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -17753,7 +17773,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.022222222222222223</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17844,10 +17864,10 @@
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="76" t="n">
         <v>2</v>
@@ -18180,10 +18200,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>111</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,10 +1771,10 @@
                   <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>26</v>
+                  <v>27</v>
                 </pt>
                 <pt idx="2">
-                  <v>18</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>50</v>
+                  <v>51</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -11261,12 +11261,12 @@
       </c>
       <c r="I73" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J73" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
@@ -11276,12 +11276,12 @@
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
+          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
         </is>
       </c>
       <c r="N73" s="33" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="O73" s="33" t="inlineStr">
         <is>
-          <t>Customer reported fire at FXI (Tier 2 supplier) causing Force Majeure at Sage Automotive Interiors. No matching EventWatch notification/WarRoom found during investigation.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
         </is>
       </c>
       <c r="P73" s="33" t="n"/>
@@ -11322,10 +11322,14 @@
           <t>EAO-13</t>
         </is>
       </c>
-      <c r="X73" s="33" t="n"/>
+      <c r="X73" s="33" t="inlineStr">
+        <is>
+          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+        </is>
+      </c>
       <c r="Y73" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z73" s="37" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -4436,7 +4436,11 @@
           <t>CAN-3242</t>
         </is>
       </c>
-      <c r="X7" s="33" t="n"/>
+      <c r="X7" s="33" t="inlineStr">
+        <is>
+          <t>Event publishing failure, root-caused by Engineering on the ticket. Supplier Impact Notifications failed because of a query timeout, which is why the Winter Storm Fern event never surfaced on the supplier portal for K Technologies, and the same event behaved the same way for CAMCO Manufacturing and SPEX Precision Machine Technologies under EATON CORP. The underlying defect was fixed under TENAR-43400 by optimising the queries and shipped in the February End Release, with no recurrence since. The repeated processing failures had left this event's data inconsistent: send_supplier_impact_notification on the event_writeup row was false although the notification had in fact been sent and delivered. That row was corrected in production and on 30-Jul-2026 the event displayed correctly across all three supplier organisations.</t>
+        </is>
+      </c>
       <c r="Y7" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -5150,7 +5154,11 @@
           <t>CAN-3263</t>
         </is>
       </c>
-      <c r="X14" s="33" t="n"/>
+      <c r="X14" s="33" t="inlineStr">
+        <is>
+          <t>Cross-tenant data contamination traced to map normalisation, not to CDIF. The sites appearing in Molex's org were created on 11-Feb-2026, a date on which no MOLEX CDIF file was uploaded; their created_by_id did not match the user who always uploads Molex CDIF files, and their source_id read HITACHI ENERGY map rather than MOLEX. Since sites created through CDIF must carry the upload date, uploader and source of that upload, and no logic exists for cross-tenant site creation through CDIF, DLA or DFI, the sites cannot have arrived that way. The cause was how normalisation was performed for the HITACHI ENERGY map, with potential to affect any other customer or supplier on that map. The incorrectly added sites were deleted under DATA-68858, Tech Support validated every impacted customer, and the irrelevant sites were confirmed removed from all affected orgs on 04-Mar-2026.</t>
+        </is>
+      </c>
       <c r="Y14" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -6481,7 +6489,11 @@
           <t>TS-22591</t>
         </is>
       </c>
-      <c r="X27" s="33" t="n"/>
+      <c r="X27" s="33" t="inlineStr">
+        <is>
+          <t>No root cause was established on the ticket. It was closed on 30-Mar-2026 with the single note that it had been created incorrectly, so the record carries no engineering finding to report.</t>
+        </is>
+      </c>
       <c r="Y27" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -10218,7 +10230,11 @@
           <t>CAN-3377</t>
         </is>
       </c>
-      <c r="X63" s="33" t="n"/>
+      <c r="X63" s="33" t="inlineStr">
+        <is>
+          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
+        </is>
+      </c>
       <c r="Y63" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -10436,7 +10452,11 @@
           <t>EAO-8</t>
         </is>
       </c>
-      <c r="X65" s="33" t="n"/>
+      <c r="X65" s="33" t="inlineStr">
+        <is>
+          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
+        </is>
+      </c>
       <c r="Y65" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -10656,7 +10676,11 @@
           <t>EAO-7</t>
         </is>
       </c>
-      <c r="X67" s="33" t="n"/>
+      <c r="X67" s="33" t="inlineStr">
+        <is>
+          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
+        </is>
+      </c>
       <c r="Y67" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -11098,7 +11122,11 @@
           <t>EAO-11</t>
         </is>
       </c>
-      <c r="X71" s="33" t="n"/>
+      <c r="X71" s="33" t="inlineStr">
+        <is>
+          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+        </is>
+      </c>
       <c r="Y71" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -11880,7 +11908,11 @@
           <t>EAO-18</t>
         </is>
       </c>
-      <c r="X78" s="33" t="n"/>
+      <c r="X78" s="33" t="inlineStr">
+        <is>
+          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
+        </is>
+      </c>
       <c r="Y78" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -12758,7 +12790,11 @@
           <t>CAN-3433</t>
         </is>
       </c>
-      <c r="X86" s="33" t="n"/>
+      <c r="X86" s="33" t="inlineStr">
+        <is>
+          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
+        </is>
+      </c>
       <c r="Y86" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -15485,7 +15521,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15518,7 +15554,11 @@
           <t>EAO-44</t>
         </is>
       </c>
-      <c r="X111" s="33" t="n"/>
+      <c r="X111" s="33" t="inlineStr">
+        <is>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+        </is>
+      </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,10 +1771,10 @@
                   <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>26</v>
+                  <v>27</v>
                 </pt>
                 <pt idx="2">
-                  <v>18</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>50</v>
+                  <v>51</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -4436,7 +4436,11 @@
           <t>CAN-3242</t>
         </is>
       </c>
-      <c r="X7" s="33" t="n"/>
+      <c r="X7" s="33" t="inlineStr">
+        <is>
+          <t>Event publishing failure, root-caused by Engineering on the ticket. Supplier Impact Notifications failed because of a query timeout, which is why the Winter Storm Fern event never surfaced on the supplier portal for K Technologies, and the same event behaved the same way for CAMCO Manufacturing and SPEX Precision Machine Technologies under EATON CORP. The underlying defect was fixed under TENAR-43400 by optimising the queries and shipped in the February End Release, with no recurrence since. The repeated processing failures had left this event's data inconsistent: send_supplier_impact_notification on the event_writeup row was false although the notification had in fact been sent and delivered. That row was corrected in production and on 30-Jul-2026 the event displayed correctly across all three supplier organisations.</t>
+        </is>
+      </c>
       <c r="Y7" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -5150,7 +5154,11 @@
           <t>CAN-3263</t>
         </is>
       </c>
-      <c r="X14" s="33" t="n"/>
+      <c r="X14" s="33" t="inlineStr">
+        <is>
+          <t>Cross-tenant data contamination traced to map normalisation, not to CDIF. The sites appearing in Molex's org were created on 11-Feb-2026, a date on which no MOLEX CDIF file was uploaded; their created_by_id did not match the user who always uploads Molex CDIF files, and their source_id read HITACHI ENERGY map rather than MOLEX. Since sites created through CDIF must carry the upload date, uploader and source of that upload, and no logic exists for cross-tenant site creation through CDIF, DLA or DFI, the sites cannot have arrived that way. The cause was how normalisation was performed for the HITACHI ENERGY map, with potential to affect any other customer or supplier on that map. The incorrectly added sites were deleted under DATA-68858, Tech Support validated every impacted customer, and the irrelevant sites were confirmed removed from all affected orgs on 04-Mar-2026.</t>
+        </is>
+      </c>
       <c r="Y14" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -6481,7 +6489,11 @@
           <t>TS-22591</t>
         </is>
       </c>
-      <c r="X27" s="33" t="n"/>
+      <c r="X27" s="33" t="inlineStr">
+        <is>
+          <t>No root cause was established on the ticket. It was closed on 30-Mar-2026 with the single note that it had been created incorrectly, so the record carries no engineering finding to report.</t>
+        </is>
+      </c>
       <c r="Y27" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -10218,7 +10230,11 @@
           <t>CAN-3377</t>
         </is>
       </c>
-      <c r="X63" s="33" t="n"/>
+      <c r="X63" s="33" t="inlineStr">
+        <is>
+          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
+        </is>
+      </c>
       <c r="Y63" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -10436,7 +10452,11 @@
           <t>EAO-8</t>
         </is>
       </c>
-      <c r="X65" s="33" t="n"/>
+      <c r="X65" s="33" t="inlineStr">
+        <is>
+          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
+        </is>
+      </c>
       <c r="Y65" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -10656,7 +10676,11 @@
           <t>EAO-7</t>
         </is>
       </c>
-      <c r="X67" s="33" t="n"/>
+      <c r="X67" s="33" t="inlineStr">
+        <is>
+          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
+        </is>
+      </c>
       <c r="Y67" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -11098,7 +11122,11 @@
           <t>EAO-11</t>
         </is>
       </c>
-      <c r="X71" s="33" t="n"/>
+      <c r="X71" s="33" t="inlineStr">
+        <is>
+          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+        </is>
+      </c>
       <c r="Y71" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -11261,12 +11289,12 @@
       </c>
       <c r="I73" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J73" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
@@ -11276,12 +11304,12 @@
       </c>
       <c r="L73" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
+          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
         </is>
       </c>
       <c r="N73" s="33" t="inlineStr">
@@ -11291,7 +11319,7 @@
       </c>
       <c r="O73" s="33" t="inlineStr">
         <is>
-          <t>Customer reported fire at FXI (Tier 2 supplier) causing Force Majeure at Sage Automotive Interiors. No matching EventWatch notification/WarRoom found during investigation.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
         </is>
       </c>
       <c r="P73" s="33" t="n"/>
@@ -11322,10 +11350,14 @@
           <t>EAO-13</t>
         </is>
       </c>
-      <c r="X73" s="33" t="n"/>
+      <c r="X73" s="33" t="inlineStr">
+        <is>
+          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+        </is>
+      </c>
       <c r="Y73" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z73" s="37" t="n">
@@ -11876,7 +11908,11 @@
           <t>EAO-18</t>
         </is>
       </c>
-      <c r="X78" s="33" t="n"/>
+      <c r="X78" s="33" t="inlineStr">
+        <is>
+          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
+        </is>
+      </c>
       <c r="Y78" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -12754,7 +12790,11 @@
           <t>CAN-3433</t>
         </is>
       </c>
-      <c r="X86" s="33" t="n"/>
+      <c r="X86" s="33" t="inlineStr">
+        <is>
+          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
+        </is>
+      </c>
       <c r="Y86" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -15481,7 +15521,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>EAO-44: Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Logged as an Inquiry and marked Clarification Provided on review; the explanation was given outside the ticket, which still shows Open in Jira with no comments.</t>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15514,7 +15554,11 @@
           <t>EAO-44</t>
         </is>
       </c>
-      <c r="X111" s="33" t="n"/>
+      <c r="X111" s="33" t="inlineStr">
+        <is>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+        </is>
+      </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="8">
-                  <v>7</v>
+                  <v>10</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,10 +2085,10 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>96</v>
+                  <v>98</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>51</v>
+                  <v>53</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2663,10 +2663,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>12</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>21</v>
+                  <v>22</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2999,7 +2999,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="6">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z112" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z115" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z112"/>
+  <dimension ref="A1:Z115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15683,6 +15683,330 @@
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B113" s="37" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C113" s="33" t="inlineStr">
+        <is>
+          <t>Litigation/Legal</t>
+        </is>
+      </c>
+      <c r="D113" s="33" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="33" t="inlineStr">
+        <is>
+          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
+        </is>
+      </c>
+      <c r="G113" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr">
+        <is>
+          <t>Duplicate WarRooms</t>
+        </is>
+      </c>
+      <c r="I113" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J113" s="33" t="inlineStr">
+        <is>
+          <t>Duplication</t>
+        </is>
+      </c>
+      <c r="K113" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L113" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M113" s="33" t="inlineStr">
+        <is>
+          <t>Duplicate detection against open and recently published WarRooms at the point of creation, so two analysts working the same news cannot each publish a WarRoom for it</t>
+        </is>
+      </c>
+      <c r="N113" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O113" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-46 (Open). Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. An RCA was requested. No investigation comments on the ticket yet, so the cause is not established.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="n"/>
+      <c r="Q113" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R113" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S113" s="39" t="n"/>
+      <c r="T113" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U113" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V113" s="33" t="inlineStr">
+        <is>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+        </is>
+      </c>
+      <c r="W113" s="33" t="inlineStr">
+        <is>
+          <t>EAO-46</t>
+        </is>
+      </c>
+      <c r="X113" s="33" t="n"/>
+      <c r="Y113" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z113" s="37" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B114" s="37" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C114" s="33" t="inlineStr">
+        <is>
+          <t>Financial Distress</t>
+        </is>
+      </c>
+      <c r="D114" s="33" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="E114" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="33" t="inlineStr">
+        <is>
+          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
+        </is>
+      </c>
+      <c r="G114" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I114" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J114" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K114" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L114" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M114" s="33" t="inlineStr">
+        <is>
+          <t>Coverage of Japanese-language business and financial press for listed suppliers, with a path for a credible but company-unconfirmed report to be staged as a monitoring story the customer can see rather than being absent entirely</t>
+        </is>
+      </c>
+      <c r="N114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O114" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="n"/>
+      <c r="Q114" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R114" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S114" s="39" t="n"/>
+      <c r="T114" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U114" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V114" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W114" s="33" t="inlineStr">
+        <is>
+          <t>EAO-47</t>
+        </is>
+      </c>
+      <c r="X114" s="33" t="n"/>
+      <c r="Y114" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z114" s="37" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B115" s="37" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C115" s="33" t="inlineStr">
+        <is>
+          <t>Transport Disruption</t>
+        </is>
+      </c>
+      <c r="D115" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E115" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="33" t="inlineStr">
+        <is>
+          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+        </is>
+      </c>
+      <c r="G115" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H115" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I115" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J115" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K115" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L115" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M115" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring of regional logistics and industry-body publications such as Exporters Western Cape, plus a rule for chronic port and corridor congestion that raises a standing condition into a reportable event when dwell times or berthing delays cross a threshold rather than never qualifying because nothing discretely happened</t>
+        </is>
+      </c>
+      <c r="N115" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O115" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+        </is>
+      </c>
+      <c r="P115" s="33" t="n"/>
+      <c r="Q115" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R115" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S115" s="39" t="n"/>
+      <c r="T115" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U115" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V115" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W115" s="33" t="inlineStr">
+        <is>
+          <t>EAO-48</t>
+        </is>
+      </c>
+      <c r="X115" s="33" t="n"/>
+      <c r="Y115" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z115" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17436,11 +17760,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.34444444444444444</v>
+        <v>0.34408602150537637</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17478,10 +17802,10 @@
         </is>
       </c>
       <c r="B68" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13333333333333333</v>
+        <v>0.13978494623655913</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17523,7 +17847,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17565,7 +17889,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.044444444444444446</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17607,7 +17931,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.044444444444444446</v>
+        <v>0.043010752688172046</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17649,7 +17973,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -17691,7 +18015,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -17733,7 +18057,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -17775,7 +18099,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -17817,7 +18141,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.022222222222222223</v>
+        <v>0.021505376344086023</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -17840,13 +18164,13 @@
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" ht="23.25" customHeight="1">
@@ -17980,13 +18304,13 @@
         </is>
       </c>
       <c r="J81" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" ht="23.25" customHeight="1">
@@ -18184,13 +18508,13 @@
         </is>
       </c>
       <c r="J89" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K89" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L89" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -18244,13 +18568,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>21</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="8">
-                  <v>10</v>
+                  <v>11</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="8">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>53</v>
+                  <v>55</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H112" s="33" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. Logged as an Inquiry on review. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026; the rest of the delay is still under investigation.</t>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
         </is>
       </c>
       <c r="P112" s="33" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="I113" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J113" s="33" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Duplicate detection against open and recently published WarRooms at the point of creation, so two analysts working the same news cannot each publish a WarRoom for it</t>
+          <t>Near-duplicate detection that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so an analyst searching for an existing WarRoom finds it even when the earlier bulletin was worded differently, and a second publication for the same event is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-46 (Open). Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. An RCA was requested. No investigation comments on the ticket yet, so the cause is not established.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. Cause established: the titles differed enough that the analyst's search for an existing bulletin returned nothing, so the second WarRoom was created in the belief that none existed. The duplicate WarRoom is to be deleted, leaving one bulletin for the event. This is Eaton's second Duplicate WarRooms complaint; the earlier one is already recorded as Fixed.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15784,10 +15784,14 @@
           <t>EAO-46</t>
         </is>
       </c>
-      <c r="X113" s="33" t="n"/>
+      <c r="X113" s="33" t="inlineStr">
+        <is>
+          <t>Not an analyst error and not a missed check. The analyst did search for an existing bulletin before creating the WarRoom but could not find it, because the two bulletins were titled differently - 'USITC Opens DRAM Patent Investigation' against 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo' - and the search matched on title rather than on the underlying event. The duplicate was created in good faith on the belief that no coverage existed. The corrective action is to delete the duplicate WarRoom so a single bulletin remains for the event.</t>
+        </is>
+      </c>
       <c r="Y113" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>
@@ -15859,7 +15863,7 @@
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
         </is>
       </c>
       <c r="P114" s="33" t="n"/>
@@ -15967,7 +15971,7 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. No investigation comments on the ticket yet, so the cause is not established and Root Cause, Sub-type and Standard Automation Focus are provisional.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
         </is>
       </c>
       <c r="P115" s="33" t="n"/>
@@ -17760,11 +17764,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.34408602150537637</v>
+        <v>0.35106382978723405</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17805,7 +17809,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13978494623655913</v>
+        <v>0.13829787234042554</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17847,7 +17851,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07526881720430108</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17889,7 +17893,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17931,7 +17935,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.043010752688172046</v>
+        <v>0.0425531914893617</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17973,7 +17977,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.031914893617021274</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18015,7 +18019,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18057,7 +18061,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18099,7 +18103,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18122,10 +18126,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -18141,7 +18145,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021505376344086023</v>
+        <v>0.02127659574468085</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18568,10 +18572,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>114</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E151" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E152" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O13" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms created; control failure acknowledged. NC raised for decision-making gap.</t>
+          <t>Duplicate WarRooms created for one Xometry CEO succession event, published under two differently worded titles. Control failure acknowledged at the time and an NC raised for a decision-making gap. Recurred on 28-Sep-2026 as EAO-46, where the cause was established as title-based matching: the analyst did search for an existing bulletin and found nothing because the wording differed. The corrective action recorded here addressed analyst decision-making rather than the detection weakness, and the same failure returned seven months later.</t>
         </is>
       </c>
       <c r="P13" s="33" t="n"/>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. Cause established: the titles differed enough that the analyst's search for an existing bulletin returned nothing, so the second WarRoom was created in the belief that none existed. The duplicate WarRoom is to be deleted, leaving one bulletin for the event. This is Eaton's second Duplicate WarRooms complaint; the earlier one is already recorded as Fixed.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. Cause established: the titles differed enough that the analyst's search for an existing bulletin returned nothing, so the second WarRoom was created in the belief that none existed. The duplicate WarRoom is to be deleted, leaving one bulletin for the event. This is a recurrence of the 25-Feb-2026 Eaton complaint on the Xometry CEO succession event, which was the same title-mismatch failure, was closed as Fixed against an NC for analyst decision-making, and therefore never addressed the detection weakness.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -18376,17 +18376,17 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="J84" s="76" t="n">
         <v>1</v>
       </c>
       <c r="K84" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="76" t="n">
         <v>1</v>
-      </c>
-      <c r="L84" s="76" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="85" ht="23.25" customHeight="1">
@@ -18400,17 +18400,17 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="J85" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K85" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" ht="23.25" customHeight="1">
@@ -18424,17 +18424,17 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K86" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -18448,17 +18448,17 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -18478,17 +18478,17 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L88" s="76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -18508,14 +18508,14 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J89" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="76" t="n">
         <v>3</v>
@@ -18538,17 +18538,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Transport Disruption</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -18566,19 +18566,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J91" s="77" t="n">
-        <v>94</v>
-      </c>
-      <c r="K91" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L91" s="77" t="n">
-        <v>114</v>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="76" t="n">
+        <v>4</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -18596,10 +18596,20 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="78" t="n"/>
-      <c r="K92" s="78" t="n"/>
-      <c r="L92" s="78" t="n"/>
+      <c r="I92" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J92" s="77" t="n">
+        <v>94</v>
+      </c>
+      <c r="K92" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="L92" s="77" t="n">
+        <v>114</v>
+      </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -19097,7 +19107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23141,6 +23151,33 @@
       <c r="E151" s="41" t="inlineStr">
         <is>
           <t>Resolution Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="30.75" customHeight="1">
+      <c r="A152" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B152" s="41" t="inlineStr">
+        <is>
+          <t>Port Disruption</t>
+        </is>
+      </c>
+      <c r="C152" s="41" t="inlineStr">
+        <is>
+          <t>Congestion or delay at a seaport and the rail and road corridors feeding it: vessel waiting and berthing delays, container dwell times, terminal equipment failure and landside bottlenecks. Distinct from Transport Disruption, which covers a route, crossing or carrier rather than a port and its hinterland.</t>
+        </is>
+      </c>
+      <c r="D152" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category</t>
+        </is>
+      </c>
+      <c r="E152" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>54</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>7</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O13" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms created for one Xometry CEO succession event, published under two differently worded titles. Control failure acknowledged at the time and an NC raised for a decision-making gap. Recurred on 28-Sep-2026 as EAO-46, where the cause was established as title-based matching: the analyst did search for an existing bulletin and found nothing because the wording differed. The corrective action recorded here addressed analyst decision-making rather than the detection weakness, and the same failure returned seven months later.</t>
+          <t>Duplicate WarRooms created; control failure acknowledged. NC raised for decision-making gap.</t>
         </is>
       </c>
       <c r="P13" s="33" t="n"/>
@@ -15721,7 +15721,7 @@
       </c>
       <c r="I113" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J113" s="33" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Near-duplicate detection that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so an analyst searching for an existing WarRoom finds it even when the earlier bulletin was worded differently, and a second publication for the same event is blocked at creation rather than found by the customer</t>
+          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts. Cause established: the titles differed enough that the analyst's search for an existing bulletin returned nothing, so the second WarRoom was created in the belief that none existed. The duplicate WarRoom is to be deleted, leaving one bulletin for the event. This is a recurrence of the 25-Feb-2026 Eaton complaint on the Xometry CEO succession event, which was the same title-mismatch failure, was closed as Fixed against an NC for analyst decision-making, and therefore never addressed the detection weakness.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15786,12 +15786,12 @@
       </c>
       <c r="X113" s="33" t="inlineStr">
         <is>
-          <t>Not an analyst error and not a missed check. The analyst did search for an existing bulletin before creating the WarRoom but could not find it, because the two bulletins were titled differently - 'USITC Opens DRAM Patent Investigation' against 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo' - and the search matched on title rather than on the underlying event. The duplicate was created in good faith on the belief that no coverage existed. The corrective action is to delete the duplicate WarRoom so a single bulletin remains for the event.</t>
+          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
         </is>
       </c>
       <c r="Y113" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -7172,7 +7172,7 @@
       </c>
       <c r="J34" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K34" s="33" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="J35" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K35" s="33" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="J36" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K36" s="33" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="J39" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K39" s="33" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="J40" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K40" s="33" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="J43" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K43" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,7 +2984,7 @@
                   <v>27</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
@@ -2999,7 +2999,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="6">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -11178,12 +11178,12 @@
       </c>
       <c r="J72" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L72" s="33" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="V72" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W72" s="33" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="X72" s="33" t="inlineStr">
         <is>
-          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but were not captured on the portal until 1 July; Engineering was asked to investigate why the 26-27 June sources were missed. RCA approved and shared 09-Jul-2026.</t>
+          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but did not reach the analyst portal until 01-Jul-2026. Engineering confirmed on the ticket that the articles were captured both by the vendor and by the Spanish-language algorithm, and were linked to the labor_disruption_es_pontevedra_vigo_update cluster - so this is neither a source gap nor a failure to identify the event. That cluster was in an inconsistent state, its status set to Update while it was also marked Not Impactful, which kept the feeds off the analyst portal and meant no WarRoom was raised. The thread asks whether this is a recurrence of the cluster-state defect fixed in the June-end release, where a null cluster id still showed as not impactful. RCA approved and shared with the customer on 09-Jul-2026 as a PDF attachment.</t>
         </is>
       </c>
       <c r="Y72" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2981,16 +2981,16 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>27</v>
+                  <v>28</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>3</v>
                 </pt>
                 <pt idx="3">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="4">
                   <v>7</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="V24" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="X24" s="33" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="M29" s="33" t="inlineStr">
         <is>
-          <t>Source coverage expansion</t>
+          <t>Escalation automation + reclassification review, so an event held under the wrong classification is re-checked rather than waiting for the next manual pass</t>
         </is>
       </c>
       <c r="N29" s="33" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="V29" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="X29" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,10 +2984,10 @@
                   <v>28</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
-                  <v>3</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="3">
                   <v>8</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="V2" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
       <c r="X2" s="33" t="n"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="V61" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Multilingual Keyword Expansion</t>
         </is>
       </c>
       <c r="X61" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="8">
-                  <v>11</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1771,7 +1771,7 @@
                   <v>44</v>
                 </pt>
                 <pt idx="1">
-                  <v>27</v>
+                  <v>28</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
@@ -2088,7 +2088,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>98</v>
+                  <v>99</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>54</v>
+                  <v>55</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>22</v>
+                  <v>23</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>28</v>
                 </pt>
                 <pt idx="1">
-                  <v>29</v>
+                  <v>30</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z115" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z116" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z115"/>
+  <dimension ref="A1:Z116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15347,16 +15347,16 @@
         <v>46266</v>
       </c>
       <c r="B110" s="37" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E110" s="39" t="n">
@@ -15364,27 +15364,27 @@
       </c>
       <c r="F110" s="33" t="inlineStr">
         <is>
-          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G110" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H110" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I110" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J110" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K110" s="33" t="inlineStr">
@@ -15394,28 +15394,28 @@
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M110" s="33" t="inlineStr">
         <is>
-          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+          <t>Coverage of ransomware-group leak-site claims and threat-intelligence reporting, so a claimed breach at a named supplier is captured when the group publishes it rather than when a customer's own threat team circulates it internally</t>
         </is>
       </c>
       <c r="N110" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O110" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue; clarification to the customer is still to follow. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P110" s="33" t="n"/>
       <c r="Q110" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R110" s="39" t="n">
@@ -15429,27 +15429,23 @@
       </c>
       <c r="U110" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V110" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W110" s="33" t="inlineStr">
-        <is>
-          <t>EAO-43</t>
-        </is>
-      </c>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W110" s="33" t="n"/>
       <c r="X110" s="33" t="inlineStr">
         <is>
-          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. Clarification to the customer is still to be provided, so nothing has been shared with General Mills yet.</t>
         </is>
       </c>
       <c r="Y110" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z110" s="37" t="n"/>
@@ -15459,11 +15455,11 @@
         <v>46266</v>
       </c>
       <c r="B111" s="37" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
@@ -15476,7 +15472,7 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
@@ -15486,17 +15482,17 @@
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15511,7 +15507,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15521,7 +15517,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15541,27 +15537,27 @@
       </c>
       <c r="U111" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
+          <t>EAO-43</t>
         </is>
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -15575,12 +15571,12 @@
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15588,17 +15584,17 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
@@ -15608,7 +15604,7 @@
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15618,40 +15614,34 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
-        </is>
-      </c>
-      <c r="P112" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P112" s="33" t="n"/>
       <c r="Q112" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R112" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S112" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S112" s="39" t="n"/>
       <c r="T112" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15659,22 +15649,22 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
@@ -15689,16 +15679,16 @@
         <v>46266</v>
       </c>
       <c r="B113" s="37" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E113" s="39" t="n">
@@ -15706,7 +15696,7 @@
       </c>
       <c r="F113" s="33" t="inlineStr">
         <is>
-          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
         </is>
       </c>
       <c r="G113" s="33" t="inlineStr">
@@ -15716,17 +15706,17 @@
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I113" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J113" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K113" s="33" t="inlineStr">
@@ -15736,12 +15726,12 @@
       </c>
       <c r="L113" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
@@ -15751,19 +15741,25 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
-        </is>
-      </c>
-      <c r="P113" s="33" t="n"/>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q113" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R113" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S113" s="39" t="n"/>
+      <c r="S113" s="39" t="n">
+        <v>252</v>
+      </c>
       <c r="T113" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15771,27 +15767,27 @@
       </c>
       <c r="U113" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V113" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W113" s="33" t="inlineStr">
         <is>
-          <t>EAO-46</t>
+          <t>EAO-45</t>
         </is>
       </c>
       <c r="X113" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
         </is>
       </c>
       <c r="Y113" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>
@@ -15805,12 +15801,12 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Litigation/Legal</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E114" s="39" t="n">
@@ -15818,7 +15814,7 @@
       </c>
       <c r="F114" s="33" t="inlineStr">
         <is>
-          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
+          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
         </is>
       </c>
       <c r="G114" s="33" t="inlineStr">
@@ -15828,17 +15824,17 @@
       </c>
       <c r="H114" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="I114" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15853,7 +15849,7 @@
       </c>
       <c r="M114" s="33" t="inlineStr">
         <is>
-          <t>Coverage of Japanese-language business and financial press for listed suppliers, with a path for a credible but company-unconfirmed report to be staged as a monitoring story the customer can see rather than being absent entirely</t>
+          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N114" s="33" t="inlineStr">
@@ -15863,13 +15859,13 @@
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
         </is>
       </c>
       <c r="P114" s="33" t="n"/>
       <c r="Q114" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R114" s="39" t="n">
@@ -15888,18 +15884,22 @@
       </c>
       <c r="V114" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W114" s="33" t="inlineStr">
         <is>
-          <t>EAO-47</t>
-        </is>
-      </c>
-      <c r="X114" s="33" t="n"/>
+          <t>EAO-46</t>
+        </is>
+      </c>
+      <c r="X114" s="33" t="inlineStr">
+        <is>
+          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
+        </is>
+      </c>
       <c r="Y114" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z114" s="37" t="n"/>
@@ -15913,12 +15913,12 @@
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E115" s="39" t="n">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="F115" s="33" t="inlineStr">
         <is>
-          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
         </is>
       </c>
       <c r="G115" s="33" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="M115" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of regional logistics and industry-body publications such as Exporters Western Cape, plus a rule for chronic port and corridor congestion that raises a standing condition into a reportable event when dwell times or berthing delays cross a threshold rather than never qualifying because nothing discretely happened</t>
+          <t>Coverage of Japanese-language business and financial press for listed suppliers, with a path for a credible but company-unconfirmed report to be staged as a monitoring story the customer can see rather than being absent entirely</t>
         </is>
       </c>
       <c r="N115" s="33" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
+          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
         </is>
       </c>
       <c r="P115" s="33" t="n"/>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="U115" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V115" s="33" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="W115" s="33" t="inlineStr">
         <is>
-          <t>EAO-48</t>
+          <t>EAO-47</t>
         </is>
       </c>
       <c r="X115" s="33" t="n"/>
@@ -16011,6 +16011,114 @@
         </is>
       </c>
       <c r="Z115" s="37" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B116" s="37" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C116" s="33" t="inlineStr">
+        <is>
+          <t>Port Disruption</t>
+        </is>
+      </c>
+      <c r="D116" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E116" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="33" t="inlineStr">
+        <is>
+          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+        </is>
+      </c>
+      <c r="G116" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H116" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I116" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J116" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K116" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L116" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M116" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring of regional logistics and industry-body publications such as Exporters Western Cape, plus a rule for chronic port and corridor congestion that raises a standing condition into a reportable event when dwell times or berthing delays cross a threshold rather than never qualifying because nothing discretely happened</t>
+        </is>
+      </c>
+      <c r="N116" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O116" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
+        </is>
+      </c>
+      <c r="P116" s="33" t="n"/>
+      <c r="Q116" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R116" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S116" s="39" t="n"/>
+      <c r="T116" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U116" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V116" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W116" s="33" t="inlineStr">
+        <is>
+          <t>EAO-48</t>
+        </is>
+      </c>
+      <c r="X116" s="33" t="n"/>
+      <c r="Y116" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z116" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17768,7 +17876,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35106382978723405</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17809,7 +17917,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13829787234042554</v>
+        <v>0.1368421052631579</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17851,7 +17959,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07446808510638298</v>
+        <v>0.07368421052631578</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -17893,7 +18001,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -17916,13 +18024,13 @@
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L70" s="76" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" ht="23.25" customHeight="1">
@@ -17935,7 +18043,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0425531914893617</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -17977,7 +18085,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031914893617021274</v>
+        <v>0.031578947368421054</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18019,7 +18127,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18061,7 +18169,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18103,7 +18211,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18145,7 +18253,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18602,13 +18710,13 @@
         </is>
       </c>
       <c r="J92" s="77" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K92" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L92" s="77" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -13035,7 +13035,7 @@
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -18488,13 +18488,13 @@
         </is>
       </c>
       <c r="J84" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K84" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" ht="23.25" customHeight="1">
@@ -18646,17 +18646,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Transport Disruption</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -18674,19 +18674,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="20" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="J91" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" s="76" t="n">
-        <v>4</v>
+      <c r="I91" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J91" s="77" t="n">
+        <v>95</v>
+      </c>
+      <c r="K91" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="L91" s="77" t="n">
+        <v>115</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -18704,20 +18704,10 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J92" s="77" t="n">
-        <v>95</v>
-      </c>
-      <c r="K92" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L92" s="77" t="n">
-        <v>115</v>
-      </c>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="78" t="n"/>
+      <c r="K92" s="78" t="n"/>
+      <c r="L92" s="78" t="n"/>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1290,7 +1290,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="7">
-                  <v>13</v>
+                  <v>15</v>
                 </pt>
                 <pt idx="8">
                   <v>12</v>
@@ -1412,7 +1412,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="7">
-                  <v>4</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="8">
                   <v>5</v>
@@ -1774,7 +1774,7 @@
                   <v>28</v>
                 </pt>
                 <pt idx="2">
-                  <v>17</v>
+                  <v>19</v>
                 </pt>
                 <pt idx="3">
                   <v>6</v>
@@ -2384,7 +2384,7 @@
                   <v>33</v>
                 </pt>
                 <pt idx="2">
-                  <v>7</v>
+                  <v>9</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2990,7 +2990,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>8</v>
+                  <v>10</v>
                 </pt>
                 <pt idx="4">
                   <v>7</v>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="G83" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H83" s="33" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
@@ -17872,11 +17872,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3473684210526316</v>
+        <v>0.36082474226804123</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17917,7 +17917,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.13402061855670103</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17959,7 +17959,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07368421052631578</v>
+        <v>0.07216494845360824</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18001,7 +18001,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18043,7 +18043,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18085,7 +18085,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031578947368421054</v>
+        <v>0.030927835051546393</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18127,7 +18127,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18169,7 +18169,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18211,7 +18211,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18234,10 +18234,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -18253,7 +18253,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="76" t="n">
         <v>2</v>
@@ -18680,10 +18680,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>115</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>15</v>
                 </pt>
                 <pt idx="8">
-                  <v>12</v>
+                  <v>11</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1415,7 +1415,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>19</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>54</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>23</v>
+                  <v>22</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>28</v>
                 </pt>
                 <pt idx="1">
-                  <v>30</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -15931,22 +15931,22 @@
       </c>
       <c r="G115" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H115" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I115" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J115" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K115" s="33" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="M115" s="33" t="inlineStr">
         <is>
-          <t>Coverage of Japanese-language business and financial press for listed suppliers, with a path for a credible but company-unconfirmed report to be staged as a monitoring story the customer can see rather than being absent entirely</t>
+          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
         </is>
       </c>
       <c r="N115" s="33" t="inlineStr">
@@ -15971,13 +15971,13 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-47 (Open). Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with the owners' equity ratio expected to fall to the 20% level; an extraordinary board meeting on 25-Sep-2026 reportedly dismissed CEO Mitsuya Kishida over the impairments. Goldman Sachs takes no view on the accuracy of the article and the company had not confirmed it, with the yuho securities report expected 30-Sep-2026. A backend check found no corresponding EventWatch event. The customer asked for a root-cause explanation and a customer-ready response. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
+          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
         </is>
       </c>
       <c r="P115" s="33" t="n"/>
       <c r="Q115" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R115" s="39" t="n">
@@ -15996,7 +15996,7 @@
       </c>
       <c r="V115" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W115" s="33" t="inlineStr">
@@ -16004,10 +16004,14 @@
           <t>EAO-47</t>
         </is>
       </c>
-      <c r="X115" s="33" t="n"/>
+      <c r="X115" s="33" t="inlineStr">
+        <is>
+          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
+        </is>
+      </c>
       <c r="Y115" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z115" s="37" t="n"/>
@@ -17876,7 +17880,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.36082474226804123</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17917,7 +17921,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13402061855670103</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17959,7 +17963,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07216494845360824</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18001,7 +18005,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18043,7 +18047,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18085,7 +18089,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030927835051546393</v>
+        <v>0.03125</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18127,7 +18131,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18169,7 +18173,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18211,7 +18215,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18253,7 +18257,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18276,10 +18280,10 @@
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="76" t="n">
         <v>2</v>
@@ -18680,10 +18684,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>115</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1272,13 +1272,13 @@
                   <v>4</v>
                 </pt>
                 <pt idx="1">
-                  <v>9</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="2">
                   <v>13</v>
                 </pt>
                 <pt idx="3">
-                  <v>12</v>
+                  <v>11</v>
                 </pt>
                 <pt idx="4">
                   <v>17</v>
@@ -1290,7 +1290,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="7">
-                  <v>15</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="8">
                   <v>11</v>
@@ -1394,13 +1394,13 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
                 </pt>
                 <pt idx="3">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="4">
                   <v>1</v>
@@ -1412,7 +1412,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="7">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="8">
                   <v>6</v>
@@ -1774,7 +1774,7 @@
                   <v>28</v>
                 </pt>
                 <pt idx="2">
-                  <v>19</v>
+                  <v>15</v>
                 </pt>
                 <pt idx="3">
                   <v>5</v>
@@ -2381,10 +2381,10 @@
                   <v>54</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
-                  <v>9</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
-                  <v>Hitachi</v>
+                  <v>Merck</v>
                 </pt>
                 <pt idx="7">
-                  <v>Merck</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="8">
-                  <v>Schneider Electric</v>
+                  <v>UVM Health Network</v>
                 </pt>
                 <pt idx="9">
-                  <v>UVM Health Network</v>
+                  <v>Belden Inc</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>35</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2690,10 +2690,10 @@
                   <v>2</v>
                 </pt>
                 <pt idx="9">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="10">
-                  <v>22</v>
+                  <v>21</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>28</v>
+                  <v>29</v>
                 </pt>
                 <pt idx="1">
                   <v>29</v>
@@ -2990,13 +2990,13 @@
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>10</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="4">
                   <v>7</v>
                 </pt>
                 <pt idx="5">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="6">
                   <v>4</v>
@@ -3005,7 +3005,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>7</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="G12" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H12" s="33" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="G38" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H38" s="33" t="inlineStr">
@@ -8600,17 +8600,17 @@
       </c>
       <c r="H48" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I48" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J48" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K48" s="33" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="M48" s="33" t="inlineStr">
         <is>
-          <t>Relevancy logic review</t>
+          <t>A software-dependency check when judging relevance, so a compromise in a package a customer's own products are built on is weighed on the product connection rather than on physical site mapping and operational disruption alone</t>
         </is>
       </c>
       <c r="N48" s="33" t="inlineStr">
@@ -8635,13 +8635,13 @@
       </c>
       <c r="O48" s="33" t="inlineStr">
         <is>
-          <t>Customer asked RCA for Axios npm compromise; classified not relevant based on mapping + no operational disruption.</t>
+          <t>Eaton asked for an RCA on the March 31 Axios npm package compromise. It was reviewed and classified not relevant on the basis of supplier mapping and the absence of operational disruption. That judgement was wrong: Eaton has a product connection to Axios and should have been notified. Counted as a miss.</t>
         </is>
       </c>
       <c r="P48" s="33" t="n"/>
       <c r="Q48" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R48" s="39" t="n">
@@ -8658,10 +8658,14 @@
       </c>
       <c r="V48" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="X48" s="33" t="n"/>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="X48" s="33" t="inlineStr">
+        <is>
+          <t>Analyst relevance judgement was wrong. The Axios npm compromise was assessed against supplier mapping and physical operational disruption, neither of which applied, and was closed as not relevant. The connection that mattered was a product one - Eaton's own software depends on the compromised package - and on that basis the event should have been notified. Not a source or keyword gap: the event was seen and judged.</t>
+        </is>
+      </c>
       <c r="Y48" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -12389,7 +12393,7 @@
       </c>
       <c r="G83" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H83" s="33" t="inlineStr">
@@ -13275,7 +13279,7 @@
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
@@ -15956,7 +15960,7 @@
       </c>
       <c r="L115" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M115" s="33" t="inlineStr">
@@ -17876,11 +17880,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3645833333333333</v>
+        <v>0.358695652173913</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17921,7 +17925,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13541666666666666</v>
+        <v>0.14130434782608695</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17963,7 +17967,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.07608695652173914</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18005,7 +18009,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18047,7 +18051,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18070,10 +18074,10 @@
         </is>
       </c>
       <c r="J71" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="76" t="n">
         <v>2</v>
-      </c>
-      <c r="K71" s="76" t="n">
-        <v>1</v>
       </c>
       <c r="L71" s="76" t="n">
         <v>3</v>
@@ -18089,7 +18093,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03125</v>
+        <v>0.03260869565217391</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18124,14 +18128,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18166,14 +18170,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18208,14 +18212,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>UVM Health Network</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18238,10 +18242,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -18250,14 +18254,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.010869565217391304</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18314,10 +18318,10 @@
         </is>
       </c>
       <c r="J77" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="76" t="n">
         <v>7</v>
@@ -18348,10 +18352,10 @@
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="76" t="n">
         <v>2</v>
@@ -18684,10 +18688,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>115</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1768,16 +1768,16 @@
                 <formatCode>General</formatCode>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>44</v>
+                  <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>28</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>15</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="H48" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I48" s="33" t="inlineStr">
@@ -14942,7 +14942,7 @@
       </c>
       <c r="L106" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M106" s="33" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="L107" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M107" s="33" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="L110" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M110" s="33" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="O110" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue; clarification to the customer is still to follow. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P110" s="33" t="n"/>
@@ -15444,7 +15444,7 @@
       <c r="W110" s="33" t="n"/>
       <c r="X110" s="33" t="inlineStr">
         <is>
-          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. Clarification to the customer is still to be provided, so nothing has been shared with General Mills yet.</t>
+          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
         </is>
       </c>
       <c r="Y110" s="33" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="L114" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M114" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1275,7 +1275,7 @@
                   <v>8</v>
                 </pt>
                 <pt idx="2">
-                  <v>13</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -1287,13 +1287,13 @@
                   <v>9</v>
                 </pt>
                 <pt idx="6">
-                  <v>6</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="7">
                   <v>13</v>
                 </pt>
                 <pt idx="8">
-                  <v>11</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1397,7 +1397,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="2">
-                  <v>1</v>
+                  <v>0</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
@@ -1409,13 +1409,13 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="7">
                   <v>4</v>
                 </pt>
                 <pt idx="8">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1771,10 +1771,10 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
-                  <v>15</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="3">
                   <v>1</v>
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>54</v>
+                  <v>56</v>
                 </pt>
                 <pt idx="1">
                   <v>34</v>
                 </pt>
                 <pt idx="2">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2693,7 +2693,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="10">
-                  <v>21</v>
+                  <v>23</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>29</v>
                 </pt>
                 <pt idx="1">
-                  <v>29</v>
+                  <v>30</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>7</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H17" s="33" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="G75" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H75" s="33" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="G108" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H108" s="33" t="inlineStr">
@@ -17880,11 +17880,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.358695652173913</v>
+        <v>0.35789473684210527</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17906,10 +17906,10 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K67" s="75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="75" t="n">
         <v>13</v>
@@ -17925,7 +17925,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.14130434782608695</v>
+        <v>0.1368421052631579</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17967,7 +17967,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07608695652173914</v>
+        <v>0.07368421052631578</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18009,7 +18009,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18051,7 +18051,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.043478260869565216</v>
+        <v>0.042105263157894736</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18093,7 +18093,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03260869565217391</v>
+        <v>0.031578947368421054</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18135,7 +18135,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18177,7 +18177,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18219,7 +18219,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021739130434782608</v>
+        <v>0.021052631578947368</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18242,10 +18242,10 @@
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="76" t="n">
         <v>16</v>
@@ -18261,7 +18261,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.010869565217391304</v>
+        <v>0.010526315789473684</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18598,10 +18598,10 @@
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K88" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L88" s="76" t="n">
         <v>8</v>
@@ -18688,10 +18688,10 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K91" s="77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
         <v>115</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -11715,7 +11715,7 @@
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
@@ -18420,7 +18420,7 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="J81" s="76" t="n">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="B141" s="41" t="inlineStr">
         <is>
-          <t>Litigation/Legal</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="C141" s="41" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>56</v>
+                  <v>55</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
-                  <v>5</v>
+                  <v>8</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6123,12 +6123,12 @@
       </c>
       <c r="I24" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J24" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K24" s="33" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="I52" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J52" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="K52" s="33" t="inlineStr">
@@ -9084,7 +9084,7 @@
       <c r="X52" s="33" t="n"/>
       <c r="Y52" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z52" s="37" t="n"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>56</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
-                  <v>8</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="J24" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K24" s="33" t="inlineStr">
@@ -9025,12 +9025,12 @@
       </c>
       <c r="I52" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J52" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K52" s="33" t="inlineStr">
@@ -9084,7 +9084,7 @@
       <c r="X52" s="33" t="n"/>
       <c r="Y52" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z52" s="37" t="n"/>
@@ -14587,12 +14587,12 @@
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,7 +2984,7 @@
                   <v>29</v>
                 </pt>
                 <pt idx="1">
-                  <v>30</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>9</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="M52" s="33" t="inlineStr">
         <is>
-          <t>Mapping validation</t>
+          <t>Feed-receipt verification on any source URL raised in an escalation, so an article whose feed never reached the application is identified as an ingestion gap at the point it is queried rather than investigated as a supplier mapping error</t>
         </is>
       </c>
       <c r="N52" s="33" t="inlineStr">
@@ -9078,10 +9078,14 @@
       </c>
       <c r="V52" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
-        </is>
-      </c>
-      <c r="X52" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="X52" s="33" t="inlineStr">
+        <is>
+          <t>The URL raised in the escalation was the page URL, not the news source URL, and was the same URL already supplied and analysed earlier. On that analysis the feed associated with that URL had not been received by the application, so the article never entered the portal. Not a supplier mapping gap: STELIA was a listed supplier and the story was never ingested to map against.</t>
+        </is>
+      </c>
       <c r="Y52" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1293,7 +1293,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="8">
-                  <v>12</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="9">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>99</v>
+                  <v>100</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2381,7 +2381,7 @@
                   <v>56</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>META</v>
+                </pt>
+                <pt idx="7">
                   <v>Merck</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>Schneider Electric</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>UVM Health Network</v>
-                </pt>
-                <pt idx="9">
-                  <v>Belden Inc</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2690,7 +2690,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="9">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="10">
                   <v>23</v>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>8</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z116" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z117" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z116"/>
+  <dimension ref="A1:Z117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16131,6 +16131,114 @@
         </is>
       </c>
       <c r="Z116" s="37" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="35" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B117" s="37" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C117" s="33" t="inlineStr">
+        <is>
+          <t>Extreme Weather</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E117" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="33" t="inlineStr">
+        <is>
+          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
+        </is>
+      </c>
+      <c r="G117" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H117" s="33" t="inlineStr">
+        <is>
+          <t>Impacted Supplier Missing</t>
+        </is>
+      </c>
+      <c r="I117" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J117" s="33" t="inlineStr">
+        <is>
+          <t>Mapping</t>
+        </is>
+      </c>
+      <c r="K117" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L117" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M117" s="33" t="inlineStr">
+        <is>
+          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
+        </is>
+      </c>
+      <c r="N117" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O117" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+        </is>
+      </c>
+      <c r="P117" s="33" t="n"/>
+      <c r="Q117" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R117" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="S117" s="39" t="n"/>
+      <c r="T117" s="35" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="U117" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V117" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W117" s="33" t="inlineStr">
+        <is>
+          <t>EAO-49</t>
+        </is>
+      </c>
+      <c r="X117" s="33" t="n"/>
+      <c r="Y117" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z117" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17888,7 +17996,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35789473684210527</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -17929,7 +18037,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1368421052631579</v>
+        <v>0.13541666666666666</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -17971,7 +18079,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07368421052631578</v>
+        <v>0.07291666666666667</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18013,7 +18121,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18055,7 +18163,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.042105263157894736</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18097,7 +18205,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.031578947368421054</v>
+        <v>0.03125</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18120,26 +18228,26 @@
         </is>
       </c>
       <c r="J72" s="76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18174,14 +18282,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18216,14 +18324,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.021052631578947368</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18258,14 +18366,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>UVM Health Network</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.010526315789473684</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18692,13 +18800,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>100</v>
+                  <v>101</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>56</v>
+                  <v>55</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>34</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2981,10 +2981,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>29</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>30</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z117" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z118" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z117"/>
+  <dimension ref="A1:Z118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16061,12 +16061,12 @@
       </c>
       <c r="I116" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J116" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K116" s="33" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="M116" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of regional logistics and industry-body publications such as Exporters Western Cape, plus a rule for chronic port and corridor congestion that raises a standing condition into a reportable event when dwell times or berthing delays cross a threshold rather than never qualifying because nothing discretely happened</t>
+          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N116" s="33" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="O116" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026: multi-day vessel waiting and berthing delays, high container dwell times, terminal equipment breakdowns and landside rail and road delays across Durban, Cape Town, Port Elizabeth/Ngqura and regional border posts. Ford's exposure is the Silverton Assembly Plant and the Struandale Engine Plant, covering inbound CKD and JIT parts and outbound vehicle and engine exports. A backend search found no corresponding event for those locations. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional freight, port operations and logistics corridors across South Africa and Africa, and has asked whether EWC is on the monitored source list and whether its two South African plants are mapped. Currently under investigation, so Root Cause, Sub-type and Standard Automation Focus remain provisional.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: an analyst overlooked the event. It was an analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P116" s="33" t="n"/>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="V116" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W116" s="33" t="inlineStr">
@@ -16127,7 +16127,7 @@
       <c r="X116" s="33" t="n"/>
       <c r="Y116" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z116" s="37" t="n"/>
@@ -16239,6 +16239,114 @@
         </is>
       </c>
       <c r="Z117" s="37" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B118" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C118" s="33" t="inlineStr">
+        <is>
+          <t>Labor Disruption</t>
+        </is>
+      </c>
+      <c r="D118" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E118" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="33" t="inlineStr">
+        <is>
+          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
+        </is>
+      </c>
+      <c r="G118" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H118" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I118" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J118" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K118" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L118" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M118" s="33" t="inlineStr">
+        <is>
+          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
+        </is>
+      </c>
+      <c r="N118" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O118" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: the analyst overlooked the event. The ticket also asks EventWatch to confirm whether the Not Impactful call was made by an analyst or by automated logic.</t>
+        </is>
+      </c>
+      <c r="P118" s="33" t="n"/>
+      <c r="Q118" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R118" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S118" s="39" t="n"/>
+      <c r="T118" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U118" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V118" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W118" s="33" t="inlineStr">
+        <is>
+          <t>EAO-50</t>
+        </is>
+      </c>
+      <c r="X118" s="33" t="n"/>
+      <c r="Y118" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z118" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -17992,11 +18100,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3541666666666667</v>
+        <v>0.36082474226804123</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18037,7 +18145,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13541666666666666</v>
+        <v>0.13402061855670103</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18079,7 +18187,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.07216494845360824</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18121,7 +18229,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18163,7 +18271,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041666666666666664</v>
+        <v>0.041237113402061855</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18205,7 +18313,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03125</v>
+        <v>0.030927835051546393</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18247,7 +18355,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18289,7 +18397,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18331,7 +18439,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18373,7 +18481,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020833333333333332</v>
+        <v>0.020618556701030927</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18488,13 +18596,13 @@
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K79" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -18800,13 +18908,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16307,7 +16307,7 @@
       </c>
       <c r="O118" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: the analyst overlooked the event. The ticket also asks EventWatch to confirm whether the Not Impactful call was made by an analyst or by automated logic.</t>
+          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
         </is>
       </c>
       <c r="P118" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16091,7 +16091,7 @@
       </c>
       <c r="O116" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: an analyst overlooked the event. It was an analyst error, not a source-coverage gap.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P116" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1290,7 +1290,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="7">
-                  <v>13</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="8">
                   <v>13</v>
@@ -1771,7 +1771,7 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
@@ -2088,7 +2088,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>101</v>
+                  <v>102</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>55</v>
+                  <v>56</v>
                 </pt>
                 <pt idx="1">
                   <v>36</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>23</v>
+                  <v>24</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>30</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z118" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z119" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z118"/>
+  <dimension ref="A1:Z119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -12927,16 +12927,16 @@
         <v>46235</v>
       </c>
       <c r="B88" s="37" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="E88" s="39" t="n">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="F88" s="33" t="inlineStr">
         <is>
-          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
+          <t>Eberhard AG Insolvency – No EventWatch Alert (Infineon)</t>
         </is>
       </c>
       <c r="G88" s="33" t="inlineStr">
@@ -12954,17 +12954,17 @@
       </c>
       <c r="H88" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I88" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J88" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K88" s="33" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="M88" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Trigger Automation</t>
+          <t>Add the bankruptcy and insolvency sources covering this supplier's region to the vendor network, so a filing at a mapped supplier is captured when it is published rather than when the customer raises it</t>
         </is>
       </c>
       <c r="N88" s="33" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="O88" s="33" t="inlineStr">
         <is>
-          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+          <t>Raised by Infineon at the weekly sync: Eberhard AG, a critical supplier, reportedly entered bankruptcy proceedings and no EventWatch alert or notification was received. The customer cited it as a case where they expected early-warning signals and bankruptcy intelligence through the Resilinc platform. Product Management reported that the sources carrying the filing are not part of the vendor network and that the vendor has been asked to include them; recorded as a source miss at the portal. There is no EAO key for this record: it was raised by email to the team rather than by opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P88" s="33" t="n"/>
@@ -13002,8 +13002,10 @@
         <v>8</v>
       </c>
       <c r="S88" s="39" t="n"/>
-      <c r="T88" s="35" t="n">
-        <v>46235</v>
+      <c r="T88" s="35" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
       </c>
       <c r="U88" s="33" t="inlineStr">
         <is>
@@ -13012,27 +13014,21 @@
       </c>
       <c r="V88" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W88" s="33" t="inlineStr">
-        <is>
-          <t>EAO-27</t>
-        </is>
-      </c>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W88" s="33" t="n"/>
       <c r="X88" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>The sources reporting the Eberhard AG insolvency are not part of the vendor network; the vendor has been asked to include them. Recorded by Product Management as a source miss at the portal.</t>
         </is>
       </c>
       <c r="Y88" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z88" s="37" t="n">
-        <v>46259</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z88" s="37" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
@@ -13043,12 +13039,12 @@
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E89" s="39" t="n">
@@ -13056,27 +13052,27 @@
       </c>
       <c r="F89" s="33" t="inlineStr">
         <is>
-          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
+          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
         </is>
       </c>
       <c r="G89" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H89" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I89" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J89" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K89" s="33" t="inlineStr">
@@ -13086,53 +13082,55 @@
       </c>
       <c r="L89" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M89" s="33" t="inlineStr">
         <is>
-          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
+          <t>WarRoom Trigger Automation</t>
         </is>
       </c>
       <c r="N89" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O89" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
-        </is>
-      </c>
+          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+        </is>
+      </c>
+      <c r="P89" s="33" t="n"/>
       <c r="Q89" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R89" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S89" s="39" t="n"/>
       <c r="T89" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U89" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V89" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W89" s="33" t="inlineStr">
         <is>
-          <t>EAO-28</t>
+          <t>EAO-27</t>
         </is>
       </c>
       <c r="X89" s="33" t="inlineStr">
         <is>
-          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y89" s="33" t="inlineStr">
@@ -13149,16 +13147,16 @@
         <v>46235</v>
       </c>
       <c r="B90" s="37" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E90" s="39" t="n">
@@ -13166,27 +13164,27 @@
       </c>
       <c r="F90" s="33" t="inlineStr">
         <is>
-          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
+          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
         </is>
       </c>
       <c r="G90" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H90" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I90" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J90" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K90" s="33" t="inlineStr">
@@ -13196,60 +13194,58 @@
       </c>
       <c r="L90" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M90" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
         </is>
       </c>
       <c r="N90" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O90" s="33" t="inlineStr">
         <is>
-          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
-        </is>
-      </c>
-      <c r="P90" s="33" t="n"/>
+          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+        </is>
+      </c>
       <c r="Q90" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R90" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S90" s="39" t="n"/>
       <c r="T90" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U90" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V90" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W90" s="33" t="inlineStr">
         <is>
-          <t>EAO-26</t>
+          <t>EAO-28</t>
         </is>
       </c>
       <c r="X90" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
         </is>
       </c>
       <c r="Y90" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z90" s="37" t="n">
@@ -13261,11 +13257,11 @@
         <v>46235</v>
       </c>
       <c r="B91" s="37" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="C91" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D91" s="33" t="inlineStr">
@@ -13278,27 +13274,27 @@
       </c>
       <c r="F91" s="33" t="inlineStr">
         <is>
-          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
+          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
         </is>
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I91" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13308,28 +13304,28 @@
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
-          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N91" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O91" s="33" t="inlineStr">
         <is>
-          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
+          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
         </is>
       </c>
       <c r="P91" s="33" t="n"/>
       <c r="Q91" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R91" s="39" t="n">
@@ -13341,31 +13337,31 @@
       </c>
       <c r="U91" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V91" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W91" s="33" t="inlineStr">
         <is>
-          <t>EAO-29</t>
+          <t>EAO-26</t>
         </is>
       </c>
       <c r="X91" s="33" t="inlineStr">
         <is>
-          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z91" s="37" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="92">
@@ -13373,44 +13369,44 @@
         <v>46235</v>
       </c>
       <c r="B92" s="37" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E92" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" s="33" t="inlineStr">
         <is>
-          <t>World Trade Bridge Closed in Laredo, Texas</t>
+          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
         </is>
       </c>
       <c r="G92" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H92" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I92" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J92" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K92" s="33" t="inlineStr">
@@ -13420,28 +13416,28 @@
       </c>
       <c r="L92" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M92" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
         </is>
       </c>
       <c r="N92" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O92" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
+          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
         </is>
       </c>
       <c r="P92" s="33" t="n"/>
       <c r="Q92" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R92" s="39" t="n">
@@ -13453,30 +13449,32 @@
       </c>
       <c r="U92" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V92" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W92" s="33" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-29</t>
         </is>
       </c>
       <c r="X92" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
         </is>
       </c>
       <c r="Y92" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z92" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z92" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="35" t="n">
@@ -13487,7 +13485,7 @@
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D93" s="33" t="inlineStr">
@@ -13500,7 +13498,7 @@
       </c>
       <c r="F93" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
+          <t>World Trade Bridge Closed in Laredo, Texas</t>
         </is>
       </c>
       <c r="G93" s="33" t="inlineStr">
@@ -13520,7 +13518,7 @@
       </c>
       <c r="J93" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -13530,7 +13528,7 @@
       </c>
       <c r="L93" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M93" s="33" t="inlineStr">
@@ -13545,7 +13543,7 @@
       </c>
       <c r="O93" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
         </is>
       </c>
       <c r="P93" s="33" t="n"/>
@@ -13593,7 +13591,7 @@
         <v>46235</v>
       </c>
       <c r="B94" s="37" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
@@ -13610,7 +13608,7 @@
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
+          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
         </is>
       </c>
       <c r="G94" s="33" t="inlineStr">
@@ -13625,12 +13623,12 @@
       </c>
       <c r="I94" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J94" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K94" s="33" t="inlineStr">
@@ -13645,7 +13643,7 @@
       </c>
       <c r="M94" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N94" s="33" t="inlineStr">
@@ -13655,7 +13653,7 @@
       </c>
       <c r="O94" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P94" s="33" t="n"/>
@@ -13678,7 +13676,7 @@
       </c>
       <c r="V94" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W94" s="33" t="inlineStr">
@@ -13693,7 +13691,7 @@
       </c>
       <c r="Y94" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z94" s="37" t="n"/>
@@ -13707,20 +13705,20 @@
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D95" s="33" t="inlineStr">
         <is>
-          <t>The American National Red Cross</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="E95" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="33" t="inlineStr">
         <is>
-          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
+          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
         </is>
       </c>
       <c r="G95" s="33" t="inlineStr">
@@ -13730,17 +13728,17 @@
       </c>
       <c r="H95" s="33" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I95" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J95" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K95" s="33" t="inlineStr">
@@ -13755,17 +13753,17 @@
       </c>
       <c r="M95" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N95" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O95" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
+          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P95" s="33" t="n"/>
@@ -13788,15 +13786,19 @@
       </c>
       <c r="V95" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W95" s="33" t="inlineStr">
         <is>
-          <t>TS-22695</t>
-        </is>
-      </c>
-      <c r="X95" s="33" t="n"/>
+          <t>EAO-25</t>
+        </is>
+      </c>
+      <c r="X95" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
       <c r="Y95" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -13809,7 +13811,7 @@
         <v>46235</v>
       </c>
       <c r="B96" s="37" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
@@ -13818,7 +13820,7 @@
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>The American National Red Cross</t>
         </is>
       </c>
       <c r="E96" s="39" t="n">
@@ -13826,7 +13828,7 @@
       </c>
       <c r="F96" s="33" t="inlineStr">
         <is>
-          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
+          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
         </is>
       </c>
       <c r="G96" s="33" t="inlineStr">
@@ -13836,17 +13838,17 @@
       </c>
       <c r="H96" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="I96" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J96" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K96" s="33" t="inlineStr">
@@ -13861,17 +13863,17 @@
       </c>
       <c r="M96" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="N96" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O96" s="33" t="inlineStr">
         <is>
-          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
         </is>
       </c>
       <c r="P96" s="33" t="n"/>
@@ -13894,27 +13896,21 @@
       </c>
       <c r="V96" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W96" s="33" t="inlineStr">
         <is>
-          <t>EAO-31</t>
-        </is>
-      </c>
-      <c r="X96" s="33" t="inlineStr">
-        <is>
-          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
-        </is>
-      </c>
+          <t>TS-22695</t>
+        </is>
+      </c>
+      <c r="X96" s="33" t="n"/>
       <c r="Y96" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z96" s="37" t="n">
-        <v>46272</v>
-      </c>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z96" s="37" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="35" t="n">
@@ -13930,7 +13926,7 @@
       </c>
       <c r="D97" s="33" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="E97" s="39" t="n">
@@ -13938,7 +13934,7 @@
       </c>
       <c r="F97" s="33" t="inlineStr">
         <is>
-          <t>Baxter International Reports a Cybersecurity Incident</t>
+          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
         </is>
       </c>
       <c r="G97" s="33" t="inlineStr">
@@ -13953,12 +13949,12 @@
       </c>
       <c r="I97" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J97" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K97" s="33" t="inlineStr">
@@ -13973,7 +13969,7 @@
       </c>
       <c r="M97" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N97" s="33" t="inlineStr">
@@ -13983,7 +13979,7 @@
       </c>
       <c r="O97" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
         </is>
       </c>
       <c r="P97" s="33" t="n"/>
@@ -14006,16 +14002,27 @@
       </c>
       <c r="V97" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="X97" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W97" s="33" t="inlineStr">
+        <is>
+          <t>EAO-31</t>
+        </is>
+      </c>
+      <c r="X97" s="33" t="inlineStr">
+        <is>
+          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
+        </is>
+      </c>
       <c r="Y97" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z97" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z97" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
@@ -14039,7 +14046,7 @@
       </c>
       <c r="F98" s="33" t="inlineStr">
         <is>
-          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
+          <t>Baxter International Reports a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G98" s="33" t="inlineStr">
@@ -14074,7 +14081,7 @@
       </c>
       <c r="M98" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Duplicate Decision Validation</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N98" s="33" t="inlineStr">
@@ -14084,7 +14091,7 @@
       </c>
       <c r="O98" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
         </is>
       </c>
       <c r="P98" s="33" t="n"/>
@@ -14127,12 +14134,12 @@
       </c>
       <c r="C99" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D99" s="33" t="inlineStr">
         <is>
-          <t>Liberty Blume</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="E99" s="39" t="n">
@@ -14140,27 +14147,27 @@
       </c>
       <c r="F99" s="33" t="inlineStr">
         <is>
-          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
+          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G99" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H99" s="33" t="inlineStr">
         <is>
-          <t>Intelligence/Advisory Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I99" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J99" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K99" s="33" t="inlineStr">
@@ -14170,55 +14177,48 @@
       </c>
       <c r="L99" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M99" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit/grey-market component intelligence briefing capability</t>
+          <t>Entity &amp; Duplicate Decision Validation</t>
         </is>
       </c>
       <c r="N99" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O99" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
-        </is>
-      </c>
+          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+        </is>
+      </c>
+      <c r="P99" s="33" t="n"/>
       <c r="Q99" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R99" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S99" s="39" t="n"/>
       <c r="T99" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U99" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V99" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W99" s="33" t="inlineStr">
-        <is>
-          <t>EAO-32</t>
-        </is>
-      </c>
-      <c r="X99" s="33" t="inlineStr">
-        <is>
-          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
-        </is>
-      </c>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="X99" s="33" t="n"/>
       <c r="Y99" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14228,19 +14228,19 @@
     </row>
     <row r="100">
       <c r="A100" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B100" s="37" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Counterfeit</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Liberty Blume</t>
         </is>
       </c>
       <c r="E100" s="39" t="n">
@@ -14248,27 +14248,27 @@
       </c>
       <c r="F100" s="33" t="inlineStr">
         <is>
-          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
+          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
         </is>
       </c>
       <c r="G100" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H100" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Intelligence/Advisory Request</t>
         </is>
       </c>
       <c r="I100" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J100" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K100" s="33" t="inlineStr">
@@ -14278,53 +14278,53 @@
       </c>
       <c r="L100" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M100" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
+          <t>Counterfeit/grey-market component intelligence briefing capability</t>
         </is>
       </c>
       <c r="N100" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O100" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
         </is>
       </c>
       <c r="Q100" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R100" s="39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T100" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="U100" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V100" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W100" s="33" t="inlineStr">
         <is>
-          <t>EAO-33</t>
+          <t>EAO-32</t>
         </is>
       </c>
       <c r="X100" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
         </is>
       </c>
       <c r="Y100" s="33" t="inlineStr">
@@ -14339,16 +14339,16 @@
         <v>46266</v>
       </c>
       <c r="B101" s="37" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D101" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E101" s="39" t="n">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="F101" s="33" t="inlineStr">
         <is>
-          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
+          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G101" s="33" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="M101" s="33" t="inlineStr">
         <is>
-          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
+          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
         </is>
       </c>
       <c r="N101" s="33" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="O101" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q101" s="33" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="W101" s="33" t="inlineStr">
         <is>
-          <t>EAO-34</t>
+          <t>EAO-33</t>
         </is>
       </c>
       <c r="X101" s="33" t="inlineStr">
@@ -14447,24 +14447,24 @@
         <v>46266</v>
       </c>
       <c r="B102" s="37" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>Eaton/Ford</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E102" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="33" t="inlineStr">
         <is>
-          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
+          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
         </is>
       </c>
       <c r="G102" s="33" t="inlineStr">
@@ -14474,17 +14474,17 @@
       </c>
       <c r="H102" s="33" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I102" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J102" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K102" s="33" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="M102" s="33" t="inlineStr">
         <is>
-          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
+          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
         </is>
       </c>
       <c r="N102" s="33" t="inlineStr">
@@ -14509,23 +14509,19 @@
       </c>
       <c r="O102" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
-        </is>
-      </c>
-      <c r="P102" s="33" t="n"/>
+          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+        </is>
+      </c>
       <c r="Q102" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R102" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S102" s="39" t="n"/>
-      <c r="T102" s="35" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="T102" s="35" t="n">
+        <v>46266</v>
       </c>
       <c r="U102" s="33" t="inlineStr">
         <is>
@@ -14534,22 +14530,22 @@
       </c>
       <c r="V102" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W102" s="33" t="inlineStr">
         <is>
-          <t>EAO-35/EAO-36</t>
+          <t>EAO-34</t>
         </is>
       </c>
       <c r="X102" s="33" t="inlineStr">
         <is>
-          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
         </is>
       </c>
       <c r="Y102" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z102" s="37" t="n"/>
@@ -14559,24 +14555,24 @@
         <v>46266</v>
       </c>
       <c r="B103" s="37" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D103" s="33" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Eaton/Ford</t>
         </is>
       </c>
       <c r="E103" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="33" t="inlineStr">
         <is>
-          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
+          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
         </is>
       </c>
       <c r="G103" s="33" t="inlineStr">
@@ -14586,17 +14582,17 @@
       </c>
       <c r="H103" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">
@@ -14611,7 +14607,7 @@
       </c>
       <c r="M103" s="33" t="inlineStr">
         <is>
-          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
+          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
         </is>
       </c>
       <c r="N103" s="33" t="inlineStr">
@@ -14621,17 +14617,13 @@
       </c>
       <c r="O103" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
-        </is>
-      </c>
-      <c r="P103" s="33" t="inlineStr">
-        <is>
-          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
-        </is>
-      </c>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
+        </is>
+      </c>
+      <c r="P103" s="33" t="n"/>
       <c r="Q103" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R103" s="39" t="n">
@@ -14650,22 +14642,22 @@
       </c>
       <c r="V103" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>AI-Assisted Geofencing</t>
         </is>
       </c>
       <c r="W103" s="33" t="inlineStr">
         <is>
-          <t>EAO-37</t>
+          <t>EAO-35/EAO-36</t>
         </is>
       </c>
       <c r="X103" s="33" t="inlineStr">
         <is>
-          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
         </is>
       </c>
       <c r="Y103" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z103" s="37" t="n"/>
@@ -14679,12 +14671,12 @@
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="E104" s="39" t="n">
@@ -14692,27 +14684,27 @@
       </c>
       <c r="F104" s="33" t="inlineStr">
         <is>
-          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
+          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
         </is>
       </c>
       <c r="G104" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H104" s="33" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I104" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14722,28 +14714,32 @@
       </c>
       <c r="L104" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M104" s="33" t="inlineStr">
         <is>
-          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
+          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
         </is>
       </c>
       <c r="N104" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
-        </is>
-      </c>
-      <c r="P104" s="33" t="n"/>
+          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
+        </is>
+      </c>
+      <c r="P104" s="33" t="inlineStr">
+        <is>
+          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q104" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R104" s="39" t="n">
@@ -14757,7 +14753,7 @@
       </c>
       <c r="U104" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V104" s="33" t="inlineStr">
@@ -14767,12 +14763,12 @@
       </c>
       <c r="W104" s="33" t="inlineStr">
         <is>
-          <t>EAO-38</t>
+          <t>EAO-37</t>
         </is>
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
+          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">
@@ -14787,16 +14783,16 @@
         <v>46266</v>
       </c>
       <c r="B105" s="37" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D105" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E105" s="39" t="n">
@@ -14804,7 +14800,7 @@
       </c>
       <c r="F105" s="33" t="inlineStr">
         <is>
-          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
+          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
         </is>
       </c>
       <c r="G105" s="33" t="inlineStr">
@@ -14814,17 +14810,17 @@
       </c>
       <c r="H105" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J105" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K105" s="33" t="inlineStr">
@@ -14839,17 +14835,17 @@
       </c>
       <c r="M105" s="33" t="inlineStr">
         <is>
-          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
+          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
         </is>
       </c>
       <c r="N105" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. The query ran on through two follow-ups, both part of the same contact rather than separate records. First, on 18-Sep-2026 the customer cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked how EventWatch separates real reporting from fake, what criteria establish that a notification is not fake, and whether the 28nm reduction is real; a written assessment was issued covering the source hierarchy, the five evidence grades and the TSMC timeline. Second, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage.</t>
+          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
         </is>
       </c>
       <c r="P105" s="33" t="n"/>
@@ -14869,27 +14865,27 @@
       </c>
       <c r="U105" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V105" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W105" s="33" t="inlineStr">
         <is>
-          <t>EAO-39</t>
+          <t>EAO-38</t>
         </is>
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
+          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z105" s="37" t="n"/>
@@ -14916,27 +14912,27 @@
       </c>
       <c r="F106" s="33" t="inlineStr">
         <is>
-          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
+          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G106" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H106" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I106" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J106" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K106" s="33" t="inlineStr">
@@ -14946,12 +14942,12 @@
       </c>
       <c r="L106" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M106" s="33" t="inlineStr">
         <is>
-          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
+          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
         </is>
       </c>
       <c r="N106" s="33" t="inlineStr">
@@ -14961,13 +14957,13 @@
       </c>
       <c r="O106" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
+          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. The query ran on through two follow-ups, both part of the same contact rather than separate records. First, on 18-Sep-2026 the customer cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked how EventWatch separates real reporting from fake, what criteria establish that a notification is not fake, and whether the 28nm reduction is real; a written assessment was issued covering the source hierarchy, the five evidence grades and the TSMC timeline. Second, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage.</t>
         </is>
       </c>
       <c r="P106" s="33" t="n"/>
       <c r="Q106" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R106" s="39" t="n">
@@ -14986,7 +14982,7 @@
       </c>
       <c r="V106" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W106" s="33" t="inlineStr">
@@ -14996,12 +14992,12 @@
       </c>
       <c r="X106" s="33" t="inlineStr">
         <is>
-          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
+          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
         </is>
       </c>
       <c r="Y106" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z106" s="37" t="n"/>
@@ -15015,12 +15011,12 @@
       </c>
       <c r="C107" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D107" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E107" s="39" t="n">
@@ -15028,7 +15024,7 @@
       </c>
       <c r="F107" s="33" t="inlineStr">
         <is>
-          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
+          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G107" s="33" t="inlineStr">
@@ -15043,12 +15039,12 @@
       </c>
       <c r="I107" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J107" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K107" s="33" t="inlineStr">
@@ -15063,7 +15059,7 @@
       </c>
       <c r="M107" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
+          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
         </is>
       </c>
       <c r="N107" s="33" t="inlineStr">
@@ -15073,7 +15069,7 @@
       </c>
       <c r="O107" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
+          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
         </is>
       </c>
       <c r="P107" s="33" t="n"/>
@@ -15093,27 +15089,27 @@
       </c>
       <c r="U107" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V107" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W107" s="33" t="inlineStr">
         <is>
-          <t>EAO-40</t>
+          <t>EAO-39</t>
         </is>
       </c>
       <c r="X107" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
+          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
         </is>
       </c>
       <c r="Y107" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z107" s="37" t="n"/>
@@ -15123,16 +15119,16 @@
         <v>46266</v>
       </c>
       <c r="B108" s="37" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E108" s="39" t="n">
@@ -15140,7 +15136,7 @@
       </c>
       <c r="F108" s="33" t="inlineStr">
         <is>
-          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
+          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
         </is>
       </c>
       <c r="G108" s="33" t="inlineStr">
@@ -15150,7 +15146,7 @@
       </c>
       <c r="H108" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I108" s="33" t="inlineStr">
@@ -15160,7 +15156,7 @@
       </c>
       <c r="J108" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K108" s="33" t="inlineStr">
@@ -15175,7 +15171,7 @@
       </c>
       <c r="M108" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
+          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
@@ -15185,7 +15181,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15205,7 +15201,7 @@
       </c>
       <c r="U108" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V108" s="33" t="inlineStr">
@@ -15215,12 +15211,12 @@
       </c>
       <c r="W108" s="33" t="inlineStr">
         <is>
-          <t>EAO-41</t>
+          <t>EAO-40</t>
         </is>
       </c>
       <c r="X108" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
         </is>
       </c>
       <c r="Y108" s="33" t="inlineStr">
@@ -15228,16 +15224,14 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z108" s="37" t="n">
-        <v>46288</v>
-      </c>
+      <c r="Z108" s="37" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B109" s="37" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
@@ -15246,7 +15240,7 @@
       </c>
       <c r="D109" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Irving Oil</t>
         </is>
       </c>
       <c r="E109" s="39" t="n">
@@ -15254,7 +15248,7 @@
       </c>
       <c r="F109" s="33" t="inlineStr">
         <is>
-          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
+          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
         </is>
       </c>
       <c r="G109" s="33" t="inlineStr">
@@ -15289,7 +15283,7 @@
       </c>
       <c r="M109" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N109" s="33" t="inlineStr">
@@ -15299,14 +15293,10 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
-        </is>
-      </c>
-      <c r="P109" s="33" t="inlineStr">
-        <is>
-          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
-        </is>
-      </c>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+        </is>
+      </c>
+      <c r="P109" s="33" t="n"/>
       <c r="Q109" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15333,12 +15323,12 @@
       </c>
       <c r="W109" s="33" t="inlineStr">
         <is>
-          <t>EAO-42</t>
+          <t>EAO-41</t>
         </is>
       </c>
       <c r="X109" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y109" s="33" t="inlineStr">
@@ -15359,12 +15349,12 @@
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E110" s="39" t="n">
@@ -15372,7 +15362,7 @@
       </c>
       <c r="F110" s="33" t="inlineStr">
         <is>
-          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
+          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
         </is>
       </c>
       <c r="G110" s="33" t="inlineStr">
@@ -15382,7 +15372,7 @@
       </c>
       <c r="H110" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I110" s="33" t="inlineStr">
@@ -15392,7 +15382,7 @@
       </c>
       <c r="J110" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K110" s="33" t="inlineStr">
@@ -15407,7 +15397,7 @@
       </c>
       <c r="M110" s="33" t="inlineStr">
         <is>
-          <t>Coverage of ransomware-group leak-site claims and threat-intelligence reporting, so a claimed breach at a named supplier is captured when the group publishes it rather than when a customer's own threat team circulates it internally</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N110" s="33" t="inlineStr">
@@ -15417,10 +15407,14 @@
       </c>
       <c r="O110" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
-        </is>
-      </c>
-      <c r="P110" s="33" t="n"/>
+          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
+        </is>
+      </c>
+      <c r="P110" s="33" t="inlineStr">
+        <is>
+          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
+        </is>
+      </c>
       <c r="Q110" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15445,10 +15439,14 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W110" s="33" t="n"/>
+      <c r="W110" s="33" t="inlineStr">
+        <is>
+          <t>EAO-42</t>
+        </is>
+      </c>
       <c r="X110" s="33" t="inlineStr">
         <is>
-          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y110" s="33" t="inlineStr">
@@ -15456,23 +15454,25 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z110" s="37" t="n"/>
+      <c r="Z110" s="37" t="n">
+        <v>46288</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B111" s="37" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E111" s="39" t="n">
@@ -15480,27 +15480,27 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15510,28 +15510,28 @@
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+          <t>Coverage of ransomware-group leak-site claims and threat-intelligence reporting, so a claimed breach at a named supplier is captured when the group publishes it rather than when a customer's own threat team circulates it internally</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
       <c r="Q111" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R111" s="39" t="n">
@@ -15545,27 +15545,23 @@
       </c>
       <c r="U111" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W111" s="33" t="inlineStr">
-        <is>
-          <t>EAO-43</t>
-        </is>
-      </c>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W111" s="33" t="n"/>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -15575,11 +15571,11 @@
         <v>46266</v>
       </c>
       <c r="B112" s="37" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
@@ -15592,7 +15588,7 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
@@ -15602,17 +15598,17 @@
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15627,7 +15623,7 @@
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
@@ -15637,7 +15633,7 @@
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
@@ -15657,27 +15653,27 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
+          <t>EAO-43</t>
         </is>
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
@@ -15691,12 +15687,12 @@
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E113" s="39" t="n">
@@ -15704,17 +15700,17 @@
       </c>
       <c r="F113" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G113" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I113" s="33" t="inlineStr">
@@ -15724,7 +15720,7 @@
       </c>
       <c r="J113" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K113" s="33" t="inlineStr">
@@ -15734,40 +15730,34 @@
       </c>
       <c r="L113" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
-        </is>
-      </c>
-      <c r="P113" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P113" s="33" t="n"/>
       <c r="Q113" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R113" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S113" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S113" s="39" t="n"/>
       <c r="T113" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15775,22 +15765,22 @@
       </c>
       <c r="U113" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V113" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W113" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X113" s="33" t="inlineStr">
         <is>
-          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
         </is>
       </c>
       <c r="Y113" s="33" t="inlineStr">
@@ -15805,16 +15795,16 @@
         <v>46266</v>
       </c>
       <c r="B114" s="37" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E114" s="39" t="n">
@@ -15822,7 +15812,7 @@
       </c>
       <c r="F114" s="33" t="inlineStr">
         <is>
-          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
         </is>
       </c>
       <c r="G114" s="33" t="inlineStr">
@@ -15832,17 +15822,17 @@
       </c>
       <c r="H114" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I114" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15852,12 +15842,12 @@
       </c>
       <c r="L114" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M114" s="33" t="inlineStr">
         <is>
-          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
         </is>
       </c>
       <c r="N114" s="33" t="inlineStr">
@@ -15867,19 +15857,25 @@
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
-        </is>
-      </c>
-      <c r="P114" s="33" t="n"/>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q114" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R114" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S114" s="39" t="n"/>
+      <c r="S114" s="39" t="n">
+        <v>252</v>
+      </c>
       <c r="T114" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15887,27 +15883,27 @@
       </c>
       <c r="U114" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V114" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W114" s="33" t="inlineStr">
         <is>
-          <t>EAO-46</t>
+          <t>EAO-45</t>
         </is>
       </c>
       <c r="X114" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
         </is>
       </c>
       <c r="Y114" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z114" s="37" t="n"/>
@@ -15921,12 +15917,12 @@
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E115" s="39" t="n">
@@ -15934,17 +15930,17 @@
       </c>
       <c r="F115" s="33" t="inlineStr">
         <is>
-          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
+          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
         </is>
       </c>
       <c r="G115" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H115" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="I115" s="33" t="inlineStr">
@@ -15954,7 +15950,7 @@
       </c>
       <c r="J115" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K115" s="33" t="inlineStr">
@@ -15964,12 +15960,12 @@
       </c>
       <c r="L115" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M115" s="33" t="inlineStr">
         <is>
-          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
+          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N115" s="33" t="inlineStr">
@@ -15979,7 +15975,7 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
         </is>
       </c>
       <c r="P115" s="33" t="n"/>
@@ -16004,17 +16000,17 @@
       </c>
       <c r="V115" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W115" s="33" t="inlineStr">
         <is>
-          <t>EAO-47</t>
+          <t>EAO-46</t>
         </is>
       </c>
       <c r="X115" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
+          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
         </is>
       </c>
       <c r="Y115" s="33" t="inlineStr">
@@ -16033,12 +16029,12 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E116" s="39" t="n">
@@ -16046,17 +16042,17 @@
       </c>
       <c r="F116" s="33" t="inlineStr">
         <is>
-          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
         </is>
       </c>
       <c r="G116" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H116" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I116" s="33" t="inlineStr">
@@ -16076,12 +16072,12 @@
       </c>
       <c r="L116" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M116" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
+          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
         </is>
       </c>
       <c r="N116" s="33" t="inlineStr">
@@ -16091,13 +16087,13 @@
       </c>
       <c r="O116" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
+          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
         </is>
       </c>
       <c r="P116" s="33" t="n"/>
       <c r="Q116" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R116" s="39" t="n">
@@ -16111,7 +16107,7 @@
       </c>
       <c r="U116" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V116" s="33" t="inlineStr">
@@ -16121,10 +16117,14 @@
       </c>
       <c r="W116" s="33" t="inlineStr">
         <is>
-          <t>EAO-48</t>
-        </is>
-      </c>
-      <c r="X116" s="33" t="n"/>
+          <t>EAO-47</t>
+        </is>
+      </c>
+      <c r="X116" s="33" t="inlineStr">
+        <is>
+          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
+        </is>
+      </c>
       <c r="Y116" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -16137,16 +16137,16 @@
         <v>46266</v>
       </c>
       <c r="B117" s="37" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E117" s="39" t="n">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="F117" s="33" t="inlineStr">
         <is>
-          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
+          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
         </is>
       </c>
       <c r="G117" s="33" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="H117" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I117" s="33" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="J117" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K117" s="33" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="M117" s="33" t="inlineStr">
         <is>
-          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
+          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N117" s="33" t="inlineStr">
@@ -16199,13 +16199,13 @@
       </c>
       <c r="O117" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P117" s="33" t="n"/>
       <c r="Q117" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R117" s="39" t="n">
@@ -16219,17 +16219,17 @@
       </c>
       <c r="U117" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V117" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W117" s="33" t="inlineStr">
         <is>
-          <t>EAO-49</t>
+          <t>EAO-48</t>
         </is>
       </c>
       <c r="X117" s="33" t="n"/>
@@ -16242,19 +16242,19 @@
     </row>
     <row r="118">
       <c r="A118" s="35" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="B118" s="37" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E118" s="39" t="n">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="F118" s="33" t="inlineStr">
         <is>
-          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
+          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
         </is>
       </c>
       <c r="G118" s="33" t="inlineStr">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="H118" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I118" s="33" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="J118" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K118" s="33" t="inlineStr">
@@ -16297,7 +16297,7 @@
       </c>
       <c r="M118" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
+          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
         </is>
       </c>
       <c r="N118" s="33" t="inlineStr">
@@ -16307,22 +16307,22 @@
       </c>
       <c r="O118" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
         </is>
       </c>
       <c r="P118" s="33" t="n"/>
       <c r="Q118" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R118" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S118" s="39" t="n"/>
       <c r="T118" s="35" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="U118" s="33" t="inlineStr">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="V118" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W118" s="33" t="inlineStr">
         <is>
-          <t>EAO-50</t>
+          <t>EAO-49</t>
         </is>
       </c>
       <c r="X118" s="33" t="n"/>
@@ -16347,6 +16347,114 @@
         </is>
       </c>
       <c r="Z118" s="37" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B119" s="37" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C119" s="33" t="inlineStr">
+        <is>
+          <t>Labor Disruption</t>
+        </is>
+      </c>
+      <c r="D119" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E119" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="33" t="inlineStr">
+        <is>
+          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
+        </is>
+      </c>
+      <c r="G119" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H119" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I119" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J119" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K119" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L119" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M119" s="33" t="inlineStr">
+        <is>
+          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
+        </is>
+      </c>
+      <c r="N119" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O119" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
+        </is>
+      </c>
+      <c r="P119" s="33" t="n"/>
+      <c r="Q119" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R119" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S119" s="39" t="n"/>
+      <c r="T119" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U119" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V119" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W119" s="33" t="inlineStr">
+        <is>
+          <t>EAO-50</t>
+        </is>
+      </c>
+      <c r="X119" s="33" t="n"/>
+      <c r="Y119" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z119" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18104,7 +18212,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.36082474226804123</v>
+        <v>0.35714285714285715</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18126,13 +18234,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -18145,7 +18253,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13402061855670103</v>
+        <v>0.1326530612244898</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18187,7 +18295,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07216494845360824</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18229,7 +18337,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18271,7 +18379,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.041237113402061855</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18313,7 +18421,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030927835051546393</v>
+        <v>0.030612244897959183</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18355,7 +18463,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18397,7 +18505,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18439,7 +18547,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18481,7 +18589,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020618556701030927</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18908,13 +19016,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="2">
-                  <v>102</v>
+                  <v>103</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>56</v>
+                  <v>57</v>
                 </pt>
                 <pt idx="1">
                   <v>36</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>General Mills</v>
+                </pt>
+                <pt idx="7">
                   <v>META</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>Merck</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>Schneider Electric</v>
-                </pt>
-                <pt idx="9">
-                  <v>UVM Health Network</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>24</v>
+                  <v>25</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z119" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z120" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E152" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E153" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z119"/>
+  <dimension ref="A1:Z120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. There is no EAO key for this record: the CSM raised it by email to the team rather than opening a Jira ticket.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15553,7 +15553,11 @@
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W111" s="33" t="n"/>
+      <c r="W111" s="33" t="inlineStr">
+        <is>
+          <t>EAO-51</t>
+        </is>
+      </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
           <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
@@ -16455,6 +16459,114 @@
         </is>
       </c>
       <c r="Z119" s="37" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B120" s="37" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C120" s="33" t="inlineStr">
+        <is>
+          <t>Utility Disruption</t>
+        </is>
+      </c>
+      <c r="D120" s="33" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="E120" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="33" t="inlineStr">
+        <is>
+          <t>Carlisle, Iowa Municipal Water Disruption – No WarRoom Created (General Mills)</t>
+        </is>
+      </c>
+      <c r="G120" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H120" s="33" t="inlineStr">
+        <is>
+          <t>Missed WarRoom</t>
+        </is>
+      </c>
+      <c r="I120" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J120" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K120" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L120" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M120" s="33" t="inlineStr">
+        <is>
+          <t>Capture of municipal utility disruptions and do-not-use-water orders, and their association with mapped customer sites in the named locality</t>
+        </is>
+      </c>
+      <c r="N120" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O120" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage, geofencing and WarRoom creation are all still open.</t>
+        </is>
+      </c>
+      <c r="P120" s="33" t="n"/>
+      <c r="Q120" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R120" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S120" s="39" t="n"/>
+      <c r="T120" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U120" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V120" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W120" s="33" t="inlineStr">
+        <is>
+          <t>EAO-52</t>
+        </is>
+      </c>
+      <c r="X120" s="33" t="n"/>
+      <c r="Y120" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z120" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18212,7 +18324,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35714285714285715</v>
+        <v>0.35353535353535354</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18230,7 +18342,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -18253,7 +18365,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1326530612244898</v>
+        <v>0.13131313131313133</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18295,7 +18407,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.0707070707070707</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18337,7 +18449,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04081632653061224</v>
+        <v>0.04040404040404041</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18379,7 +18491,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04081632653061224</v>
+        <v>0.04040404040404041</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18421,7 +18533,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030612244897959183</v>
+        <v>0.030303030303030304</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18456,14 +18568,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.020202020202020204</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18498,14 +18610,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.020202020202020204</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18540,14 +18652,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.020202020202020204</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18582,14 +18694,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>UVM Health Network</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02040816326530612</v>
+        <v>0.020202020202020204</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -18982,17 +19094,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Utility Disruption</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="76" t="n">
         <v>1</v>
-      </c>
-      <c r="L90" s="76" t="n">
-        <v>4</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19010,19 +19122,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J91" s="77" t="n">
-        <v>98</v>
-      </c>
-      <c r="K91" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L91" s="77" t="n">
-        <v>118</v>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="76" t="n">
+        <v>4</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -19040,10 +19152,20 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="78" t="n"/>
-      <c r="K92" s="78" t="n"/>
-      <c r="L92" s="78" t="n"/>
+      <c r="I92" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J92" s="77" t="n">
+        <v>99</v>
+      </c>
+      <c r="K92" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="L92" s="77" t="n">
+        <v>119</v>
+      </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -19541,7 +19663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23610,6 +23732,33 @@
         </is>
       </c>
       <c r="E152" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30.75" customHeight="1">
+      <c r="A153" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B153" s="41" t="inlineStr">
+        <is>
+          <t>Utility Disruption</t>
+        </is>
+      </c>
+      <c r="C153" s="41" t="inlineStr">
+        <is>
+          <t>Loss or interruption of a non-electrical utility serving a facility - municipal water, gas or steam - including a do-not-use order that halts normal operations.</t>
+        </is>
+      </c>
+      <c r="D153" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use Power Outage where the utility lost is electricity.</t>
+        </is>
+      </c>
+      <c r="E153" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D143" s="41" t="inlineStr">
         <is>
-          <t>Standard event category. Use for grid and utility failures; use Extreme Weather where the outage is incidental to a storm already being reported.</t>
+          <t>Standard event category. Use for electrical supply failures only - a water, gas or steam outage is Utility Disruption; use Extreme Weather where the outage is incidental to a storm already being reported.</t>
         </is>
       </c>
       <c r="E143" s="41" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E153" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E152" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -16469,7 +16469,7 @@
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>Utility Disruption</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
@@ -18342,7 +18342,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -18960,13 +18960,13 @@
         </is>
       </c>
       <c r="J85" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K85" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L85" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" ht="23.25" customHeight="1">
@@ -19094,17 +19094,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Utility Disruption</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K90" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L90" s="76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19122,19 +19122,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="20" t="inlineStr">
-        <is>
-          <t>Wildfire</t>
-        </is>
-      </c>
-      <c r="J91" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" s="76" t="n">
-        <v>4</v>
+      <c r="I91" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J91" s="77" t="n">
+        <v>99</v>
+      </c>
+      <c r="K91" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="L91" s="77" t="n">
+        <v>119</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -19152,20 +19152,10 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J92" s="77" t="n">
-        <v>99</v>
-      </c>
-      <c r="K92" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L92" s="77" t="n">
-        <v>119</v>
-      </c>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="78" t="n"/>
+      <c r="K92" s="78" t="n"/>
+      <c r="L92" s="78" t="n"/>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -19663,7 +19653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23480,12 +23470,12 @@
       </c>
       <c r="C143" s="41" t="inlineStr">
         <is>
-          <t>Loss or failure of electrical power supply affecting a facility, region, or grid.</t>
+          <t>Loss or failure of a utility supply affecting a facility, region, or grid: electrical power, and also water, internet and other utility cuts, which are all notified under this one type.</t>
         </is>
       </c>
       <c r="D143" s="41" t="inlineStr">
         <is>
-          <t>Standard event category. Use for electrical supply failures only - a water, gas or steam outage is Utility Disruption; use Extreme Weather where the outage is incidental to a storm already being reported.</t>
+          <t>Standard event category. Use for grid and utility failures; use Extreme Weather where the outage is incidental to a storm already being reported.</t>
         </is>
       </c>
       <c r="E143" s="41" t="inlineStr">
@@ -23732,33 +23722,6 @@
         </is>
       </c>
       <c r="E152" s="41" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="30.75" customHeight="1">
-      <c r="A153" s="42" t="inlineStr">
-        <is>
-          <t>Event type</t>
-        </is>
-      </c>
-      <c r="B153" s="41" t="inlineStr">
-        <is>
-          <t>Utility Disruption</t>
-        </is>
-      </c>
-      <c r="C153" s="41" t="inlineStr">
-        <is>
-          <t>Loss or interruption of a non-electrical utility serving a facility - municipal water, gas or steam - including a do-not-use order that halts normal operations.</t>
-        </is>
-      </c>
-      <c r="D153" s="41" t="inlineStr">
-        <is>
-          <t>Standard event category. Use Power Outage where the utility lost is electricity.</t>
-        </is>
-      </c>
-      <c r="E153" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="L117" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M117" s="33" t="inlineStr">
@@ -16236,13 +16236,19 @@
           <t>EAO-48</t>
         </is>
       </c>
-      <c r="X117" s="33" t="n"/>
+      <c r="X117" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+        </is>
+      </c>
       <c r="Y117" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z117" s="37" t="n"/>
+      <c r="Z117" s="37" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="35" t="n">
@@ -16452,7 +16458,11 @@
           <t>EAO-50</t>
         </is>
       </c>
-      <c r="X119" s="33" t="n"/>
+      <c r="X119" s="33" t="inlineStr">
+        <is>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA is with internal review and has not gone to the customer.</t>
+        </is>
+      </c>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16460,7 +16460,7 @@
       </c>
       <c r="X119" s="33" t="inlineStr">
         <is>
-          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA is with internal review and has not gone to the customer.</t>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y119" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2085,7 +2085,7 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="2">
                   <v>103</v>
@@ -2381,7 +2381,7 @@
                   <v>57</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>35</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>32</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z120" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z121" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z120"/>
+  <dimension ref="A1:Z121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Coverage of ransomware-group leak-site claims and threat-intelligence reporting, so a claimed breach at a named supplier is captured when the group publishes it rather than when a customer's own threat team circulates it internally</t>
+          <t>A Not-Impactful decision check on clusters naming a mapped customer supplier, so a breach claim that is clustered and then dismissed is re-examined before it is dropped</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
+          <t>Engineering confirmed on the ticket that the article was captured by the portal and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful. The event was therefore captured on 15-Sep and dismissed, not missed by coverage; the WarRoom was published on 29-Sep, fourteen days after the first report. The ticket does not say whether an analyst or automated logic marked the cluster, which is what separates People / Review from Product / Review.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="J120" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K120" s="33" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="M120" s="33" t="inlineStr">
         <is>
-          <t>Capture of municipal utility disruptions and do-not-use-water orders, and their association with mapped customer sites in the named locality</t>
+          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
         </is>
       </c>
       <c r="N120" s="33" t="inlineStr">
@@ -16570,13 +16570,125 @@
           <t>EAO-52</t>
         </is>
       </c>
-      <c r="X120" s="33" t="n"/>
+      <c r="X120" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
+        </is>
+      </c>
       <c r="Y120" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z120" s="37" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B121" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C121" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E121" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G121" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I121" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J121" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K121" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L121" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M121" s="33" t="inlineStr">
+        <is>
+          <t>Detection of bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is captured when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N121" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O121" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P121" s="33" t="n"/>
+      <c r="Q121" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R121" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S121" s="39" t="n"/>
+      <c r="T121" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U121" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V121" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="inlineStr">
+        <is>
+          <t>EAO-53</t>
+        </is>
+      </c>
+      <c r="X121" s="33" t="n"/>
+      <c r="Y121" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z121" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18330,11 +18442,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35353535353535354</v>
+        <v>0.36</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18356,13 +18468,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -18375,7 +18487,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13131313131313133</v>
+        <v>0.13</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18417,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18459,7 +18571,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.04</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18501,7 +18613,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.04</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18543,7 +18655,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030303030303030304</v>
+        <v>0.03</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18585,7 +18697,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18627,7 +18739,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18669,7 +18781,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18711,7 +18823,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19138,13 +19250,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1771,7 +1771,7 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
@@ -2085,7 +2085,7 @@
                   <v>0</v>
                 </pt>
                 <pt idx="1">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="2">
                   <v>103</v>
@@ -2381,7 +2381,7 @@
                   <v>57</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>35</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>32</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z120" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z121" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z120"/>
+  <dimension ref="A1:Z121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Coverage of ransomware-group leak-site claims and threat-intelligence reporting, so a claimed breach at a named supplier is captured when the group publishes it rather than when a customer's own threat team circulates it internally</t>
+          <t>A Not-Impactful decision check on clusters naming a mapped customer supplier, so a breach claim that is clustered and then dismissed is re-examined before it is dropped</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Internal investigation found that the ADM breach was not captured on the EventWatch portal, and attributes the miss to source coverage. The finding has been shared with General Mills.</t>
+          <t>Engineering confirmed on the ticket that the article was captured by the portal and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful. The event was therefore captured on 15-Sep and dismissed, not missed by coverage; the WarRoom was published on 29-Sep, fourteen days after the first report. The ticket does not say whether an analyst or automated logic marked the cluster, which is what separates People / Review from Product / Review.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="L117" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M117" s="33" t="inlineStr">
@@ -16236,13 +16236,19 @@
           <t>EAO-48</t>
         </is>
       </c>
-      <c r="X117" s="33" t="n"/>
+      <c r="X117" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+        </is>
+      </c>
       <c r="Y117" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z117" s="37" t="n"/>
+      <c r="Z117" s="37" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="35" t="n">
@@ -16452,7 +16458,11 @@
           <t>EAO-50</t>
         </is>
       </c>
-      <c r="X119" s="33" t="n"/>
+      <c r="X119" s="33" t="inlineStr">
+        <is>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
+        </is>
+      </c>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -16502,7 +16512,7 @@
       </c>
       <c r="J120" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K120" s="33" t="inlineStr">
@@ -16517,7 +16527,7 @@
       </c>
       <c r="M120" s="33" t="inlineStr">
         <is>
-          <t>Capture of municipal utility disruptions and do-not-use-water orders, and their association with mapped customer sites in the named locality</t>
+          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
         </is>
       </c>
       <c r="N120" s="33" t="inlineStr">
@@ -16560,13 +16570,125 @@
           <t>EAO-52</t>
         </is>
       </c>
-      <c r="X120" s="33" t="n"/>
+      <c r="X120" s="33" t="inlineStr">
+        <is>
+          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
+        </is>
+      </c>
       <c r="Y120" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z120" s="37" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B121" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C121" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D121" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E121" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G121" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I121" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J121" s="33" t="inlineStr">
+        <is>
+          <t>Source Coverage</t>
+        </is>
+      </c>
+      <c r="K121" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L121" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M121" s="33" t="inlineStr">
+        <is>
+          <t>Detection of bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is captured when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N121" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O121" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P121" s="33" t="n"/>
+      <c r="Q121" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R121" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S121" s="39" t="n"/>
+      <c r="T121" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U121" s="33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V121" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="inlineStr">
+        <is>
+          <t>EAO-53</t>
+        </is>
+      </c>
+      <c r="X121" s="33" t="n"/>
+      <c r="Y121" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z121" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18320,11 +18442,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35353535353535354</v>
+        <v>0.36</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18346,13 +18468,13 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" s="75" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="23.25" customHeight="1">
@@ -18365,7 +18487,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13131313131313133</v>
+        <v>0.13</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18407,7 +18529,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.0707070707070707</v>
+        <v>0.07</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18449,7 +18571,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.04</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18491,7 +18613,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04040404040404041</v>
+        <v>0.04</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18533,7 +18655,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.030303030303030304</v>
+        <v>0.03</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18575,7 +18697,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18617,7 +18739,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18659,7 +18781,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18701,7 +18823,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.020202020202020204</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19128,13 +19250,13 @@
         </is>
       </c>
       <c r="J91" s="77" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K91" s="77" t="n">
         <v>20</v>
       </c>
       <c r="L91" s="77" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>57</v>
+                  <v>58</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2981,10 +2981,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15510,12 +15510,12 @@
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>A Not-Impactful decision check on clusters naming a mapped customer supplier, so a breach claim that is clustered and then dismissed is re-examined before it is dropped</t>
+          <t>Keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Engineering confirmed on the ticket that the article was captured by the portal and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful. The event was therefore captured on 15-Sep and dismissed, not missed by coverage; the WarRoom was published on 29-Sep, fourteen days after the first report. The ticket does not say whether an analyst or automated logic marked the cluster, which is what separates People / Review from Product / Review.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for. The owner reads the overall miss as a keyword gap, and Nitin has asked Ankit to confirm. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="J121" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K121" s="33" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="M121" s="33" t="inlineStr">
         <is>
-          <t>Detection of bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is captured when it is published rather than when the customer raises it</t>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
         </is>
       </c>
       <c r="N121" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
+          <t>Keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it; and a not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner classifies this as Product plus human - a keyword gap on the three that were never captured, and an analyst not-impactful decision on the one that was. The tracker holds one Root Cause per row, so the row stays Product / Keyword Update, which is the half the ticket is still open on and the half that sets its routing, and the human half is recorded in RCA Details rather than on a second row: a second row would be a second customer email, and there was only one.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for. The owner reads the overall miss as a keyword gap, and Nitin has asked Ankit to confirm. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are still not accounted for. So there are two failures inside one incident: a keyword gap on the three that were never captured, and a not-impactful decision on the one that was. The owner classifies the cause as Product plus human and confirms that the not-impactful call was made by a person, not by automated logic. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet, and the keyword half is still open with PM.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>58</v>
+                  <v>57</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2981,10 +2981,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it; and a not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look</t>
+          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner classifies this as Product plus human - a keyword gap on the three that were never captured, and an analyst not-impactful decision on the one that was. The tracker holds one Root Cause per row, so the row stays Product / Keyword Update, which is the half the ticket is still open on and the half that sets its routing, and the human half is recorded in RCA Details rather than on a second row: a second row would be a second customer email, and there was only one.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are still not accounted for. So there are two failures inside one incident: a keyword gap on the three that were never captured, and a not-impactful decision on the one that was. The owner classifies the cause as Product plus human and confirms that the not-impactful call was made by a person, not by automated logic. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet, and the keyword half is still open with PM.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>58</v>
+                  <v>57</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2981,10 +2981,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -15495,12 +15495,12 @@
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
+          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
         </is>
       </c>
       <c r="P111" s="33" t="n"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for. The owner reads the overall miss as a keyword gap, and Nitin has asked Ankit to confirm. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z111" s="37" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16537,7 +16537,7 @@
       </c>
       <c r="O120" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage, geofencing and WarRoom creation are all still open.</t>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="P120" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1418,7 +1418,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="9">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>103</v>
+                  <v>104</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z121" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z122" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E152" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E153" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z121"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16587,16 +16587,16 @@
         <v>46296</v>
       </c>
       <c r="B121" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E121" s="39" t="n">
@@ -16604,27 +16604,27 @@
       </c>
       <c r="F121" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
         </is>
       </c>
       <c r="G121" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H121" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I121" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J121" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K121" s="33" t="inlineStr">
@@ -16634,28 +16634,28 @@
       </c>
       <c r="L121" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M121" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
         </is>
       </c>
       <c r="N121" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
       <c r="Q121" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R121" s="39" t="n">
@@ -16669,26 +16669,134 @@
       </c>
       <c r="U121" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V121" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="n"/>
+      <c r="X121" s="33" t="inlineStr">
+        <is>
+          <t>The WarRoom was created because NVIDIA is a mapped partner and the existing EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. On reassessment the price increase affected only the Shield TV Pro, which is not a product the customer procures, so there was no direct impact on products or services supplied to them. EventWatch agreed that an EventWatch bulletin without a WarRoom would have been the more appropriate treatment, and committed to reinforcing guidance to evaluate product-level relevance and customer exposure, not supplier mapping alone, before creating WarRooms for similar price fluctuation events.</t>
+        </is>
+      </c>
+      <c r="Y121" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z121" s="37" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B122" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C122" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D122" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E122" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G122" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I122" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J122" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K122" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L122" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M122" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N122" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O122" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P122" s="33" t="n"/>
+      <c r="Q122" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R122" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S122" s="39" t="n"/>
+      <c r="T122" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U122" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V121" s="33" t="inlineStr">
+      <c r="V122" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W121" s="33" t="inlineStr">
+      <c r="W122" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X121" s="33" t="n"/>
-      <c r="Y121" s="33" t="inlineStr">
+      <c r="X122" s="33" t="n"/>
+      <c r="Y122" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z121" s="37" t="n"/>
+      <c r="Z122" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18464,7 +18572,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -19102,17 +19210,17 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K86" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -19126,17 +19234,17 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K87" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -19156,17 +19264,17 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K88" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -19186,17 +19294,17 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J89" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L89" s="76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -19216,17 +19324,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19244,19 +19352,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J91" s="77" t="n">
-        <v>100</v>
-      </c>
-      <c r="K91" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L91" s="77" t="n">
-        <v>120</v>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="76" t="n">
+        <v>4</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -19274,10 +19382,20 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="78" t="n"/>
-      <c r="K92" s="78" t="n"/>
-      <c r="L92" s="78" t="n"/>
+      <c r="I92" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J92" s="77" t="n">
+        <v>100</v>
+      </c>
+      <c r="K92" s="77" t="n">
+        <v>21</v>
+      </c>
+      <c r="L92" s="77" t="n">
+        <v>121</v>
+      </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -19775,7 +19893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23844,6 +23962,33 @@
         </is>
       </c>
       <c r="E152" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30.75" customHeight="1">
+      <c r="A153" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B153" s="41" t="inlineStr">
+        <is>
+          <t>Price Fluctuation</t>
+        </is>
+      </c>
+      <c r="C153" s="41" t="inlineStr">
+        <is>
+          <t>A significant change in the price of a supplier's product or service, such as a cost-driven list-price increase.</t>
+        </is>
+      </c>
+      <c r="D153" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. A mapped supplier's price move is in scope; check whether the affected product is one the customer actually procures before raising a WarRoom.</t>
+        </is>
+      </c>
+      <c r="E153" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1418,7 +1418,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="9">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>103</v>
+                  <v>104</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z121" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z122" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E152" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E153" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z121"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="O120" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage, geofencing and WarRoom creation are all still open.</t>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="P120" s="33" t="n"/>
@@ -16587,16 +16587,16 @@
         <v>46296</v>
       </c>
       <c r="B121" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E121" s="39" t="n">
@@ -16604,27 +16604,27 @@
       </c>
       <c r="F121" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
         </is>
       </c>
       <c r="G121" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H121" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I121" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J121" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K121" s="33" t="inlineStr">
@@ -16634,28 +16634,28 @@
       </c>
       <c r="L121" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M121" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
         </is>
       </c>
       <c r="N121" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
       <c r="Q121" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R121" s="39" t="n">
@@ -16669,26 +16669,134 @@
       </c>
       <c r="U121" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V121" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="n"/>
+      <c r="X121" s="33" t="inlineStr">
+        <is>
+          <t>The WarRoom was created because NVIDIA is a mapped partner and the existing EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. On reassessment the price increase affected only the Shield TV Pro, which is not a product the customer procures, so there was no direct impact on products or services supplied to them. EventWatch agreed that an EventWatch bulletin without a WarRoom would have been the more appropriate treatment, and committed to reinforcing guidance to evaluate product-level relevance and customer exposure, not supplier mapping alone, before creating WarRooms for similar price fluctuation events.</t>
+        </is>
+      </c>
+      <c r="Y121" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z121" s="37" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B122" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C122" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D122" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E122" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G122" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I122" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J122" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K122" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L122" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M122" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N122" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O122" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P122" s="33" t="n"/>
+      <c r="Q122" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R122" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S122" s="39" t="n"/>
+      <c r="T122" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U122" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V121" s="33" t="inlineStr">
+      <c r="V122" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W121" s="33" t="inlineStr">
+      <c r="W122" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X121" s="33" t="n"/>
-      <c r="Y121" s="33" t="inlineStr">
+      <c r="X122" s="33" t="n"/>
+      <c r="Y122" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z121" s="37" t="n"/>
+      <c r="Z122" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18464,7 +18572,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L91">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -19102,17 +19210,17 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K86" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -19126,17 +19234,17 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K87" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -19156,17 +19264,17 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K88" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -19186,17 +19294,17 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J89" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="K89" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L89" s="76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -19216,17 +19324,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19244,19 +19352,19 @@
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
       <c r="H91" s="3" t="n"/>
-      <c r="I91" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J91" s="77" t="n">
-        <v>100</v>
-      </c>
-      <c r="K91" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="L91" s="77" t="n">
-        <v>120</v>
+      <c r="I91" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="76" t="n">
+        <v>4</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -19274,10 +19382,20 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="78" t="n"/>
-      <c r="K92" s="78" t="n"/>
-      <c r="L92" s="78" t="n"/>
+      <c r="I92" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J92" s="77" t="n">
+        <v>100</v>
+      </c>
+      <c r="K92" s="77" t="n">
+        <v>21</v>
+      </c>
+      <c r="L92" s="77" t="n">
+        <v>121</v>
+      </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
@@ -19775,7 +19893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23844,6 +23962,33 @@
         </is>
       </c>
       <c r="E152" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30.75" customHeight="1">
+      <c r="A153" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B153" s="41" t="inlineStr">
+        <is>
+          <t>Price Fluctuation</t>
+        </is>
+      </c>
+      <c r="C153" s="41" t="inlineStr">
+        <is>
+          <t>A significant change in the price of a supplier's product or service, such as a cost-driven list-price increase.</t>
+        </is>
+      </c>
+      <c r="D153" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. A mapped supplier's price move is in scope; check whether the affected product is one the customer actually procures before raising a WarRoom.</t>
+        </is>
+      </c>
+      <c r="E153" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16649,7 +16649,7 @@
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification.</t>
+          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification. The outcome is a process enhancement rather than a correction: the WarRoom met the threshold the guidance actually set, and what the scenario exposed is that the threshold tested supplier mapping without testing whether the affected product is one the customer buys.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
@@ -16680,7 +16680,7 @@
       <c r="W121" s="33" t="n"/>
       <c r="X121" s="33" t="inlineStr">
         <is>
-          <t>The WarRoom was created because NVIDIA is a mapped partner and the existing EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. On reassessment the price increase affected only the Shield TV Pro, which is not a product the customer procures, so there was no direct impact on products or services supplied to them. EventWatch agreed that an EventWatch bulletin without a WarRoom would have been the more appropriate treatment, and committed to reinforcing guidance to evaluate product-level relevance and customer exposure, not supplier mapping alone, before creating WarRooms for similar price fluctuation events.</t>
+          <t>The WarRoom was created correctly under the guidance as written: NVIDIA is a mapped partner, and the EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. The affected product was the Shield TV Pro, which the customer does not procure, so there was no direct impact on products or services supplied to them. EventWatch and the customer agreed that for this scenario an EventWatch bulletin without a WarRoom is the right treatment - and the guidance did not carry that scenario at all: its threshold tested supplier mapping alone and said nothing about product-level relevance or customer exposure. This is a process enhancement, not a defect; no guideline was broken and no fault was admitted. The team committed to reinforcing the guidance so that product-level relevance and customer exposure are evaluated alongside supplier mapping before a WarRoom is created for a similar price fluctuation event.</t>
         </is>
       </c>
       <c r="Y121" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>104</v>
+                  <v>105</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>57</v>
+                  <v>58</v>
                 </pt>
                 <pt idx="1">
                   <v>37</v>
@@ -2648,7 +2648,7 @@
                   <v>Merck</v>
                 </pt>
                 <pt idx="9">
-                  <v>Schneider Electric</v>
+                  <v>NVR</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>25</v>
+                  <v>26</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>9</v>
+                  <v>10</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z122" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z123" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z122"/>
+  <dimension ref="A1:Z123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16695,16 +16695,16 @@
         <v>46296</v>
       </c>
       <c r="B122" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="E122" s="39" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F122" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>MasterBrand Cabinets to Lay Off Employees at Its Facility in Kinston, North Carolina, USA</t>
         </is>
       </c>
       <c r="G122" s="33" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="H122" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I122" s="33" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="J122" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K122" s="33" t="inlineStr">
@@ -16747,23 +16747,23 @@
       </c>
       <c r="M122" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Site-level mapping coverage check, so a bulletin naming a facility of an already-mapped supplier flags the unmapped site to the customer rather than passing silently with no WarRoom</t>
         </is>
       </c>
       <c r="N122" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O122" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>NVR raised two asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although both were reported as impacted and the Kinston event was widely covered in the news. EventWatch did identify and publish the Kinston event as a bulletin. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database; the Kinston site was not mapped, so the bulletin published with no WarRoom for NVR. This was not a missed EventWatch event. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added in future. Nitin Rindhe asked Ankit Gupta to verify. No confirmation appears in the thread reviewed, so this ask is still open, and it is why the row is Pending while ask 1 is answered. Raised by email; no Jira ticket was opened, so the daily Pending re-check has no ticket to pull and ask 2 will only close when a human clears it.</t>
         </is>
       </c>
       <c r="P122" s="33" t="n"/>
       <c r="Q122" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R122" s="39" t="n">
@@ -16777,26 +16777,134 @@
       </c>
       <c r="U122" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V122" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W122" s="33" t="n"/>
+      <c r="X122" s="33" t="inlineStr">
+        <is>
+          <t>The Kinston event was identified and published as an EventWatch bulletin. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not mapped, so the bulletin published without a WarRoom for NVR. The event did reach the customer; what did not reach them was their own site on a WarRoom, which is why this is not recorded as a missed event. Source coverage for the four outlets NVR named is a separate ask, still being verified, and is not part of this finding.</t>
+        </is>
+      </c>
+      <c r="Y122" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z122" s="37" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B123" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C123" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D123" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E123" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G123" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H123" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I123" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J123" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K123" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L123" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M123" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N123" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O123" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P123" s="33" t="n"/>
+      <c r="Q123" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R123" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S123" s="39" t="n"/>
+      <c r="T123" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U123" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V122" s="33" t="inlineStr">
+      <c r="V123" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W122" s="33" t="inlineStr">
+      <c r="W123" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X122" s="33" t="n"/>
-      <c r="Y122" s="33" t="inlineStr">
+      <c r="X123" s="33" t="n"/>
+      <c r="Y123" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z122" s="37" t="n"/>
+      <c r="Z123" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18554,7 +18662,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.36</v>
+        <v>0.3564356435643564</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18595,7 +18703,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13</v>
+        <v>0.12871287128712872</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18637,7 +18745,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18679,7 +18787,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04</v>
+        <v>0.039603960396039604</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18721,7 +18829,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04</v>
+        <v>0.039603960396039604</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18763,7 +18871,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03</v>
+        <v>0.0297029702970297</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18805,7 +18913,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18847,7 +18955,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18889,7 +18997,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -18924,14 +19032,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19046,13 +19154,13 @@
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K79" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -19388,13 +19496,13 @@
         </is>
       </c>
       <c r="J92" s="77" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K92" s="77" t="n">
         <v>21</v>
       </c>
       <c r="L92" s="77" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1418,7 +1418,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="9">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,10 +2088,10 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>105</v>
+                  <v>104</v>
                 </pt>
                 <pt idx="3">
-                  <v>11</v>
+                  <v>12</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>58</v>
+                  <v>57</v>
                 </pt>
                 <pt idx="1">
                   <v>37</v>
@@ -2648,7 +2648,7 @@
                   <v>Merck</v>
                 </pt>
                 <pt idx="9">
-                  <v>NVR</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>26</v>
+                  <v>25</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2993,7 +2993,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="4">
-                  <v>10</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -16717,17 +16717,17 @@
       </c>
       <c r="G122" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H122" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I122" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J122" s="33" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="M122" s="33" t="inlineStr">
         <is>
-          <t>Site-level mapping coverage check, so a bulletin naming a facility of an already-mapped supplier flags the unmapped site to the customer rather than passing silently with no WarRoom</t>
+          <t>A site-data completeness review with the customer, so facilities of an already-mapped supplier are shared and on file before an event names one, rather than the gap surfacing when a WarRoom does not appear</t>
         </is>
       </c>
       <c r="N122" s="33" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="O122" s="33" t="inlineStr">
         <is>
-          <t>NVR raised two asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although both were reported as impacted and the Kinston event was widely covered in the news. EventWatch did identify and publish the Kinston event as a bulletin. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database; the Kinston site was not mapped, so the bulletin published with no WarRoom for NVR. This was not a missed EventWatch event. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added in future. Nitin Rindhe asked Ankit Gupta to verify. No confirmation appears in the thread reviewed, so this ask is still open, and it is why the row is Pending while ask 1 is answered. Raised by email; no Jira ticket was opened, so the daily Pending re-check has no ticket to pull and ask 2 will only close when a human clears it.</t>
+          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so the verification is still open and the row stays Pending. Raised by email; no Jira ticket was opened, so the daily Pending re-check has no ticket to pull.</t>
         </is>
       </c>
       <c r="P122" s="33" t="n"/>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="U122" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V122" s="33" t="inlineStr">
@@ -16788,12 +16788,12 @@
       <c r="W122" s="33" t="n"/>
       <c r="X122" s="33" t="inlineStr">
         <is>
-          <t>The Kinston event was identified and published as an EventWatch bulletin. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not mapped, so the bulletin published without a WarRoom for NVR. The event did reach the customer; what did not reach them was their own site on a WarRoom, which is why this is not recorded as a missed event. Source coverage for the four outlets NVR named is a separate ask, still being verified, and is not part of this finding.</t>
+          <t>The Kinston event was identified and published as an EventWatch bulletin, so monitoring carried it. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not among the sites NVR had shared, so no WarRoom could be created for them. Nothing in the platform or in analyst review failed here. What is missing is a process for collecting a customer's facility data completely enough that a site of a mapped supplier is on file before an event names it. The source-coverage question NVR raised alongside is being verified separately and carries no finding of a miss, since the event was published.</t>
         </is>
       </c>
       <c r="Y122" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z122" s="37" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3564356435643564</v>
+        <v>0.36</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18703,7 +18703,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12871287128712872</v>
+        <v>0.13</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18745,7 +18745,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06930693069306931</v>
+        <v>0.07</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18787,7 +18787,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.04</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18829,7 +18829,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.04</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18871,7 +18871,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.0297029702970297</v>
+        <v>0.03</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18913,7 +18913,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18955,7 +18955,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.02</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18997,7 +18997,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19032,14 +19032,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19154,10 +19154,10 @@
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="76" t="n">
         <v>7</v>
@@ -19496,10 +19496,10 @@
         </is>
       </c>
       <c r="J92" s="77" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K92" s="77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L92" s="77" t="n">
         <v>122</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -16742,7 +16742,7 @@
       </c>
       <c r="L122" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M122" s="33" t="inlineStr">
@@ -16757,7 +16757,7 @@
       </c>
       <c r="O122" s="33" t="inlineStr">
         <is>
-          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so the verification is still open and the row stays Pending. Raised by email; no Jira ticket was opened, so the daily Pending re-check has no ticket to pull.</t>
+          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so that verification is still outstanding and is recorded here rather than in the status field. The row is Clarification Provided because that is what went back to NVR on ask 1. It is not Pending: this was raised by email with no Jira ticket, so the daily Pending re-check would have no ticket to pull and nothing would ever move the flag off. The open source check is a manual follow-up with Ankit Gupta.</t>
         </is>
       </c>
       <c r="P122" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>13</v>
                 </pt>
                 <pt idx="9">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>104</v>
+                  <v>105</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>57</v>
+                  <v>58</v>
                 </pt>
                 <pt idx="1">
                   <v>37</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>25</v>
+                  <v>26</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                   <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z123" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z124" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E153" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E154" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z123"/>
+  <dimension ref="A1:Z124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -16803,16 +16803,16 @@
         <v>46296</v>
       </c>
       <c r="B123" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C123" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>FDA/EMA/OSHA Action</t>
         </is>
       </c>
       <c r="D123" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Suntory Spirits</t>
         </is>
       </c>
       <c r="E123" s="39" t="n">
@@ -16820,7 +16820,7 @@
       </c>
       <c r="F123" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan</t>
         </is>
       </c>
       <c r="G123" s="33" t="inlineStr">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="H123" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="I123" s="33" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="J123" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="M123" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Timeliness monitoring for regulator and competition-authority actions against mapped suppliers, so a publicly reported raid or probe is matched and published before a customer asks where the coverage is</t>
         </is>
       </c>
       <c r="N123" s="33" t="inlineStr">
@@ -16865,7 +16865,7 @@
       </c>
       <c r="O123" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Suntory Spirits raised two asks by email on 09-Oct-2026 about the Japanese antitrust investigation into four major brewers. ASK 1, why there was no EventWatch coverage. The customer saw news of the investigation naming Suntory Spirits and could not find corresponding coverage in EventWatch, and questioned whether this event type is monitored at all. ASK 2, whether the sources reporting the investigation are inside the monitoring ecosystem, and whether monitoring can be expanded so future developments are captured earlier. The timeline is what makes this a miss rather than a coverage question. Authorities conducted searches on 07-Oct-2026 and the investigation was publicly reported before any EventWatch bulletin existed. The customer wrote in on 09-Oct. The bulletin, titled Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan, published at 12:07 AM IST on 10-Oct-2026 - after the escalation. So ask 2 is not a generic source-coverage question: the customer is asking whether sources that already carried the story were being monitored, which makes it a monitoring-gap inquiry. Under investigation and deliberately left open; the Sub-type is a staging guess. Captured Late is the one reading the timeline supports on its own, since a bulletin did publish, and it does not prejudge whether the delay came from a source gap, a keyword gap or pipeline lag - which is exactly what is still being established. Raised by email; no Jira ticket has been opened, so the daily Pending re-check has no ticket to pull and this row needs a human to carry it.</t>
         </is>
       </c>
       <c r="P123" s="33" t="n"/>
@@ -16885,26 +16885,134 @@
       </c>
       <c r="U123" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V123" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W123" s="33" t="n"/>
+      <c r="X123" s="33" t="inlineStr">
+        <is>
+          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+        </is>
+      </c>
+      <c r="Y123" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z123" s="37" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B124" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C124" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D124" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E124" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G124" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H124" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I124" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J124" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K124" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L124" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M124" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N124" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O124" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P124" s="33" t="n"/>
+      <c r="Q124" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R124" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S124" s="39" t="n"/>
+      <c r="T124" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U124" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V123" s="33" t="inlineStr">
+      <c r="V124" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W123" s="33" t="inlineStr">
+      <c r="W124" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X123" s="33" t="n"/>
-      <c r="Y123" s="33" t="inlineStr">
+      <c r="X124" s="33" t="n"/>
+      <c r="Y124" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z123" s="37" t="n"/>
+      <c r="Z124" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18662,7 +18770,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.36</v>
+        <v>0.3564356435643564</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18680,7 +18788,7 @@
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="18" t="str" cm="1">
-        <f t="array" ref="I67:L92">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
+        <f t="array" ref="I67:L93">_xlfn.LET(_xlpm.e,_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER(ComplaintTracker[Event type],ComplaintTracker[Event type]&lt;&gt;""))),_xlpm.c,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Complaint"),_xlpm.q,COUNTIFS(ComplaintTracker[Event type],_xlpm.e,ComplaintTracker[Issue Type],"Inquiry"),_xlfn.VSTACK(_xlfn.HSTACK(_xlpm.e,_xlpm.c,_xlpm.q,_xlpm.c+_xlpm.q),_xlfn.HSTACK("Total",SUM(_xlpm.c),SUM(_xlpm.q),SUM(_xlpm.c+_xlpm.q))))</f>
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
@@ -18703,7 +18811,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13</v>
+        <v>0.12871287128712872</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18745,7 +18853,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07</v>
+        <v>0.06930693069306931</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18787,7 +18895,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04</v>
+        <v>0.039603960396039604</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18829,7 +18937,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04</v>
+        <v>0.039603960396039604</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18871,7 +18979,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03</v>
+        <v>0.0297029702970297</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -18913,7 +19021,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -18932,7 +19040,7 @@
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="20" t="inlineStr">
         <is>
-          <t>Factory Closure</t>
+          <t>FDA/EMA/OSHA Action</t>
         </is>
       </c>
       <c r="J73" s="76" t="n">
@@ -18955,7 +19063,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -18974,7 +19082,7 @@
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="20" t="inlineStr">
         <is>
-          <t>Factory Disruption</t>
+          <t>Factory Closure</t>
         </is>
       </c>
       <c r="J74" s="76" t="n">
@@ -18997,7 +19105,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19016,17 +19124,17 @@
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="20" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Factory Disruption</t>
         </is>
       </c>
       <c r="J75" s="76" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K75" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L75" s="76" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" ht="23.25" customHeight="1">
@@ -19039,7 +19147,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19058,17 +19166,17 @@
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="20" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K76" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="76" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" ht="23.25" customHeight="1">
@@ -19092,17 +19200,17 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="J77" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K77" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="76" t="n">
         <v>2</v>
-      </c>
-      <c r="L77" s="76" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -19126,17 +19234,17 @@
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="20" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="J78" s="76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K78" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L78" s="76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" ht="23.25" customHeight="1">
@@ -19150,17 +19258,17 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="20" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -19174,17 +19282,17 @@
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="20" t="inlineStr">
         <is>
-          <t>Leadership Transition</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="J80" s="76" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K80" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L80" s="76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -19198,17 +19306,17 @@
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="20" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Leadership Transition</t>
         </is>
       </c>
       <c r="J81" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" ht="23.25" customHeight="1">
@@ -19222,17 +19330,17 @@
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="20" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="J82" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K82" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="76" t="n">
         <v>2</v>
-      </c>
-      <c r="L82" s="76" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="83" ht="23.25" customHeight="1">
@@ -19246,17 +19354,17 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="20" t="inlineStr">
         <is>
-          <t>Platform/Data Quality</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="J83" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K83" s="76" t="n">
         <v>2</v>
       </c>
-      <c r="K83" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -19270,17 +19378,17 @@
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="20" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Platform/Data Quality</t>
         </is>
       </c>
       <c r="J84" s="76" t="n">
         <v>2</v>
       </c>
       <c r="K84" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" ht="23.25" customHeight="1">
@@ -19294,7 +19402,7 @@
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="20" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="J85" s="76" t="n">
@@ -19318,17 +19426,17 @@
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="20" t="inlineStr">
         <is>
-          <t>Price Fluctuation</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="J86" s="76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L86" s="76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -19342,17 +19450,17 @@
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="20" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="J87" s="76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K87" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M87" s="3" t="n"/>
       <c r="N87" s="3" t="n"/>
@@ -19372,17 +19480,17 @@
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="20" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="J88" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K88" s="76" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M88" s="3" t="n"/>
       <c r="N88" s="3" t="n"/>
@@ -19402,17 +19510,17 @@
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="20" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="J89" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K89" s="76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L89" s="76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
@@ -19432,17 +19540,17 @@
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="20" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="J90" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="K90" s="76" t="n">
-        <v>0</v>
-      </c>
       <c r="L90" s="76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19462,17 +19570,17 @@
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="20" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="J91" s="76" t="n">
         <v>3</v>
       </c>
       <c r="K91" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
@@ -19490,19 +19598,19 @@
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
-      <c r="I92" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J92" s="77" t="n">
-        <v>100</v>
-      </c>
-      <c r="K92" s="77" t="n">
-        <v>22</v>
-      </c>
-      <c r="L92" s="77" t="n">
-        <v>122</v>
+      <c r="I92" s="20" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="J92" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="76" t="n">
+        <v>4</v>
       </c>
       <c r="M92" s="3" t="n"/>
       <c r="N92" s="3" t="n"/>
@@ -19520,10 +19628,20 @@
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
       <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="78" t="n"/>
-      <c r="K93" s="78" t="n"/>
-      <c r="L93" s="78" t="n"/>
+      <c r="I93" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J93" s="77" t="n">
+        <v>101</v>
+      </c>
+      <c r="K93" s="77" t="n">
+        <v>22</v>
+      </c>
+      <c r="L93" s="77" t="n">
+        <v>123</v>
+      </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>
       <c r="O93" s="3" t="n"/>
@@ -20001,7 +20119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24097,6 +24215,33 @@
         </is>
       </c>
       <c r="E153" s="41" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="30.75" customHeight="1">
+      <c r="A154" s="42" t="inlineStr">
+        <is>
+          <t>Event type</t>
+        </is>
+      </c>
+      <c r="B154" s="41" t="inlineStr">
+        <is>
+          <t>FDA/EMA/OSHA Action</t>
+        </is>
+      </c>
+      <c r="C154" s="41" t="inlineStr">
+        <is>
+          <t>Enforcement or investigative action by a regulator or competition authority against a company, such as an inspection, raid, recall order, warning letter or antitrust probe.</t>
+        </is>
+      </c>
+      <c r="D154" s="41" t="inlineStr">
+        <is>
+          <t>Standard event category. Use for an authority acting against a named company; use Regulatory Change where a rule or policy itself changes, and Legal Action for private or commercial litigation.</t>
+        </is>
+      </c>
+      <c r="E154" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
         </is>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1281,7 +1281,7 @@
                   <v>11</v>
                 </pt>
                 <pt idx="4">
-                  <v>17</v>
+                  <v>18</v>
                 </pt>
                 <pt idx="5">
                   <v>9</v>
@@ -1293,7 +1293,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="8">
-                  <v>13</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="9">
                   <v>4</v>
@@ -1415,7 +1415,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="8">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="9">
                   <v>2</v>
@@ -1771,10 +1771,10 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
-                  <v>17</v>
+                  <v>16</v>
                 </pt>
                 <pt idx="3">
                   <v>6</v>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>105</v>
+                  <v>106</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>58</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>Belden Inc</v>
+                </pt>
+                <pt idx="7">
                   <v>General Mills</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>META</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>Merck</v>
-                </pt>
-                <pt idx="9">
-                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2672,7 +2672,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="4">
                   <v>4</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>26</v>
+                  <v>27</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2999,13 +2999,13 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>6</v>
+                  <v>10</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z124" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z125" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E154" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E155" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z124"/>
+  <dimension ref="A1:Z125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="O56" s="33" t="inlineStr">
         <is>
-          <t>Fire started May 18 11am; WarRoom created May 19 9:30am (~22.5 hr delay). Investigation pending.</t>
+          <t>The system successfully captured and classified the wildfire-related feeds on May 18, 2026. During analyst review, the event was placed under monitoring because early impact visibility was limited, and additional contextual validation was not performed. The event was reassessed after further updates on May 19 and escalated through WarRoom creation. Final classification: People - Published Late. Evidence Status: Confirmed RCA. The Sub-type remains Prioritization in this change set because Published Late is not yet an introduced value; it is recorded here as the final classification.</t>
         </is>
       </c>
       <c r="P56" s="33" t="inlineStr">
@@ -9546,22 +9546,22 @@
       </c>
       <c r="I57" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J57" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K57" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L57" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M57" s="33" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="O57" s="33" t="inlineStr">
         <is>
-          <t>Fire started May 19 11am; WarRoom created next day ~8am (~21 hr delay). Investigation pending.</t>
+          <t>The EventWatch system successfully captured wildfire-related feeds on May 19, 2026. A feed-ingestion failure prevented the feeds from reaching the EventWatch portal and reporting workflow for analyst review and escalation. Additional updates on May 20 became available in the workflow, after which the event was reviewed and escalated through WarRoom creation. Alerting Gap Type: Captured Feed Not Surfaced to Analyst Workflow. Evidence Status: Confirmed. This is an Alerting Gap because analysts did not have usable workflow visibility before the customer-impacting delay. The fact that analysts reviewed the event after it became available does not change the originating root cause.</t>
         </is>
       </c>
       <c r="P57" s="33" t="inlineStr">
@@ -9605,13 +9605,13 @@
       </c>
       <c r="V57" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="X57" s="33" t="n"/>
       <c r="Y57" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z57" s="37" t="n"/>
@@ -9826,19 +9826,19 @@
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="B60" s="37" t="n">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="E60" s="39" t="n">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="F60" s="33" t="inlineStr">
         <is>
-          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
+          <t>Potential Strike Action at Thales Defence Facilities in Glasgow and Reading, UK</t>
         </is>
       </c>
       <c r="G60" s="33" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="H60" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="I60" s="33" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="J60" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K60" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M60" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Feed-to-portal ingestion monitoring, so an upstream-identified feed that fails to enter the portal workflow is detected before the reporting and escalation queues go without it</t>
         </is>
       </c>
       <c r="N60" s="33" t="inlineStr">
@@ -9891,21 +9891,27 @@
       </c>
       <c r="O60" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
-        </is>
-      </c>
-      <c r="P60" s="33" t="n"/>
+          <t>Relevant labor-action feeds were identified upstream but were not ingested into the EventWatch portal workflow on May 26, 2026. The feeds therefore did not reach the reporting and escalation queues in time. The WarRoom was created on May 28, 2026. Internal validation confirmed an ingestion gap between feed capture and portal availability. Raised by Steven Brandt in the complaint thread on 28-May-2026; no Jira ticket was opened. Alerting Gap Type: Feed-to-Portal Ingestion Failure. Evidence Status: Confirmed.</t>
+        </is>
+      </c>
+      <c r="P60" s="33" t="inlineStr">
+        <is>
+          <t>~2 days (26-May articles → 28-May WarRoom)</t>
+        </is>
+      </c>
       <c r="Q60" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R60" s="39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S60" s="39" t="n"/>
-      <c r="T60" s="35" t="n">
-        <v>46174</v>
+      <c r="T60" s="35" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -9914,10 +9920,15 @@
       </c>
       <c r="V60" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="X60" s="33" t="n"/>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+      <c r="W60" s="33" t="n"/>
+      <c r="X60" s="33" t="inlineStr">
+        <is>
+          <t>The feeds were identified upstream but were not ingested into the EventWatch portal workflow, which prevented them from reaching the reporting and escalation queues in a timely manner. Internal review confirmed an ingestion gap between feed capture and portal availability.</t>
+        </is>
+      </c>
       <c r="Y60" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -9930,14 +9941,14 @@
         <v>46174</v>
       </c>
       <c r="B61" s="37" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
-        </is>
-      </c>
-      <c r="D61" s="34" t="inlineStr">
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D61" s="33" t="inlineStr">
         <is>
           <t>Ford</t>
         </is>
@@ -9947,7 +9958,7 @@
       </c>
       <c r="F61" s="33" t="inlineStr">
         <is>
-          <t>ANTAC Transport Blockades in Mexico</t>
+          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
         </is>
       </c>
       <c r="G61" s="33" t="inlineStr">
@@ -9967,7 +9978,7 @@
       </c>
       <c r="J61" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K61" s="33" t="inlineStr">
@@ -9977,7 +9988,7 @@
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M61" s="33" t="inlineStr">
@@ -9992,7 +10003,7 @@
       </c>
       <c r="O61" s="33" t="inlineStr">
         <is>
-          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
+          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
         </is>
       </c>
       <c r="P61" s="33" t="n"/>
@@ -10015,7 +10026,7 @@
       </c>
       <c r="V61" s="33" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="X61" s="33" t="n"/>
@@ -10031,16 +10042,16 @@
         <v>46174</v>
       </c>
       <c r="B62" s="37" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>Factory Disruption</t>
-        </is>
-      </c>
-      <c r="D62" s="33" t="inlineStr">
-        <is>
-          <t>Eaton</t>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E62" s="39" t="n">
@@ -10048,7 +10059,7 @@
       </c>
       <c r="F62" s="33" t="inlineStr">
         <is>
-          <t>Burnstein von Seelen Precision Casting Operational Disruption</t>
+          <t>ANTAC Transport Blockades in Mexico</t>
         </is>
       </c>
       <c r="G62" s="33" t="inlineStr">
@@ -10063,12 +10074,12 @@
       </c>
       <c r="I62" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J62" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K62" s="33" t="inlineStr">
@@ -10083,7 +10094,7 @@
       </c>
       <c r="M62" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware escalation model + Not Impactful override validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N62" s="33" t="inlineStr">
@@ -10093,7 +10104,7 @@
       </c>
       <c r="O62" s="33" t="inlineStr">
         <is>
-          <t>RCA shared; analyst classified event as Not Impactful. Event was successfully received and reviewed but incorrectly classified and therefore not escalated.</t>
+          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
         </is>
       </c>
       <c r="P62" s="33" t="n"/>
@@ -10116,43 +10127,32 @@
       </c>
       <c r="V62" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W62" s="33" t="inlineStr">
-        <is>
-          <t>EAO-1</t>
-        </is>
-      </c>
-      <c r="X62" s="33" t="inlineStr">
-        <is>
-          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
-        </is>
-      </c>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="X62" s="33" t="n"/>
       <c r="Y62" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z62" s="37" t="n">
-        <v>46181</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B63" s="37" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Factory Disruption</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E63" s="39" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="F63" s="33" t="inlineStr">
         <is>
-          <t>Credit Suisse / UBS Acquisition Alert Missing from EventWatch News Dashboard (Ford)</t>
+          <t>Burnstein von Seelen Precision Casting Operational Disruption</t>
         </is>
       </c>
       <c r="G63" s="33" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="H63" s="33" t="inlineStr">
         <is>
-          <t>News dashboard visibility gap</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I63" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J63" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K63" s="33" t="inlineStr">
@@ -10190,38 +10190,36 @@
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M63" s="33" t="inlineStr">
         <is>
-          <t>Parity checking between Global Search and the EventWatch News Dashboard so a published alert cannot be findable in one and absent from the other</t>
+          <t>Supplier-aware escalation model + Not Impactful override validation</t>
         </is>
       </c>
       <c r="N63" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O63" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected.</t>
+          <t>RCA shared; analyst classified event as Not Impactful. Event was successfully received and reviewed but incorrectly classified and therefore not escalated.</t>
         </is>
       </c>
       <c r="P63" s="33" t="n"/>
       <c r="Q63" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R63" s="39" t="n">
         <v>6</v>
       </c>
       <c r="S63" s="39" t="n"/>
-      <c r="T63" s="35" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
+      <c r="T63" s="35" t="n">
+        <v>46174</v>
       </c>
       <c r="U63" s="33" t="inlineStr">
         <is>
@@ -10230,41 +10228,43 @@
       </c>
       <c r="V63" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W63" s="33" t="inlineStr">
         <is>
-          <t>CAN-3377</t>
+          <t>EAO-1</t>
         </is>
       </c>
       <c r="X63" s="33" t="inlineStr">
         <is>
-          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
+          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
         </is>
       </c>
       <c r="Y63" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z63" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z63" s="37" t="n">
+        <v>46181</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B64" s="37" t="n">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>Chemical Spill</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E64" s="39" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F64" s="33" t="inlineStr">
         <is>
-          <t>CO₂ Leak at Schaeffler India Plant, Pune</t>
+          <t>Credit Suisse / UBS Acquisition Alert Missing from EventWatch News Dashboard (Ford)</t>
         </is>
       </c>
       <c r="G64" s="33" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H64" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>News dashboard visibility gap</t>
         </is>
       </c>
       <c r="I64" s="33" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="J64" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K64" s="33" t="inlineStr">
@@ -10302,36 +10302,38 @@
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M64" s="33" t="inlineStr">
         <is>
-          <t>Hazardous gas leak detection + mapped supplier escalation model</t>
+          <t>Parity checking between Global Search and the EventWatch News Dashboard so a published alert cannot be findable in one and absent from the other</t>
         </is>
       </c>
       <c r="N64" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O64" s="33" t="inlineStr">
         <is>
-          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility.</t>
+          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected.</t>
         </is>
       </c>
       <c r="P64" s="33" t="n"/>
       <c r="Q64" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R64" s="39" t="n">
         <v>6</v>
       </c>
       <c r="S64" s="39" t="n"/>
-      <c r="T64" s="35" t="n">
-        <v>46174</v>
+      <c r="T64" s="35" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
       </c>
       <c r="U64" s="33" t="inlineStr">
         <is>
@@ -10340,17 +10342,17 @@
       </c>
       <c r="V64" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W64" s="33" t="inlineStr">
         <is>
-          <t>EAO-4</t>
+          <t>CAN-3377</t>
         </is>
       </c>
       <c r="X64" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
+          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
         </is>
       </c>
       <c r="Y64" s="33" t="inlineStr">
@@ -10358,9 +10360,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z64" s="37" t="n">
-        <v>46191</v>
-      </c>
+      <c r="Z64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Chemical Spill</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E65" s="39" t="n">
@@ -10384,27 +10384,27 @@
       </c>
       <c r="F65" s="33" t="inlineStr">
         <is>
-          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
+          <t>CO₂ Leak at Schaeffler India Plant, Pune</t>
         </is>
       </c>
       <c r="G65" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H65" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I65" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K65" s="33" t="inlineStr">
@@ -10414,28 +10414,28 @@
       </c>
       <c r="L65" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M65" s="33" t="inlineStr">
         <is>
-          <t>Forecast vs Event differentiation</t>
+          <t>Hazardous gas leak detection + mapped supplier escalation model</t>
         </is>
       </c>
       <c r="N65" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O65" s="33" t="inlineStr">
         <is>
-          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
+          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility.</t>
         </is>
       </c>
       <c r="P65" s="33" t="n"/>
       <c r="Q65" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R65" s="39" t="n">
@@ -10452,26 +10452,26 @@
       </c>
       <c r="V65" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W65" s="33" t="inlineStr">
         <is>
-          <t>EAO-8</t>
+          <t>EAO-4</t>
         </is>
       </c>
       <c r="X65" s="33" t="inlineStr">
         <is>
-          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
+          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y65" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>46202</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="66">
@@ -10479,16 +10479,16 @@
         <v>46174</v>
       </c>
       <c r="B66" s="37" t="n">
-        <v>46196</v>
+        <v>46188</v>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E66" s="39" t="n">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="F66" s="33" t="inlineStr">
         <is>
-          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
+          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
         </is>
       </c>
       <c r="G66" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H66" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I66" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J66" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K66" s="33" t="inlineStr">
@@ -10526,22 +10526,22 @@
       </c>
       <c r="L66" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M66" s="33" t="inlineStr">
         <is>
-          <t>Supplier relationship validation + impacted entity completeness checks</t>
+          <t>Forecast vs Event differentiation</t>
         </is>
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O66" s="33" t="inlineStr">
         <is>
-          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
+          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
         </is>
       </c>
       <c r="P66" s="33" t="n"/>
@@ -10564,17 +10564,17 @@
       </c>
       <c r="V66" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W66" s="33" t="inlineStr">
         <is>
-          <t>EAO-6</t>
+          <t>EAO-8</t>
         </is>
       </c>
       <c r="X66" s="33" t="inlineStr">
         <is>
-          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
+          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
         </is>
       </c>
       <c r="Y66" s="33" t="inlineStr">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>46217</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="67">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E67" s="39" t="n">
@@ -10608,27 +10608,27 @@
       </c>
       <c r="F67" s="33" t="inlineStr">
         <is>
-          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
+          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
         </is>
       </c>
       <c r="G67" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H67" s="33" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I67" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J67" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K67" s="33" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="L67" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M67" s="33" t="inlineStr">
         <is>
-          <t>Route-risk monitoring enhancement</t>
+          <t>Supplier relationship validation + impacted entity completeness checks</t>
         </is>
       </c>
       <c r="N67" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O67" s="33" t="inlineStr">
         <is>
-          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
+          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
         </is>
       </c>
       <c r="P67" s="33" t="n"/>
@@ -10676,17 +10676,17 @@
       </c>
       <c r="V67" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W67" s="33" t="inlineStr">
         <is>
-          <t>EAO-7</t>
+          <t>EAO-6</t>
         </is>
       </c>
       <c r="X67" s="33" t="inlineStr">
         <is>
-          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
+          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
         </is>
       </c>
       <c r="Y67" s="33" t="inlineStr">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>46198</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="68">
@@ -10703,11 +10703,11 @@
         <v>46174</v>
       </c>
       <c r="B68" s="37" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
@@ -10720,27 +10720,27 @@
       </c>
       <c r="F68" s="33" t="inlineStr">
         <is>
-          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
+          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
         </is>
       </c>
       <c r="G68" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H68" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="I68" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J68" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K68" s="33" t="inlineStr">
@@ -10750,28 +10750,28 @@
       </c>
       <c r="L68" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M68" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware cyber incident escalation model</t>
+          <t>Route-risk monitoring enhancement</t>
         </is>
       </c>
       <c r="N68" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O68" s="33" t="inlineStr">
         <is>
-          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
+          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
         </is>
       </c>
       <c r="P68" s="33" t="n"/>
       <c r="Q68" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R68" s="39" t="n">
@@ -10788,17 +10788,17 @@
       </c>
       <c r="V68" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W68" s="33" t="inlineStr">
         <is>
-          <t>EAO-10</t>
+          <t>EAO-7</t>
         </is>
       </c>
       <c r="X68" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
+          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
         </is>
       </c>
       <c r="Y68" s="33" t="inlineStr">
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>46202</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="69">
@@ -10815,16 +10815,16 @@
         <v>46174</v>
       </c>
       <c r="B69" s="37" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E69" s="39" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F69" s="33" t="inlineStr">
         <is>
-          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
+          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
         </is>
       </c>
       <c r="G69" s="33" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="I69" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J69" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K69" s="33" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="M69" s="33" t="inlineStr">
         <is>
-          <t>Entity-location-aware clustering + cluster separation validation</t>
+          <t>Supplier-aware cyber incident escalation model</t>
         </is>
       </c>
       <c r="N69" s="33" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="O69" s="33" t="inlineStr">
         <is>
-          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
+          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
         </is>
       </c>
       <c r="P69" s="33" t="n"/>
@@ -10900,22 +10900,22 @@
       </c>
       <c r="V69" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W69" s="33" t="inlineStr">
         <is>
-          <t>EAO-9</t>
+          <t>EAO-10</t>
         </is>
       </c>
       <c r="X69" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
+          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y69" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z69" s="37" t="n">
@@ -10927,16 +10927,16 @@
         <v>46174</v>
       </c>
       <c r="B70" s="37" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>Woodward</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E70" s="39" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F70" s="33" t="inlineStr">
         <is>
-          <t>Severe Storms Trigger Disruptions Across the Midwest USA – Geographic Misclassification</t>
+          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
         </is>
       </c>
       <c r="G70" s="33" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I70" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K70" s="33" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="L70" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M70" s="33" t="inlineStr">
         <is>
-          <t>Cluster integrity validation + geographic consistency checks</t>
+          <t>Entity-location-aware clustering + cluster separation validation</t>
         </is>
       </c>
       <c r="N70" s="33" t="inlineStr">
@@ -10989,13 +10989,13 @@
       </c>
       <c r="O70" s="33" t="inlineStr">
         <is>
-          <t>California sites were incorrectly included because two different events were merged into the same WarRoom.</t>
+          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
         </is>
       </c>
       <c r="P70" s="33" t="n"/>
       <c r="Q70" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R70" s="39" t="n">
@@ -11012,41 +11012,43 @@
       </c>
       <c r="V70" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W70" s="33" t="inlineStr">
         <is>
-          <t>EAO-5</t>
+          <t>EAO-9</t>
         </is>
       </c>
       <c r="X70" s="33" t="inlineStr">
         <is>
-          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
+          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
         </is>
       </c>
       <c r="Y70" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z70" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z70" s="37" t="n">
+        <v>46202</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B71" s="37" t="n">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Woodward</t>
         </is>
       </c>
       <c r="E71" s="39" t="n">
@@ -11054,27 +11056,27 @@
       </c>
       <c r="F71" s="33" t="inlineStr">
         <is>
-          <t>Isselguss / Isselburg Foundry Naming Clarification</t>
+          <t>Severe Storms Trigger Disruptions Across the Midwest USA – Geographic Misclassification</t>
         </is>
       </c>
       <c r="G71" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="I71" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K71" s="33" t="inlineStr">
@@ -11084,22 +11086,22 @@
       </c>
       <c r="L71" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M71" s="33" t="inlineStr">
         <is>
-          <t>Company alias management</t>
+          <t>Cluster integrity validation + geographic consistency checks</t>
         </is>
       </c>
       <c r="N71" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O71" s="33" t="inlineStr">
         <is>
-          <t>Isselguss and Isselburg Foundry refer to the same facility. Title updated to align with customer terminology preference and not due to a reporting error.</t>
+          <t>California sites were incorrectly included because two different events were merged into the same WarRoom.</t>
         </is>
       </c>
       <c r="P71" s="33" t="n"/>
@@ -11122,17 +11124,17 @@
       </c>
       <c r="V71" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W71" s="33" t="inlineStr">
         <is>
-          <t>EAO-11</t>
+          <t>EAO-5</t>
         </is>
       </c>
       <c r="X71" s="33" t="inlineStr">
         <is>
-          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
         </is>
       </c>
       <c r="Y71" s="33" t="inlineStr">
@@ -11140,25 +11142,23 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z71" s="37" t="n">
-        <v>46204</v>
-      </c>
+      <c r="Z71" s="37" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="B72" s="37" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
+        <v>46203</v>
+      </c>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E72" s="39" t="n">
@@ -11166,32 +11166,32 @@
       </c>
       <c r="F72" s="33" t="inlineStr">
         <is>
-          <t>BorgWarner Indefinite Strike – Vigo Metropolitan Area, Spain</t>
+          <t>Isselguss / Isselburg Foundry Naming Clarification</t>
         </is>
       </c>
       <c r="G72" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H72" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="I72" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J72" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Improvement</t>
         </is>
       </c>
       <c r="L72" s="33" t="inlineStr">
@@ -11201,63 +11201,59 @@
       </c>
       <c r="M72" s="33" t="inlineStr">
         <is>
-          <t>Vendor-to-portal feed validation + cluster state integrity monitoring</t>
+          <t>Company alias management</t>
         </is>
       </c>
       <c r="N72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O72" s="33" t="inlineStr">
         <is>
-          <t>Customer reported missed EventWatch notification for an indefinite strike at BorgWarner facilities in Zamáns, O Porriño, and Nigrán. CS investigation confirmed two previous strike notifications were successfully delivered to Ford, but no notification was generated for the July 1 event. Internal investigation notes indicate the articles were captured by the vendor and Spanish language algorithm but did not appear in the analyst portal. Engineering review referenced an inconsistent cluster state condition during the affected period.</t>
-        </is>
-      </c>
-      <c r="P72" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Isselguss and Isselburg Foundry refer to the same facility. Title updated to align with customer terminology preference and not due to a reporting error.</t>
+        </is>
+      </c>
+      <c r="P72" s="33" t="n"/>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R72" s="39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S72" s="39" t="n"/>
       <c r="T72" s="35" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U72" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V72" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W72" s="33" t="inlineStr">
+        <is>
+          <t>EAO-11</t>
+        </is>
+      </c>
+      <c r="X72" s="33" t="inlineStr">
+        <is>
+          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+        </is>
+      </c>
+      <c r="Y72" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z72" s="37" t="n">
         <v>46204</v>
-      </c>
-      <c r="U72" s="33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V72" s="33" t="inlineStr">
-        <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
-        </is>
-      </c>
-      <c r="W72" s="33" t="inlineStr">
-        <is>
-          <t>EAO-12</t>
-        </is>
-      </c>
-      <c r="X72" s="33" t="inlineStr">
-        <is>
-          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but did not reach the analyst portal until 01-Jul-2026. Engineering confirmed on the ticket that the articles were captured both by the vendor and by the Spanish-language algorithm, and were linked to the labor_disruption_es_pontevedra_vigo_update cluster - so this is neither a source gap nor a failure to identify the event. That cluster was in an inconsistent state, its status set to Update while it was also marked Not Impactful, which kept the feeds off the analyst portal and meant no WarRoom was raised. The thread asks whether this is a recurrence of the cluster-state defect fixed in the June-end release, where a null cluster id still showed as not impactful. RCA approved and shared with the customer on 09-Jul-2026 as a PDF attachment.</t>
-        </is>
-      </c>
-      <c r="Y72" s="33" t="inlineStr">
-        <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z72" s="37" t="n">
-        <v>46216</v>
       </c>
     </row>
     <row r="73">
@@ -11265,11 +11261,11 @@
         <v>46204</v>
       </c>
       <c r="B73" s="37" t="n">
-        <v>46209</v>
-      </c>
-      <c r="C73" s="33" t="inlineStr">
-        <is>
-          <t>Factory Fire</t>
+        <v>46204</v>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
@@ -11282,7 +11278,7 @@
       </c>
       <c r="F73" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI Foam Manufacturing Plant in Cuautitlan, Mexico</t>
+          <t>BorgWarner Indefinite Strike – Vigo Metropolitan Area, Spain</t>
         </is>
       </c>
       <c r="G73" s="33" t="inlineStr">
@@ -11302,12 +11298,12 @@
       </c>
       <c r="J73" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L73" s="33" t="inlineStr">
@@ -11317,7 +11313,7 @@
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
+          <t>Vendor-to-portal feed validation + cluster state integrity monitoring</t>
         </is>
       </c>
       <c r="N73" s="33" t="inlineStr">
@@ -11327,10 +11323,14 @@
       </c>
       <c r="O73" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
-        </is>
-      </c>
-      <c r="P73" s="33" t="n"/>
+          <t>The articles were captured by the vendor and by the Spanish-language detection flow but did not reach the analyst portal until July 1, 2026. The failure occurred after feed capture and before timely analyst visibility. Alerting Gap Type: Captured Feed Surfaced Late. Evidence Status: Confirmed and Closed.</t>
+        </is>
+      </c>
+      <c r="P73" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q73" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11350,17 +11350,17 @@
       </c>
       <c r="V73" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W73" s="33" t="inlineStr">
         <is>
-          <t>EAO-13</t>
+          <t>EAO-12</t>
         </is>
       </c>
       <c r="X73" s="33" t="inlineStr">
         <is>
-          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but did not reach the analyst portal until 01-Jul-2026. Engineering confirmed on the ticket that the articles were captured both by the vendor and by the Spanish-language algorithm, and were linked to the labor_disruption_es_pontevedra_vigo_update cluster - so this is neither a source gap nor a failure to identify the event. That cluster was in an inconsistent state, its status set to Update while it was also marked Not Impactful, which kept the feeds off the analyst portal and meant no WarRoom was raised. The thread asks whether this is a recurrence of the cluster-state defect fixed in the June-end release, where a null cluster id still showed as not impactful. RCA approved and shared with the customer on 09-Jul-2026 as a PDF attachment.</t>
         </is>
       </c>
       <c r="Y73" s="33" t="inlineStr">
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="74">
@@ -11377,7 +11377,7 @@
         <v>46204</v>
       </c>
       <c r="B74" s="37" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="F74" s="33" t="inlineStr">
         <is>
-          <t>New World International Co. Factory Fire, Thailand</t>
+          <t>Fire at FXI Foam Manufacturing Plant in Cuautitlan, Mexico</t>
         </is>
       </c>
       <c r="G74" s="33" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M74" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
+          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
         </is>
       </c>
       <c r="N74" s="33" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Feeds were received and event was reportedly marked Not Impactful despite destruction of production/storage facility. Investigation ongoing.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11467,21 +11467,21 @@
       </c>
       <c r="W74" s="33" t="inlineStr">
         <is>
-          <t>EAO-14</t>
+          <t>EAO-13</t>
         </is>
       </c>
       <c r="X74" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
+          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
         </is>
       </c>
       <c r="Y74" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z74" s="37" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="75">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E75" s="39" t="n">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="F75" s="33" t="inlineStr">
         <is>
-          <t>Samsung DRAM Price Increase Alert – WarRoom Not Created</t>
+          <t>New World International Co. Factory Fire, Thailand</t>
         </is>
       </c>
       <c r="G75" s="33" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="H75" s="33" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I75" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J75" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K75" s="33" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M75" s="33" t="inlineStr">
         <is>
-          <t>Site Selection Suggestion based on unnormalized supplier names</t>
+          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
         </is>
       </c>
       <c r="N75" s="33" t="inlineStr">
@@ -11551,14 +11551,10 @@
       </c>
       <c r="O75" s="33" t="inlineStr">
         <is>
-          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing.</t>
-        </is>
-      </c>
-      <c r="P75" s="33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Feeds were received and event was reportedly marked Not Impactful despite destruction of production/storage facility. Investigation ongoing.</t>
+        </is>
+      </c>
+      <c r="P75" s="33" t="n"/>
       <c r="Q75" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11573,22 +11569,22 @@
       </c>
       <c r="U75" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V75" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W75" s="33" t="inlineStr">
         <is>
-          <t>EAO-15</t>
+          <t>EAO-14</t>
         </is>
       </c>
       <c r="X75" s="33" t="inlineStr">
         <is>
-          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
+          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y75" s="33" t="inlineStr">
@@ -11597,7 +11593,7 @@
         </is>
       </c>
       <c r="Z75" s="37" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="76">
@@ -11605,16 +11601,16 @@
         <v>46204</v>
       </c>
       <c r="B76" s="37" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E76" s="39" t="n">
@@ -11622,17 +11618,17 @@
       </c>
       <c r="F76" s="33" t="inlineStr">
         <is>
-          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
+          <t>Samsung DRAM Price Increase Alert – WarRoom Not Created</t>
         </is>
       </c>
       <c r="G76" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="I76" s="33" t="inlineStr">
@@ -11642,7 +11638,7 @@
       </c>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -11657,27 +11653,33 @@
       </c>
       <c r="M76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
+          <t>Site Selection Suggestion based on unnormalized supplier names</t>
         </is>
       </c>
       <c r="N76" s="33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O76" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing.</t>
+        </is>
+      </c>
+      <c r="P76" s="33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O76" s="33" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
-        </is>
-      </c>
       <c r="Q76" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R76" s="39" t="n">
         <v>7</v>
       </c>
+      <c r="S76" s="39" t="n"/>
       <c r="T76" s="35" t="n">
         <v>46204</v>
       </c>
@@ -11688,17 +11690,17 @@
       </c>
       <c r="V76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W76" s="33" t="inlineStr">
         <is>
-          <t>EAO-16</t>
+          <t>EAO-15</t>
         </is>
       </c>
       <c r="X76" s="33" t="inlineStr">
         <is>
-          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
+          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
         </is>
       </c>
       <c r="Y76" s="33" t="inlineStr">
@@ -11707,7 +11709,7 @@
         </is>
       </c>
       <c r="Z76" s="37" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="77">
@@ -11719,12 +11721,12 @@
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E77" s="39" t="n">
@@ -11732,27 +11734,27 @@
       </c>
       <c r="F77" s="33" t="inlineStr">
         <is>
-          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
+          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
         </is>
       </c>
       <c r="G77" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I77" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J77" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K77" s="33" t="inlineStr">
@@ -11762,27 +11764,27 @@
       </c>
       <c r="L77" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M77" s="33" t="inlineStr">
         <is>
-          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
+          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
         </is>
       </c>
       <c r="N77" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O77" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
+          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
         </is>
       </c>
       <c r="Q77" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R77" s="39" t="n">
@@ -11793,31 +11795,31 @@
       </c>
       <c r="U77" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V77" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W77" s="33" t="inlineStr">
         <is>
-          <t>EAO-17</t>
+          <t>EAO-16</t>
         </is>
       </c>
       <c r="X77" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
+          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
         </is>
       </c>
       <c r="Y77" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z77" s="37" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="78">
@@ -11825,16 +11827,16 @@
         <v>46204</v>
       </c>
       <c r="B78" s="37" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="E78" s="39" t="n">
@@ -11842,27 +11844,27 @@
       </c>
       <c r="F78" s="33" t="inlineStr">
         <is>
-          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
+          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
         </is>
       </c>
       <c r="G78" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H78" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I78" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J78" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K78" s="33" t="inlineStr">
@@ -11872,27 +11874,27 @@
       </c>
       <c r="L78" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M78" s="33" t="inlineStr">
         <is>
-          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
+          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
         </is>
       </c>
       <c r="N78" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O78" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
         </is>
       </c>
       <c r="Q78" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R78" s="39" t="n">
@@ -11903,31 +11905,31 @@
       </c>
       <c r="U78" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V78" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W78" s="33" t="inlineStr">
         <is>
-          <t>EAO-18</t>
+          <t>EAO-17</t>
         </is>
       </c>
       <c r="X78" s="33" t="inlineStr">
         <is>
-          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
+          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y78" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z78" s="37" t="n">
-        <v>46224</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="79">
@@ -11935,16 +11937,16 @@
         <v>46204</v>
       </c>
       <c r="B79" s="37" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E79" s="39" t="n">
@@ -11952,7 +11954,7 @@
       </c>
       <c r="F79" s="33" t="inlineStr">
         <is>
-          <t>RFI – Power Grid Failure Monitoring Strategy</t>
+          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
         </is>
       </c>
       <c r="G79" s="33" t="inlineStr">
@@ -11962,7 +11964,7 @@
       </c>
       <c r="H79" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I79" s="33" t="inlineStr">
@@ -11987,7 +11989,7 @@
       </c>
       <c r="M79" s="33" t="inlineStr">
         <is>
-          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
+          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
         </is>
       </c>
       <c r="N79" s="33" t="inlineStr">
@@ -11997,7 +11999,7 @@
       </c>
       <c r="O79" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
+          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q79" s="33" t="inlineStr">
@@ -12023,12 +12025,12 @@
       </c>
       <c r="W79" s="33" t="inlineStr">
         <is>
-          <t>EAO-19</t>
+          <t>EAO-18</t>
         </is>
       </c>
       <c r="X79" s="33" t="inlineStr">
         <is>
-          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
+          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
         </is>
       </c>
       <c r="Y79" s="33" t="inlineStr">
@@ -12037,7 +12039,7 @@
         </is>
       </c>
       <c r="Z79" s="37" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="80">
@@ -12045,16 +12047,16 @@
         <v>46204</v>
       </c>
       <c r="B80" s="37" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E80" s="39" t="n">
@@ -12062,27 +12064,27 @@
       </c>
       <c r="F80" s="33" t="inlineStr">
         <is>
-          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
+          <t>RFI – Power Grid Failure Monitoring Strategy</t>
         </is>
       </c>
       <c r="G80" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H80" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I80" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J80" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K80" s="33" t="inlineStr">
@@ -12092,27 +12094,27 @@
       </c>
       <c r="L80" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M80" s="33" t="inlineStr">
         <is>
-          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
+          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
         </is>
       </c>
       <c r="N80" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O80" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
+          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
         </is>
       </c>
       <c r="Q80" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R80" s="39" t="n">
@@ -12123,31 +12125,31 @@
       </c>
       <c r="U80" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V80" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W80" s="33" t="inlineStr">
         <is>
-          <t>EAO-20</t>
+          <t>EAO-19</t>
         </is>
       </c>
       <c r="X80" s="33" t="inlineStr">
         <is>
-          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
+          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
         </is>
       </c>
       <c r="Y80" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z80" s="37" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="81">
@@ -12159,12 +12161,12 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="E81" s="39" t="n">
@@ -12172,7 +12174,7 @@
       </c>
       <c r="F81" s="33" t="inlineStr">
         <is>
-          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
+          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
         </is>
       </c>
       <c r="G81" s="33" t="inlineStr">
@@ -12182,17 +12184,17 @@
       </c>
       <c r="H81" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I81" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J81" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K81" s="33" t="inlineStr">
@@ -12202,12 +12204,12 @@
       </c>
       <c r="L81" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M81" s="33" t="inlineStr">
         <is>
-          <t>Escalation automation for environmental-hazard advisories</t>
+          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
         </is>
       </c>
       <c r="N81" s="33" t="inlineStr">
@@ -12217,7 +12219,7 @@
       </c>
       <c r="O81" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
+          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
         </is>
       </c>
       <c r="Q81" s="33" t="inlineStr">
@@ -12238,26 +12240,26 @@
       </c>
       <c r="V81" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W81" s="33" t="inlineStr">
         <is>
-          <t>EAO-21</t>
+          <t>EAO-20</t>
         </is>
       </c>
       <c r="X81" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
+          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
         </is>
       </c>
       <c r="Y81" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z81" s="37" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="82">
@@ -12265,16 +12267,16 @@
         <v>46204</v>
       </c>
       <c r="B82" s="37" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="D82" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E82" s="39" t="n">
@@ -12282,27 +12284,27 @@
       </c>
       <c r="F82" s="33" t="inlineStr">
         <is>
-          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
+          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
         </is>
       </c>
       <c r="G82" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H82" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I82" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J82" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K82" s="33" t="inlineStr">
@@ -12312,27 +12314,27 @@
       </c>
       <c r="L82" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M82" s="33" t="inlineStr">
         <is>
-          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
+          <t>Escalation automation for environmental-hazard advisories</t>
         </is>
       </c>
       <c r="N82" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O82" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
         </is>
       </c>
       <c r="Q82" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R82" s="39" t="n">
@@ -12353,12 +12355,12 @@
       </c>
       <c r="W82" s="33" t="inlineStr">
         <is>
-          <t>EAO-22</t>
+          <t>EAO-21</t>
         </is>
       </c>
       <c r="X82" s="33" t="inlineStr">
         <is>
-          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
+          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y82" s="33" t="inlineStr">
@@ -12367,24 +12369,24 @@
         </is>
       </c>
       <c r="Z82" s="37" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B83" s="37" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E83" s="39" t="n">
@@ -12392,7 +12394,7 @@
       </c>
       <c r="F83" s="33" t="inlineStr">
         <is>
-          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
+          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G83" s="33" t="inlineStr">
@@ -12402,7 +12404,7 @@
       </c>
       <c r="H83" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I83" s="33" t="inlineStr">
@@ -12412,7 +12414,7 @@
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12427,7 +12429,7 @@
       </c>
       <c r="M83" s="33" t="inlineStr">
         <is>
-          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
+          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
         </is>
       </c>
       <c r="N83" s="33" t="inlineStr">
@@ -12437,21 +12439,19 @@
       </c>
       <c r="O83" s="33" t="inlineStr">
         <is>
-          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
-        </is>
-      </c>
-      <c r="P83" s="33" t="n"/>
+          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+        </is>
+      </c>
       <c r="Q83" s="33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="R83" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S83" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T83" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U83" s="33" t="inlineStr">
         <is>
@@ -12460,17 +12460,17 @@
       </c>
       <c r="V83" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W83" s="33" t="inlineStr">
         <is>
-          <t>EAO-24</t>
+          <t>EAO-22</t>
         </is>
       </c>
       <c r="X83" s="33" t="inlineStr">
         <is>
-          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
+          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
         </is>
       </c>
       <c r="Y83" s="33" t="inlineStr">
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="Z83" s="37" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="84">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="D84" s="33" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E84" s="39" t="n">
@@ -12504,27 +12504,27 @@
       </c>
       <c r="F84" s="33" t="inlineStr">
         <is>
-          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
+          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
         </is>
       </c>
       <c r="G84" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H84" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I84" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J84" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K84" s="33" t="inlineStr">
@@ -12534,32 +12534,34 @@
       </c>
       <c r="L84" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M84" s="33" t="inlineStr">
         <is>
-          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
+          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
         </is>
       </c>
       <c r="N84" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O84" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
-        </is>
-      </c>
+          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
+        </is>
+      </c>
+      <c r="P84" s="33" t="n"/>
       <c r="Q84" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R84" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S84" s="39" t="n"/>
       <c r="T84" s="35" t="n">
         <v>46235</v>
       </c>
@@ -12570,25 +12572,27 @@
       </c>
       <c r="V84" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W84" s="33" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-24</t>
         </is>
       </c>
       <c r="X84" s="33" t="inlineStr">
         <is>
-          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
+          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
         </is>
       </c>
       <c r="Y84" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z84" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z84" s="37" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -12599,7 +12603,7 @@
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
@@ -12612,7 +12616,7 @@
       </c>
       <c r="F85" s="33" t="inlineStr">
         <is>
-          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
+          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
         </is>
       </c>
       <c r="G85" s="33" t="inlineStr">
@@ -12657,7 +12661,7 @@
       </c>
       <c r="O85" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
         </is>
       </c>
       <c r="Q85" s="33" t="inlineStr">
@@ -12703,16 +12707,16 @@
         <v>46235</v>
       </c>
       <c r="B86" s="37" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E86" s="39" t="n">
@@ -12720,7 +12724,7 @@
       </c>
       <c r="F86" s="33" t="inlineStr">
         <is>
-          <t>Disruption Agent Returns Only Tier 1 Suppliers for Kumamoto Earthquake Query (Hitachi)</t>
+          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
         </is>
       </c>
       <c r="G86" s="33" t="inlineStr">
@@ -12730,7 +12734,7 @@
       </c>
       <c r="H86" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I86" s="33" t="inlineStr">
@@ -12740,7 +12744,7 @@
       </c>
       <c r="J86" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K86" s="33" t="inlineStr">
@@ -12750,57 +12754,53 @@
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M86" s="33" t="inlineStr">
         <is>
-          <t>Disruption Agent response completeness checks so a prompt asking for multiple supplier tiers returns all of them in one response</t>
+          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
         </is>
       </c>
       <c r="N86" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O86" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
-        </is>
-      </c>
-      <c r="P86" s="33" t="n"/>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+        </is>
+      </c>
       <c r="Q86" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R86" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S86" s="39" t="n"/>
-      <c r="T86" s="35" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
+      <c r="T86" s="35" t="n">
+        <v>46235</v>
       </c>
       <c r="U86" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V86" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W86" s="33" t="inlineStr">
         <is>
-          <t>CAN-3433</t>
+          <t>EAO-25</t>
         </is>
       </c>
       <c r="X86" s="33" t="inlineStr">
         <is>
-          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
+          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
         </is>
       </c>
       <c r="Y86" s="33" t="inlineStr">
@@ -12815,16 +12815,16 @@
         <v>46235</v>
       </c>
       <c r="B87" s="37" t="n">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="E87" s="39" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="F87" s="33" t="inlineStr">
         <is>
-          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
+          <t>Disruption Agent Returns Only Tier 1 Suppliers for Kumamoto Earthquake Query (Hitachi)</t>
         </is>
       </c>
       <c r="G87" s="33" t="inlineStr">
@@ -12842,17 +12842,17 @@
       </c>
       <c r="H87" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I87" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J87" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K87" s="33" t="inlineStr">
@@ -12862,81 +12862,81 @@
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M87" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Disruption Agent response completeness checks so a prompt asking for multiple supplier tiers returns all of them in one response</t>
         </is>
       </c>
       <c r="N87" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
+          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
         </is>
       </c>
       <c r="P87" s="33" t="n"/>
       <c r="Q87" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R87" s="39" t="n">
         <v>8</v>
       </c>
       <c r="S87" s="39" t="n"/>
-      <c r="T87" s="35" t="n">
-        <v>46235</v>
+      <c r="T87" s="35" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
       </c>
       <c r="U87" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V87" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W87" s="33" t="inlineStr">
         <is>
-          <t>EAO-23</t>
+          <t>CAN-3433</t>
         </is>
       </c>
       <c r="X87" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
+          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
         </is>
       </c>
       <c r="Y87" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z87" s="37" t="n">
-        <v>46252</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z87" s="37" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="B88" s="37" t="n">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E88" s="39" t="n">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="F88" s="33" t="inlineStr">
         <is>
-          <t>Eberhard AG Insolvency – No EventWatch Alert (Infineon)</t>
+          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
         </is>
       </c>
       <c r="G88" s="33" t="inlineStr">
@@ -12954,17 +12954,17 @@
       </c>
       <c r="H88" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I88" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J88" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K88" s="33" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="M88" s="33" t="inlineStr">
         <is>
-          <t>Add the bankruptcy and insolvency sources covering this supplier's region to the vendor network, so a filing at a mapped supplier is captured when it is published rather than when the customer raises it</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N88" s="33" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="O88" s="33" t="inlineStr">
         <is>
-          <t>Raised by Infineon at the weekly sync: Eberhard AG, a critical supplier, reportedly entered bankruptcy proceedings and no EventWatch alert or notification was received. The customer cited it as a case where they expected early-warning signals and bankruptcy intelligence through the Resilinc platform. Product Management reported that the sources carrying the filing are not part of the vendor network and that the vendor has been asked to include them; recorded as a source miss at the portal. There is no EAO key for this record: it was raised by email to the team rather than by opening a Jira ticket.</t>
+          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P88" s="33" t="n"/>
@@ -13002,10 +13002,8 @@
         <v>8</v>
       </c>
       <c r="S88" s="39" t="n"/>
-      <c r="T88" s="35" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
+      <c r="T88" s="35" t="n">
+        <v>46235</v>
       </c>
       <c r="U88" s="33" t="inlineStr">
         <is>
@@ -13014,37 +13012,43 @@
       </c>
       <c r="V88" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W88" s="33" t="n"/>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W88" s="33" t="inlineStr">
+        <is>
+          <t>EAO-23</t>
+        </is>
+      </c>
       <c r="X88" s="33" t="inlineStr">
         <is>
-          <t>The sources reporting the Eberhard AG insolvency are not part of the vendor network; the vendor has been asked to include them. Recorded by Product Management as a source miss at the portal.</t>
+          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y88" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z88" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z88" s="37" t="n">
+        <v>46252</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="B89" s="37" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="E89" s="39" t="n">
@@ -13052,7 +13056,7 @@
       </c>
       <c r="F89" s="33" t="inlineStr">
         <is>
-          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
+          <t>Eberhard AG Insolvency – No EventWatch Alert (Infineon)</t>
         </is>
       </c>
       <c r="G89" s="33" t="inlineStr">
@@ -13062,17 +13066,17 @@
       </c>
       <c r="H89" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I89" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J89" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K89" s="33" t="inlineStr">
@@ -13087,7 +13091,7 @@
       </c>
       <c r="M89" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Trigger Automation</t>
+          <t>Add the bankruptcy and insolvency sources covering this supplier's region to the vendor network, so a filing at a mapped supplier is captured when it is published rather than when the customer raises it</t>
         </is>
       </c>
       <c r="N89" s="33" t="inlineStr">
@@ -13097,7 +13101,7 @@
       </c>
       <c r="O89" s="33" t="inlineStr">
         <is>
-          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+          <t>Raised by Infineon at the weekly sync: Eberhard AG, a critical supplier, reportedly entered bankruptcy proceedings and no EventWatch alert or notification was received. The customer cited it as a case where they expected early-warning signals and bankruptcy intelligence through the Resilinc platform. Product Management reported that the sources carrying the filing are not part of the vendor network and that the vendor has been asked to include them; recorded as a source miss at the portal. There is no EAO key for this record: it was raised by email to the team rather than by opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P89" s="33" t="n"/>
@@ -13110,8 +13114,10 @@
         <v>8</v>
       </c>
       <c r="S89" s="39" t="n"/>
-      <c r="T89" s="35" t="n">
-        <v>46235</v>
+      <c r="T89" s="35" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
       </c>
       <c r="U89" s="33" t="inlineStr">
         <is>
@@ -13120,27 +13126,21 @@
       </c>
       <c r="V89" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W89" s="33" t="inlineStr">
-        <is>
-          <t>EAO-27</t>
-        </is>
-      </c>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W89" s="33" t="n"/>
       <c r="X89" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>The sources reporting the Eberhard AG insolvency are not part of the vendor network; the vendor has been asked to include them. Recorded by Product Management as a source miss at the portal.</t>
         </is>
       </c>
       <c r="Y89" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z89" s="37" t="n">
-        <v>46259</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z89" s="37" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E90" s="39" t="n">
@@ -13164,27 +13164,27 @@
       </c>
       <c r="F90" s="33" t="inlineStr">
         <is>
-          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
+          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
         </is>
       </c>
       <c r="G90" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H90" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I90" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J90" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K90" s="33" t="inlineStr">
@@ -13194,53 +13194,55 @@
       </c>
       <c r="L90" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M90" s="33" t="inlineStr">
         <is>
-          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
+          <t>WarRoom Trigger Automation</t>
         </is>
       </c>
       <c r="N90" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O90" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
-        </is>
-      </c>
+          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+        </is>
+      </c>
+      <c r="P90" s="33" t="n"/>
       <c r="Q90" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R90" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S90" s="39" t="n"/>
       <c r="T90" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U90" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V90" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W90" s="33" t="inlineStr">
         <is>
-          <t>EAO-28</t>
+          <t>EAO-27</t>
         </is>
       </c>
       <c r="X90" s="33" t="inlineStr">
         <is>
-          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y90" s="33" t="inlineStr">
@@ -13257,16 +13259,16 @@
         <v>46235</v>
       </c>
       <c r="B91" s="37" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="C91" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D91" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E91" s="39" t="n">
@@ -13274,27 +13276,27 @@
       </c>
       <c r="F91" s="33" t="inlineStr">
         <is>
-          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
+          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
         </is>
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I91" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13304,60 +13306,58 @@
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
         </is>
       </c>
       <c r="N91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O91" s="33" t="inlineStr">
         <is>
-          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
-        </is>
-      </c>
-      <c r="P91" s="33" t="n"/>
+          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+        </is>
+      </c>
       <c r="Q91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R91" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S91" s="39" t="n"/>
       <c r="T91" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U91" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V91" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W91" s="33" t="inlineStr">
         <is>
-          <t>EAO-26</t>
+          <t>EAO-28</t>
         </is>
       </c>
       <c r="X91" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
         </is>
       </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z91" s="37" t="n">
@@ -13369,11 +13369,11 @@
         <v>46235</v>
       </c>
       <c r="B92" s="37" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
@@ -13386,27 +13386,27 @@
       </c>
       <c r="F92" s="33" t="inlineStr">
         <is>
-          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
+          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
         </is>
       </c>
       <c r="G92" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H92" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I92" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J92" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K92" s="33" t="inlineStr">
@@ -13416,28 +13416,28 @@
       </c>
       <c r="L92" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M92" s="33" t="inlineStr">
         <is>
-          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N92" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O92" s="33" t="inlineStr">
         <is>
-          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
+          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
         </is>
       </c>
       <c r="P92" s="33" t="n"/>
       <c r="Q92" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R92" s="39" t="n">
@@ -13449,31 +13449,31 @@
       </c>
       <c r="U92" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V92" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W92" s="33" t="inlineStr">
         <is>
-          <t>EAO-29</t>
+          <t>EAO-26</t>
         </is>
       </c>
       <c r="X92" s="33" t="inlineStr">
         <is>
-          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y92" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z92" s="37" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="93">
@@ -13481,44 +13481,44 @@
         <v>46235</v>
       </c>
       <c r="B93" s="37" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D93" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E93" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="33" t="inlineStr">
         <is>
-          <t>World Trade Bridge Closed in Laredo, Texas</t>
+          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
         </is>
       </c>
       <c r="G93" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H93" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I93" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J93" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -13528,28 +13528,28 @@
       </c>
       <c r="L93" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M93" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
         </is>
       </c>
       <c r="N93" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O93" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
+          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
         </is>
       </c>
       <c r="P93" s="33" t="n"/>
       <c r="Q93" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R93" s="39" t="n">
@@ -13561,30 +13561,32 @@
       </c>
       <c r="U93" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V93" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W93" s="33" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-29</t>
         </is>
       </c>
       <c r="X93" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
         </is>
       </c>
       <c r="Y93" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z93" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z93" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -13595,7 +13597,7 @@
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D94" s="33" t="inlineStr">
@@ -13608,7 +13610,7 @@
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
+          <t>World Trade Bridge Closed in Laredo, Texas</t>
         </is>
       </c>
       <c r="G94" s="33" t="inlineStr">
@@ -13628,7 +13630,7 @@
       </c>
       <c r="J94" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K94" s="33" t="inlineStr">
@@ -13638,7 +13640,7 @@
       </c>
       <c r="L94" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M94" s="33" t="inlineStr">
@@ -13653,7 +13655,7 @@
       </c>
       <c r="O94" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
         </is>
       </c>
       <c r="P94" s="33" t="n"/>
@@ -13701,7 +13703,7 @@
         <v>46235</v>
       </c>
       <c r="B95" s="37" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
@@ -13718,7 +13720,7 @@
       </c>
       <c r="F95" s="33" t="inlineStr">
         <is>
-          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
+          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
         </is>
       </c>
       <c r="G95" s="33" t="inlineStr">
@@ -13733,12 +13735,12 @@
       </c>
       <c r="I95" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J95" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K95" s="33" t="inlineStr">
@@ -13753,7 +13755,7 @@
       </c>
       <c r="M95" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N95" s="33" t="inlineStr">
@@ -13763,7 +13765,7 @@
       </c>
       <c r="O95" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P95" s="33" t="n"/>
@@ -13786,7 +13788,7 @@
       </c>
       <c r="V95" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W95" s="33" t="inlineStr">
@@ -13801,7 +13803,7 @@
       </c>
       <c r="Y95" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z95" s="37" t="n"/>
@@ -13815,20 +13817,20 @@
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>The American National Red Cross</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="E96" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="33" t="inlineStr">
         <is>
-          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
+          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
         </is>
       </c>
       <c r="G96" s="33" t="inlineStr">
@@ -13838,17 +13840,17 @@
       </c>
       <c r="H96" s="33" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I96" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J96" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K96" s="33" t="inlineStr">
@@ -13863,17 +13865,17 @@
       </c>
       <c r="M96" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N96" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O96" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
+          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P96" s="33" t="n"/>
@@ -13896,15 +13898,19 @@
       </c>
       <c r="V96" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W96" s="33" t="inlineStr">
         <is>
-          <t>TS-22695</t>
-        </is>
-      </c>
-      <c r="X96" s="33" t="n"/>
+          <t>EAO-25</t>
+        </is>
+      </c>
+      <c r="X96" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
       <c r="Y96" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -13917,7 +13923,7 @@
         <v>46235</v>
       </c>
       <c r="B97" s="37" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C97" s="33" t="inlineStr">
         <is>
@@ -13926,7 +13932,7 @@
       </c>
       <c r="D97" s="33" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>The American National Red Cross</t>
         </is>
       </c>
       <c r="E97" s="39" t="n">
@@ -13934,7 +13940,7 @@
       </c>
       <c r="F97" s="33" t="inlineStr">
         <is>
-          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
+          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
         </is>
       </c>
       <c r="G97" s="33" t="inlineStr">
@@ -13944,17 +13950,17 @@
       </c>
       <c r="H97" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="I97" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J97" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K97" s="33" t="inlineStr">
@@ -13969,17 +13975,17 @@
       </c>
       <c r="M97" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="N97" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O97" s="33" t="inlineStr">
         <is>
-          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
         </is>
       </c>
       <c r="P97" s="33" t="n"/>
@@ -14002,27 +14008,21 @@
       </c>
       <c r="V97" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W97" s="33" t="inlineStr">
         <is>
-          <t>EAO-31</t>
-        </is>
-      </c>
-      <c r="X97" s="33" t="inlineStr">
-        <is>
-          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
-        </is>
-      </c>
+          <t>TS-22695</t>
+        </is>
+      </c>
+      <c r="X97" s="33" t="n"/>
       <c r="Y97" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z97" s="37" t="n">
-        <v>46272</v>
-      </c>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z97" s="37" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="E98" s="39" t="n">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="F98" s="33" t="inlineStr">
         <is>
-          <t>Baxter International Reports a Cybersecurity Incident</t>
+          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
         </is>
       </c>
       <c r="G98" s="33" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="I98" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J98" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K98" s="33" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="M98" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N98" s="33" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="O98" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
         </is>
       </c>
       <c r="P98" s="33" t="n"/>
@@ -14114,16 +14114,27 @@
       </c>
       <c r="V98" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="X98" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W98" s="33" t="inlineStr">
+        <is>
+          <t>EAO-31</t>
+        </is>
+      </c>
+      <c r="X98" s="33" t="inlineStr">
+        <is>
+          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
+        </is>
+      </c>
       <c r="Y98" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z98" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z98" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="n">
@@ -14147,7 +14158,7 @@
       </c>
       <c r="F99" s="33" t="inlineStr">
         <is>
-          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
+          <t>Baxter International Reports a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G99" s="33" t="inlineStr">
@@ -14182,7 +14193,7 @@
       </c>
       <c r="M99" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Duplicate Decision Validation</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N99" s="33" t="inlineStr">
@@ -14192,7 +14203,7 @@
       </c>
       <c r="O99" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
         </is>
       </c>
       <c r="P99" s="33" t="n"/>
@@ -14235,12 +14246,12 @@
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>Liberty Blume</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="E100" s="39" t="n">
@@ -14248,27 +14259,27 @@
       </c>
       <c r="F100" s="33" t="inlineStr">
         <is>
-          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
+          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G100" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H100" s="33" t="inlineStr">
         <is>
-          <t>Intelligence/Advisory Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I100" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J100" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K100" s="33" t="inlineStr">
@@ -14278,55 +14289,48 @@
       </c>
       <c r="L100" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M100" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit/grey-market component intelligence briefing capability</t>
+          <t>Entity &amp; Duplicate Decision Validation</t>
         </is>
       </c>
       <c r="N100" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O100" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
-        </is>
-      </c>
+          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+        </is>
+      </c>
+      <c r="P100" s="33" t="n"/>
       <c r="Q100" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R100" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S100" s="39" t="n"/>
       <c r="T100" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U100" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V100" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W100" s="33" t="inlineStr">
-        <is>
-          <t>EAO-32</t>
-        </is>
-      </c>
-      <c r="X100" s="33" t="inlineStr">
-        <is>
-          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
-        </is>
-      </c>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="X100" s="33" t="n"/>
       <c r="Y100" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14336,19 +14340,19 @@
     </row>
     <row r="101">
       <c r="A101" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B101" s="37" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Counterfeit</t>
         </is>
       </c>
       <c r="D101" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Liberty Blume</t>
         </is>
       </c>
       <c r="E101" s="39" t="n">
@@ -14356,27 +14360,27 @@
       </c>
       <c r="F101" s="33" t="inlineStr">
         <is>
-          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
+          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
         </is>
       </c>
       <c r="G101" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H101" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Intelligence/Advisory Request</t>
         </is>
       </c>
       <c r="I101" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J101" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K101" s="33" t="inlineStr">
@@ -14386,53 +14390,53 @@
       </c>
       <c r="L101" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M101" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
+          <t>Counterfeit/grey-market component intelligence briefing capability</t>
         </is>
       </c>
       <c r="N101" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O101" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
         </is>
       </c>
       <c r="Q101" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R101" s="39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="U101" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V101" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W101" s="33" t="inlineStr">
         <is>
-          <t>EAO-33</t>
+          <t>EAO-32</t>
         </is>
       </c>
       <c r="X101" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
         </is>
       </c>
       <c r="Y101" s="33" t="inlineStr">
@@ -14447,16 +14451,16 @@
         <v>46266</v>
       </c>
       <c r="B102" s="37" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E102" s="39" t="n">
@@ -14464,7 +14468,7 @@
       </c>
       <c r="F102" s="33" t="inlineStr">
         <is>
-          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
+          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G102" s="33" t="inlineStr">
@@ -14499,7 +14503,7 @@
       </c>
       <c r="M102" s="33" t="inlineStr">
         <is>
-          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
+          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
         </is>
       </c>
       <c r="N102" s="33" t="inlineStr">
@@ -14509,7 +14513,7 @@
       </c>
       <c r="O102" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q102" s="33" t="inlineStr">
@@ -14535,7 +14539,7 @@
       </c>
       <c r="W102" s="33" t="inlineStr">
         <is>
-          <t>EAO-34</t>
+          <t>EAO-33</t>
         </is>
       </c>
       <c r="X102" s="33" t="inlineStr">
@@ -14555,24 +14559,24 @@
         <v>46266</v>
       </c>
       <c r="B103" s="37" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="D103" s="33" t="inlineStr">
         <is>
-          <t>Eaton/Ford</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E103" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="33" t="inlineStr">
         <is>
-          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
+          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
         </is>
       </c>
       <c r="G103" s="33" t="inlineStr">
@@ -14582,17 +14586,17 @@
       </c>
       <c r="H103" s="33" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">
@@ -14607,7 +14611,7 @@
       </c>
       <c r="M103" s="33" t="inlineStr">
         <is>
-          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
+          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
         </is>
       </c>
       <c r="N103" s="33" t="inlineStr">
@@ -14617,23 +14621,19 @@
       </c>
       <c r="O103" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
-        </is>
-      </c>
-      <c r="P103" s="33" t="n"/>
+          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+        </is>
+      </c>
       <c r="Q103" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R103" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S103" s="39" t="n"/>
-      <c r="T103" s="35" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="T103" s="35" t="n">
+        <v>46266</v>
       </c>
       <c r="U103" s="33" t="inlineStr">
         <is>
@@ -14642,22 +14642,22 @@
       </c>
       <c r="V103" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W103" s="33" t="inlineStr">
         <is>
-          <t>EAO-35/EAO-36</t>
+          <t>EAO-34</t>
         </is>
       </c>
       <c r="X103" s="33" t="inlineStr">
         <is>
-          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
         </is>
       </c>
       <c r="Y103" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z103" s="37" t="n"/>
@@ -14667,24 +14667,24 @@
         <v>46266</v>
       </c>
       <c r="B104" s="37" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Eaton/Ford</t>
         </is>
       </c>
       <c r="E104" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="33" t="inlineStr">
         <is>
-          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
+          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
         </is>
       </c>
       <c r="G104" s="33" t="inlineStr">
@@ -14694,17 +14694,17 @@
       </c>
       <c r="H104" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="I104" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="M104" s="33" t="inlineStr">
         <is>
-          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
+          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
         </is>
       </c>
       <c r="N104" s="33" t="inlineStr">
@@ -14729,17 +14729,13 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
-        </is>
-      </c>
-      <c r="P104" s="33" t="inlineStr">
-        <is>
-          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
-        </is>
-      </c>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
+        </is>
+      </c>
+      <c r="P104" s="33" t="n"/>
       <c r="Q104" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R104" s="39" t="n">
@@ -14758,22 +14754,22 @@
       </c>
       <c r="V104" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>AI-Assisted Geofencing</t>
         </is>
       </c>
       <c r="W104" s="33" t="inlineStr">
         <is>
-          <t>EAO-37</t>
+          <t>EAO-35/EAO-36</t>
         </is>
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z104" s="37" t="n"/>
@@ -14787,12 +14783,12 @@
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D105" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="E105" s="39" t="n">
@@ -14800,27 +14796,27 @@
       </c>
       <c r="F105" s="33" t="inlineStr">
         <is>
-          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
+          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
         </is>
       </c>
       <c r="G105" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H105" s="33" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J105" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K105" s="33" t="inlineStr">
@@ -14830,28 +14826,32 @@
       </c>
       <c r="L105" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M105" s="33" t="inlineStr">
         <is>
-          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
+          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
         </is>
       </c>
       <c r="N105" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
-        </is>
-      </c>
-      <c r="P105" s="33" t="n"/>
+          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
+        </is>
+      </c>
+      <c r="P105" s="33" t="inlineStr">
+        <is>
+          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q105" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R105" s="39" t="n">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="U105" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V105" s="33" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="W105" s="33" t="inlineStr">
         <is>
-          <t>EAO-38</t>
+          <t>EAO-37</t>
         </is>
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
+          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
@@ -14895,16 +14895,16 @@
         <v>46266</v>
       </c>
       <c r="B106" s="37" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E106" s="39" t="n">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="F106" s="33" t="inlineStr">
         <is>
-          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
+          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
         </is>
       </c>
       <c r="G106" s="33" t="inlineStr">
@@ -14922,17 +14922,17 @@
       </c>
       <c r="H106" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="I106" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J106" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K106" s="33" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="M106" s="33" t="inlineStr">
         <is>
-          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
+          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
         </is>
       </c>
       <c r="N106" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O106" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. The query ran on through two follow-ups, both part of the same contact rather than separate records. First, on 18-Sep-2026 the customer cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked how EventWatch separates real reporting from fake, what criteria establish that a notification is not fake, and whether the 28nm reduction is real; a written assessment was issued covering the source hierarchy, the five evidence grades and the TSMC timeline. Second, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage.</t>
+          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
         </is>
       </c>
       <c r="P106" s="33" t="n"/>
@@ -14977,27 +14977,27 @@
       </c>
       <c r="U106" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V106" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W106" s="33" t="inlineStr">
         <is>
-          <t>EAO-39</t>
+          <t>EAO-38</t>
         </is>
       </c>
       <c r="X106" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
+          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
         </is>
       </c>
       <c r="Y106" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z106" s="37" t="n"/>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="F107" s="33" t="inlineStr">
         <is>
-          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
+          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G107" s="33" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="H107" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I107" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J107" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K107" s="33" t="inlineStr">
@@ -15054,12 +15054,12 @@
       </c>
       <c r="L107" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M107" s="33" t="inlineStr">
         <is>
-          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
+          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
         </is>
       </c>
       <c r="N107" s="33" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="O107" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
+          <t>The relevant TSMC article was captured by the feed-harvesting flow but did not appear on the analyst portal for review. The case was confirmed and closed as an Alerting Gap. Alerting Gap Type: Feed/Application-to-Analyst Handoff Gap. Evidence Status: Confirmed and Closed.</t>
         </is>
       </c>
       <c r="P107" s="33" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="V107" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W107" s="33" t="inlineStr">
@@ -15104,12 +15104,12 @@
       </c>
       <c r="X107" s="33" t="inlineStr">
         <is>
-          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
+          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
         </is>
       </c>
       <c r="Y107" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z107" s="37" t="n"/>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E108" s="39" t="n">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="F108" s="33" t="inlineStr">
         <is>
-          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
+          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G108" s="33" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="I108" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J108" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K108" s="33" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="M108" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
+          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
+          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15201,27 +15201,27 @@
       </c>
       <c r="U108" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V108" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W108" s="33" t="inlineStr">
         <is>
-          <t>EAO-40</t>
+          <t>EAO-39</t>
         </is>
       </c>
       <c r="X108" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
+          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
         </is>
       </c>
       <c r="Y108" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z108" s="37" t="n"/>
@@ -15231,16 +15231,16 @@
         <v>46266</v>
       </c>
       <c r="B109" s="37" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D109" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E109" s="39" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="F109" s="33" t="inlineStr">
         <is>
-          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
+          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
         </is>
       </c>
       <c r="G109" s="33" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="H109" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I109" s="33" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="J109" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K109" s="33" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="M109" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
+          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
         </is>
       </c>
       <c r="N109" s="33" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
         </is>
       </c>
       <c r="P109" s="33" t="n"/>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="U109" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V109" s="33" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="W109" s="33" t="inlineStr">
         <is>
-          <t>EAO-41</t>
+          <t>EAO-40</t>
         </is>
       </c>
       <c r="X109" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
         </is>
       </c>
       <c r="Y109" s="33" t="inlineStr">
@@ -15336,16 +15336,14 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z109" s="37" t="n">
-        <v>46288</v>
-      </c>
+      <c r="Z109" s="37" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B110" s="37" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
@@ -15354,7 +15352,7 @@
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Irving Oil</t>
         </is>
       </c>
       <c r="E110" s="39" t="n">
@@ -15362,7 +15360,7 @@
       </c>
       <c r="F110" s="33" t="inlineStr">
         <is>
-          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
+          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
         </is>
       </c>
       <c r="G110" s="33" t="inlineStr">
@@ -15397,7 +15395,7 @@
       </c>
       <c r="M110" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N110" s="33" t="inlineStr">
@@ -15407,14 +15405,10 @@
       </c>
       <c r="O110" s="33" t="inlineStr">
         <is>
-          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
-        </is>
-      </c>
-      <c r="P110" s="33" t="inlineStr">
-        <is>
-          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
-        </is>
-      </c>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+        </is>
+      </c>
+      <c r="P110" s="33" t="n"/>
       <c r="Q110" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15441,12 +15435,12 @@
       </c>
       <c r="W110" s="33" t="inlineStr">
         <is>
-          <t>EAO-42</t>
+          <t>EAO-41</t>
         </is>
       </c>
       <c r="X110" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y110" s="33" t="inlineStr">
@@ -15467,12 +15461,12 @@
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E111" s="39" t="n">
@@ -15480,7 +15474,7 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
+          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
@@ -15490,17 +15484,17 @@
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15510,12 +15504,12 @@
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15525,10 +15519,14 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
-        </is>
-      </c>
-      <c r="P111" s="33" t="n"/>
+          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
+        </is>
+      </c>
+      <c r="P111" s="33" t="inlineStr">
+        <is>
+          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
+        </is>
+      </c>
       <c r="Q111" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15550,41 +15548,43 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
         <is>
-          <t>EAO-51</t>
+          <t>EAO-42</t>
         </is>
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z111" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z111" s="37" t="n">
+        <v>46288</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B112" s="37" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15622,28 +15622,28 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
       <c r="Q112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R112" s="39" t="n">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-43</t>
+          <t>EAO-51</t>
         </is>
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
@@ -15687,11 +15687,11 @@
         <v>46266</v>
       </c>
       <c r="B113" s="37" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="F113" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
         </is>
       </c>
       <c r="G113" s="33" t="inlineStr">
@@ -15714,17 +15714,17 @@
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I113" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J113" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K113" s="33" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15769,27 +15769,27 @@
       </c>
       <c r="U113" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V113" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W113" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
+          <t>EAO-43</t>
         </is>
       </c>
       <c r="X113" s="33" t="inlineStr">
         <is>
-          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
         </is>
       </c>
       <c r="Y113" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E114" s="39" t="n">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="F114" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G114" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H114" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I114" s="33" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15846,40 +15846,34 @@
       </c>
       <c r="L114" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M114" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N114" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
-        </is>
-      </c>
-      <c r="P114" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="n"/>
       <c r="Q114" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R114" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S114" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S114" s="39" t="n"/>
       <c r="T114" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15887,22 +15881,22 @@
       </c>
       <c r="U114" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V114" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W114" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X114" s="33" t="inlineStr">
         <is>
-          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
         </is>
       </c>
       <c r="Y114" s="33" t="inlineStr">
@@ -15917,16 +15911,16 @@
         <v>46266</v>
       </c>
       <c r="B115" s="37" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E115" s="39" t="n">
@@ -15934,7 +15928,7 @@
       </c>
       <c r="F115" s="33" t="inlineStr">
         <is>
-          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
         </is>
       </c>
       <c r="G115" s="33" t="inlineStr">
@@ -15944,17 +15938,17 @@
       </c>
       <c r="H115" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I115" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J115" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K115" s="33" t="inlineStr">
@@ -15964,12 +15958,12 @@
       </c>
       <c r="L115" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M115" s="33" t="inlineStr">
         <is>
-          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
         </is>
       </c>
       <c r="N115" s="33" t="inlineStr">
@@ -15979,19 +15973,25 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
-        </is>
-      </c>
-      <c r="P115" s="33" t="n"/>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P115" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q115" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R115" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S115" s="39" t="n"/>
+      <c r="S115" s="39" t="n">
+        <v>252</v>
+      </c>
       <c r="T115" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15999,27 +15999,27 @@
       </c>
       <c r="U115" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V115" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W115" s="33" t="inlineStr">
         <is>
-          <t>EAO-46</t>
+          <t>EAO-45</t>
         </is>
       </c>
       <c r="X115" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
         </is>
       </c>
       <c r="Y115" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z115" s="37" t="n"/>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E116" s="39" t="n">
@@ -16046,17 +16046,17 @@
       </c>
       <c r="F116" s="33" t="inlineStr">
         <is>
-          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
+          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
         </is>
       </c>
       <c r="G116" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H116" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="I116" s="33" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="J116" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K116" s="33" t="inlineStr">
@@ -16076,12 +16076,12 @@
       </c>
       <c r="L116" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M116" s="33" t="inlineStr">
         <is>
-          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
+          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N116" s="33" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="O116" s="33" t="inlineStr">
         <is>
-          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
         </is>
       </c>
       <c r="P116" s="33" t="n"/>
@@ -16116,17 +16116,17 @@
       </c>
       <c r="V116" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W116" s="33" t="inlineStr">
         <is>
-          <t>EAO-47</t>
+          <t>EAO-46</t>
         </is>
       </c>
       <c r="X116" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
+          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
         </is>
       </c>
       <c r="Y116" s="33" t="inlineStr">
@@ -16145,12 +16145,12 @@
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E117" s="39" t="n">
@@ -16158,17 +16158,17 @@
       </c>
       <c r="F117" s="33" t="inlineStr">
         <is>
-          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
         </is>
       </c>
       <c r="G117" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H117" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I117" s="33" t="inlineStr">
@@ -16188,12 +16188,12 @@
       </c>
       <c r="L117" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M117" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
+          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
         </is>
       </c>
       <c r="N117" s="33" t="inlineStr">
@@ -16203,13 +16203,13 @@
       </c>
       <c r="O117" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
+          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
         </is>
       </c>
       <c r="P117" s="33" t="n"/>
       <c r="Q117" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R117" s="39" t="n">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="U117" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V117" s="33" t="inlineStr">
@@ -16233,12 +16233,12 @@
       </c>
       <c r="W117" s="33" t="inlineStr">
         <is>
-          <t>EAO-48</t>
+          <t>EAO-47</t>
         </is>
       </c>
       <c r="X117" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
         </is>
       </c>
       <c r="Y117" s="33" t="inlineStr">
@@ -16246,25 +16246,23 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z117" s="37" t="n">
-        <v>46302</v>
-      </c>
+      <c r="Z117" s="37" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B118" s="37" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E118" s="39" t="n">
@@ -16272,7 +16270,7 @@
       </c>
       <c r="F118" s="33" t="inlineStr">
         <is>
-          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
+          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
         </is>
       </c>
       <c r="G118" s="33" t="inlineStr">
@@ -16282,7 +16280,7 @@
       </c>
       <c r="H118" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I118" s="33" t="inlineStr">
@@ -16292,7 +16290,7 @@
       </c>
       <c r="J118" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K118" s="33" t="inlineStr">
@@ -16302,12 +16300,12 @@
       </c>
       <c r="L118" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M118" s="33" t="inlineStr">
         <is>
-          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
+          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N118" s="33" t="inlineStr">
@@ -16317,13 +16315,13 @@
       </c>
       <c r="O118" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P118" s="33" t="n"/>
       <c r="Q118" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R118" s="39" t="n">
@@ -16337,42 +16335,48 @@
       </c>
       <c r="U118" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V118" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W118" s="33" t="inlineStr">
         <is>
-          <t>EAO-49</t>
-        </is>
-      </c>
-      <c r="X118" s="33" t="n"/>
+          <t>EAO-48</t>
+        </is>
+      </c>
+      <c r="X118" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+        </is>
+      </c>
       <c r="Y118" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z118" s="37" t="n"/>
+      <c r="Z118" s="37" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="35" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="B119" s="37" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D119" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E119" s="39" t="n">
@@ -16380,7 +16384,7 @@
       </c>
       <c r="F119" s="33" t="inlineStr">
         <is>
-          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
+          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
         </is>
       </c>
       <c r="G119" s="33" t="inlineStr">
@@ -16390,7 +16394,7 @@
       </c>
       <c r="H119" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I119" s="33" t="inlineStr">
@@ -16400,7 +16404,7 @@
       </c>
       <c r="J119" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K119" s="33" t="inlineStr">
@@ -16415,7 +16419,7 @@
       </c>
       <c r="M119" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
+          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
         </is>
       </c>
       <c r="N119" s="33" t="inlineStr">
@@ -16425,22 +16429,22 @@
       </c>
       <c r="O119" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
         </is>
       </c>
       <c r="P119" s="33" t="n"/>
       <c r="Q119" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R119" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S119" s="39" t="n"/>
       <c r="T119" s="35" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="U119" s="33" t="inlineStr">
@@ -16450,19 +16454,15 @@
       </c>
       <c r="V119" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W119" s="33" t="inlineStr">
         <is>
-          <t>EAO-50</t>
-        </is>
-      </c>
-      <c r="X119" s="33" t="inlineStr">
-        <is>
-          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
-        </is>
-      </c>
+          <t>EAO-49</t>
+        </is>
+      </c>
+      <c r="X119" s="33" t="n"/>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -16475,16 +16475,16 @@
         <v>46296</v>
       </c>
       <c r="B120" s="37" t="n">
-        <v>46303</v>
+        <v>46296</v>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E120" s="39" t="n">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="F120" s="33" t="inlineStr">
         <is>
-          <t>Carlisle, Iowa Municipal Water Disruption – No WarRoom Created (General Mills)</t>
+          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
         </is>
       </c>
       <c r="G120" s="33" t="inlineStr">
@@ -16502,17 +16502,17 @@
       </c>
       <c r="H120" s="33" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I120" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J120" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K120" s="33" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="M120" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
+          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N120" s="33" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="O120" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
+          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
         </is>
       </c>
       <c r="P120" s="33" t="n"/>
@@ -16562,22 +16562,22 @@
       </c>
       <c r="V120" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W120" s="33" t="inlineStr">
         <is>
-          <t>EAO-52</t>
+          <t>EAO-50</t>
         </is>
       </c>
       <c r="X120" s="33" t="inlineStr">
         <is>
-          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y120" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z120" s="37" t="n"/>
@@ -16587,16 +16587,16 @@
         <v>46296</v>
       </c>
       <c r="B121" s="37" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Price Fluctuation</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E121" s="39" t="n">
@@ -16604,27 +16604,27 @@
       </c>
       <c r="F121" s="33" t="inlineStr">
         <is>
-          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
+          <t>Carlisle, Iowa Municipal Water Disruption – No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G121" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H121" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="I121" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J121" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K121" s="33" t="inlineStr">
@@ -16634,28 +16634,28 @@
       </c>
       <c r="L121" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M121" s="33" t="inlineStr">
         <is>
-          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
+          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
         </is>
       </c>
       <c r="N121" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification. The outcome is a process enhancement rather than a correction: the WarRoom met the threshold the guidance actually set, and what the scenario exposed is that the threshold tested supplier mapping without testing whether the affected product is one the customer buys.</t>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
       <c r="Q121" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R121" s="39" t="n">
@@ -16674,18 +16674,22 @@
       </c>
       <c r="V121" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W121" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="inlineStr">
+        <is>
+          <t>EAO-52</t>
+        </is>
+      </c>
       <c r="X121" s="33" t="inlineStr">
         <is>
-          <t>The WarRoom was created correctly under the guidance as written: NVIDIA is a mapped partner, and the EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. The affected product was the Shield TV Pro, which the customer does not procure, so there was no direct impact on products or services supplied to them. EventWatch and the customer agreed that for this scenario an EventWatch bulletin without a WarRoom is the right treatment - and the guidance did not carry that scenario at all: its threshold tested supplier mapping alone and said nothing about product-level relevance or customer exposure. This is a process enhancement, not a defect; no guideline was broken and no fault was admitted. The team committed to reinforcing the guidance so that product-level relevance and customer exposure are evaluated alongside supplier mapping before a WarRoom is created for a similar price fluctuation event.</t>
+          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
         </is>
       </c>
       <c r="Y121" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z121" s="37" t="n"/>
@@ -16699,12 +16703,12 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E122" s="39" t="n">
@@ -16712,7 +16716,7 @@
       </c>
       <c r="F122" s="33" t="inlineStr">
         <is>
-          <t>MasterBrand Cabinets to Lay Off Employees at Its Facility in Kinston, North Carolina, USA</t>
+          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
         </is>
       </c>
       <c r="G122" s="33" t="inlineStr">
@@ -16722,7 +16726,7 @@
       </c>
       <c r="H122" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I122" s="33" t="inlineStr">
@@ -16732,7 +16736,7 @@
       </c>
       <c r="J122" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K122" s="33" t="inlineStr">
@@ -16747,7 +16751,7 @@
       </c>
       <c r="M122" s="33" t="inlineStr">
         <is>
-          <t>A site-data completeness review with the customer, so facilities of an already-mapped supplier are shared and on file before an event names one, rather than the gap surfacing when a WarRoom does not appear</t>
+          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
         </is>
       </c>
       <c r="N122" s="33" t="inlineStr">
@@ -16757,7 +16761,7 @@
       </c>
       <c r="O122" s="33" t="inlineStr">
         <is>
-          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so that verification is still outstanding and is recorded here rather than in the status field. The row is Clarification Provided because that is what went back to NVR on ask 1. It is not Pending: this was raised by email with no Jira ticket, so the daily Pending re-check would have no ticket to pull and nothing would ever move the flag off. The open source check is a manual follow-up with Ankit Gupta.</t>
+          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification. The outcome is a process enhancement rather than a correction: the WarRoom met the threshold the guidance actually set, and what the scenario exposed is that the threshold tested supplier mapping without testing whether the affected product is one the customer buys.</t>
         </is>
       </c>
       <c r="P122" s="33" t="n"/>
@@ -16777,18 +16781,18 @@
       </c>
       <c r="U122" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V122" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W122" s="33" t="n"/>
       <c r="X122" s="33" t="inlineStr">
         <is>
-          <t>The Kinston event was identified and published as an EventWatch bulletin, so monitoring carried it. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not among the sites NVR had shared, so no WarRoom could be created for them. Nothing in the platform or in analyst review failed here. What is missing is a process for collecting a customer's facility data completely enough that a site of a mapped supplier is on file before an event names it. The source-coverage question NVR raised alongside is being verified separately and carries no finding of a miss, since the event was published.</t>
+          <t>The WarRoom was created correctly under the guidance as written: NVIDIA is a mapped partner, and the EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. The affected product was the Shield TV Pro, which the customer does not procure, so there was no direct impact on products or services supplied to them. EventWatch and the customer agreed that for this scenario an EventWatch bulletin without a WarRoom is the right treatment - and the guidance did not carry that scenario at all: its threshold tested supplier mapping alone and said nothing about product-level relevance or customer exposure. This is a process enhancement, not a defect; no guideline was broken and no fault was admitted. The team committed to reinforcing the guidance so that product-level relevance and customer exposure are evaluated alongside supplier mapping before a WarRoom is created for a similar price fluctuation event.</t>
         </is>
       </c>
       <c r="Y122" s="33" t="inlineStr">
@@ -16807,12 +16811,12 @@
       </c>
       <c r="C123" s="33" t="inlineStr">
         <is>
-          <t>FDA/EMA/OSHA Action</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D123" s="33" t="inlineStr">
         <is>
-          <t>Suntory Spirits</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="E123" s="39" t="n">
@@ -16820,27 +16824,27 @@
       </c>
       <c r="F123" s="33" t="inlineStr">
         <is>
-          <t>Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan</t>
+          <t>MasterBrand Cabinets to Lay Off Employees at Its Facility in Kinston, North Carolina, USA</t>
         </is>
       </c>
       <c r="G123" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H123" s="33" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I123" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J123" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -16850,28 +16854,28 @@
       </c>
       <c r="L123" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M123" s="33" t="inlineStr">
         <is>
-          <t>Timeliness monitoring for regulator and competition-authority actions against mapped suppliers, so a publicly reported raid or probe is matched and published before a customer asks where the coverage is</t>
+          <t>A site-data completeness review with the customer, so facilities of an already-mapped supplier are shared and on file before an event names one, rather than the gap surfacing when a WarRoom does not appear</t>
         </is>
       </c>
       <c r="N123" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O123" s="33" t="inlineStr">
         <is>
-          <t>Suntory Spirits raised two asks by email on 09-Oct-2026 about the Japanese antitrust investigation into four major brewers. ASK 1, why there was no EventWatch coverage. The customer saw news of the investigation naming Suntory Spirits and could not find corresponding coverage in EventWatch, and questioned whether this event type is monitored at all. ASK 2, whether the sources reporting the investigation are inside the monitoring ecosystem, and whether monitoring can be expanded so future developments are captured earlier. The timeline is what makes this a miss rather than a coverage question. Authorities conducted searches on 07-Oct-2026 and the investigation was publicly reported before any EventWatch bulletin existed. The customer wrote in on 09-Oct. The bulletin, titled Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan, published at 12:07 AM IST on 10-Oct-2026 - after the escalation. So ask 2 is not a generic source-coverage question: the customer is asking whether sources that already carried the story were being monitored, which makes it a monitoring-gap inquiry. Under investigation and deliberately left open; the Sub-type is a staging guess. Captured Late is the one reading the timeline supports on its own, since a bulletin did publish, and it does not prejudge whether the delay came from a source gap, a keyword gap or pipeline lag - which is exactly what is still being established. Raised by email; no Jira ticket has been opened, so the daily Pending re-check has no ticket to pull and this row needs a human to carry it.</t>
+          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so that verification is still outstanding and is recorded here rather than in the status field. The row is Clarification Provided because that is what went back to NVR on ask 1. It is not Pending: this was raised by email with no Jira ticket, so the daily Pending re-check would have no ticket to pull and nothing would ever move the flag off. The open source check is a manual follow-up with Ankit Gupta.</t>
         </is>
       </c>
       <c r="P123" s="33" t="n"/>
       <c r="Q123" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R123" s="39" t="n">
@@ -16885,23 +16889,23 @@
       </c>
       <c r="U123" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V123" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W123" s="33" t="n"/>
       <c r="X123" s="33" t="inlineStr">
         <is>
-          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+          <t>The Kinston event was identified and published as an EventWatch bulletin, so monitoring carried it. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not among the sites NVR had shared, so no WarRoom could be created for them. Nothing in the platform or in analyst review failed here. What is missing is a process for collecting a customer's facility data completely enough that a site of a mapped supplier is on file before an event names it. The source-coverage question NVR raised alongside is being verified separately and carries no finding of a miss, since the event was published.</t>
         </is>
       </c>
       <c r="Y123" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z123" s="37" t="n"/>
@@ -16911,16 +16915,16 @@
         <v>46296</v>
       </c>
       <c r="B124" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>FDA/EMA/OSHA Action</t>
         </is>
       </c>
       <c r="D124" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Suntory Spirits</t>
         </is>
       </c>
       <c r="E124" s="39" t="n">
@@ -16928,7 +16932,7 @@
       </c>
       <c r="F124" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan</t>
         </is>
       </c>
       <c r="G124" s="33" t="inlineStr">
@@ -16938,7 +16942,7 @@
       </c>
       <c r="H124" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="I124" s="33" t="inlineStr">
@@ -16948,7 +16952,7 @@
       </c>
       <c r="J124" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K124" s="33" t="inlineStr">
@@ -16963,7 +16967,7 @@
       </c>
       <c r="M124" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Timeliness monitoring for regulator and competition-authority actions against mapped suppliers, so a publicly reported raid or probe is matched and published before a customer asks where the coverage is</t>
         </is>
       </c>
       <c r="N124" s="33" t="inlineStr">
@@ -16973,7 +16977,7 @@
       </c>
       <c r="O124" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Suntory Spirits raised two asks by email on 09-Oct-2026 about the Japanese antitrust investigation into four major brewers. ASK 1, why there was no EventWatch coverage. The customer saw news of the investigation naming Suntory Spirits and could not find corresponding coverage in EventWatch, and questioned whether this event type is monitored at all. ASK 2, whether the sources reporting the investigation are inside the monitoring ecosystem, and whether monitoring can be expanded so future developments are captured earlier. The timeline is what makes this a miss rather than a coverage question. Authorities conducted searches on 07-Oct-2026 and the investigation was publicly reported before any EventWatch bulletin existed. The customer wrote in on 09-Oct. The bulletin, titled Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan, published at 12:07 AM IST on 10-Oct-2026 - after the escalation. So ask 2 is not a generic source-coverage question: the customer is asking whether sources that already carried the story were being monitored, which makes it a monitoring-gap inquiry. Under investigation and deliberately left open; the Sub-type is a staging guess. Captured Late is the one reading the timeline supports on its own, since a bulletin did publish, and it does not prejudge whether the delay came from a source gap, a keyword gap or pipeline lag - which is exactly what is still being established. Raised by email; no Jira ticket has been opened, so the daily Pending re-check has no ticket to pull and this row needs a human to carry it.</t>
         </is>
       </c>
       <c r="P124" s="33" t="n"/>
@@ -16993,26 +16997,134 @@
       </c>
       <c r="U124" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V124" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W124" s="33" t="n"/>
+      <c r="X124" s="33" t="inlineStr">
+        <is>
+          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+        </is>
+      </c>
+      <c r="Y124" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z124" s="37" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B125" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C125" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E125" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G125" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H125" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I125" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J125" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K125" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L125" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M125" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N125" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O125" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P125" s="33" t="n"/>
+      <c r="Q125" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R125" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S125" s="39" t="n"/>
+      <c r="T125" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U125" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V124" s="33" t="inlineStr">
+      <c r="V125" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W124" s="33" t="inlineStr">
+      <c r="W125" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X124" s="33" t="n"/>
-      <c r="Y124" s="33" t="inlineStr">
+      <c r="X125" s="33" t="n"/>
+      <c r="Y125" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z124" s="37" t="n"/>
+      <c r="Z125" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18770,7 +18882,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3564356435643564</v>
+        <v>0.34951456310679613</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18811,7 +18923,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12871287128712872</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18853,7 +18965,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06930693069306931</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18892,10 +19004,10 @@
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18937,7 +19049,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.038834951456310676</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18979,7 +19091,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.0297029702970297</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19014,14 +19126,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19056,14 +19168,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19098,14 +19210,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19140,14 +19252,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19286,13 +19398,13 @@
         </is>
       </c>
       <c r="J80" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K80" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L80" s="76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -19544,10 +19656,10 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L90" s="76" t="n">
         <v>8</v>
@@ -19634,13 +19746,13 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>
@@ -20119,7 +20231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24244,6 +24356,33 @@
       <c r="E154" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="30.75" customHeight="1">
+      <c r="A155" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B155" s="41" t="inlineStr">
+        <is>
+          <t>Alerting Gap</t>
+        </is>
+      </c>
+      <c r="C155" s="41" t="inlineStr">
+        <is>
+          <t>A relevant article or feed was captured by the Product-controlled harvesting or monitoring flow, but an ingestion, database, portal, UI or workflow failure prevented it from reaching analysts as a usable item in time for review and escalation.</t>
+        </is>
+      </c>
+      <c r="D155" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Include: feed identified upstream but not ingested into the portal; algorithm captured the article but it did not reach the application or analyst queue; a captured feed that surfaced in the analyst workflow only after a Product-caused delay. Exclude: source or vendor never captured it, a keyword or language-detection miss, Product's first usable capture being late, wrong clustering, incorrect AI classification, an analyst marking it Not Impactful, an analyst deprioritising an available event, a published item the customer could not see, and customer configuration filtering it out.</t>
+        </is>
+      </c>
+      <c r="E155" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,10 +1771,10 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
-                  <v>16</v>
+                  <v>15</v>
                 </pt>
                 <pt idx="3">
                   <v>6</v>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="L107" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M107" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1281,7 +1281,7 @@
                   <v>11</v>
                 </pt>
                 <pt idx="4">
-                  <v>17</v>
+                  <v>18</v>
                 </pt>
                 <pt idx="5">
                   <v>9</v>
@@ -1293,7 +1293,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="8">
-                  <v>13</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="9">
                   <v>4</v>
@@ -1415,7 +1415,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="8">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="9">
                   <v>2</v>
@@ -1771,10 +1771,10 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
-                  <v>17</v>
+                  <v>15</v>
                 </pt>
                 <pt idx="3">
                   <v>6</v>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>105</v>
+                  <v>106</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>58</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>Belden Inc</v>
+                </pt>
+                <pt idx="7">
                   <v>General Mills</v>
                 </pt>
-                <pt idx="7">
+                <pt idx="8">
                   <v>META</v>
                 </pt>
-                <pt idx="8">
+                <pt idx="9">
                   <v>Merck</v>
-                </pt>
-                <pt idx="9">
-                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2672,7 +2672,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="4">
                   <v>4</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>26</v>
+                  <v>27</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2981,7 +2981,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="9"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>31</v>
                 </pt>
                 <pt idx="1">
                   <v>33</v>
@@ -2999,13 +2999,13 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>6</v>
+                  <v>10</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3318,7 +3318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z124" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z125" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3376,7 +3376,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E154" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E155" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -3680,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z124"/>
+  <dimension ref="A1:Z125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="O56" s="33" t="inlineStr">
         <is>
-          <t>Fire started May 18 11am; WarRoom created May 19 9:30am (~22.5 hr delay). Investigation pending.</t>
+          <t>The system successfully captured and classified the wildfire-related feeds on May 18, 2026. During analyst review, the event was placed under monitoring because early impact visibility was limited, and additional contextual validation was not performed. The event was reassessed after further updates on May 19 and escalated through WarRoom creation. Final classification: People - Published Late. Evidence Status: Confirmed RCA. The Sub-type remains Prioritization in this change set because Published Late is not yet an introduced value; it is recorded here as the final classification.</t>
         </is>
       </c>
       <c r="P56" s="33" t="inlineStr">
@@ -9546,22 +9546,22 @@
       </c>
       <c r="I57" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J57" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K57" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L57" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M57" s="33" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="O57" s="33" t="inlineStr">
         <is>
-          <t>Fire started May 19 11am; WarRoom created next day ~8am (~21 hr delay). Investigation pending.</t>
+          <t>The EventWatch system successfully captured wildfire-related feeds on May 19, 2026. A feed-ingestion failure prevented the feeds from reaching the EventWatch portal and reporting workflow for analyst review and escalation. Additional updates on May 20 became available in the workflow, after which the event was reviewed and escalated through WarRoom creation. Alerting Gap Type: Captured Feed Not Surfaced to Analyst Workflow. Evidence Status: Confirmed. This is an Alerting Gap because analysts did not have usable workflow visibility before the customer-impacting delay. The fact that analysts reviewed the event after it became available does not change the originating root cause.</t>
         </is>
       </c>
       <c r="P57" s="33" t="inlineStr">
@@ -9605,13 +9605,13 @@
       </c>
       <c r="V57" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="X57" s="33" t="n"/>
       <c r="Y57" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z57" s="37" t="n"/>
@@ -9826,19 +9826,19 @@
     </row>
     <row r="60">
       <c r="A60" s="35" t="n">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="B60" s="37" t="n">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="C60" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D60" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="E60" s="39" t="n">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="F60" s="33" t="inlineStr">
         <is>
-          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
+          <t>Potential Strike Action at Thales Defence Facilities in Glasgow and Reading, UK</t>
         </is>
       </c>
       <c r="G60" s="33" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="H60" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Delayed WarRoom</t>
         </is>
       </c>
       <c r="I60" s="33" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="J60" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K60" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L60" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M60" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Feed-to-portal ingestion monitoring, so an upstream-identified feed that fails to enter the portal workflow is detected before the reporting and escalation queues go without it</t>
         </is>
       </c>
       <c r="N60" s="33" t="inlineStr">
@@ -9891,21 +9891,27 @@
       </c>
       <c r="O60" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
-        </is>
-      </c>
-      <c r="P60" s="33" t="n"/>
+          <t>Relevant labor-action feeds were identified upstream but were not ingested into the EventWatch portal workflow on May 26, 2026. The feeds therefore did not reach the reporting and escalation queues in time. The WarRoom was created on May 28, 2026. Internal validation confirmed an ingestion gap between feed capture and portal availability. Raised by Steven Brandt in the complaint thread on 28-May-2026; no Jira ticket was opened. Alerting Gap Type: Feed-to-Portal Ingestion Failure. Evidence Status: Confirmed.</t>
+        </is>
+      </c>
+      <c r="P60" s="33" t="inlineStr">
+        <is>
+          <t>~2 days (26-May articles → 28-May WarRoom)</t>
+        </is>
+      </c>
       <c r="Q60" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="R60" s="39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S60" s="39" t="n"/>
-      <c r="T60" s="35" t="n">
-        <v>46174</v>
+      <c r="T60" s="35" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -9914,10 +9920,15 @@
       </c>
       <c r="V60" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="X60" s="33" t="n"/>
+          <t>Notification Visibility Monitoring</t>
+        </is>
+      </c>
+      <c r="W60" s="33" t="n"/>
+      <c r="X60" s="33" t="inlineStr">
+        <is>
+          <t>The feeds were identified upstream but were not ingested into the EventWatch portal workflow, which prevented them from reaching the reporting and escalation queues in a timely manner. Internal review confirmed an ingestion gap between feed capture and portal availability.</t>
+        </is>
+      </c>
       <c r="Y60" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
@@ -9930,14 +9941,14 @@
         <v>46174</v>
       </c>
       <c r="B61" s="37" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="C61" s="33" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
-        </is>
-      </c>
-      <c r="D61" s="34" t="inlineStr">
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D61" s="33" t="inlineStr">
         <is>
           <t>Ford</t>
         </is>
@@ -9947,7 +9958,7 @@
       </c>
       <c r="F61" s="33" t="inlineStr">
         <is>
-          <t>ANTAC Transport Blockades in Mexico</t>
+          <t>CROMTRYCK s.r.o. Insolvency (Czech Republic)</t>
         </is>
       </c>
       <c r="G61" s="33" t="inlineStr">
@@ -9967,7 +9978,7 @@
       </c>
       <c r="J61" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K61" s="33" t="inlineStr">
@@ -9977,7 +9988,7 @@
       </c>
       <c r="L61" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M61" s="33" t="inlineStr">
@@ -9992,7 +10003,7 @@
       </c>
       <c r="O61" s="33" t="inlineStr">
         <is>
-          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
+          <t>Missed insolvency event due to regional insolvency source coverage limitations and restricted/paywalled source visibility. Vendor source expansion requested.</t>
         </is>
       </c>
       <c r="P61" s="33" t="n"/>
@@ -10015,7 +10026,7 @@
       </c>
       <c r="V61" s="33" t="inlineStr">
         <is>
-          <t>Multilingual Keyword Expansion</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="X61" s="33" t="n"/>
@@ -10031,16 +10042,16 @@
         <v>46174</v>
       </c>
       <c r="B62" s="37" t="n">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="C62" s="33" t="inlineStr">
         <is>
-          <t>Factory Disruption</t>
-        </is>
-      </c>
-      <c r="D62" s="33" t="inlineStr">
-        <is>
-          <t>Eaton</t>
+          <t>Protest/Riot</t>
+        </is>
+      </c>
+      <c r="D62" s="34" t="inlineStr">
+        <is>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E62" s="39" t="n">
@@ -10048,7 +10059,7 @@
       </c>
       <c r="F62" s="33" t="inlineStr">
         <is>
-          <t>Burnstein von Seelen Precision Casting Operational Disruption</t>
+          <t>ANTAC Transport Blockades in Mexico</t>
         </is>
       </c>
       <c r="G62" s="33" t="inlineStr">
@@ -10063,12 +10074,12 @@
       </c>
       <c r="I62" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J62" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K62" s="33" t="inlineStr">
@@ -10083,7 +10094,7 @@
       </c>
       <c r="M62" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware escalation model + Not Impactful override validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N62" s="33" t="inlineStr">
@@ -10093,7 +10104,7 @@
       </c>
       <c r="O62" s="33" t="inlineStr">
         <is>
-          <t>RCA shared; analyst classified event as Not Impactful. Event was successfully received and reviewed but incorrectly classified and therefore not escalated.</t>
+          <t>RCA completed; keyword gap identified and corrective actions implemented. Spanish-language detection logic did not recognize transportation disruption and protest terminology. Relevant keywords were added.</t>
         </is>
       </c>
       <c r="P62" s="33" t="n"/>
@@ -10116,43 +10127,32 @@
       </c>
       <c r="V62" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W62" s="33" t="inlineStr">
-        <is>
-          <t>EAO-1</t>
-        </is>
-      </c>
-      <c r="X62" s="33" t="inlineStr">
-        <is>
-          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
-        </is>
-      </c>
+          <t>Multilingual Keyword Expansion</t>
+        </is>
+      </c>
+      <c r="X62" s="33" t="n"/>
       <c r="Y62" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z62" s="37" t="n">
-        <v>46181</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z62" s="37" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B63" s="37" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="C63" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Factory Disruption</t>
         </is>
       </c>
       <c r="D63" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E63" s="39" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="F63" s="33" t="inlineStr">
         <is>
-          <t>Credit Suisse / UBS Acquisition Alert Missing from EventWatch News Dashboard (Ford)</t>
+          <t>Burnstein von Seelen Precision Casting Operational Disruption</t>
         </is>
       </c>
       <c r="G63" s="33" t="inlineStr">
@@ -10170,17 +10170,17 @@
       </c>
       <c r="H63" s="33" t="inlineStr">
         <is>
-          <t>News dashboard visibility gap</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I63" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J63" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K63" s="33" t="inlineStr">
@@ -10190,38 +10190,36 @@
       </c>
       <c r="L63" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M63" s="33" t="inlineStr">
         <is>
-          <t>Parity checking between Global Search and the EventWatch News Dashboard so a published alert cannot be findable in one and absent from the other</t>
+          <t>Supplier-aware escalation model + Not Impactful override validation</t>
         </is>
       </c>
       <c r="N63" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O63" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected.</t>
+          <t>RCA shared; analyst classified event as Not Impactful. Event was successfully received and reviewed but incorrectly classified and therefore not escalated.</t>
         </is>
       </c>
       <c r="P63" s="33" t="n"/>
       <c r="Q63" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R63" s="39" t="n">
         <v>6</v>
       </c>
       <c r="S63" s="39" t="n"/>
-      <c r="T63" s="35" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
+      <c r="T63" s="35" t="n">
+        <v>46174</v>
       </c>
       <c r="U63" s="33" t="inlineStr">
         <is>
@@ -10230,41 +10228,43 @@
       </c>
       <c r="V63" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W63" s="33" t="inlineStr">
         <is>
-          <t>CAN-3377</t>
+          <t>EAO-1</t>
         </is>
       </c>
       <c r="X63" s="33" t="inlineStr">
         <is>
-          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
+          <t>Articles on the Burnstein von Seelen disruption did reach the portal, but the analyst classified the event Not Impactful and did not escalate it, so it never reached WarRoom consideration. Corrective: analyst coaching on law-enforcement, regulatory and workforce disruptions, plus an internal non-conformance raised against the reporting workflow. Preventive: extra review controls before a Not Impactful call on a monitored supplier, stronger supplier-context visibility during review, expanded audits of analyst overrides, and AI-assisted relevance work with Product/Data Science.</t>
         </is>
       </c>
       <c r="Y63" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z63" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z63" s="37" t="n">
+        <v>46181</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B64" s="37" t="n">
-        <v>46188</v>
+        <v>46183</v>
       </c>
       <c r="C64" s="33" t="inlineStr">
         <is>
-          <t>Chemical Spill</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D64" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E64" s="39" t="n">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="F64" s="33" t="inlineStr">
         <is>
-          <t>CO₂ Leak at Schaeffler India Plant, Pune</t>
+          <t>Credit Suisse / UBS Acquisition Alert Missing from EventWatch News Dashboard (Ford)</t>
         </is>
       </c>
       <c r="G64" s="33" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H64" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>News dashboard visibility gap</t>
         </is>
       </c>
       <c r="I64" s="33" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="J64" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K64" s="33" t="inlineStr">
@@ -10302,36 +10302,38 @@
       </c>
       <c r="L64" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M64" s="33" t="inlineStr">
         <is>
-          <t>Hazardous gas leak detection + mapped supplier escalation model</t>
+          <t>Parity checking between Global Search and the EventWatch News Dashboard so a published alert cannot be findable in one and absent from the other</t>
         </is>
       </c>
       <c r="N64" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O64" s="33" t="inlineStr">
         <is>
-          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility.</t>
+          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected.</t>
         </is>
       </c>
       <c r="P64" s="33" t="n"/>
       <c r="Q64" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R64" s="39" t="n">
         <v>6</v>
       </c>
       <c r="S64" s="39" t="n"/>
-      <c r="T64" s="35" t="n">
-        <v>46174</v>
+      <c r="T64" s="35" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
       </c>
       <c r="U64" s="33" t="inlineStr">
         <is>
@@ -10340,17 +10342,17 @@
       </c>
       <c r="V64" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W64" s="33" t="inlineStr">
         <is>
-          <t>EAO-4</t>
+          <t>CAN-3377</t>
         </is>
       </c>
       <c r="X64" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
+          <t>The ticket carries no root-cause statement. It sat unprioritised by the Transformation team through July with no committed date, was picked up later that month, and the fix was verified on Azure staging on 28-Jul-2026 as working as expected and marked resolved. What was wrong and what was changed are not recorded on the ticket.</t>
         </is>
       </c>
       <c r="Y64" s="33" t="inlineStr">
@@ -10358,9 +10360,7 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z64" s="37" t="n">
-        <v>46191</v>
-      </c>
+      <c r="Z64" s="37" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="C65" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Chemical Spill</t>
         </is>
       </c>
       <c r="D65" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E65" s="39" t="n">
@@ -10384,27 +10384,27 @@
       </c>
       <c r="F65" s="33" t="inlineStr">
         <is>
-          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
+          <t>CO₂ Leak at Schaeffler India Plant, Pune</t>
         </is>
       </c>
       <c r="G65" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H65" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I65" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K65" s="33" t="inlineStr">
@@ -10414,28 +10414,28 @@
       </c>
       <c r="L65" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M65" s="33" t="inlineStr">
         <is>
-          <t>Forecast vs Event differentiation</t>
+          <t>Hazardous gas leak detection + mapped supplier escalation model</t>
         </is>
       </c>
       <c r="N65" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O65" s="33" t="inlineStr">
         <is>
-          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
+          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility.</t>
         </is>
       </c>
       <c r="P65" s="33" t="n"/>
       <c r="Q65" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R65" s="39" t="n">
@@ -10452,26 +10452,26 @@
       </c>
       <c r="V65" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W65" s="33" t="inlineStr">
         <is>
-          <t>EAO-8</t>
+          <t>EAO-4</t>
         </is>
       </c>
       <c r="X65" s="33" t="inlineStr">
         <is>
-          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
+          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y65" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>46202</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="66">
@@ -10479,16 +10479,16 @@
         <v>46174</v>
       </c>
       <c r="B66" s="37" t="n">
-        <v>46196</v>
+        <v>46188</v>
       </c>
       <c r="C66" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D66" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E66" s="39" t="n">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="F66" s="33" t="inlineStr">
         <is>
-          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
+          <t>MLCC Supply Chain Alert Related to AI Demand Growth</t>
         </is>
       </c>
       <c r="G66" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H66" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I66" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J66" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K66" s="33" t="inlineStr">
@@ -10526,22 +10526,22 @@
       </c>
       <c r="L66" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M66" s="33" t="inlineStr">
         <is>
-          <t>Supplier relationship validation + impacted entity completeness checks</t>
+          <t>Forecast vs Event differentiation</t>
         </is>
       </c>
       <c r="N66" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O66" s="33" t="inlineStr">
         <is>
-          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
+          <t>Article was an investment and market outlook discussing future MLCC demand and did not meet EventWatch reporting thresholds.</t>
         </is>
       </c>
       <c r="P66" s="33" t="n"/>
@@ -10564,17 +10564,17 @@
       </c>
       <c r="V66" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W66" s="33" t="inlineStr">
         <is>
-          <t>EAO-6</t>
+          <t>EAO-8</t>
         </is>
       </c>
       <c r="X66" s="33" t="inlineStr">
         <is>
-          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
+          <t>Not an event under the reporting criteria. The article was a financial and market outlook on future demand and investment opportunity in the AI supply chain. It highlights potential growth in MLCC demand but identifies no actual supply chain risk or disruption, and an investment outlook rather than a report of a disruption does not meet the EventWatch Threshold criteria.</t>
         </is>
       </c>
       <c r="Y66" s="33" t="inlineStr">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>46217</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="67">
@@ -10595,12 +10595,12 @@
       </c>
       <c r="C67" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D67" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E67" s="39" t="n">
@@ -10608,27 +10608,27 @@
       </c>
       <c r="F67" s="33" t="inlineStr">
         <is>
-          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
+          <t>Dana Incorporated to Merge with Eaton's Mobility Business</t>
         </is>
       </c>
       <c r="G67" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H67" s="33" t="inlineStr">
         <is>
-          <t>Customer Requested Verification</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I67" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J67" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K67" s="33" t="inlineStr">
@@ -10638,22 +10638,22 @@
       </c>
       <c r="L67" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M67" s="33" t="inlineStr">
         <is>
-          <t>Route-risk monitoring enhancement</t>
+          <t>Supplier relationship validation + impacted entity completeness checks</t>
         </is>
       </c>
       <c r="N67" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O67" s="33" t="inlineStr">
         <is>
-          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
+          <t>Customer-facing RCA requested and RCA document prepared. Dana Holding Corporation was not included in impacted supplier selection during initial WarRoom creation and was subsequently added.</t>
         </is>
       </c>
       <c r="P67" s="33" t="n"/>
@@ -10676,17 +10676,17 @@
       </c>
       <c r="V67" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W67" s="33" t="inlineStr">
         <is>
-          <t>EAO-7</t>
+          <t>EAO-6</t>
         </is>
       </c>
       <c r="X67" s="33" t="inlineStr">
         <is>
-          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
+          <t>The primary transaction participants were identified correctly, but Dana Holdings was omitted during the initial review of related corporate entities and supplier relationships; a WarRoom update was issued to add it. Preventive: mandatory secondary review for impacted-supplier assessments involving mergers, acquisitions, restructurings and other multi-entity transactions. RCA shared 13-Jul-2026.</t>
         </is>
       </c>
       <c r="Y67" s="33" t="inlineStr">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>46198</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="68">
@@ -10703,11 +10703,11 @@
         <v>46174</v>
       </c>
       <c r="B68" s="37" t="n">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="C68" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D68" s="33" t="inlineStr">
@@ -10720,27 +10720,27 @@
       </c>
       <c r="F68" s="33" t="inlineStr">
         <is>
-          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
+          <t>Inquiry on Route Disruption – Sepone Bridge, Laos</t>
         </is>
       </c>
       <c r="G68" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H68" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Customer Requested Verification</t>
         </is>
       </c>
       <c r="I68" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J68" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K68" s="33" t="inlineStr">
@@ -10750,28 +10750,28 @@
       </c>
       <c r="L68" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M68" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware cyber incident escalation model</t>
+          <t>Route-risk monitoring enhancement</t>
         </is>
       </c>
       <c r="N68" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O68" s="33" t="inlineStr">
         <is>
-          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
+          <t>Review of English and local-language sources did not identify any verified disruption, closure, or logistic impact.</t>
         </is>
       </c>
       <c r="P68" s="33" t="n"/>
       <c r="Q68" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R68" s="39" t="n">
@@ -10788,17 +10788,17 @@
       </c>
       <c r="V68" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W68" s="33" t="inlineStr">
         <is>
-          <t>EAO-10</t>
+          <t>EAO-7</t>
         </is>
       </c>
       <c r="X68" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
+          <t>No public source existed to report from. A review of publicly available sources, covering English as well as Lao and regional local-language coverage, found no official confirmation from government authorities, logistics providers or credible media of a bridge closure, restriction or disruption to freight movement near Sepone in Savannakhet Province, and no verified reports of impact to trucking operations or access to the Savannakhet ICD. The customer was asked to share any specific article or source they held so it could be reviewed.</t>
         </is>
       </c>
       <c r="Y68" s="33" t="inlineStr">
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>46202</v>
+        <v>46198</v>
       </c>
     </row>
     <row r="69">
@@ -10815,16 +10815,16 @@
         <v>46174</v>
       </c>
       <c r="B69" s="37" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="C69" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D69" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E69" s="39" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F69" s="33" t="inlineStr">
         <is>
-          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
+          <t>Nidec Chaun Choung Technology Suffers Ransomware Attack</t>
         </is>
       </c>
       <c r="G69" s="33" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="I69" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J69" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K69" s="33" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="M69" s="33" t="inlineStr">
         <is>
-          <t>Entity-location-aware clustering + cluster separation validation</t>
+          <t>Supplier-aware cyber incident escalation model</t>
         </is>
       </c>
       <c r="N69" s="33" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="O69" s="33" t="inlineStr">
         <is>
-          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
+          <t>RCA prepared; analyst impact-assessment failure identified. Event was captured successfully but incorrectly assessed as Not Impactful during analyst review and therefore not escalated.</t>
         </is>
       </c>
       <c r="P69" s="33" t="n"/>
@@ -10900,22 +10900,22 @@
       </c>
       <c r="V69" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W69" s="33" t="inlineStr">
         <is>
-          <t>EAO-9</t>
+          <t>EAO-10</t>
         </is>
       </c>
       <c r="X69" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
+          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y69" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z69" s="37" t="n">
@@ -10927,16 +10927,16 @@
         <v>46174</v>
       </c>
       <c r="B70" s="37" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="C70" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D70" s="33" t="inlineStr">
         <is>
-          <t>Woodward</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E70" s="39" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F70" s="33" t="inlineStr">
         <is>
-          <t>Severe Storms Trigger Disruptions Across the Midwest USA – Geographic Misclassification</t>
+          <t>Fire at the Isselguss GmbH Facility in Isselburg, Germany</t>
         </is>
       </c>
       <c r="G70" s="33" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I70" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K70" s="33" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="L70" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M70" s="33" t="inlineStr">
         <is>
-          <t>Cluster integrity validation + geographic consistency checks</t>
+          <t>Entity-location-aware clustering + cluster separation validation</t>
         </is>
       </c>
       <c r="N70" s="33" t="inlineStr">
@@ -10989,13 +10989,13 @@
       </c>
       <c r="O70" s="33" t="inlineStr">
         <is>
-          <t>California sites were incorrectly included because two different events were merged into the same WarRoom.</t>
+          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
         </is>
       </c>
       <c r="P70" s="33" t="n"/>
       <c r="Q70" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R70" s="39" t="n">
@@ -11012,41 +11012,43 @@
       </c>
       <c r="V70" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W70" s="33" t="inlineStr">
         <is>
-          <t>EAO-5</t>
+          <t>EAO-9</t>
         </is>
       </c>
       <c r="X70" s="33" t="inlineStr">
         <is>
-          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
+          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
         </is>
       </c>
       <c r="Y70" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z70" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z70" s="37" t="n">
+        <v>46202</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="35" t="n">
         <v>46174</v>
       </c>
       <c r="B71" s="37" t="n">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="C71" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D71" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Woodward</t>
         </is>
       </c>
       <c r="E71" s="39" t="n">
@@ -11054,27 +11056,27 @@
       </c>
       <c r="F71" s="33" t="inlineStr">
         <is>
-          <t>Isselguss / Isselburg Foundry Naming Clarification</t>
+          <t>Severe Storms Trigger Disruptions Across the Midwest USA – Geographic Misclassification</t>
         </is>
       </c>
       <c r="G71" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>Customer Terminology Preference</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="I71" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K71" s="33" t="inlineStr">
@@ -11084,22 +11086,22 @@
       </c>
       <c r="L71" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M71" s="33" t="inlineStr">
         <is>
-          <t>Company alias management</t>
+          <t>Cluster integrity validation + geographic consistency checks</t>
         </is>
       </c>
       <c r="N71" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O71" s="33" t="inlineStr">
         <is>
-          <t>Isselguss and Isselburg Foundry refer to the same facility. Title updated to align with customer terminology preference and not due to a reporting error.</t>
+          <t>California sites were incorrectly included because two different events were merged into the same WarRoom.</t>
         </is>
       </c>
       <c r="P71" s="33" t="n"/>
@@ -11122,17 +11124,17 @@
       </c>
       <c r="V71" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W71" s="33" t="inlineStr">
         <is>
-          <t>EAO-11</t>
+          <t>EAO-5</t>
         </is>
       </c>
       <c r="X71" s="33" t="inlineStr">
         <is>
-          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+          <t>Analyst-side grouping error, not a geofencing or source defect. The reporting team clubbed two separate events together, so California sites were attached to the Midwest Storm WarRoom where they did not belong. A DATA ticket was raised and the California sites were removed from the WarRoom.</t>
         </is>
       </c>
       <c r="Y71" s="33" t="inlineStr">
@@ -11140,25 +11142,23 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z71" s="37" t="n">
-        <v>46204</v>
-      </c>
+      <c r="Z71" s="37" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="35" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="B72" s="37" t="n">
-        <v>46204</v>
-      </c>
-      <c r="C72" s="28" t="inlineStr">
-        <is>
-          <t>Labor Disruption</t>
+        <v>46203</v>
+      </c>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D72" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E72" s="39" t="n">
@@ -11166,32 +11166,32 @@
       </c>
       <c r="F72" s="33" t="inlineStr">
         <is>
-          <t>BorgWarner Indefinite Strike – Vigo Metropolitan Area, Spain</t>
+          <t>Isselguss / Isselburg Foundry Naming Clarification</t>
         </is>
       </c>
       <c r="G72" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H72" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Customer Terminology Preference</t>
         </is>
       </c>
       <c r="I72" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J72" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Improvement</t>
         </is>
       </c>
       <c r="L72" s="33" t="inlineStr">
@@ -11201,63 +11201,59 @@
       </c>
       <c r="M72" s="33" t="inlineStr">
         <is>
-          <t>Vendor-to-portal feed validation + cluster state integrity monitoring</t>
+          <t>Company alias management</t>
         </is>
       </c>
       <c r="N72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O72" s="33" t="inlineStr">
         <is>
-          <t>Customer reported missed EventWatch notification for an indefinite strike at BorgWarner facilities in Zamáns, O Porriño, and Nigrán. CS investigation confirmed two previous strike notifications were successfully delivered to Ford, but no notification was generated for the July 1 event. Internal investigation notes indicate the articles were captured by the vendor and Spanish language algorithm but did not appear in the analyst portal. Engineering review referenced an inconsistent cluster state condition during the affected period.</t>
-        </is>
-      </c>
-      <c r="P72" s="33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Isselguss and Isselburg Foundry refer to the same facility. Title updated to align with customer terminology preference and not due to a reporting error.</t>
+        </is>
+      </c>
+      <c r="P72" s="33" t="n"/>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R72" s="39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S72" s="39" t="n"/>
       <c r="T72" s="35" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U72" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V72" s="33" t="inlineStr">
+        <is>
+          <t>Entity &amp; Supplier Resolution</t>
+        </is>
+      </c>
+      <c r="W72" s="33" t="inlineStr">
+        <is>
+          <t>EAO-11</t>
+        </is>
+      </c>
+      <c r="X72" s="33" t="inlineStr">
+        <is>
+          <t>Not an error, a terminology preference. Isselguss, or Isselguss, is the commonly used shorthand for Isselburg Guss und Bearbeitung GmbH, the Isselburg foundry; the formal company name and the short name refer to the same operation. Initial local and regional coverage of the incident used Isselguss because that is the locally recognisable name of the site, while other coverage described the same location simply as the foundry in Isselburg. The bulletin was updated to Isselburg foundry to match the customer's preferred terminology, and that change should not be read as correcting a mistake.</t>
+        </is>
+      </c>
+      <c r="Y72" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z72" s="37" t="n">
         <v>46204</v>
-      </c>
-      <c r="U72" s="33" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="V72" s="33" t="inlineStr">
-        <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
-        </is>
-      </c>
-      <c r="W72" s="33" t="inlineStr">
-        <is>
-          <t>EAO-12</t>
-        </is>
-      </c>
-      <c r="X72" s="33" t="inlineStr">
-        <is>
-          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but did not reach the analyst portal until 01-Jul-2026. Engineering confirmed on the ticket that the articles were captured both by the vendor and by the Spanish-language algorithm, and were linked to the labor_disruption_es_pontevedra_vigo_update cluster - so this is neither a source gap nor a failure to identify the event. That cluster was in an inconsistent state, its status set to Update while it was also marked Not Impactful, which kept the feeds off the analyst portal and meant no WarRoom was raised. The thread asks whether this is a recurrence of the cluster-state defect fixed in the June-end release, where a null cluster id still showed as not impactful. RCA approved and shared with the customer on 09-Jul-2026 as a PDF attachment.</t>
-        </is>
-      </c>
-      <c r="Y72" s="33" t="inlineStr">
-        <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z72" s="37" t="n">
-        <v>46216</v>
       </c>
     </row>
     <row r="73">
@@ -11265,11 +11261,11 @@
         <v>46204</v>
       </c>
       <c r="B73" s="37" t="n">
-        <v>46209</v>
-      </c>
-      <c r="C73" s="33" t="inlineStr">
-        <is>
-          <t>Factory Fire</t>
+        <v>46204</v>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D73" s="33" t="inlineStr">
@@ -11282,7 +11278,7 @@
       </c>
       <c r="F73" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI Foam Manufacturing Plant in Cuautitlan, Mexico</t>
+          <t>BorgWarner Indefinite Strike – Vigo Metropolitan Area, Spain</t>
         </is>
       </c>
       <c r="G73" s="33" t="inlineStr">
@@ -11302,12 +11298,12 @@
       </c>
       <c r="J73" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K73" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L73" s="33" t="inlineStr">
@@ -11317,7 +11313,7 @@
       </c>
       <c r="M73" s="33" t="inlineStr">
         <is>
-          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
+          <t>Vendor-to-portal feed validation + cluster state integrity monitoring</t>
         </is>
       </c>
       <c r="N73" s="33" t="inlineStr">
@@ -11327,10 +11323,14 @@
       </c>
       <c r="O73" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
-        </is>
-      </c>
-      <c r="P73" s="33" t="n"/>
+          <t>The articles were captured by the vendor and by the Spanish-language detection flow but did not reach the analyst portal until July 1, 2026. The failure occurred after feed capture and before timely analyst visibility. Alerting Gap Type: Captured Feed Surfaced Late. Evidence Status: Confirmed and Closed.</t>
+        </is>
+      </c>
+      <c r="P73" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="Q73" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11350,17 +11350,17 @@
       </c>
       <c r="V73" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W73" s="33" t="inlineStr">
         <is>
-          <t>EAO-13</t>
+          <t>EAO-12</t>
         </is>
       </c>
       <c r="X73" s="33" t="inlineStr">
         <is>
-          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+          <t>Feeds covering the BorgWarner Vigo indefinite strike were in the public domain from 26-Jun-2026 but did not reach the analyst portal until 01-Jul-2026. Engineering confirmed on the ticket that the articles were captured both by the vendor and by the Spanish-language algorithm, and were linked to the labor_disruption_es_pontevedra_vigo_update cluster - so this is neither a source gap nor a failure to identify the event. That cluster was in an inconsistent state, its status set to Update while it was also marked Not Impactful, which kept the feeds off the analyst portal and meant no WarRoom was raised. The thread asks whether this is a recurrence of the cluster-state defect fixed in the June-end release, where a null cluster id still showed as not impactful. RCA approved and shared with the customer on 09-Jul-2026 as a PDF attachment.</t>
         </is>
       </c>
       <c r="Y73" s="33" t="inlineStr">
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="74">
@@ -11377,7 +11377,7 @@
         <v>46204</v>
       </c>
       <c r="B74" s="37" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="C74" s="33" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="F74" s="33" t="inlineStr">
         <is>
-          <t>New World International Co. Factory Fire, Thailand</t>
+          <t>Fire at FXI Foam Manufacturing Plant in Cuautitlan, Mexico</t>
         </is>
       </c>
       <c r="G74" s="33" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="L74" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M74" s="33" t="inlineStr">
         <is>
-          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
+          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
         </is>
       </c>
       <c r="N74" s="33" t="inlineStr">
@@ -11439,7 +11439,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Feeds were received and event was reportedly marked Not Impactful despite destruction of production/storage facility. Investigation ongoing.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11467,21 +11467,21 @@
       </c>
       <c r="W74" s="33" t="inlineStr">
         <is>
-          <t>EAO-14</t>
+          <t>EAO-13</t>
         </is>
       </c>
       <c r="X74" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
+          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
         </is>
       </c>
       <c r="Y74" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z74" s="37" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="75">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="C75" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D75" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E75" s="39" t="n">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="F75" s="33" t="inlineStr">
         <is>
-          <t>Samsung DRAM Price Increase Alert – WarRoom Not Created</t>
+          <t>New World International Co. Factory Fire, Thailand</t>
         </is>
       </c>
       <c r="G75" s="33" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="H75" s="33" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I75" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J75" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K75" s="33" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="M75" s="33" t="inlineStr">
         <is>
-          <t>Site Selection Suggestion based on unnormalized supplier names</t>
+          <t>Supplier-aware factory fire escalation model + Not Impactful override validation</t>
         </is>
       </c>
       <c r="N75" s="33" t="inlineStr">
@@ -11551,14 +11551,10 @@
       </c>
       <c r="O75" s="33" t="inlineStr">
         <is>
-          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing.</t>
-        </is>
-      </c>
-      <c r="P75" s="33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Feeds were received and event was reportedly marked Not Impactful despite destruction of production/storage facility. Investigation ongoing.</t>
+        </is>
+      </c>
+      <c r="P75" s="33" t="n"/>
       <c r="Q75" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11573,22 +11569,22 @@
       </c>
       <c r="U75" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V75" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W75" s="33" t="inlineStr">
         <is>
-          <t>EAO-15</t>
+          <t>EAO-14</t>
         </is>
       </c>
       <c r="X75" s="33" t="inlineStr">
         <is>
-          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
+          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y75" s="33" t="inlineStr">
@@ -11597,7 +11593,7 @@
         </is>
       </c>
       <c r="Z75" s="37" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="76">
@@ -11605,16 +11601,16 @@
         <v>46204</v>
       </c>
       <c r="B76" s="37" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="C76" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D76" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E76" s="39" t="n">
@@ -11622,17 +11618,17 @@
       </c>
       <c r="F76" s="33" t="inlineStr">
         <is>
-          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
+          <t>Samsung DRAM Price Increase Alert – WarRoom Not Created</t>
         </is>
       </c>
       <c r="G76" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="I76" s="33" t="inlineStr">
@@ -11642,7 +11638,7 @@
       </c>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -11657,27 +11653,33 @@
       </c>
       <c r="M76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
+          <t>Site Selection Suggestion based on unnormalized supplier names</t>
         </is>
       </c>
       <c r="N76" s="33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O76" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing.</t>
+        </is>
+      </c>
+      <c r="P76" s="33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O76" s="33" t="inlineStr">
-        <is>
-          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
-        </is>
-      </c>
       <c r="Q76" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R76" s="39" t="n">
         <v>7</v>
       </c>
+      <c r="S76" s="39" t="n"/>
       <c r="T76" s="35" t="n">
         <v>46204</v>
       </c>
@@ -11688,17 +11690,17 @@
       </c>
       <c r="V76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W76" s="33" t="inlineStr">
         <is>
-          <t>EAO-16</t>
+          <t>EAO-15</t>
         </is>
       </c>
       <c r="X76" s="33" t="inlineStr">
         <is>
-          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
+          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
         </is>
       </c>
       <c r="Y76" s="33" t="inlineStr">
@@ -11707,7 +11709,7 @@
         </is>
       </c>
       <c r="Z76" s="37" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="77">
@@ -11719,12 +11721,12 @@
       </c>
       <c r="C77" s="33" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D77" s="33" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E77" s="39" t="n">
@@ -11732,27 +11734,27 @@
       </c>
       <c r="F77" s="33" t="inlineStr">
         <is>
-          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
+          <t>Super Typhoon Bavi WarRoom Timing Clarification (Taiwan)</t>
         </is>
       </c>
       <c r="G77" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H77" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I77" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J77" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K77" s="33" t="inlineStr">
@@ -11762,27 +11764,27 @@
       </c>
       <c r="L77" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M77" s="33" t="inlineStr">
         <is>
-          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
+          <t>WarRoom trigger-criteria explanation template for post-peak activations</t>
         </is>
       </c>
       <c r="N77" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O77" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
+          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
         </is>
       </c>
       <c r="Q77" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R77" s="39" t="n">
@@ -11793,31 +11795,31 @@
       </c>
       <c r="U77" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V77" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W77" s="33" t="inlineStr">
         <is>
-          <t>EAO-17</t>
+          <t>EAO-16</t>
         </is>
       </c>
       <c r="X77" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
+          <t>EventWatch captured multiple Philippines articles before the dedicated Philippines WarRoom was created, but they were assessed Not Impactful during reporting review, when available reports still described preparedness and localized impacts. Root cause: human assessment error underestimating the significance of the evolving Philippines impacts, which delayed WarRoom creation. Preventive: multi-country weather events assessed independently for each affected geography rather than inferred from the wider storm.</t>
         </is>
       </c>
       <c r="Y77" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z77" s="37" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="78">
@@ -11825,16 +11827,16 @@
         <v>46204</v>
       </c>
       <c r="B78" s="37" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="C78" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D78" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="E78" s="39" t="n">
@@ -11842,27 +11844,27 @@
       </c>
       <c r="F78" s="33" t="inlineStr">
         <is>
-          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
+          <t>Jacobs Engineering/CH2M Hill Forced Labor Lawsuit – Missed EventWatch Notification (Micron)</t>
         </is>
       </c>
       <c r="G78" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H78" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I78" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J78" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K78" s="33" t="inlineStr">
@@ -11872,27 +11874,27 @@
       </c>
       <c r="L78" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M78" s="33" t="inlineStr">
         <is>
-          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
+          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
         </is>
       </c>
       <c r="N78" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O78" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
         </is>
       </c>
       <c r="Q78" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R78" s="39" t="n">
@@ -11903,31 +11905,31 @@
       </c>
       <c r="U78" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V78" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W78" s="33" t="inlineStr">
         <is>
-          <t>EAO-18</t>
+          <t>EAO-17</t>
         </is>
       </c>
       <c r="X78" s="33" t="inlineStr">
         <is>
-          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
+          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y78" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z78" s="37" t="n">
-        <v>46224</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="79">
@@ -11935,16 +11937,16 @@
         <v>46204</v>
       </c>
       <c r="B79" s="37" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="C79" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D79" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E79" s="39" t="n">
@@ -11952,7 +11954,7 @@
       </c>
       <c r="F79" s="33" t="inlineStr">
         <is>
-          <t>RFI – Power Grid Failure Monitoring Strategy</t>
+          <t>Suspension Baseplate Supply Risk Monitoring Request (Fujita Plating/NHK/OSK)</t>
         </is>
       </c>
       <c r="G79" s="33" t="inlineStr">
@@ -11962,7 +11964,7 @@
       </c>
       <c r="H79" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I79" s="33" t="inlineStr">
@@ -11987,7 +11989,7 @@
       </c>
       <c r="M79" s="33" t="inlineStr">
         <is>
-          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
+          <t>Supplier decommitment/capacity-risk monitoring for sub-tier component makers</t>
         </is>
       </c>
       <c r="N79" s="33" t="inlineStr">
@@ -11997,7 +11999,7 @@
       </c>
       <c r="O79" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
+          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q79" s="33" t="inlineStr">
@@ -12023,12 +12025,12 @@
       </c>
       <c r="W79" s="33" t="inlineStr">
         <is>
-          <t>EAO-19</t>
+          <t>EAO-18</t>
         </is>
       </c>
       <c r="X79" s="33" t="inlineStr">
         <is>
-          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
+          <t>No publicly verifiable evidence existed, so the reported risk could not be published. Research across English and Japanese public sources found no credible reports confirming production constraints or operational disruption at Fujita Plating, no decommitments by NHK or OSK, no Force Majeure declaration and no publicly confirmed factory, labour or supply shortage event connected to the situation. No public statements were identified from Fujita Plating, NHK Spring, TDK, MPT or any other involved company. The reported risk appears to have originated in supplier-network communication rather than the public domain. EventWatch publishes on verified public information, so the topic was placed under monitoring with a story created, to be reassessed and published if credible public confirmation appears. Closed on 21-Jul-2026 with no follow-up question from the customer.</t>
         </is>
       </c>
       <c r="Y79" s="33" t="inlineStr">
@@ -12037,7 +12039,7 @@
         </is>
       </c>
       <c r="Z79" s="37" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="80">
@@ -12045,16 +12047,16 @@
         <v>46204</v>
       </c>
       <c r="B80" s="37" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="C80" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D80" s="33" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E80" s="39" t="n">
@@ -12062,27 +12064,27 @@
       </c>
       <c r="F80" s="33" t="inlineStr">
         <is>
-          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
+          <t>RFI – Power Grid Failure Monitoring Strategy</t>
         </is>
       </c>
       <c r="G80" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H80" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I80" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J80" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K80" s="33" t="inlineStr">
@@ -12092,27 +12094,27 @@
       </c>
       <c r="L80" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M80" s="33" t="inlineStr">
         <is>
-          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
+          <t>Published monitoring-scope documentation for power-grid/infrastructure failure events</t>
         </is>
       </c>
       <c r="N80" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O80" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
+          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
         </is>
       </c>
       <c r="Q80" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R80" s="39" t="n">
@@ -12123,31 +12125,31 @@
       </c>
       <c r="U80" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V80" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W80" s="33" t="inlineStr">
         <is>
-          <t>EAO-20</t>
+          <t>EAO-19</t>
         </is>
       </c>
       <c r="X80" s="33" t="inlineStr">
         <is>
-          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
+          <t>Not a miss - an inquiry answered in full. EventWatch monitors power infrastructure continuously across utilities and transmission operators, government and emergency agencies, grid operators, news sources and official outage maps. Reporting is risk-based rather than every outage: mapped supplier sites in the affected region, impact on manufacturing hubs, ports, warehouses and logistics, expected outage duration, and public confirmation of operational disruption, all against regional reporting thresholds.</t>
         </is>
       </c>
       <c r="Y80" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z80" s="37" t="n">
-        <v>46224</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="81">
@@ -12159,12 +12161,12 @@
       </c>
       <c r="C81" s="33" t="inlineStr">
         <is>
-          <t>Wildfire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D81" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="E81" s="39" t="n">
@@ -12172,7 +12174,7 @@
       </c>
       <c r="F81" s="33" t="inlineStr">
         <is>
-          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
+          <t>ASSMANN WSW Components GmbH Bankruptcy Filing – Missed Coverage (Honeywell Tier 1 Supplier)</t>
         </is>
       </c>
       <c r="G81" s="33" t="inlineStr">
@@ -12182,17 +12184,17 @@
       </c>
       <c r="H81" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I81" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J81" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K81" s="33" t="inlineStr">
@@ -12202,12 +12204,12 @@
       </c>
       <c r="L81" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M81" s="33" t="inlineStr">
         <is>
-          <t>Escalation automation for environmental-hazard advisories</t>
+          <t>Tier-1 supplier bankruptcy/insolvency filing source coverage expansion (EU registries)</t>
         </is>
       </c>
       <c r="N81" s="33" t="inlineStr">
@@ -12217,7 +12219,7 @@
       </c>
       <c r="O81" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
+          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
         </is>
       </c>
       <c r="Q81" s="33" t="inlineStr">
@@ -12238,26 +12240,26 @@
       </c>
       <c r="V81" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W81" s="33" t="inlineStr">
         <is>
-          <t>EAO-21</t>
+          <t>EAO-20</t>
         </is>
       </c>
       <c r="X81" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
+          <t>German-language sources reporting the ASSMANN WSW Components insolvency were not captured by the portal; Engineering was asked to investigate the feed gap. RCA reviewed and shared with the customer 20-Jul-2026.</t>
         </is>
       </c>
       <c r="Y81" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z81" s="37" t="n">
-        <v>46230</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="82">
@@ -12265,16 +12267,16 @@
         <v>46204</v>
       </c>
       <c r="B82" s="37" t="n">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="C82" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Wildfire</t>
         </is>
       </c>
       <c r="D82" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E82" s="39" t="n">
@@ -12282,27 +12284,27 @@
       </c>
       <c r="F82" s="33" t="inlineStr">
         <is>
-          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
+          <t>Severe Air Quality Degradation – Canadian Wildfires Missed Alert (Midwest/Northeast US)</t>
         </is>
       </c>
       <c r="G82" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H82" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I82" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J82" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K82" s="33" t="inlineStr">
@@ -12312,27 +12314,27 @@
       </c>
       <c r="L82" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M82" s="33" t="inlineStr">
         <is>
-          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
+          <t>Escalation automation for environmental-hazard advisories</t>
         </is>
       </c>
       <c r="N82" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O82" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
         </is>
       </c>
       <c r="Q82" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R82" s="39" t="n">
@@ -12353,12 +12355,12 @@
       </c>
       <c r="W82" s="33" t="inlineStr">
         <is>
-          <t>EAO-22</t>
+          <t>EAO-21</t>
         </is>
       </c>
       <c r="X82" s="33" t="inlineStr">
         <is>
-          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
+          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y82" s="33" t="inlineStr">
@@ -12367,24 +12369,24 @@
         </is>
       </c>
       <c r="Z82" s="37" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B83" s="37" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="C83" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D83" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E83" s="39" t="n">
@@ -12392,7 +12394,7 @@
       </c>
       <c r="F83" s="33" t="inlineStr">
         <is>
-          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
+          <t>Romania ANCPI Cyberattack – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G83" s="33" t="inlineStr">
@@ -12402,7 +12404,7 @@
       </c>
       <c r="H83" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I83" s="33" t="inlineStr">
@@ -12412,7 +12414,7 @@
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12427,7 +12429,7 @@
       </c>
       <c r="M83" s="33" t="inlineStr">
         <is>
-          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
+          <t>A feedback path from a disputed Not Impactful classification back into the reporting criteria, so a customer telling us a government-services disruption does affect them tunes the model rather than closing as no further context</t>
         </is>
       </c>
       <c r="N83" s="33" t="inlineStr">
@@ -12437,21 +12439,19 @@
       </c>
       <c r="O83" s="33" t="inlineStr">
         <is>
-          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
-        </is>
-      </c>
-      <c r="P83" s="33" t="n"/>
+          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+        </is>
+      </c>
       <c r="Q83" s="33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="R83" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S83" s="39" t="n"/>
+        <v>7</v>
+      </c>
       <c r="T83" s="35" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="U83" s="33" t="inlineStr">
         <is>
@@ -12460,17 +12460,17 @@
       </c>
       <c r="V83" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W83" s="33" t="inlineStr">
         <is>
-          <t>EAO-24</t>
+          <t>EAO-22</t>
         </is>
       </c>
       <c r="X83" s="33" t="inlineStr">
         <is>
-          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
+          <t>Not a miss and not a coverage gap. The EventWatch feed harvesting algorithms did capture reports of the ransomware attack on Romania's National Agency for Cadastre and Public Registry (ANCPI). The AI classification models evaluated it against the current EventWatch reporting criteria and classified it Not Impactful: the attack disrupted ANCPI's land registry services, but the assessment found no evidence of impact on customer industries, suppliers, manufacturing, logistics or transportation, and no reports of production delays or distribution disruption. The disruption was limited to government services and did not warrant a supply chain risk notification. The customer was told this, invited to share any operational impact or dependency on ANCPI services so the models and criteria could be tuned, and the ticket was closed when no further context came back. A written explanation was provided; no RCA was issued or owed.</t>
         </is>
       </c>
       <c r="Y83" s="33" t="inlineStr">
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="Z83" s="37" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="84">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="D84" s="33" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E84" s="39" t="n">
@@ -12504,27 +12504,27 @@
       </c>
       <c r="F84" s="33" t="inlineStr">
         <is>
-          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
+          <t>TOHOKU Chemical Japan Fire – Sub-tier Cashew Dust Supplier</t>
         </is>
       </c>
       <c r="G84" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H84" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I84" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J84" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K84" s="33" t="inlineStr">
@@ -12534,32 +12534,34 @@
       </c>
       <c r="L84" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M84" s="33" t="inlineStr">
         <is>
-          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
+          <t>A customer-reported event with no public source should register as a monitoring story the customer can see, and publish automatically once a credible public source appears, rather than the customer having to ask again</t>
         </is>
       </c>
       <c r="N84" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O84" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
-        </is>
-      </c>
+          <t>EAO-24: No proactive alert was generated for the July 21 fire. Customer requested RCA, ICA, and PCA for the missed coverage. RCA shared.</t>
+        </is>
+      </c>
+      <c r="P84" s="33" t="n"/>
       <c r="Q84" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R84" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S84" s="39" t="n"/>
       <c r="T84" s="35" t="n">
         <v>46235</v>
       </c>
@@ -12570,25 +12572,27 @@
       </c>
       <c r="V84" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W84" s="33" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-24</t>
         </is>
       </c>
       <c r="X84" s="33" t="inlineStr">
         <is>
-          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
+          <t>No public source existed to report from. An extensive search across English and Japanese public sources found no credible news articles or official announcements confirming a fire at TOHOKU Chemical Japan on 21-Jul-2026, and TOHOKU Chemical's own website and news releases do not reference a fire or related disruption in that period. The incident appears to have reached the customer through non-public channels such as direct supplier communication. EventWatch reports only on publicly available and verifiable information, so a monitoring story was created and public sources in both languages continue to be scanned; the alert publishes if credible public information appears. The customer was asked to share any public source they hold. A written explanation was provided; no RCA was issued or owed.</t>
         </is>
       </c>
       <c r="Y84" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z84" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z84" s="37" t="n">
+        <v>46239</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="35" t="n">
@@ -12599,7 +12603,7 @@
       </c>
       <c r="C85" s="33" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D85" s="33" t="inlineStr">
@@ -12612,7 +12616,7 @@
       </c>
       <c r="F85" s="33" t="inlineStr">
         <is>
-          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
+          <t>Fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China</t>
         </is>
       </c>
       <c r="G85" s="33" t="inlineStr">
@@ -12657,7 +12661,7 @@
       </c>
       <c r="O85" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
         </is>
       </c>
       <c r="Q85" s="33" t="inlineStr">
@@ -12703,16 +12707,16 @@
         <v>46235</v>
       </c>
       <c r="B86" s="37" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Tornado</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
         <is>
-          <t>Hitachi</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E86" s="39" t="n">
@@ -12720,7 +12724,7 @@
       </c>
       <c r="F86" s="33" t="inlineStr">
         <is>
-          <t>Disruption Agent Returns Only Tier 1 Suppliers for Kumamoto Earthquake Query (Hitachi)</t>
+          <t>Chicago Heights, Illinois Tornado – Trialco Impact Not Identified</t>
         </is>
       </c>
       <c r="G86" s="33" t="inlineStr">
@@ -12730,7 +12734,7 @@
       </c>
       <c r="H86" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I86" s="33" t="inlineStr">
@@ -12740,7 +12744,7 @@
       </c>
       <c r="J86" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K86" s="33" t="inlineStr">
@@ -12750,57 +12754,53 @@
       </c>
       <c r="L86" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M86" s="33" t="inlineStr">
         <is>
-          <t>Disruption Agent response completeness checks so a prompt asking for multiple supplier tiers returns all of them in one response</t>
+          <t>Cluster-assignment validation so an article grouped into the wrong cluster is caught before analyst review</t>
         </is>
       </c>
       <c r="N86" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O86" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
-        </is>
-      </c>
-      <c r="P86" s="33" t="n"/>
+          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+        </is>
+      </c>
       <c r="Q86" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R86" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S86" s="39" t="n"/>
-      <c r="T86" s="35" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
+      <c r="T86" s="35" t="n">
+        <v>46235</v>
       </c>
       <c r="U86" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V86" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W86" s="33" t="inlineStr">
         <is>
-          <t>CAN-3433</t>
+          <t>EAO-25</t>
         </is>
       </c>
       <c r="X86" s="33" t="inlineStr">
         <is>
-          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
+          <t>Captured, but grouped into the wrong event cluster, so the analyst reviewing that cluster marked it Not Impactful and it never reached WarRoom consideration. The miss is a clustering defect rather than a source-coverage gap or an analyst-judgement failure: the article was in the system and the grouping put it in front of the wrong decision. The cluster logic has since been enhanced.</t>
         </is>
       </c>
       <c r="Y86" s="33" t="inlineStr">
@@ -12815,16 +12815,16 @@
         <v>46235</v>
       </c>
       <c r="B87" s="37" t="n">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="C87" s="33" t="inlineStr">
         <is>
-          <t>Regulatory Change</t>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="D87" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Hitachi</t>
         </is>
       </c>
       <c r="E87" s="39" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="F87" s="33" t="inlineStr">
         <is>
-          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
+          <t>Disruption Agent Returns Only Tier 1 Suppliers for Kumamoto Earthquake Query (Hitachi)</t>
         </is>
       </c>
       <c r="G87" s="33" t="inlineStr">
@@ -12842,17 +12842,17 @@
       </c>
       <c r="H87" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I87" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J87" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K87" s="33" t="inlineStr">
@@ -12862,81 +12862,81 @@
       </c>
       <c r="L87" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M87" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Disruption Agent response completeness checks so a prompt asking for multiple supplier tiers returns all of them in one response</t>
         </is>
       </c>
       <c r="N87" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
+          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
         </is>
       </c>
       <c r="P87" s="33" t="n"/>
       <c r="Q87" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R87" s="39" t="n">
         <v>8</v>
       </c>
       <c r="S87" s="39" t="n"/>
-      <c r="T87" s="35" t="n">
-        <v>46235</v>
+      <c r="T87" s="35" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
       </c>
       <c r="U87" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V87" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W87" s="33" t="inlineStr">
         <is>
-          <t>EAO-23</t>
+          <t>CAN-3433</t>
         </is>
       </c>
       <c r="X87" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
+          <t>A data hygiene defect on the EventWatch side: leading and trailing spaces in the values the Disruption Agent matched on. They were stripped under TENAR-45367 and the fix was verified on stage on 07-Aug-2026.</t>
         </is>
       </c>
       <c r="Y87" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z87" s="37" t="n">
-        <v>46252</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z87" s="37" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="B88" s="37" t="n">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Regulatory Change</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E88" s="39" t="n">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="F88" s="33" t="inlineStr">
         <is>
-          <t>Eberhard AG Insolvency – No EventWatch Alert (Infineon)</t>
+          <t>China MOFCOM Announcement No. 30 of 2026 (Export Control Watchlist)</t>
         </is>
       </c>
       <c r="G88" s="33" t="inlineStr">
@@ -12954,17 +12954,17 @@
       </c>
       <c r="H88" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I88" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J88" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K88" s="33" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="M88" s="33" t="inlineStr">
         <is>
-          <t>Add the bankruptcy and insolvency sources covering this supplier's region to the vendor network, so a filing at a mapped supplier is captured when it is published rather than when the customer raises it</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N88" s="33" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="O88" s="33" t="inlineStr">
         <is>
-          <t>Raised by Infineon at the weekly sync: Eberhard AG, a critical supplier, reportedly entered bankruptcy proceedings and no EventWatch alert or notification was received. The customer cited it as a case where they expected early-warning signals and bankruptcy intelligence through the Resilinc platform. Product Management reported that the sources carrying the filing are not part of the vendor network and that the vendor has been asked to include them; recorded as a source miss at the portal. There is no EAO key for this record: it was raised by email to the team rather than by opening a Jira ticket.</t>
+          <t>EAO-23: News was captured but initially classified as Not Impactful by AI. Human-in-the-loop review did not escalate the event. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P88" s="33" t="n"/>
@@ -13002,10 +13002,8 @@
         <v>8</v>
       </c>
       <c r="S88" s="39" t="n"/>
-      <c r="T88" s="35" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
+      <c r="T88" s="35" t="n">
+        <v>46235</v>
       </c>
       <c r="U88" s="33" t="inlineStr">
         <is>
@@ -13014,37 +13012,43 @@
       </c>
       <c r="V88" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
-        </is>
-      </c>
-      <c r="W88" s="33" t="n"/>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W88" s="33" t="inlineStr">
+        <is>
+          <t>EAO-23</t>
+        </is>
+      </c>
       <c r="X88" s="33" t="inlineStr">
         <is>
-          <t>The sources reporting the Eberhard AG insolvency are not part of the vendor network; the vendor has been asked to include them. Recorded by Product Management as a source miss at the portal.</t>
+          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y88" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z88" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z88" s="37" t="n">
+        <v>46252</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="B89" s="37" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="C89" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D89" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="E89" s="39" t="n">
@@ -13052,7 +13056,7 @@
       </c>
       <c r="F89" s="33" t="inlineStr">
         <is>
-          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
+          <t>Eberhard AG Insolvency – No EventWatch Alert (Infineon)</t>
         </is>
       </c>
       <c r="G89" s="33" t="inlineStr">
@@ -13062,17 +13066,17 @@
       </c>
       <c r="H89" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I89" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J89" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K89" s="33" t="inlineStr">
@@ -13087,7 +13091,7 @@
       </c>
       <c r="M89" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Trigger Automation</t>
+          <t>Add the bankruptcy and insolvency sources covering this supplier's region to the vendor network, so a filing at a mapped supplier is captured when it is published rather than when the customer raises it</t>
         </is>
       </c>
       <c r="N89" s="33" t="inlineStr">
@@ -13097,7 +13101,7 @@
       </c>
       <c r="O89" s="33" t="inlineStr">
         <is>
-          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+          <t>Raised by Infineon at the weekly sync: Eberhard AG, a critical supplier, reportedly entered bankruptcy proceedings and no EventWatch alert or notification was received. The customer cited it as a case where they expected early-warning signals and bankruptcy intelligence through the Resilinc platform. Product Management reported that the sources carrying the filing are not part of the vendor network and that the vendor has been asked to include them; recorded as a source miss at the portal. There is no EAO key for this record: it was raised by email to the team rather than by opening a Jira ticket.</t>
         </is>
       </c>
       <c r="P89" s="33" t="n"/>
@@ -13110,8 +13114,10 @@
         <v>8</v>
       </c>
       <c r="S89" s="39" t="n"/>
-      <c r="T89" s="35" t="n">
-        <v>46235</v>
+      <c r="T89" s="35" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
       </c>
       <c r="U89" s="33" t="inlineStr">
         <is>
@@ -13120,27 +13126,21 @@
       </c>
       <c r="V89" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W89" s="33" t="inlineStr">
-        <is>
-          <t>EAO-27</t>
-        </is>
-      </c>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W89" s="33" t="n"/>
       <c r="X89" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>The sources reporting the Eberhard AG insolvency are not part of the vendor network; the vendor has been asked to include them. Recorded by Product Management as a source miss at the portal.</t>
         </is>
       </c>
       <c r="Y89" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z89" s="37" t="n">
-        <v>46259</v>
-      </c>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z89" s="37" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="35" t="n">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E90" s="39" t="n">
@@ -13164,27 +13164,27 @@
       </c>
       <c r="F90" s="33" t="inlineStr">
         <is>
-          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
+          <t>Ceuta Border Security &amp; Humanitarian Crisis</t>
         </is>
       </c>
       <c r="G90" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H90" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I90" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J90" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K90" s="33" t="inlineStr">
@@ -13194,53 +13194,55 @@
       </c>
       <c r="L90" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M90" s="33" t="inlineStr">
         <is>
-          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
+          <t>WarRoom Trigger Automation</t>
         </is>
       </c>
       <c r="N90" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O90" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
-        </is>
-      </c>
+          <t>EAO-27: Customer reported a missed EventWatch alert and requested an update. RCA shared following review of the event.</t>
+        </is>
+      </c>
+      <c r="P90" s="33" t="n"/>
       <c r="Q90" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R90" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S90" s="39" t="n"/>
       <c r="T90" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U90" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V90" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W90" s="33" t="inlineStr">
         <is>
-          <t>EAO-28</t>
+          <t>EAO-27</t>
         </is>
       </c>
       <c r="X90" s="33" t="inlineStr">
         <is>
-          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y90" s="33" t="inlineStr">
@@ -13257,16 +13259,16 @@
         <v>46235</v>
       </c>
       <c r="B91" s="37" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="C91" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D91" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E91" s="39" t="n">
@@ -13274,27 +13276,27 @@
       </c>
       <c r="F91" s="33" t="inlineStr">
         <is>
-          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
+          <t>Kandla Port Cargo Congestion – Supplier Impact Notification Clarification (Eaton)</t>
         </is>
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H91" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I91" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13304,60 +13306,58 @@
       </c>
       <c r="L91" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M91" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Impact-confirmation notification criteria documentation for port/logistics bulletins</t>
         </is>
       </c>
       <c r="N91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O91" s="33" t="inlineStr">
         <is>
-          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
-        </is>
-      </c>
-      <c r="P91" s="33" t="n"/>
+          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+        </is>
+      </c>
       <c r="Q91" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R91" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="S91" s="39" t="n"/>
       <c r="T91" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U91" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V91" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W91" s="33" t="inlineStr">
         <is>
-          <t>EAO-26</t>
+          <t>EAO-28</t>
         </is>
       </c>
       <c r="X91" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>No RCA document issued - the team shares one only where there was a miss. Clarification given instead: EventWatch published the Kandla congestion event on reports of clearance delays up to 40 days and container shortages. The source article highlighted rice exports, but nothing indicated the congestion was confined to rice cargo, so mapped supplier sites within the impact area were sent Supplier Impact Confirmation requests as proactive validation. The outreach was not a statement that those suppliers were already impacted.</t>
         </is>
       </c>
       <c r="Y91" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z91" s="37" t="n">
@@ -13369,11 +13369,11 @@
         <v>46235</v>
       </c>
       <c r="B92" s="37" t="n">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>Hurricane/Typhoon</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
@@ -13386,27 +13386,27 @@
       </c>
       <c r="F92" s="33" t="inlineStr">
         <is>
-          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
+          <t>Sasol Polyethylene Plant Fire / Shutdown</t>
         </is>
       </c>
       <c r="G92" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H92" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I92" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J92" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K92" s="33" t="inlineStr">
@@ -13416,28 +13416,28 @@
       </c>
       <c r="L92" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M92" s="33" t="inlineStr">
         <is>
-          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N92" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O92" s="33" t="inlineStr">
         <is>
-          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
+          <t>EAO-26: Customer reported a missed EventWatch alert for the Sasol polyethylene plant fire and shutdown. Investigation and RCA were requested; RCA shared.</t>
         </is>
       </c>
       <c r="P92" s="33" t="n"/>
       <c r="Q92" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R92" s="39" t="n">
@@ -13449,31 +13449,31 @@
       </c>
       <c r="U92" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V92" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W92" s="33" t="inlineStr">
         <is>
-          <t>EAO-29</t>
+          <t>EAO-26</t>
         </is>
       </c>
       <c r="X92" s="33" t="inlineStr">
         <is>
-          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
+          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
         </is>
       </c>
       <c r="Y92" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z92" s="37" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="93">
@@ -13481,44 +13481,44 @@
         <v>46235</v>
       </c>
       <c r="B93" s="37" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="C93" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Hurricane/Typhoon</t>
         </is>
       </c>
       <c r="D93" s="33" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E93" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="33" t="inlineStr">
         <is>
-          <t>World Trade Bridge Closed in Laredo, Texas</t>
+          <t>Typhoon Dolphin Bulletins Distributed Across Two WarRooms</t>
         </is>
       </c>
       <c r="G93" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H93" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I93" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J93" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -13528,28 +13528,28 @@
       </c>
       <c r="L93" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M93" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Make the shared update sequence legible on the bulletin itself, so a jump from Update 2 to Update 5 in one country's WarRoom shows which storm-lifecycle updates ran under the other WarRooms instead of reading as missing bulletins</t>
         </is>
       </c>
       <c r="N93" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O93" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
+          <t>EAO-29: Bulletins were distributed across two WarRooms, resulting in gaps in the update sequence. Customer requested RCA; RCA shared.</t>
         </is>
       </c>
       <c r="P93" s="33" t="n"/>
       <c r="Q93" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R93" s="39" t="n">
@@ -13561,30 +13561,32 @@
       </c>
       <c r="U93" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V93" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W93" s="33" t="inlineStr">
         <is>
-          <t>EAO-25</t>
+          <t>EAO-29</t>
         </is>
       </c>
       <c r="X93" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Not duplicate WarRooms and not a defect: a question about a deliberate internal convention. Country-specific WarRooms for one storm share a single update sequence so the chronology of the underlying event stays end to end. A storm evolves over days, changes direction and intensity and crosses borders, and a shared sequence lets a customer exposed in several geographies see where each development sits in the overall lifecycle. It also signals maturity of the threat: restarting the numbering for each new country would make an established, highly disruptive typhoon appear as an Initial Bulletin. It further preserves cross-country traceability, since independent numbering would produce several Update 1s and Update 2s for the same storm. The WarRoom says where a development is relevant; the update number says where it falls in the storm's lifecycle. So when the China WarRoom runs from Update 2 to Update 5, Updates 3 and 4 are not missing - they were intervening Typhoon Dolphin developments relevant to Japan and published under the Japan WarRoom, the same principle covering Update 7 for Taiwan. The explanation was shared with the customer, who was invited to give further feedback.</t>
         </is>
       </c>
       <c r="Y93" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z93" s="37" t="n"/>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z93" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="35" t="n">
@@ -13595,7 +13597,7 @@
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D94" s="33" t="inlineStr">
@@ -13608,7 +13610,7 @@
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
+          <t>World Trade Bridge Closed in Laredo, Texas</t>
         </is>
       </c>
       <c r="G94" s="33" t="inlineStr">
@@ -13628,7 +13630,7 @@
       </c>
       <c r="J94" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K94" s="33" t="inlineStr">
@@ -13638,7 +13640,7 @@
       </c>
       <c r="L94" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M94" s="33" t="inlineStr">
@@ -13653,7 +13655,7 @@
       </c>
       <c r="O94" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was missed due to a keyword gap. Keyword was added and the article is now being captured.</t>
         </is>
       </c>
       <c r="P94" s="33" t="n"/>
@@ -13701,7 +13703,7 @@
         <v>46235</v>
       </c>
       <c r="B95" s="37" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="C95" s="33" t="inlineStr">
         <is>
@@ -13718,7 +13720,7 @@
       </c>
       <c r="F95" s="33" t="inlineStr">
         <is>
-          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
+          <t>Fire at FXI de Cuautitlán, S.A. de C.V.</t>
         </is>
       </c>
       <c r="G95" s="33" t="inlineStr">
@@ -13733,12 +13735,12 @@
       </c>
       <c r="I95" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J95" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K95" s="33" t="inlineStr">
@@ -13753,7 +13755,7 @@
       </c>
       <c r="M95" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N95" s="33" t="inlineStr">
@@ -13763,7 +13765,7 @@
       </c>
       <c r="O95" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P95" s="33" t="n"/>
@@ -13786,7 +13788,7 @@
       </c>
       <c r="V95" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W95" s="33" t="inlineStr">
@@ -13801,7 +13803,7 @@
       </c>
       <c r="Y95" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z95" s="37" t="n"/>
@@ -13815,20 +13817,20 @@
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>The American National Red Cross</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="E96" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="33" t="inlineStr">
         <is>
-          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
+          <t>Fire at Nemak Factory in Monterrey, Mexico</t>
         </is>
       </c>
       <c r="G96" s="33" t="inlineStr">
@@ -13838,17 +13840,17 @@
       </c>
       <c r="H96" s="33" t="inlineStr">
         <is>
-          <t>WarRoom not visible in customer profile</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I96" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J96" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K96" s="33" t="inlineStr">
@@ -13863,17 +13865,17 @@
       </c>
       <c r="M96" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N96" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O96" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
+          <t>EAO-25: News processing captured the article and attached it to an updated factory-fire cluster. The event was later marked Not Impactful by the analyst. RCA shared based on the investigation trail.</t>
         </is>
       </c>
       <c r="P96" s="33" t="n"/>
@@ -13896,15 +13898,19 @@
       </c>
       <c r="V96" s="33" t="inlineStr">
         <is>
-          <t>Notification Visibility Monitoring</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W96" s="33" t="inlineStr">
         <is>
-          <t>TS-22695</t>
-        </is>
-      </c>
-      <c r="X96" s="33" t="n"/>
+          <t>EAO-25</t>
+        </is>
+      </c>
+      <c r="X96" s="33" t="inlineStr">
+        <is>
+          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+        </is>
+      </c>
       <c r="Y96" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -13917,7 +13923,7 @@
         <v>46235</v>
       </c>
       <c r="B97" s="37" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C97" s="33" t="inlineStr">
         <is>
@@ -13926,7 +13932,7 @@
       </c>
       <c r="D97" s="33" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>The American National Red Cross</t>
         </is>
       </c>
       <c r="E97" s="39" t="n">
@@ -13934,7 +13940,7 @@
       </c>
       <c r="F97" s="33" t="inlineStr">
         <is>
-          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
+          <t>Uber Freight Investigates Reported Cyberattack After Hackers Claim Data Breach</t>
         </is>
       </c>
       <c r="G97" s="33" t="inlineStr">
@@ -13944,17 +13950,17 @@
       </c>
       <c r="H97" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>WarRoom not visible in customer profile</t>
         </is>
       </c>
       <c r="I97" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J97" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="K97" s="33" t="inlineStr">
@@ -13969,17 +13975,17 @@
       </c>
       <c r="M97" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="N97" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O97" s="33" t="inlineStr">
         <is>
-          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
         </is>
       </c>
       <c r="P97" s="33" t="n"/>
@@ -14002,27 +14008,21 @@
       </c>
       <c r="V97" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W97" s="33" t="inlineStr">
         <is>
-          <t>EAO-31</t>
-        </is>
-      </c>
-      <c r="X97" s="33" t="inlineStr">
-        <is>
-          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
-        </is>
-      </c>
+          <t>TS-22695</t>
+        </is>
+      </c>
+      <c r="X97" s="33" t="n"/>
       <c r="Y97" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
-        </is>
-      </c>
-      <c r="Z97" s="37" t="n">
-        <v>46272</v>
-      </c>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z97" s="37" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="35" t="n">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="E98" s="39" t="n">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="F98" s="33" t="inlineStr">
         <is>
-          <t>Baxter International Reports a Cybersecurity Incident</t>
+          <t>Gindre India Data Breach – EventWatch Alert/WarRoom Missing</t>
         </is>
       </c>
       <c r="G98" s="33" t="inlineStr">
@@ -14061,12 +14061,12 @@
       </c>
       <c r="I98" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J98" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K98" s="33" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="M98" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="N98" s="33" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="O98" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>EAO-31: No corresponding EventWatch event or WarRoom was found for the reported data breach. Source coverage review completed and RCA shared.</t>
         </is>
       </c>
       <c r="P98" s="33" t="n"/>
@@ -14114,16 +14114,27 @@
       </c>
       <c r="V98" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="X98" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W98" s="33" t="inlineStr">
+        <is>
+          <t>EAO-31</t>
+        </is>
+      </c>
+      <c r="X98" s="33" t="inlineStr">
+        <is>
+          <t>Feeds reporting the Qilin ransomware breach at Gindre India were not captured on the EventWatch portal; Engineering investigation requested 31-Aug-2026. RCA reviewed and shared with the customer 03-Sep-2026.</t>
+        </is>
+      </c>
       <c r="Y98" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z98" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z98" s="37" t="n">
+        <v>46272</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="35" t="n">
@@ -14147,7 +14158,7 @@
       </c>
       <c r="F99" s="33" t="inlineStr">
         <is>
-          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
+          <t>Baxter International Reports a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G99" s="33" t="inlineStr">
@@ -14182,7 +14193,7 @@
       </c>
       <c r="M99" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Duplicate Decision Validation</t>
+          <t>Not Impactful Decision Validation</t>
         </is>
       </c>
       <c r="N99" s="33" t="inlineStr">
@@ -14192,7 +14203,7 @@
       </c>
       <c r="O99" s="33" t="inlineStr">
         <is>
-          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+          <t>Customer reported the missed Baxter ransomware incident. EventWatch captured the report on August 14, but human review incorrectly marked it Not Impactful; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
         </is>
       </c>
       <c r="P99" s="33" t="n"/>
@@ -14235,12 +14246,12 @@
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>Liberty Blume</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="E100" s="39" t="n">
@@ -14248,27 +14259,27 @@
       </c>
       <c r="F100" s="33" t="inlineStr">
         <is>
-          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
+          <t>McKesson Corporation Confirms Data Breach Following a Cybersecurity Incident</t>
         </is>
       </c>
       <c r="G100" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H100" s="33" t="inlineStr">
         <is>
-          <t>Intelligence/Advisory Request</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I100" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J100" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K100" s="33" t="inlineStr">
@@ -14278,55 +14289,48 @@
       </c>
       <c r="L100" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M100" s="33" t="inlineStr">
         <is>
-          <t>Counterfeit/grey-market component intelligence briefing capability</t>
+          <t>Entity &amp; Duplicate Decision Validation</t>
         </is>
       </c>
       <c r="N100" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O100" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
-        </is>
-      </c>
+          <t>Customer reported the missed McKesson data-breach incident. EventWatch captured the report on August 28, but human review assumed it was already covered; the event was re-evaluated, a WarRoom was created, and an NC was raised.</t>
+        </is>
+      </c>
+      <c r="P100" s="33" t="n"/>
       <c r="Q100" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R100" s="39" t="n">
         <v>8</v>
       </c>
+      <c r="S100" s="39" t="n"/>
       <c r="T100" s="35" t="n">
         <v>46235</v>
       </c>
       <c r="U100" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V100" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
-        </is>
-      </c>
-      <c r="W100" s="33" t="inlineStr">
-        <is>
-          <t>EAO-32</t>
-        </is>
-      </c>
-      <c r="X100" s="33" t="inlineStr">
-        <is>
-          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
-        </is>
-      </c>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="X100" s="33" t="n"/>
       <c r="Y100" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14336,19 +14340,19 @@
     </row>
     <row r="101">
       <c r="A101" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B101" s="37" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="C101" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical</t>
+          <t>Counterfeit</t>
         </is>
       </c>
       <c r="D101" s="33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Liberty Blume</t>
         </is>
       </c>
       <c r="E101" s="39" t="n">
@@ -14356,27 +14360,27 @@
       </c>
       <c r="F101" s="33" t="inlineStr">
         <is>
-          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
+          <t>Ciena 400G Optics Counterfeit Risk Intelligence Request (Liberty Blume)</t>
         </is>
       </c>
       <c r="G101" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H101" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Intelligence/Advisory Request</t>
         </is>
       </c>
       <c r="I101" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J101" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K101" s="33" t="inlineStr">
@@ -14386,53 +14390,53 @@
       </c>
       <c r="L101" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M101" s="33" t="inlineStr">
         <is>
-          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
+          <t>Counterfeit/grey-market component intelligence briefing capability</t>
         </is>
       </c>
       <c r="N101" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O101" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
+          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
         </is>
       </c>
       <c r="Q101" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R101" s="39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T101" s="35" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="U101" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V101" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Other Control Automation</t>
         </is>
       </c>
       <c r="W101" s="33" t="inlineStr">
         <is>
-          <t>EAO-33</t>
+          <t>EAO-32</t>
         </is>
       </c>
       <c r="X101" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
+          <t>No RCA: an intelligence request, not a service miss. Liberty Blume asked for further detail on Ciena 400G optics counterfeit risk. EventWatch confirmed to the customer that no such reporting is available in the public domain and that the topic remains under active monitoring; the customer accepted that position, so the item is closed rather than open.</t>
         </is>
       </c>
       <c r="Y101" s="33" t="inlineStr">
@@ -14447,16 +14451,16 @@
         <v>46266</v>
       </c>
       <c r="B102" s="37" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>Protest/Riot</t>
+          <t>Geopolitical</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E102" s="39" t="n">
@@ -14464,7 +14468,7 @@
       </c>
       <c r="F102" s="33" t="inlineStr">
         <is>
-          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
+          <t>Taiwan Strait Conflict Risk Assessment – Missed EventWatch Notification</t>
         </is>
       </c>
       <c r="G102" s="33" t="inlineStr">
@@ -14499,7 +14503,7 @@
       </c>
       <c r="M102" s="33" t="inlineStr">
         <is>
-          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
+          <t>Geopolitical conflict risk-assessment scenario monitoring and escalation</t>
         </is>
       </c>
       <c r="N102" s="33" t="inlineStr">
@@ -14509,7 +14513,7 @@
       </c>
       <c r="O102" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q102" s="33" t="inlineStr">
@@ -14535,7 +14539,7 @@
       </c>
       <c r="W102" s="33" t="inlineStr">
         <is>
-          <t>EAO-34</t>
+          <t>EAO-33</t>
         </is>
       </c>
       <c r="X102" s="33" t="inlineStr">
@@ -14555,24 +14559,24 @@
         <v>46266</v>
       </c>
       <c r="B103" s="37" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="C103" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Protest/Riot</t>
         </is>
       </c>
       <c r="D103" s="33" t="inlineStr">
         <is>
-          <t>Eaton/Ford</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E103" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" s="33" t="inlineStr">
         <is>
-          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
+          <t>Western Balkans Truck Driver/EU Border Blockade – August 31 Update Missed Alert (Ford)</t>
         </is>
       </c>
       <c r="G103" s="33" t="inlineStr">
@@ -14582,17 +14586,17 @@
       </c>
       <c r="H103" s="33" t="inlineStr">
         <is>
-          <t>Geographic Misclassification</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I103" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J103" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K103" s="33" t="inlineStr">
@@ -14607,7 +14611,7 @@
       </c>
       <c r="M103" s="33" t="inlineStr">
         <is>
-          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
+          <t>Recurring/evolving-event WarRoom update monitoring and re-escalation detection</t>
         </is>
       </c>
       <c r="N103" s="33" t="inlineStr">
@@ -14617,23 +14621,19 @@
       </c>
       <c r="O103" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
-        </is>
-      </c>
-      <c r="P103" s="33" t="n"/>
+          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+        </is>
+      </c>
       <c r="Q103" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R103" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S103" s="39" t="n"/>
-      <c r="T103" s="35" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="T103" s="35" t="n">
+        <v>46266</v>
       </c>
       <c r="U103" s="33" t="inlineStr">
         <is>
@@ -14642,22 +14642,22 @@
       </c>
       <c r="V103" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W103" s="33" t="inlineStr">
         <is>
-          <t>EAO-35/EAO-36</t>
+          <t>EAO-34</t>
         </is>
       </c>
       <c r="X103" s="33" t="inlineStr">
         <is>
-          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+          <t>Human error. The analyst marked the event Not Impactful while clearing stories at pace, so it was never escalated for WarRoom consideration. The event was captured and available for review; ingestion, source coverage and mapping did not contribute.</t>
         </is>
       </c>
       <c r="Y103" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z103" s="37" t="n"/>
@@ -14667,24 +14667,24 @@
         <v>46266</v>
       </c>
       <c r="B104" s="37" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Eaton/Ford</t>
         </is>
       </c>
       <c r="E104" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" s="33" t="inlineStr">
         <is>
-          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
+          <t>Punjab Region Risk Event – Supplier Sites Outside the Impact Area Mapped for Impact Confirmation (Eaton/Ford)</t>
         </is>
       </c>
       <c r="G104" s="33" t="inlineStr">
@@ -14694,17 +14694,17 @@
       </c>
       <c r="H104" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Geographic Misclassification</t>
         </is>
       </c>
       <c r="I104" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="M104" s="33" t="inlineStr">
         <is>
-          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
+          <t>Geographic validation of supplier site geocodes against the event impact polygon before impact-confirmation requests are issued, so sites outside the affected region cannot be attached to an event</t>
         </is>
       </c>
       <c r="N104" s="33" t="inlineStr">
@@ -14729,17 +14729,13 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
-        </is>
-      </c>
-      <c r="P104" s="33" t="inlineStr">
-        <is>
-          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
-        </is>
-      </c>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
+        </is>
+      </c>
+      <c r="P104" s="33" t="n"/>
       <c r="Q104" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R104" s="39" t="n">
@@ -14758,22 +14754,22 @@
       </c>
       <c r="V104" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>AI-Assisted Geofencing</t>
         </is>
       </c>
       <c r="W104" s="33" t="inlineStr">
         <is>
-          <t>EAO-37</t>
+          <t>EAO-35/EAO-36</t>
         </is>
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z104" s="37" t="n"/>
@@ -14787,12 +14783,12 @@
       </c>
       <c r="C105" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D105" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="E105" s="39" t="n">
@@ -14800,27 +14796,27 @@
       </c>
       <c r="F105" s="33" t="inlineStr">
         <is>
-          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
+          <t>Record Heavy Rain in Yokkaichi City, Japan – No EventWatch Notification (Sandisk)</t>
         </is>
       </c>
       <c r="G105" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H105" s="33" t="inlineStr">
         <is>
-          <t>Severity / consolidation handling concern</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I105" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J105" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K105" s="33" t="inlineStr">
@@ -14830,28 +14826,32 @@
       </c>
       <c r="L105" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M105" s="33" t="inlineStr">
         <is>
-          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
+          <t>Timeliness monitoring that flags a region already producing captured stories where a related event has not been published within the reporting window</t>
         </is>
       </c>
       <c r="N105" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
-        </is>
-      </c>
-      <c r="P105" s="33" t="n"/>
+          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
+        </is>
+      </c>
+      <c r="P105" s="33" t="inlineStr">
+        <is>
+          <t>~1 day (customer query 08-Sep-2026 -&gt; EventWatch report 09-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q105" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R105" s="39" t="n">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="U105" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V105" s="33" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="W105" s="33" t="inlineStr">
         <is>
-          <t>EAO-38</t>
+          <t>EAO-37</t>
         </is>
       </c>
       <c r="X105" s="33" t="inlineStr">
         <is>
-          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
+          <t>Not a coverage gap and not a Not Impactful call. The news was in the public domain and other Japan flooding stories were being captured on the analyst portal at the time; this one was delayed in reporting and only published on 09-Sep-2026, after the customer had raised the query on 08-Sep. Sandisk's complaint is that it never reached the notified section of their portal, which is the downstream effect of the reporting delay rather than a separate visibility defect.</t>
         </is>
       </c>
       <c r="Y105" s="33" t="inlineStr">
@@ -14895,16 +14895,16 @@
         <v>46266</v>
       </c>
       <c r="B106" s="37" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>Supply Shortage</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E106" s="39" t="n">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="F106" s="33" t="inlineStr">
         <is>
-          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
+          <t>Vertiv Acquires UtilityInnovation Group – Supplier Notification and Medium Risk Classification Queried (Eaton)</t>
         </is>
       </c>
       <c r="G106" s="33" t="inlineStr">
@@ -14922,17 +14922,17 @@
       </c>
       <c r="H106" s="33" t="inlineStr">
         <is>
-          <t>Coverage Verification Request</t>
+          <t>Severity / consolidation handling concern</t>
         </is>
       </c>
       <c r="I106" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J106" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K106" s="33" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="M106" s="33" t="inlineStr">
         <is>
-          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
+          <t>Automated enforcement of the M&amp;A notification threshold so acquiring-side suppliers are excluded from impact-confirmation requests, plus a documented basis for the risk classification</t>
         </is>
       </c>
       <c r="N106" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O106" s="33" t="inlineStr">
         <is>
-          <t>EAO-39: Belden asked why they received no EventWatch notification and saw no related news for TSMC's 28nm production capacity reduction. The query ran on through two follow-ups, both part of the same contact rather than separate records. First, on 18-Sep-2026 the customer cited a 22-Jun-2026 report that TSMC denied phasing out 28nm and asked how EventWatch separates real reporting from fake, what criteria establish that a notification is not fake, and whether the 28nm reduction is real; a written assessment was issued covering the source hierarchy, the five evidence grades and the TSMC timeline. Second, on 22-Sep-2026 the customer corrected their own position and confirmed TSMC is not mapped in their BOM - they source the wafer via Broadcom, and the Taiwan Semiconductor entity they had mapped covers resistors and MOSFETs - so no customer notification was owed. Reclassified on review from Complaint to Inquiry with Missed_Flag No, and logged under Source Coverage.</t>
+          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
         </is>
       </c>
       <c r="P106" s="33" t="n"/>
@@ -14977,27 +14977,27 @@
       </c>
       <c r="U106" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V106" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W106" s="33" t="inlineStr">
         <is>
-          <t>EAO-39</t>
+          <t>EAO-38</t>
         </is>
       </c>
       <c r="X106" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
+          <t>Not a defect, and the rule has since changed. The Supplier Impact Confirmation was issued in line with one of the customers mapped to that supplier, whose settings called for it, so the request was correct for that account even though Eaton reads the M&amp;A threshold as excluding an acquiring supplier. Under the new process supplier impact is sent to all mapped customers regardless of which side of the transaction the supplier is on, and Eaton was given that explanation together with the basis for the risk grade.</t>
         </is>
       </c>
       <c r="Y106" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z106" s="37" t="n"/>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="F107" s="33" t="inlineStr">
         <is>
-          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
+          <t>TSMC 28nm Production Capacity Reduction – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G107" s="33" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="H107" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Coverage Verification Request</t>
         </is>
       </c>
       <c r="I107" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J107" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Alerting Gap</t>
         </is>
       </c>
       <c r="K107" s="33" t="inlineStr">
@@ -15059,7 +15059,7 @@
       </c>
       <c r="M107" s="33" t="inlineStr">
         <is>
-          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
+          <t>Reconciliation between what the vendor feeds deliver and what actually reaches the analyst portal, so a harvested item that never surfaces is caught rather than found by a customer; plus an evidence grade carried on the event itself - confirmed, credible but unconfirmed, disputed, unsubstantiated, demonstrably false - so a customer can see the basis of a report without asking, and name-collision detection on the mapping surface so a near-identical supplier name is flagged at mapping time</t>
         </is>
       </c>
       <c r="N107" s="33" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="O107" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
+          <t>The relevant TSMC article was captured by the feed-harvesting flow but did not appear on the analyst portal for review. The case was confirmed and closed as an Alerting Gap. Alerting Gap Type: Feed/Application-to-Analyst Handoff Gap. Evidence Status: Confirmed and Closed.</t>
         </is>
       </c>
       <c r="P107" s="33" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="V107" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Notification Visibility Monitoring</t>
         </is>
       </c>
       <c r="W107" s="33" t="inlineStr">
@@ -15104,12 +15104,12 @@
       </c>
       <c r="X107" s="33" t="inlineStr">
         <is>
-          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
+          <t>Not a source-coverage gap in the ingestion sense. The news was captured by the vendor sources but never surfaced on the analyst portal, so it was never available for review and no coverage was created; the failure sits between ingestion and the analyst queue. The customer's exposure claim did not hold either: Belden confirmed on 22-Sep-2026 that TSMC is not mapped in their BOM, having mapped Taiwan Semiconductor Co., Ltd. (resistors and MOSFETs) rather than Taiwan Semiconductor Manufacturing Company. The two are different suppliers in different commodities and the near-identical name is what led the customer to expect coverage; nothing in the mapping surface flags that collision. On the authenticity question the report was assessed as credible but unconfirmed public reporting of a selective production and capacity shift at Fab 15A: Commercial Times (22-Jun-2026) reported monthly 28nm wafer starts falling from roughly 200,000 to 150,000 with migration toward 12nm and reallocation to silicon-interposer production, Economic Daily News (May 2026) reported Fab 15A converting toward 4nm, and TrendForce, SemiMedia, Tech in Asia and GuruFocus carried or analysed the same upstream reporting. TSMC stated on 22-Jun-2026 that its overall mature-node strategy was unchanged, which is not contradictory - an unchanged strategy is compatible with selective conversion at one fab. The specific 25 percent reduction came from supply-chain sources and was never confirmed by TSMC, so it is not classified as fake.</t>
         </is>
       </c>
       <c r="Y107" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z107" s="37" t="n"/>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E108" s="39" t="n">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="F108" s="33" t="inlineStr">
         <is>
-          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
+          <t>Murata MLCC Product Line Discontinuation – No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G108" s="33" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="I108" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J108" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K108" s="33" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="M108" s="33" t="inlineStr">
         <is>
-          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
+          <t>Validation step on high-impact component end-of-life and discontinuation notices before an analyst can clear them, so a major supplier's EOL announcement cannot be dismissed at review</t>
         </is>
       </c>
       <c r="N108" s="33" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
+          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15201,27 +15201,27 @@
       </c>
       <c r="U108" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V108" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W108" s="33" t="inlineStr">
         <is>
-          <t>EAO-40</t>
+          <t>EAO-39</t>
         </is>
       </c>
       <c r="X108" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
+          <t>Analyst miss. The event was available for review and was not escalated into EventWatch coverage. Ingestion and source coverage did not contribute.</t>
         </is>
       </c>
       <c r="Y108" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z108" s="37" t="n"/>
@@ -15231,16 +15231,16 @@
         <v>46266</v>
       </c>
       <c r="B109" s="37" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="C109" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D109" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E109" s="39" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="F109" s="33" t="inlineStr">
         <is>
-          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
+          <t>Precision Resource Facility Fire, Mt. Sterling, Kentucky – Deep-Tier Supplier Event Not Captured (Ford)</t>
         </is>
       </c>
       <c r="G109" s="33" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="H109" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I109" s="33" t="inlineStr">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="J109" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K109" s="33" t="inlineStr">
@@ -15283,7 +15283,7 @@
       </c>
       <c r="M109" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
+          <t>Monitoring of local and regional outlets covering industrial incidents at deep-tier supplier sites, with event-to-supply-chain correlation so a sub-tier fire is linked to the OEMs exposed through it</t>
         </is>
       </c>
       <c r="N109" s="33" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
         </is>
       </c>
       <c r="P109" s="33" t="n"/>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="U109" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V109" s="33" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="W109" s="33" t="inlineStr">
         <is>
-          <t>EAO-41</t>
+          <t>EAO-40</t>
         </is>
       </c>
       <c r="X109" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
         </is>
       </c>
       <c r="Y109" s="33" t="inlineStr">
@@ -15336,16 +15336,14 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z109" s="37" t="n">
-        <v>46288</v>
-      </c>
+      <c r="Z109" s="37" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B110" s="37" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
@@ -15354,7 +15352,7 @@
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Irving Oil</t>
         </is>
       </c>
       <c r="E110" s="39" t="n">
@@ -15362,7 +15360,7 @@
       </c>
       <c r="F110" s="33" t="inlineStr">
         <is>
-          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
+          <t>Paystone CCAA Filing – No EventWatch Notification (Irving Oil)</t>
         </is>
       </c>
       <c r="G110" s="33" t="inlineStr">
@@ -15397,7 +15395,7 @@
       </c>
       <c r="M110" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type such as CCAA is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N110" s="33" t="inlineStr">
@@ -15407,14 +15405,10 @@
       </c>
       <c r="O110" s="33" t="inlineStr">
         <is>
-          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
-        </is>
-      </c>
-      <c r="P110" s="33" t="inlineStr">
-        <is>
-          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
-        </is>
-      </c>
+          <t>EAO-41: Irving Oil asked why Paystone's CCAA filing was missed, raised to them by their own senior leadership rather than by EventWatch. Customer Support verified the Irving Oil org and found no corresponding notification, and found no evidence across any customer org that the event notification was generated or sent. Source was insolvencyinsider.ca. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding new keywords. RCA prepared and reviewed; the CSM closed the ticket on 23-Sep-2026 with no further customer questions outstanding. Logged as an Inquiry on review: the customer raised it as a question and the product connection to Paystone is weak. Missed_Flag stays Yes because the keyword gap and its fix are established, independent of how the contact is classified.</t>
+        </is>
+      </c>
+      <c r="P110" s="33" t="n"/>
       <c r="Q110" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15441,12 +15435,12 @@
       </c>
       <c r="W110" s="33" t="inlineStr">
         <is>
-          <t>EAO-42</t>
+          <t>EAO-41</t>
         </is>
       </c>
       <c r="X110" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding new keywords. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y110" s="33" t="inlineStr">
@@ -15467,12 +15461,12 @@
       </c>
       <c r="C111" s="33" t="inlineStr">
         <is>
-          <t>Cyber Attack</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D111" s="33" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E111" s="39" t="n">
@@ -15480,7 +15474,7 @@
       </c>
       <c r="F111" s="33" t="inlineStr">
         <is>
-          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
+          <t>Pollmann Austria GmbH Insolvency – No EventWatch Notification (Eaton)</t>
         </is>
       </c>
       <c r="G111" s="33" t="inlineStr">
@@ -15490,17 +15484,17 @@
       </c>
       <c r="H111" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Missed insolvency alert</t>
         </is>
       </c>
       <c r="I111" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J111" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K111" s="33" t="inlineStr">
@@ -15510,12 +15504,12 @@
       </c>
       <c r="L111" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M111" s="33" t="inlineStr">
         <is>
-          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
+          <t>Keyword coverage for insolvency and restructuring terminology in the bankruptcy algorithm, with a regression check when a filing type is added, so the same class of filing is not missed twice</t>
         </is>
       </c>
       <c r="N111" s="33" t="inlineStr">
@@ -15525,10 +15519,14 @@
       </c>
       <c r="O111" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
-        </is>
-      </c>
-      <c r="P111" s="33" t="n"/>
+          <t>EAO-42: Eaton reported that Pollmann Austria GmbH entered insolvency/restructuring proceedings on 01-Sep-2026, found through their own supplier engagement rather than EventWatch. No alert had been generated as of 15-Sep, a 15-day awareness delay. Publicly reported by KSV1870, the Austrian credit protection registry, and by ORF. Cause established as a keyword miss in the bankruptcy algorithm, fixed by adding a new keyword. RCA reviewed and approved internally on 20-Sep-2026 and shared with the customer; ticket closed 23-Sep-2026 with no follow-up received.</t>
+        </is>
+      </c>
+      <c r="P111" s="33" t="inlineStr">
+        <is>
+          <t>15 days (01-Sep proceedings - 15-Sep escalation, never published)</t>
+        </is>
+      </c>
       <c r="Q111" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15550,41 +15548,43 @@
       </c>
       <c r="V111" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W111" s="33" t="inlineStr">
         <is>
-          <t>EAO-51</t>
+          <t>EAO-42</t>
         </is>
       </c>
       <c r="X111" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
+          <t>Keyword miss in the bankruptcy algorithm: the filing was not matched because the algorithm's keyword set did not cover this filing's terminology. Fixed by adding a new keyword. Not a registry or source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. This is the second keyword miss in the same bankruptcy algorithm in a week, after EAO-41. RCA was issued as a PDF attachment whose text is not in Jira.</t>
         </is>
       </c>
       <c r="Y111" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
-        </is>
-      </c>
-      <c r="Z111" s="37" t="n"/>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z111" s="37" t="n">
+        <v>46288</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B112" s="37" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Cyber Attack</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E112" s="39" t="n">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="F112" s="33" t="inlineStr">
         <is>
-          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
+          <t>ADM Data Breach Exposes Personal Data - No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G112" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H112" s="33" t="inlineStr">
         <is>
-          <t>Monitoring Strategy RFI</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15622,28 +15622,28 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
         <is>
-          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
+          <t>A not-impactful decision check on clusters naming a mapped supplier, so a captured article is not closed out without a second look; and keyword coverage for ransomware leak-site and data-breach reporting, so a claimed breach at a mapped supplier is matched when it is published rather than when a customer's own threat team circulates it</t>
         </is>
       </c>
       <c r="N112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
       <c r="Q112" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R112" s="39" t="n">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="U112" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V112" s="33" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="W112" s="33" t="inlineStr">
         <is>
-          <t>EAO-43</t>
+          <t>EAO-51</t>
         </is>
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
@@ -15687,11 +15687,11 @@
         <v>46266</v>
       </c>
       <c r="B113" s="37" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="C113" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>Merger &amp; Acquisition</t>
         </is>
       </c>
       <c r="D113" s="33" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="F113" s="33" t="inlineStr">
         <is>
-          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
+          <t>Clarification on Impact Confirmation Requests for Supplier Acquisitions (Eaton)</t>
         </is>
       </c>
       <c r="G113" s="33" t="inlineStr">
@@ -15714,17 +15714,17 @@
       </c>
       <c r="H113" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Monitoring Strategy RFI</t>
         </is>
       </c>
       <c r="I113" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J113" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K113" s="33" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="M113" s="33" t="inlineStr">
         <is>
-          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
+          <t>Publish the M&amp;A impact-confirmation trigger criteria in-product, so the rationale for an acquiring-side outreach is visible on the request itself instead of being explained per account after the fact</t>
         </is>
       </c>
       <c r="N113" s="33" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15769,27 +15769,27 @@
       </c>
       <c r="U113" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V113" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W113" s="33" t="inlineStr">
         <is>
-          <t>EAO-44</t>
+          <t>EAO-43</t>
         </is>
       </c>
       <c r="X113" s="33" t="inlineStr">
         <is>
-          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
+          <t>Not a defect. Under the updated EventWatch Supplier Impact Confirmation methodology the outreach criteria were widened across event types in response to customer requests for greater visibility. For a Merger &amp; Acquisition the confirmation request validates whether the transaction has created operational or supply-chain impact that is not yet publicly known; a 'no impact' reply is itself useful because it confirms continuity of supply, and disruption is not assumed. The trigger ladder given to the customer: Low, neither company mapped and the transaction is an informational industry development, so no confirmation is sent; Medium, a mapped Tier-1 acquires a non-mapped company with no confirmed disruption, so outreach may be initiated to validate impact; High, a mapped company or site has confirmed operational or supply-chain disruption. Where the company being acquired or sold is itself mapped, the event is handled under Business Sale criteria.</t>
         </is>
       </c>
       <c r="Y113" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z113" s="37" t="n"/>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>Factory Fire</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E114" s="39" t="n">
@@ -15816,17 +15816,17 @@
       </c>
       <c r="F114" s="33" t="inlineStr">
         <is>
-          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
+          <t>UPG Enterprises Chapter 11 Mapped to Mapes &amp; Sprowl - Mapping and Severity Queried (Eaton)</t>
         </is>
       </c>
       <c r="G114" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H114" s="33" t="inlineStr">
         <is>
-          <t>Delayed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I114" s="33" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15846,40 +15846,34 @@
       </c>
       <c r="L114" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M114" s="33" t="inlineStr">
         <is>
-          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
+          <t>Scope check on parent-subsidiary linkage for insolvency filings, so a WarRoom is not raised against a subsidiary the filing text explicitly excludes, plus a recorded basis for the severity grade</t>
         </is>
       </c>
       <c r="N114" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
-        </is>
-      </c>
-      <c r="P114" s="33" t="inlineStr">
-        <is>
-          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
-        </is>
-      </c>
+          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+        </is>
+      </c>
+      <c r="P114" s="33" t="n"/>
       <c r="Q114" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R114" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S114" s="39" t="n">
-        <v>252</v>
-      </c>
+      <c r="S114" s="39" t="n"/>
       <c r="T114" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15887,22 +15881,22 @@
       </c>
       <c r="U114" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V114" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W114" s="33" t="inlineStr">
         <is>
-          <t>EAO-45</t>
+          <t>EAO-44</t>
         </is>
       </c>
       <c r="X114" s="33" t="inlineStr">
         <is>
-          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
+          <t>Deliberate precautionary scoping, explained to the customer on 24-Sep-2026. Mapes &amp; Sprowl is an affiliate operating within the UPG family of companies, and the official press release stated that UPG Enterprises LLC filed for Chapter 11 together with certain of its affiliates. That announcement did name UPG's international operations and UPG Electrical and its subsidiaries as outside the filing, but Mapes &amp; Sprowl was not among the entities explicitly excluded. Given the complex corporate hierarchies typical of industrial holding groups and the broad umbrella language of the initial disclosure, connected entities were included in the WarRoom as a precautionary early-warning measure to minimise visibility gaps. Inclusion was not a statement that Mapes &amp; Sprowl had itself filed: the WarRoom gives supply chain and procurement teams a workspace to begin supplier outreach, establish which operating entities fall inside the filing scope, and assess upstream or downstream impact from the parent's restructuring. On severity, the Bankruptcy-specific reporting guideline in the EventWatch Thresholds and Guidelines states that a mapped company is reported with High severity, and Mapes &amp; Sprowl was identified as mapped during the initial assessment, so High followed from that rule.</t>
         </is>
       </c>
       <c r="Y114" s="33" t="inlineStr">
@@ -15917,16 +15911,16 @@
         <v>46266</v>
       </c>
       <c r="B115" s="37" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="C115" s="33" t="inlineStr">
         <is>
-          <t>Legal Action</t>
+          <t>Factory Fire</t>
         </is>
       </c>
       <c r="D115" s="33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E115" s="39" t="n">
@@ -15934,7 +15928,7 @@
       </c>
       <c r="F115" s="33" t="inlineStr">
         <is>
-          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
+          <t>Purflux Group Filter Systems Maroc Facility Fire - 10-11 Day Alert Delay (Ford)</t>
         </is>
       </c>
       <c r="G115" s="33" t="inlineStr">
@@ -15944,17 +15938,17 @@
       </c>
       <c r="H115" s="33" t="inlineStr">
         <is>
-          <t>Duplicate WarRooms</t>
+          <t>Delayed Event</t>
         </is>
       </c>
       <c r="I115" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J115" s="33" t="inlineStr">
         <is>
-          <t>Duplication</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K115" s="33" t="inlineStr">
@@ -15964,12 +15958,12 @@
       </c>
       <c r="L115" s="33" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M115" s="33" t="inlineStr">
         <is>
-          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
+          <t>Latency monitoring on the gap between an incident's first public report and EventWatch publication, so a multi-day lag on a Tier-1 manufacturing site raises an internal alarm instead of waiting for the customer to notice</t>
         </is>
       </c>
       <c r="N115" s="33" t="inlineStr">
@@ -15979,19 +15973,25 @@
       </c>
       <c r="O115" s="33" t="inlineStr">
         <is>
-          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
-        </is>
-      </c>
-      <c r="P115" s="33" t="n"/>
+          <t>EAO-45: Ford reported a fire at Purflux Group's Filter Systems Maroc plant in Morocco on 11/12-Sep-2026 that Resilinc published only on 22-Sep-2026, a 10 to 11 day lag. Purflux supplies oil, fuel, air and cabin filtration to automotive powertrain and vehicle assembly lines, and the company issued its own official statement at the time. Ford has requested a formal RCA plus interim and permanent corrective actions covering regional event detection across North African and European manufacturing hubs. EventWatch review established that no article carrying the company name was captured on the portal on 11-Sep-2026, so nothing was available to publish on that date. Logged as a Complaint under Source Coverage on that basis: the gap is in what the sources delivered, not in how quickly a captured item was handled. The remainder of the interval to the 22-Sep publication is still under investigation.</t>
+        </is>
+      </c>
+      <c r="P115" s="33" t="inlineStr">
+        <is>
+          <t>~10-11 days (event 11/12-Sep-2026 -&gt; published 22-Sep-2026)</t>
+        </is>
+      </c>
       <c r="Q115" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R115" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="S115" s="39" t="n"/>
+      <c r="S115" s="39" t="n">
+        <v>252</v>
+      </c>
       <c r="T115" s="35" t="inlineStr">
         <is>
           <t>Sep 2026</t>
@@ -15999,27 +15999,27 @@
       </c>
       <c r="U115" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V115" s="33" t="inlineStr">
         <is>
-          <t>Cluster Integrity &amp; Duplicate Prevention</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W115" s="33" t="inlineStr">
         <is>
-          <t>EAO-46</t>
+          <t>EAO-45</t>
         </is>
       </c>
       <c r="X115" s="33" t="inlineStr">
         <is>
-          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
+          <t>No news article carrying the company name was captured on the EventWatch portal on 11-Sep-2026, the date Ford gives for the incident, so there was no item available to publish on that date. The remainder of the interval to the 22-Sep-2026 publication is still under investigation, so Root Cause, Sub-type and Standard Automation Focus on this record remain provisional.</t>
         </is>
       </c>
       <c r="Y115" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z115" s="37" t="n"/>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>Financial Distress</t>
+          <t>Legal Action</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E116" s="39" t="n">
@@ -16046,17 +16046,17 @@
       </c>
       <c r="F116" s="33" t="inlineStr">
         <is>
-          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
+          <t>USITC DRAM Patent Investigation - Duplicate WarRooms Published for One Event (Eaton)</t>
         </is>
       </c>
       <c r="G116" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H116" s="33" t="inlineStr">
         <is>
-          <t>Wrong Relevancy</t>
+          <t>Duplicate WarRooms</t>
         </is>
       </c>
       <c r="I116" s="33" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="J116" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Duplication</t>
         </is>
       </c>
       <c r="K116" s="33" t="inlineStr">
@@ -16076,12 +16076,12 @@
       </c>
       <c r="L116" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M116" s="33" t="inlineStr">
         <is>
-          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
+          <t>Near-duplicate detection at publication that matches on the underlying event rather than the bulletin title - entities, location, date and source article - so a second WarRoom for an event already covered is blocked at creation rather than found by the customer</t>
         </is>
       </c>
       <c r="N116" s="33" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="O116" s="33" t="inlineStr">
         <is>
-          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
+          <t>EAO-46: Eaton reported two WarRooms published for one event: 'USITC Opens DRAM Patent Investigation' and 'U.S. ITC Launches Patent Investigation into Micron, Supermicro, HPE, and Lenovo'. Customer Support reviewed both and confirmed they cover the same underlying news, and that they were created by two different EventWatch analysts, Deepika Rao and Namrata Kar. Cause is human error: the analyst failed to check for an existing bulletin before publishing the second WarRoom. The fix is deleting the duplicate WarRoom only. This is the same failure as the 25-Feb-2026 Eaton duplicate-WarRoom complaint on the Xometry CEO succession event.</t>
         </is>
       </c>
       <c r="P116" s="33" t="n"/>
@@ -16116,17 +16116,17 @@
       </c>
       <c r="V116" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W116" s="33" t="inlineStr">
         <is>
-          <t>EAO-47</t>
+          <t>EAO-46</t>
         </is>
       </c>
       <c r="X116" s="33" t="inlineStr">
         <is>
-          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
+          <t>Human error. The analyst did not check for an existing bulletin before creating a second WarRoom for the USITC DRAM patent investigation, so one event was published twice under differently worded titles by two different analysts. The corrective action is to delete the duplicate WarRoom, leaving a single bulletin for the event. No product or detection change is claimed here.</t>
         </is>
       </c>
       <c r="Y116" s="33" t="inlineStr">
@@ -16145,12 +16145,12 @@
       </c>
       <c r="C117" s="33" t="inlineStr">
         <is>
-          <t>Port Disruption</t>
+          <t>Financial Distress</t>
         </is>
       </c>
       <c r="D117" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E117" s="39" t="n">
@@ -16158,17 +16158,17 @@
       </c>
       <c r="F117" s="33" t="inlineStr">
         <is>
-          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
+          <t>Nidec Reported 1tn Yen Impairment and CEO Dismissal - No EventWatch Event Created (Western Digital)</t>
         </is>
       </c>
       <c r="G117" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H117" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Wrong Relevancy</t>
         </is>
       </c>
       <c r="I117" s="33" t="inlineStr">
@@ -16188,12 +16188,12 @@
       </c>
       <c r="L117" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M117" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
+          <t>A mapped-partner check at the point an analyst marks an event Not Impactful, so an event touching a customer's own mapped supplier cannot be closed out of their feed without that being surfaced to the reviewer</t>
         </is>
       </c>
       <c r="N117" s="33" t="inlineStr">
@@ -16203,13 +16203,13 @@
       </c>
       <c r="O117" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
+          <t>EAO-47: Western Digital reported that a Nidec Corporation (6594.T) event was absent from EventWatch. Per a Goldman Sachs First Take dated 28-Sep-2026 citing Diamond Online, Nidec is reported to be planning impairment losses of approximately 1 trillion yen, around 300 billion tied to correcting accounting irregularities and around 600 billion largely in the appliance business, with an extraordinary board meeting on 25-Sep-2026 reportedly dismissing CEO Mitsuya Kishida. Investigation found the event had in fact been captured and created: the analyst overlooked it, did not check whether Nidec is a mapped partner of Western Digital, and classified it Not Impactful, which kept it out of their feed. The customer was informed that the event was reported, so this is not counted as a missed event; the failure is analyst review and impact classification.</t>
         </is>
       </c>
       <c r="P117" s="33" t="n"/>
       <c r="Q117" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R117" s="39" t="n">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="U117" s="33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V117" s="33" t="inlineStr">
@@ -16233,12 +16233,12 @@
       </c>
       <c r="W117" s="33" t="inlineStr">
         <is>
-          <t>EAO-48</t>
+          <t>EAO-47</t>
         </is>
       </c>
       <c r="X117" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+          <t>Not a source-coverage gap and not a missed event. The Nidec reporting was captured and an event was created; the analyst then classified it Not Impactful without checking whether Nidec is a mapped partner of Western Digital, so it never reached them. Western Digital was told the event had been reported. The failure is the impact classification, not coverage.</t>
         </is>
       </c>
       <c r="Y117" s="33" t="inlineStr">
@@ -16246,25 +16246,23 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z117" s="37" t="n">
-        <v>46302</v>
-      </c>
+      <c r="Z117" s="37" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="35" t="n">
         <v>46266</v>
       </c>
       <c r="B118" s="37" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>Extreme Weather</t>
+          <t>Port Disruption</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E118" s="39" t="n">
@@ -16272,7 +16270,7 @@
       </c>
       <c r="F118" s="33" t="inlineStr">
         <is>
-          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
+          <t>South Africa Port and Corridor Congestion - EWC Cargo Movement Update Not Flagged (Ford)</t>
         </is>
       </c>
       <c r="G118" s="33" t="inlineStr">
@@ -16282,7 +16280,7 @@
       </c>
       <c r="H118" s="33" t="inlineStr">
         <is>
-          <t>Impacted Supplier Missing</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I118" s="33" t="inlineStr">
@@ -16292,7 +16290,7 @@
       </c>
       <c r="J118" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K118" s="33" t="inlineStr">
@@ -16302,12 +16300,12 @@
       </c>
       <c r="L118" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M118" s="33" t="inlineStr">
         <is>
-          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
+          <t>Not Impactful decision validation for port and corridor congestion, so a multi-day vessel waiting or berthing delay reported by a regional logistics body is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N118" s="33" t="inlineStr">
@@ -16317,13 +16315,13 @@
       </c>
       <c r="O118" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P118" s="33" t="n"/>
       <c r="Q118" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R118" s="39" t="n">
@@ -16337,42 +16335,48 @@
       </c>
       <c r="U118" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="V118" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W118" s="33" t="inlineStr">
         <is>
-          <t>EAO-49</t>
-        </is>
-      </c>
-      <c r="X118" s="33" t="n"/>
+          <t>EAO-48</t>
+        </is>
+      </c>
+      <c r="X118" s="33" t="inlineStr">
+        <is>
+          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+        </is>
+      </c>
       <c r="Y118" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z118" s="37" t="n"/>
+      <c r="Z118" s="37" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="35" t="n">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="B119" s="37" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C119" s="33" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Extreme Weather</t>
         </is>
       </c>
       <c r="D119" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E119" s="39" t="n">
@@ -16380,7 +16384,7 @@
       </c>
       <c r="F119" s="33" t="inlineStr">
         <is>
-          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
+          <t>Disaster Zone Declared in Bangkok, Thailand, Following Widespread Flooding</t>
         </is>
       </c>
       <c r="G119" s="33" t="inlineStr">
@@ -16390,7 +16394,7 @@
       </c>
       <c r="H119" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Impacted Supplier Missing</t>
         </is>
       </c>
       <c r="I119" s="33" t="inlineStr">
@@ -16400,7 +16404,7 @@
       </c>
       <c r="J119" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K119" s="33" t="inlineStr">
@@ -16415,7 +16419,7 @@
       </c>
       <c r="M119" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
+          <t>Geographic completeness prompt at WarRoom creation, so an analyst scoping a flood or other area event is shown the impacted region beyond the named city before the initial impacted-site list is fixed, and a site added by a later update is flagged as a creation-time gap rather than found by the customer</t>
         </is>
       </c>
       <c r="N119" s="33" t="inlineStr">
@@ -16425,22 +16429,22 @@
       </c>
       <c r="O119" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
         </is>
       </c>
       <c r="P119" s="33" t="n"/>
       <c r="Q119" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R119" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S119" s="39" t="n"/>
       <c r="T119" s="35" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="U119" s="33" t="inlineStr">
@@ -16450,19 +16454,15 @@
       </c>
       <c r="V119" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W119" s="33" t="inlineStr">
         <is>
-          <t>EAO-50</t>
-        </is>
-      </c>
-      <c r="X119" s="33" t="inlineStr">
-        <is>
-          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
-        </is>
-      </c>
+          <t>EAO-49</t>
+        </is>
+      </c>
+      <c r="X119" s="33" t="n"/>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -16475,16 +16475,16 @@
         <v>46296</v>
       </c>
       <c r="B120" s="37" t="n">
-        <v>46303</v>
+        <v>46296</v>
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>Power Outage</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="E120" s="39" t="n">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="F120" s="33" t="inlineStr">
         <is>
-          <t>Carlisle, Iowa Municipal Water Disruption – No WarRoom Created (General Mills)</t>
+          <t>Planned Strike at AGC Display Glass, Yunlin County, Taiwan (5 Oct 2026) Not Reported (Ford)</t>
         </is>
       </c>
       <c r="G120" s="33" t="inlineStr">
@@ -16502,17 +16502,17 @@
       </c>
       <c r="H120" s="33" t="inlineStr">
         <is>
-          <t>Missed WarRoom</t>
+          <t>Missed Event</t>
         </is>
       </c>
       <c r="I120" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J120" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K120" s="33" t="inlineStr">
@@ -16527,7 +16527,7 @@
       </c>
       <c r="M120" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
+          <t>Not Impactful decision validation for planned labour actions, so a strike carrying a published start date is escalated for a second review rather than closed at editorial review</t>
         </is>
       </c>
       <c r="N120" s="33" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="O120" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
+          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
         </is>
       </c>
       <c r="P120" s="33" t="n"/>
@@ -16562,22 +16562,22 @@
       </c>
       <c r="V120" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W120" s="33" t="inlineStr">
         <is>
-          <t>EAO-52</t>
+          <t>EAO-50</t>
         </is>
       </c>
       <c r="X120" s="33" t="inlineStr">
         <is>
-          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y120" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z120" s="37" t="n"/>
@@ -16587,16 +16587,16 @@
         <v>46296</v>
       </c>
       <c r="B121" s="37" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="C121" s="33" t="inlineStr">
         <is>
-          <t>Price Fluctuation</t>
+          <t>Power Outage</t>
         </is>
       </c>
       <c r="D121" s="33" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="E121" s="39" t="n">
@@ -16604,27 +16604,27 @@
       </c>
       <c r="F121" s="33" t="inlineStr">
         <is>
-          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
+          <t>Carlisle, Iowa Municipal Water Disruption – No WarRoom Created (General Mills)</t>
         </is>
       </c>
       <c r="G121" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H121" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+          <t>Missed WarRoom</t>
         </is>
       </c>
       <c r="I121" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J121" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K121" s="33" t="inlineStr">
@@ -16634,28 +16634,28 @@
       </c>
       <c r="L121" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M121" s="33" t="inlineStr">
         <is>
-          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
+          <t>Keyword coverage for municipal utility disruptions and do-not-use-water orders, so a named-locality utility failure is matched against mapped customer sites rather than passing the algorithm unrecognised</t>
         </is>
       </c>
       <c r="N121" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification. The outcome is a process enhancement rather than a correction: the WarRoom met the threshold the guidance actually set, and what the scenario exposed is that the threshold tested supplier mapping without testing whether the affected product is one the customer buys.</t>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
       <c r="Q121" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R121" s="39" t="n">
@@ -16674,18 +16674,22 @@
       </c>
       <c r="V121" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
-        </is>
-      </c>
-      <c r="W121" s="33" t="n"/>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W121" s="33" t="inlineStr">
+        <is>
+          <t>EAO-52</t>
+        </is>
+      </c>
       <c r="X121" s="33" t="inlineStr">
         <is>
-          <t>The WarRoom was created correctly under the guidance as written: NVIDIA is a mapped partner, and the EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. The affected product was the Shield TV Pro, which the customer does not procure, so there was no direct impact on products or services supplied to them. EventWatch and the customer agreed that for this scenario an EventWatch bulletin without a WarRoom is the right treatment - and the guidance did not carry that scenario at all: its threshold tested supplier mapping alone and said nothing about product-level relevance or customer exposure. This is a process enhancement, not a defect; no guideline was broken and no fault was admitted. The team committed to reinforcing the guidance so that product-level relevance and customer exposure are evaluated alongside supplier mapping before a WarRoom is created for a similar price fluctuation event.</t>
+          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
         </is>
       </c>
       <c r="Y121" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z121" s="37" t="n"/>
@@ -16699,12 +16703,12 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>Labor Disruption</t>
+          <t>Price Fluctuation</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="E122" s="39" t="n">
@@ -16712,7 +16716,7 @@
       </c>
       <c r="F122" s="33" t="inlineStr">
         <is>
-          <t>MasterBrand Cabinets to Lay Off Employees at Its Facility in Kinston, North Carolina, USA</t>
+          <t>Nvidia Shield TV Pro Price Increase WarRoom Trigger Clarification (META)</t>
         </is>
       </c>
       <c r="G122" s="33" t="inlineStr">
@@ -16722,7 +16726,7 @@
       </c>
       <c r="H122" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Mapping Clarification</t>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
         </is>
       </c>
       <c r="I122" s="33" t="inlineStr">
@@ -16732,7 +16736,7 @@
       </c>
       <c r="J122" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Process Clarification</t>
         </is>
       </c>
       <c r="K122" s="33" t="inlineStr">
@@ -16747,7 +16751,7 @@
       </c>
       <c r="M122" s="33" t="inlineStr">
         <is>
-          <t>A site-data completeness review with the customer, so facilities of an already-mapped supplier are shared and on file before an event names one, rather than the gap surfacing when a WarRoom does not appear</t>
+          <t>Product-level relevance check before WarRoom creation on a price fluctuation event, so a mapped supplier's price move raises a WarRoom only where the affected product is one the customer procures</t>
         </is>
       </c>
       <c r="N122" s="33" t="inlineStr">
@@ -16757,7 +16761,7 @@
       </c>
       <c r="O122" s="33" t="inlineStr">
         <is>
-          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so that verification is still outstanding and is recorded here rather than in the status field. The row is Clarification Provided because that is what went back to NVR on ask 1. It is not Pending: this was raised by email with no Jira ticket, so the daily Pending re-check would have no ticket to pull and nothing would ever move the flag off. The open source check is a manual follow-up with Ankit Gupta.</t>
+          <t>Rick Freeman, Sr. Director of Expert Services, asked on behalf of META why a WarRoom had been created for the NVIDIA Shield TV Pro price increase when META does not purchase Shield TV products, and whether a standard EventWatch notification would have been the more appropriate treatment. The bulletin covered a 50% rise in the Shield TV Pro, from $199.99 to $299.99, which NVIDIA attributed to higher component and memory costs; it was classified as a Price Fluctuation event and a supplier impact notification was issued. Justin Cerullo acknowledged the query and committed to investigate. Raised by email; no Jira ticket was opened. META accepted the explanation and thanked the team for the quick clarification. The outcome is a process enhancement rather than a correction: the WarRoom met the threshold the guidance actually set, and what the scenario exposed is that the threshold tested supplier mapping without testing whether the affected product is one the customer buys.</t>
         </is>
       </c>
       <c r="P122" s="33" t="n"/>
@@ -16777,18 +16781,18 @@
       </c>
       <c r="U122" s="33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="V122" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W122" s="33" t="n"/>
       <c r="X122" s="33" t="inlineStr">
         <is>
-          <t>The Kinston event was identified and published as an EventWatch bulletin, so monitoring carried it. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not among the sites NVR had shared, so no WarRoom could be created for them. Nothing in the platform or in analyst review failed here. What is missing is a process for collecting a customer's facility data completely enough that a site of a mapped supplier is on file before an event names it. The source-coverage question NVR raised alongside is being verified separately and carries no finding of a miss, since the event was published.</t>
+          <t>The WarRoom was created correctly under the guidance as written: NVIDIA is a mapped partner, and the EventWatch guidelines for Price Fluctuation events call for a WarRoom when a mapped supplier is directly involved. The affected product was the Shield TV Pro, which the customer does not procure, so there was no direct impact on products or services supplied to them. EventWatch and the customer agreed that for this scenario an EventWatch bulletin without a WarRoom is the right treatment - and the guidance did not carry that scenario at all: its threshold tested supplier mapping alone and said nothing about product-level relevance or customer exposure. This is a process enhancement, not a defect; no guideline was broken and no fault was admitted. The team committed to reinforcing the guidance so that product-level relevance and customer exposure are evaluated alongside supplier mapping before a WarRoom is created for a similar price fluctuation event.</t>
         </is>
       </c>
       <c r="Y122" s="33" t="inlineStr">
@@ -16807,12 +16811,12 @@
       </c>
       <c r="C123" s="33" t="inlineStr">
         <is>
-          <t>FDA/EMA/OSHA Action</t>
+          <t>Labor Disruption</t>
         </is>
       </c>
       <c r="D123" s="33" t="inlineStr">
         <is>
-          <t>Suntory Spirits</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="E123" s="39" t="n">
@@ -16820,27 +16824,27 @@
       </c>
       <c r="F123" s="33" t="inlineStr">
         <is>
-          <t>Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan</t>
+          <t>MasterBrand Cabinets to Lay Off Employees at Its Facility in Kinston, North Carolina, USA</t>
         </is>
       </c>
       <c r="G123" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H123" s="33" t="inlineStr">
         <is>
-          <t>Missing EventWatch coverage / feeds not captured</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I123" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J123" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -16850,28 +16854,28 @@
       </c>
       <c r="L123" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M123" s="33" t="inlineStr">
         <is>
-          <t>Timeliness monitoring for regulator and competition-authority actions against mapped suppliers, so a publicly reported raid or probe is matched and published before a customer asks where the coverage is</t>
+          <t>A site-data completeness review with the customer, so facilities of an already-mapped supplier are shared and on file before an event names one, rather than the gap surfacing when a WarRoom does not appear</t>
         </is>
       </c>
       <c r="N123" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O123" s="33" t="inlineStr">
         <is>
-          <t>Suntory Spirits raised two asks by email on 09-Oct-2026 about the Japanese antitrust investigation into four major brewers. ASK 1, why there was no EventWatch coverage. The customer saw news of the investigation naming Suntory Spirits and could not find corresponding coverage in EventWatch, and questioned whether this event type is monitored at all. ASK 2, whether the sources reporting the investigation are inside the monitoring ecosystem, and whether monitoring can be expanded so future developments are captured earlier. The timeline is what makes this a miss rather than a coverage question. Authorities conducted searches on 07-Oct-2026 and the investigation was publicly reported before any EventWatch bulletin existed. The customer wrote in on 09-Oct. The bulletin, titled Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan, published at 12:07 AM IST on 10-Oct-2026 - after the escalation. So ask 2 is not a generic source-coverage question: the customer is asking whether sources that already carried the story were being monitored, which makes it a monitoring-gap inquiry. Under investigation and deliberately left open; the Sub-type is a staging guess. Captured Late is the one reading the timeline supports on its own, since a bulletin did publish, and it does not prejudge whether the delay came from a source gap, a keyword gap or pipeline lag - which is exactly what is still being established. Raised by email; no Jira ticket has been opened, so the daily Pending re-check has no ticket to pull and this row needs a human to carry it.</t>
+          <t>NVR raised two separate asks in one thread about the MasterBrand Kinston, North Carolina layoff bulletin published 30-Sep-2026 at 02:05 PM PST. ASK 1, why no WarRoom was created for the Kinston facility. NVR received a WarRoom for the American Woodmark Gas City, Indiana facility but none for MasterBrand Kinston, although the Kinston layoffs were reported by multiple news outlets. EventWatch confirmed the Kinston event was identified and published. A customer-specific WarRoom is created only where the affected supplier site is mapped in the Resilinc database, and the Kinston site was not among the sites NVR had shared, so a bulletin published and no WarRoom followed. This was not a missed EventWatch event, and it is neither a platform nor an analyst failure: the site was never shared with us, so there was nothing for the event to match against. ASK 2, whether Neuse News, Triangle Business Journal, Woodworking Network and WITN are part of the monitoring vendor network and can be added going forward. Nitin Rindhe asked Ankit Gupta to verify. This is a source-coverage validation question, not an allegation that the event was missed: EventWatch had already published a bulletin on the Kinston event, so monitoring did carry it. No confirmation appears in the thread reviewed, so that verification is still outstanding and is recorded here rather than in the status field. The row is Clarification Provided because that is what went back to NVR on ask 1. It is not Pending: this was raised by email with no Jira ticket, so the daily Pending re-check would have no ticket to pull and nothing would ever move the flag off. The open source check is a manual follow-up with Ankit Gupta.</t>
         </is>
       </c>
       <c r="P123" s="33" t="n"/>
       <c r="Q123" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R123" s="39" t="n">
@@ -16885,23 +16889,23 @@
       </c>
       <c r="U123" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V123" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W123" s="33" t="n"/>
       <c r="X123" s="33" t="inlineStr">
         <is>
-          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+          <t>The Kinston event was identified and published as an EventWatch bulletin, so monitoring carried it. A customer-specific WarRoom is raised only where the affected supplier site is mapped in the Resilinc database, and the MasterBrand Kinston site was not among the sites NVR had shared, so no WarRoom could be created for them. Nothing in the platform or in analyst review failed here. What is missing is a process for collecting a customer's facility data completely enough that a site of a mapped supplier is on file before an event names it. The source-coverage question NVR raised alongside is being verified separately and carries no finding of a miss, since the event was published.</t>
         </is>
       </c>
       <c r="Y123" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z123" s="37" t="n"/>
@@ -16911,16 +16915,16 @@
         <v>46296</v>
       </c>
       <c r="B124" s="37" t="n">
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>FDA/EMA/OSHA Action</t>
         </is>
       </c>
       <c r="D124" s="33" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Suntory Spirits</t>
         </is>
       </c>
       <c r="E124" s="39" t="n">
@@ -16928,7 +16932,7 @@
       </c>
       <c r="F124" s="33" t="inlineStr">
         <is>
-          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+          <t>Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan</t>
         </is>
       </c>
       <c r="G124" s="33" t="inlineStr">
@@ -16938,7 +16942,7 @@
       </c>
       <c r="H124" s="33" t="inlineStr">
         <is>
-          <t>Missed insolvency alert</t>
+          <t>Missing EventWatch coverage / feeds not captured</t>
         </is>
       </c>
       <c r="I124" s="33" t="inlineStr">
@@ -16948,7 +16952,7 @@
       </c>
       <c r="J124" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Captured Late</t>
         </is>
       </c>
       <c r="K124" s="33" t="inlineStr">
@@ -16963,7 +16967,7 @@
       </c>
       <c r="M124" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Timeliness monitoring for regulator and competition-authority actions against mapped suppliers, so a publicly reported raid or probe is matched and published before a customer asks where the coverage is</t>
         </is>
       </c>
       <c r="N124" s="33" t="inlineStr">
@@ -16973,7 +16977,7 @@
       </c>
       <c r="O124" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Suntory Spirits raised two asks by email on 09-Oct-2026 about the Japanese antitrust investigation into four major brewers. ASK 1, why there was no EventWatch coverage. The customer saw news of the investigation naming Suntory Spirits and could not find corresponding coverage in EventWatch, and questioned whether this event type is monitored at all. ASK 2, whether the sources reporting the investigation are inside the monitoring ecosystem, and whether monitoring can be expanded so future developments are captured earlier. The timeline is what makes this a miss rather than a coverage question. Authorities conducted searches on 07-Oct-2026 and the investigation was publicly reported before any EventWatch bulletin existed. The customer wrote in on 09-Oct. The bulletin, titled Antitrust Raids at Suntory Spirits, Asahi Breweries, Kirin Brewery, and Sapporo Breweries in Japan, published at 12:07 AM IST on 10-Oct-2026 - after the escalation. So ask 2 is not a generic source-coverage question: the customer is asking whether sources that already carried the story were being monitored, which makes it a monitoring-gap inquiry. Under investigation and deliberately left open; the Sub-type is a staging guess. Captured Late is the one reading the timeline supports on its own, since a bulletin did publish, and it does not prejudge whether the delay came from a source gap, a keyword gap or pipeline lag - which is exactly what is still being established. Raised by email; no Jira ticket has been opened, so the daily Pending re-check has no ticket to pull and this row needs a human to carry it.</t>
         </is>
       </c>
       <c r="P124" s="33" t="n"/>
@@ -16993,26 +16997,134 @@
       </c>
       <c r="U124" s="33" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V124" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W124" s="33" t="n"/>
+      <c r="X124" s="33" t="inlineStr">
+        <is>
+          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+        </is>
+      </c>
+      <c r="Y124" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z124" s="37" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B125" s="37" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C125" s="33" t="inlineStr">
+        <is>
+          <t>Bankruptcy</t>
+        </is>
+      </c>
+      <c r="D125" s="33" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="E125" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="33" t="inlineStr">
+        <is>
+          <t>BER Automotive Bankruptcy, Bursa Türkiye – No EventWatch Alert (Ford)</t>
+        </is>
+      </c>
+      <c r="G125" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H125" s="33" t="inlineStr">
+        <is>
+          <t>Missed insolvency alert</t>
+        </is>
+      </c>
+      <c r="I125" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J125" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K125" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L125" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M125" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+        </is>
+      </c>
+      <c r="N125" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O125" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+        </is>
+      </c>
+      <c r="P125" s="33" t="n"/>
+      <c r="Q125" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R125" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S125" s="39" t="n"/>
+      <c r="T125" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U125" s="33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="V124" s="33" t="inlineStr">
+      <c r="V125" s="33" t="inlineStr">
         <is>
           <t>Dynamic Source Discovery</t>
         </is>
       </c>
-      <c r="W124" s="33" t="inlineStr">
+      <c r="W125" s="33" t="inlineStr">
         <is>
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X124" s="33" t="n"/>
-      <c r="Y124" s="33" t="inlineStr">
+      <c r="X125" s="33" t="n"/>
+      <c r="Y125" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z124" s="37" t="n"/>
+      <c r="Z125" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18770,7 +18882,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3564356435643564</v>
+        <v>0.34951456310679613</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18811,7 +18923,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12871287128712872</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18853,7 +18965,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06930693069306931</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -18892,10 +19004,10 @@
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -18937,7 +19049,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.039603960396039604</v>
+        <v>0.038834951456310676</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -18979,7 +19091,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.0297029702970297</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19014,14 +19126,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19056,14 +19168,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19098,14 +19210,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19140,14 +19252,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.019801980198019802</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="25" t="inlineStr">
@@ -19286,13 +19398,13 @@
         </is>
       </c>
       <c r="J80" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K80" s="76" t="n">
         <v>1</v>
       </c>
       <c r="L80" s="76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -19544,10 +19656,10 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L90" s="76" t="n">
         <v>8</v>
@@ -19634,13 +19746,13 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>
@@ -20119,7 +20231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24244,6 +24356,33 @@
       <c r="E154" s="41" t="inlineStr">
         <is>
           <t>Event type</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="30.75" customHeight="1">
+      <c r="A155" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B155" s="41" t="inlineStr">
+        <is>
+          <t>Alerting Gap</t>
+        </is>
+      </c>
+      <c r="C155" s="41" t="inlineStr">
+        <is>
+          <t>A relevant article or feed was captured by the Product-controlled harvesting or monitoring flow, but an ingestion, database, portal, UI or workflow failure prevented it from reaching analysts as a usable item in time for review and escalation.</t>
+        </is>
+      </c>
+      <c r="D155" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Include: feed identified upstream but not ingested into the portal; algorithm captured the article but it did not reach the application or analyst queue; a captured feed that surfaced in the analyst workflow only after a Product-caused delay. Exclude: source or vendor never captured it, a keyword or language-detection miss, Product's first usable capture being late, wrong clustering, incorrect AI classification, an analyst marking it Not Impactful, an analyst deprioritising an available event, a published item the customer could not see, and customer configuration filtering it out.</t>
+        </is>
+      </c>
+      <c r="E155" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>38</v>
                 </pt>
                 <pt idx="2">
                   <v>15</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="L112" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M112" s="33" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. Under investigation: no agreed RCA yet.</t>
+          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. An RCA was issued to General Mills on 13-Oct-2026 as an attachment on EAO-51. Its text is not in the ticket, so it is not reproduced here. The ticket is still open at Approval Requested, and three of the four articles raised with monitoring are not yet accounted for.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2941,9 +2941,9 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>Dashboard!$E$67:$E$75</f>
+              <f>Dashboard!$E$67:$E$76</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>WarRoom &amp; Decision Validation</v>
                 </pt>
@@ -2971,15 +2971,18 @@
                 <pt idx="8">
                   <v>Notification Visibility Monitoring</v>
                 </pt>
+                <pt idx="9">
+                  <v>Classification &amp; Impact Validation</v>
+                </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$F$67:$F$75</f>
+              <f>Dashboard!$F$67:$F$76</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>31</v>
                 </pt>
@@ -3006,6 +3009,9 @@
                 </pt>
                 <pt idx="8">
                   <v>10</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3376,7 +3382,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E155" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E166" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -19262,17 +19268,17 @@
         <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
-      <c r="E76" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F76" s="26">
-        <f>SUM(F67:F75)</f>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>Classification &amp; Impact Validation</t>
+        </is>
+      </c>
+      <c r="F76" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E76)</f>
         <v/>
       </c>
-      <c r="G76" s="27">
-        <f>SUM(G67:G75)</f>
+      <c r="G76" s="24">
+        <f>F76/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
       <c r="H76" s="3" t="n"/>
@@ -19306,9 +19312,19 @@
         <v/>
       </c>
       <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F77" s="26">
+        <f>SUM(F67:F76)</f>
+        <v/>
+      </c>
+      <c r="G77" s="27">
+        <f>SUM(G67:G76)</f>
+        <v/>
+      </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
@@ -20231,7 +20247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24383,6 +24399,303 @@
       <c r="E155" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30.75" customHeight="1">
+      <c r="A156" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B156" s="41" t="inlineStr">
+        <is>
+          <t>Published Late</t>
+        </is>
+      </c>
+      <c r="C156" s="41" t="inlineStr">
+        <is>
+          <t>The event was available to analysts in time for review, but publication or escalation occurred materially late because of delayed analysis, prioritization, research, or operational handling.</t>
+        </is>
+      </c>
+      <c r="D156" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The story reached a person in time; what was late was the decision to raise it. Use Alerting Gap where the item never reached the analyst, and Captured Late where our own first usable capture came late.</t>
+        </is>
+      </c>
+      <c r="E156" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30.75" customHeight="1">
+      <c r="A157" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B157" s="41" t="inlineStr">
+        <is>
+          <t>Methodology Weakness</t>
+        </is>
+      </c>
+      <c r="C157" s="41" t="inlineStr">
+        <is>
+          <t>The available methodology, reporting guidance, or evaluation approach was inadequate and led to the wrong outcome, even though the workflow was performed as designed.</t>
+        </is>
+      </c>
+      <c r="D157" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Nobody departed from the guidance; the guidance itself was deficient and the deficiency was accepted. Use Deliberate Rule where the rule was adequate and the customer simply queried it.</t>
+        </is>
+      </c>
+      <c r="E157" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30.75" customHeight="1">
+      <c r="A158" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B158" s="41" t="inlineStr">
+        <is>
+          <t>Deliberate Rule</t>
+        </is>
+      </c>
+      <c r="C158" s="41" t="inlineStr">
+        <is>
+          <t>The system or team acted according to an approved reporting rule, threshold, or internal convention. The customer questioned the rule, but no miss or defect occurred under the rule then in force.</t>
+        </is>
+      </c>
+      <c r="D158" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. A rule changed afterwards is an enhancement, not a fault, and the record stays here. Use Methodology Weakness where the rule itself was accepted as deficient.</t>
+        </is>
+      </c>
+      <c r="E158" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30.75" customHeight="1">
+      <c r="A159" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B159" s="41" t="inlineStr">
+        <is>
+          <t>Platform Bug</t>
+        </is>
+      </c>
+      <c r="C159" s="41" t="inlineStr">
+        <is>
+          <t>A confirmed software, code, system, or data-processing defect produced incorrect Product behavior and does not fit the more specific categories of Alerting Gap, Clustering / Duplication Defect, Model Classification Defect, or Mapping / Routing Defect.</t>
+        </is>
+      </c>
+      <c r="D159" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The residual Product defect category, used only once the four specific defect categories have been ruled out. Requires a confirmed defect, not a suspected one.</t>
+        </is>
+      </c>
+      <c r="E159" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30.75" customHeight="1">
+      <c r="A160" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B160" s="41" t="inlineStr">
+        <is>
+          <t>Mapping / Routing Defect</t>
+        </is>
+      </c>
+      <c r="C160" s="41" t="inlineStr">
+        <is>
+          <t>Incorrect system data, association, coordinates, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
+        </is>
+      </c>
+      <c r="D160" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers geocoding and address-to-coordinate mismatches, cross-tenant leakage and entity mislinkage. Use Supplier / Site Not Shared where the data was never provided at all.</t>
+        </is>
+      </c>
+      <c r="E160" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30.75" customHeight="1">
+      <c r="A161" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B161" s="41" t="inlineStr">
+        <is>
+          <t>Supplier / Site Not Shared</t>
+        </is>
+      </c>
+      <c r="C161" s="41" t="inlineStr">
+        <is>
+          <t>The affected supplier, company, or site was not present in the customer-provided or customer-maintained data available to EventWatch. The issue is an input-data dependency rather than a Product or analyst failure.</t>
+        </is>
+      </c>
+      <c r="D161" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. There was nothing for the event to match against, so neither the platform nor analyst review failed. The remedy is our process for collecting the customer's facility data.</t>
+        </is>
+      </c>
+      <c r="E161" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30.75" customHeight="1">
+      <c r="A162" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B162" s="41" t="inlineStr">
+        <is>
+          <t>Analyst Review Miss</t>
+        </is>
+      </c>
+      <c r="C162" s="41" t="inlineStr">
+        <is>
+          <t>The relevant story was available for human review, but it was incorrectly rejected, closed, deprioritized, or insufficiently researched, resulting in a missed customer notification.</t>
+        </is>
+      </c>
+      <c r="D162" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. A person had it in front of them and the quality of that look is the failure. Use Model Classification Defect where an automated model made the call, and Published Late where the item was eventually raised but too late.</t>
+        </is>
+      </c>
+      <c r="E162" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="30.75" customHeight="1">
+      <c r="A163" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B163" s="41" t="inlineStr">
+        <is>
+          <t>Supplier Selection Miss</t>
+        </is>
+      </c>
+      <c r="C163" s="41" t="inlineStr">
+        <is>
+          <t>The relevant supplier, company, facility, location, or impact area was available during bulletin or WarRoom preparation but was omitted from the initial impacted selection.</t>
+        </is>
+      </c>
+      <c r="D163" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The event was published and the supplier data was on file; an analyst left it out of the initial selection or geofence. Normally carries Missed_Flag No, since the customer did receive the event.</t>
+        </is>
+      </c>
+      <c r="E163" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30.75" customHeight="1">
+      <c r="A164" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B164" s="41" t="inlineStr">
+        <is>
+          <t>Clustering / Duplication Defect</t>
+        </is>
+      </c>
+      <c r="C164" s="41" t="inlineStr">
+        <is>
+          <t>Product incorrectly grouped, split, duplicated, or associated stories or bulletins across clusters or WarRooms, resulting in incomplete, duplicate, or disrupted event handling.</t>
+        </is>
+      </c>
+      <c r="D164" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Covers a split update sequence, a duplicated WarRoom and a cluster state that mishandles a correctly captured story.</t>
+        </is>
+      </c>
+      <c r="E164" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30.75" customHeight="1">
+      <c r="A165" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B165" s="41" t="inlineStr">
+        <is>
+          <t>Model Classification Defect</t>
+        </is>
+      </c>
+      <c r="C165" s="41" t="inlineStr">
+        <is>
+          <t>The relevant article or event was captured and entered the Product workflow, but an automated classification model assigned an incorrect event, relevance, or impact outcome, causing the item to be excluded, misrouted, or handled incorrectly.</t>
+        </is>
+      </c>
+      <c r="D165" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The model made the call. A human review that failed to correct the model is a contributing factor recorded in Comments, not a reason to file the record under Analyst Review Miss.</t>
+        </is>
+      </c>
+      <c r="E165" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30.75" customHeight="1">
+      <c r="A166" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B166" s="41" t="inlineStr">
+        <is>
+          <t>Classification &amp; Impact Validation</t>
+        </is>
+      </c>
+      <c r="C166" s="41" t="inlineStr">
+        <is>
+          <t>Controls that validate automated event, relevance, and impact classifications and identify cases where model output requires correction before final disposition.</t>
+        </is>
+      </c>
+      <c r="D166" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E166" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>38</v>
+                  <v>39</v>
                 </pt>
                 <pt idx="2">
-                  <v>15</v>
+                  <v>16</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>60</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2987,7 +2987,7 @@
                   <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3011,7 +3011,7 @@
                   <v>10</v>
                 </pt>
                 <pt idx="9">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="J14" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Mapping / Routing Defect</t>
         </is>
       </c>
       <c r="K14" s="33" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="O14" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3263 (Closed). Molex is an EventWatch-only customer with no SCVs launched, so no sites should show with source Partner, yet ARROW ELECTRONICS - GBR BERKSHIRE READING appeared at Tier 1. The site_shareable record under the Molex tenant had its source_id mapped to the HITACHI ENERGY MAP demo org, so demo-org sites leaked into a production portal.</t>
+          <t>From Jira CAN-3263 (Closed). Molex is an EventWatch-only customer with no SCVs launched, so no sites should show with source Partner, yet ARROW ELECTRONICS - GBR BERKSHIRE READING appeared at Tier 1. The site_shareable record under the Molex tenant had its source_id mapped to the HITACHI ENERGY MAP demo org, so demo-org sites leaked into a production portal. Cross-Tenant Data Contamination.</t>
         </is>
       </c>
       <c r="P14" s="33" t="n"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="J29" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Analyst Review Miss</t>
         </is>
       </c>
       <c r="K29" s="33" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="O29" s="33" t="inlineStr">
         <is>
-          <t>25-day delay flagged by customer; blocked source + misclassification. Retraining completed.</t>
+          <t>25-day delay flagged by customer; blocked source + misclassification. Retraining completed. Blocked initial source.</t>
         </is>
       </c>
       <c r="P29" s="33" t="inlineStr">
@@ -6713,7 +6713,11 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="X29" s="33" t="n"/>
+      <c r="X29" s="33" t="inlineStr">
+        <is>
+          <t>The initial source associated with the Murata cyberattack was blocked. During review, the event was misclassified and was not escalated at the appropriate time, resulting in a missed WarRoom and delayed customer notification. The case was reviewed with the reporting team, validation requirements were reinforced, and additional focus was placed on cyber events and blocked-source scenarios. The primary root cause was an incorrect review and escalation decision; the blocked source was a contributing factor.</t>
+        </is>
+      </c>
       <c r="Y29" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -7886,12 +7890,12 @@
       </c>
       <c r="I41" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J41" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K41" s="33" t="inlineStr">
@@ -7948,7 +7952,11 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="X41" s="33" t="n"/>
+      <c r="X41" s="33" t="inlineStr">
+        <is>
+          <t>The first public report was published on April 28, 2026, at 3:07 PM PST. EventWatch captured the report at 4:39 PM PST and correctly identified it as an event. The reporting team subsequently deprioritized the event despite indications of increasing severity, delaying escalation. Additional feeds received on April 29 prompted reassessment, and a WarRoom was created at 1:02 PM PST. The investigation concluded that this was an analysis and escalation lapse rather than a detection gap.</t>
+        </is>
+      </c>
       <c r="Y41" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -9450,7 +9458,7 @@
       </c>
       <c r="J56" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K56" s="33" t="inlineStr">
@@ -10634,7 +10642,7 @@
       </c>
       <c r="J67" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier Selection Miss</t>
         </is>
       </c>
       <c r="K67" s="33" t="inlineStr">
@@ -11415,12 +11423,12 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Methodology Weakness</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11483,7 +11491,7 @@
       </c>
       <c r="Y74" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z74" s="37" t="n">
@@ -12420,7 +12428,7 @@
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12858,7 +12866,7 @@
       </c>
       <c r="J87" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Platform Bug</t>
         </is>
       </c>
       <c r="K87" s="33" t="inlineStr">
@@ -12883,7 +12891,7 @@
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
+          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt. Whitespace / data-hygiene matching defect fixed under TENAR-45367.</t>
         </is>
       </c>
       <c r="P87" s="33" t="n"/>
@@ -13302,7 +13310,7 @@
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13519,12 +13527,12 @@
       </c>
       <c r="I93" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J93" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Clustering / Duplication Defect</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -13534,7 +13542,7 @@
       </c>
       <c r="L93" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M93" s="33" t="inlineStr">
@@ -13587,7 +13595,7 @@
       </c>
       <c r="Y93" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z93" s="37" t="n">
@@ -14710,7 +14718,7 @@
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Mapping / Routing Defect</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14735,7 +14743,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Probable geocoding / address-to-coordinate mismatch. The impact polygon and automated selection operated on the coordinates available in the system. Detailed validation of the coordinate source and assignment process was referred to the Data team.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14938,7 +14946,7 @@
       </c>
       <c r="J106" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K106" s="33" t="inlineStr">
@@ -15613,12 +15621,12 @@
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Model Classification Defect</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15643,7 +15651,7 @@
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. Internal RCA completed. EventWatch captured the relevant articles, but the AI classification models incorrectly categorized them as Not Impactful, and the subsequent human-in-the-loop review did not correct the misclassification. The event was re-evaluated and published following the customer inquiry. Current investigation loop closed; reopen only if additional customer questions require further review.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
@@ -15668,7 +15676,7 @@
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Classification &amp; Impact Validation</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
@@ -15678,12 +15686,12 @@
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. An RCA was issued to General Mills on 13-Oct-2026 as an attachment on EAO-51. Its text is not in the ticket, so it is not reproduced here. The ticket is still open at Approval Requested, and three of the four articles raised with monitoring are not yet accounted for.</t>
+          <t>EventWatch successfully captured the relevant articles. The AI classification models incorrectly categorized the feeds as Not Impactful. The subsequent human-in-the-loop review did not identify or correct the misclassification, so the event was excluded from publication despite meeting the applicable cybersecurity reporting criteria. Following the customer inquiry the event was re-evaluated and published. The internal RCA is complete and attached to EAO-51, and was reviewed for corrective and preventive measures. Four articles were raised with monitoring; engineering traced one of them (undercodenews) to cluster cyber_attack_dt_20260915155539357_not.impactful., and the other three remain open with PM.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
@@ -15837,12 +15845,12 @@
       </c>
       <c r="I114" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15907,7 +15915,7 @@
       </c>
       <c r="Y114" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z114" s="37" t="n"/>
@@ -16410,7 +16418,7 @@
       </c>
       <c r="J119" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier Selection Miss</t>
         </is>
       </c>
       <c r="K119" s="33" t="inlineStr">
@@ -16420,7 +16428,7 @@
       </c>
       <c r="L119" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M119" s="33" t="inlineStr">
@@ -16850,7 +16858,7 @@
       </c>
       <c r="J123" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier / Site Not Shared</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -16953,12 +16961,12 @@
       </c>
       <c r="I124" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J124" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Analyst Review Miss</t>
         </is>
       </c>
       <c r="K124" s="33" t="inlineStr">
@@ -16968,7 +16976,7 @@
       </c>
       <c r="L124" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M124" s="33" t="inlineStr">
@@ -17008,18 +17016,18 @@
       </c>
       <c r="V124" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W124" s="33" t="n"/>
       <c r="X124" s="33" t="inlineStr">
         <is>
-          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+          <t>EventWatch captured the relevant articles on 07-Oct-2026 and 08-Oct-2026. The event was classified Not Impactful during human-in-the-loop review. The customer inquiry was received on 09-Oct-2026, the event was re-evaluated and a WarRoom was created, and the bulletin published on 10-Oct-2026. The RCA identifies incorrect human assessment as the root cause.</t>
         </is>
       </c>
       <c r="Y124" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z124" s="37" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -11453,7 +11453,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="X74" s="33" t="inlineStr">
         <is>
-          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+          <t>A methodology weakness that Resilinc accepted, rather than an analyst execution error. EventWatch captured multiple public reports of the June 28, 2026 fire at the foam-manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models categorized the event as Not Impactful based on the relevance assessment, including the absence of confirmed downstream supply-chain impact in the available reporting. The reporting team reviewed the captured articles through the human-in-the-loop process and concurred with the classification, so the event was not published. The investigation concluded that the weakness was in the relevance-assessment methodology itself. Significant industrial incidents required greater evaluation based on incident severity, manufacturing activity, facility type, industry relevance, and potential downstream impact, even when the available reporting did not yet confirm a direct supply-chain disruption. Resilinc accepted this methodology weakness, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models. An earlier version of this entry listed the company's absence from the supplier database as a ground for the Not Impactful classification. That explanation is superseded. Supplier mapping was not a dominant input to the Event/Non-Event or Impactful/Not-Impactful classification decision.</t>
         </is>
       </c>
       <c r="Y74" s="33" t="inlineStr">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="O119" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Analyst research and site-selection issue. Available reporting described flooding beyond Bangkok, but the initial assessment focused only on Bangkok and did not evaluate the other affected regions. The relevant Delta Electronics site was consequently omitted from the initial WarRoom. Ticket remains open with no formal RCA; status retained as Clarification Provided.</t>
         </is>
       </c>
       <c r="P119" s="33" t="n"/>
@@ -16476,7 +16476,11 @@
           <t>EAO-49</t>
         </is>
       </c>
-      <c r="X119" s="33" t="n"/>
+      <c r="X119" s="33" t="inlineStr">
+        <is>
+          <t>The initial EventWatch assessment focused on Bangkok and did not sufficiently evaluate the broader affected geography identified in the available reporting. The articles indicated that flooding extended beyond Bangkok into other affected regions. However, the analyst did not complete the additional regional research required to assess those locations and identify the relevant Delta Electronics site for inclusion in the initial WarRoom. The relevant site was omitted because the initial assessment remained limited to Bangkok, rather than because of a Product mapping, geocoding, portal-visibility, or source-detection failure. The issue originated in incomplete analyst research and impacted-site selection.</t>
+        </is>
+      </c>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>38</v>
+                  <v>39</v>
                 </pt>
                 <pt idx="2">
-                  <v>15</v>
+                  <v>16</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>60</v>
                 </pt>
                 <pt idx="1">
-                  <v>36</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>6</v>
@@ -2941,9 +2941,9 @@
           </dLbls>
           <cat>
             <strRef>
-              <f>Dashboard!$E$67:$E$75</f>
+              <f>Dashboard!$E$67:$E$76</f>
               <strCache>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>WarRoom &amp; Decision Validation</v>
                 </pt>
@@ -2971,20 +2971,23 @@
                 <pt idx="8">
                   <v>Notification Visibility Monitoring</v>
                 </pt>
+                <pt idx="9">
+                  <v>Classification &amp; Impact Validation</v>
+                </pt>
               </strCache>
             </strRef>
           </cat>
           <val>
             <numRef>
-              <f>Dashboard!$F$67:$F$75</f>
+              <f>Dashboard!$F$67:$F$76</f>
               <numCache>
                 <formatCode>General</formatCode>
-                <ptCount val="9"/>
+                <ptCount val="10"/>
                 <pt idx="0">
                   <v>31</v>
                 </pt>
                 <pt idx="1">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3006,6 +3009,9 @@
                 </pt>
                 <pt idx="8">
                   <v>10</v>
+                </pt>
+                <pt idx="9">
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -3376,7 +3382,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E155" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E166" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -5096,7 +5102,7 @@
       </c>
       <c r="J14" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Mapping / Routing Defect</t>
         </is>
       </c>
       <c r="K14" s="33" t="inlineStr">
@@ -5121,7 +5127,7 @@
       </c>
       <c r="O14" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3263 (Closed). Molex is an EventWatch-only customer with no SCVs launched, so no sites should show with source Partner, yet ARROW ELECTRONICS - GBR BERKSHIRE READING appeared at Tier 1. The site_shareable record under the Molex tenant had its source_id mapped to the HITACHI ENERGY MAP demo org, so demo-org sites leaked into a production portal.</t>
+          <t>From Jira CAN-3263 (Closed). Molex is an EventWatch-only customer with no SCVs launched, so no sites should show with source Partner, yet ARROW ELECTRONICS - GBR BERKSHIRE READING appeared at Tier 1. The site_shareable record under the Molex tenant had its source_id mapped to the HITACHI ENERGY MAP demo org, so demo-org sites leaked into a production portal. Cross-Tenant Data Contamination.</t>
         </is>
       </c>
       <c r="P14" s="33" t="n"/>
@@ -6650,7 +6656,7 @@
       </c>
       <c r="J29" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Analyst Review Miss</t>
         </is>
       </c>
       <c r="K29" s="33" t="inlineStr">
@@ -6675,7 +6681,7 @@
       </c>
       <c r="O29" s="33" t="inlineStr">
         <is>
-          <t>25-day delay flagged by customer; blocked source + misclassification. Retraining completed.</t>
+          <t>25-day delay flagged by customer; blocked source + misclassification. Retraining completed. Blocked initial source.</t>
         </is>
       </c>
       <c r="P29" s="33" t="inlineStr">
@@ -6707,7 +6713,11 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="X29" s="33" t="n"/>
+      <c r="X29" s="33" t="inlineStr">
+        <is>
+          <t>The initial source associated with the Murata cyberattack was blocked. During review, the event was misclassified and was not escalated at the appropriate time, resulting in a missed WarRoom and delayed customer notification. The case was reviewed with the reporting team, validation requirements were reinforced, and additional focus was placed on cyber events and blocked-source scenarios. The primary root cause was an incorrect review and escalation decision; the blocked source was a contributing factor.</t>
+        </is>
+      </c>
       <c r="Y29" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -7880,12 +7890,12 @@
       </c>
       <c r="I41" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J41" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K41" s="33" t="inlineStr">
@@ -7942,7 +7952,11 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="X41" s="33" t="n"/>
+      <c r="X41" s="33" t="inlineStr">
+        <is>
+          <t>The first public report was published on April 28, 2026, at 3:07 PM PST. EventWatch captured the report at 4:39 PM PST and correctly identified it as an event. The reporting team subsequently deprioritized the event despite indications of increasing severity, delaying escalation. Additional feeds received on April 29 prompted reassessment, and a WarRoom was created at 1:02 PM PST. The investigation concluded that this was an analysis and escalation lapse rather than a detection gap.</t>
+        </is>
+      </c>
       <c r="Y41" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -9444,7 +9458,7 @@
       </c>
       <c r="J56" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K56" s="33" t="inlineStr">
@@ -10628,7 +10642,7 @@
       </c>
       <c r="J67" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier Selection Miss</t>
         </is>
       </c>
       <c r="K67" s="33" t="inlineStr">
@@ -11409,12 +11423,12 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Methodology Weakness</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11439,7 +11453,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. Established as a relevance-scoring weakness rather than an analyst error: the event was captured, classified Not Impactful because the company was unmapped, and the analyst review concurred. Resilinc accepted the customer's challenge to the methodology, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models by end July 2026.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11472,12 +11486,12 @@
       </c>
       <c r="X74" s="33" t="inlineStr">
         <is>
-          <t>A methodology weakness that Resilinc accepted, not an analyst error. EventWatch did capture multiple public reports of the 28-Jun-2026 fire at the foam manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models then categorised it Not Impactful on three grounds: the company was not a mapped supplier in the database, no mapped supplier sites sat near the incident, and public reporting described a mattress/foam plant fire with no confirmed downstream impact. The reporting team reviewed the captured articles under human-in-the-loop validation and concurred, so nothing was published. The Force Majeure that Sage Automotive Interiors issued could not be confirmed in English or Spanish public sources and appears to have gone through direct supplier channels, so EventWatch could not publish it either; a monitoring record was created to catch any public confirmation. The customer challenged the methodology itself - why supplier presence in an internal database filters an assessment that is meant to rest on public information - and Resilinc agreed the observation was right. Interim corrective action, in force now: major industrial incidents at manufacturing facilities initially classified Not Impactful get an additional manual review, and are no longer closed solely on the absence of mapped suppliers or immediately confirmed downstream impact; analysts weigh facility type, manufacturing activity, incident severity, industry relevance and downstream potential before the publication decision. Permanent corrective action: the AI relevance-scoring models are being enhanced so supplier mapping is no longer a dominant factor, shared with Data Science and on the AI roadmap, targeted for deployment by end July 2026, at which point the interim manual control folds into the automated decision.</t>
+          <t>A methodology weakness that Resilinc accepted, rather than an analyst execution error. EventWatch captured multiple public reports of the June 28, 2026 fire at the foam-manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models categorized the event as Not Impactful based on the relevance assessment, including the absence of confirmed downstream supply-chain impact in the available reporting. The reporting team reviewed the captured articles through the human-in-the-loop process and concurred with the classification, so the event was not published. The investigation concluded that the weakness was in the relevance-assessment methodology itself. Significant industrial incidents required greater evaluation based on incident severity, manufacturing activity, facility type, industry relevance, and potential downstream impact, even when the available reporting did not yet confirm a direct supply-chain disruption. Resilinc accepted this methodology weakness, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models. An earlier version of this entry listed the company's absence from the supplier database as a ground for the Not Impactful classification. That explanation is superseded. Supplier mapping was not a dominant input to the Event/Non-Event or Impactful/Not-Impactful classification decision.</t>
         </is>
       </c>
       <c r="Y74" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z74" s="37" t="n">
@@ -12414,7 +12428,7 @@
       </c>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K83" s="33" t="inlineStr">
@@ -12852,7 +12866,7 @@
       </c>
       <c r="J87" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Platform Bug</t>
         </is>
       </c>
       <c r="K87" s="33" t="inlineStr">
@@ -12877,7 +12891,7 @@
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt.</t>
+          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt. Whitespace / data-hygiene matching defect fixed under TENAR-45367.</t>
         </is>
       </c>
       <c r="P87" s="33" t="n"/>
@@ -13296,7 +13310,7 @@
       </c>
       <c r="J91" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K91" s="33" t="inlineStr">
@@ -13513,12 +13527,12 @@
       </c>
       <c r="I93" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J93" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Clustering / Duplication Defect</t>
         </is>
       </c>
       <c r="K93" s="33" t="inlineStr">
@@ -13528,7 +13542,7 @@
       </c>
       <c r="L93" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M93" s="33" t="inlineStr">
@@ -13581,7 +13595,7 @@
       </c>
       <c r="Y93" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z93" s="37" t="n">
@@ -14704,7 +14718,7 @@
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Mapping / Routing Defect</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14729,7 +14743,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Probable geocoding / address-to-coordinate mismatch. The impact polygon and automated selection operated on the coordinates available in the system. Detailed validation of the coordinate source and assignment process was referred to the Data team.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14932,7 +14946,7 @@
       </c>
       <c r="J106" s="33" t="inlineStr">
         <is>
-          <t>Policy/Logic</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K106" s="33" t="inlineStr">
@@ -15607,12 +15621,12 @@
       </c>
       <c r="I112" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J112" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Model Classification Defect</t>
         </is>
       </c>
       <c r="K112" s="33" t="inlineStr">
@@ -15637,7 +15651,7 @@
       </c>
       <c r="O112" s="33" t="inlineStr">
         <is>
-          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. The owner has classified this as a People issue: the article that was captured reached the portal, and a person marked its cluster not impactful, which is the analyst-overlooked test - so the row is People / Review, routed to EventWatch Ops, with a not-impactful decision check as the remedy. The keyword question on the three articles not yet accounted for stays open with PM, but it is not what this row is filed under.</t>
+          <t>General Mills asked why no WarRoom was created for the ADM data breach, which reached them on 16-Sep-2026 through their own internal cross-functional threat teams rather than through EventWatch. ADM is reported to be targeted by the Qilin ransomware group, which claims to have infiltrated ADM's network; potentially exposed information includes employee records and contact details, financial and internal business information, login credentials and possibly Social Security numbers. Scope and timeline are unconfirmed - ADM has not publicly disclosed the number of affected individuals, the discovery date, the duration of unauthorised access, investigation details or regulatory notifications. Follow-on risks the customer names are phishing, credential compromise, identity theft and exposure of sensitive corporate information. Internal investigation found the event was not captured on the portal and identifies it as a source coverage issue, and that finding has been shared with the customer. The CSM first raised this by email rather than by opening a ticket; EAO-51 was opened on 08-Oct-2026 for the same incident and this row carries that key. The open question there is why the event was not notified on 15-Sep: a WarRoom titled 'Archer-Daniels-Midland Company Named in Qilin Ransomware Data Theft Claim' was created on 29-Sep-2026, so the event was captured late rather than never, and the monitoring team has been asked why four named news articles were not picked up by the portal at the time. Engineering has since traced one of the four articles; the other three remain open with PM. Internal RCA completed. EventWatch captured the relevant articles, but the AI classification models incorrectly categorized them as Not Impactful, and the subsequent human-in-the-loop review did not correct the misclassification. The event was re-evaluated and published following the customer inquiry. Current investigation loop closed; reopen only if additional customer questions require further review.</t>
         </is>
       </c>
       <c r="P112" s="33" t="n"/>
@@ -15662,7 +15676,7 @@
       </c>
       <c r="V112" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Classification &amp; Impact Validation</t>
         </is>
       </c>
       <c r="W112" s="33" t="inlineStr">
@@ -15672,12 +15686,12 @@
       </c>
       <c r="X112" s="33" t="inlineStr">
         <is>
-          <t>Four articles were raised with monitoring. Engineering traced one of them (undercodenews) and found it had been captured by the cyber attack RSS and linked to an existing cluster (cyber_attack_dt_20260915155539357_not.impactful._) which was later marked as not impactful; the other three are not accounted for yet. The owner classifies this as a People issue: the story did reach the portal and the not-impactful call was made by a person, so the failure is the quality of that review rather than the reach of the system. Not a source-coverage gap - the row carried that reading before the investigation reported, and it is corrected here. An RCA was issued to General Mills on 13-Oct-2026 as an attachment on EAO-51. Its text is not in the ticket, so it is not reproduced here. The ticket is still open at Approval Requested, and three of the four articles raised with monitoring are not yet accounted for.</t>
+          <t>EventWatch successfully captured the relevant articles. The AI classification models incorrectly categorized the feeds as Not Impactful. The subsequent human-in-the-loop review did not identify or correct the misclassification, so the event was excluded from publication despite meeting the applicable cybersecurity reporting criteria. Following the customer inquiry the event was re-evaluated and published. The internal RCA is complete and attached to EAO-51, and was reviewed for corrective and preventive measures. Four articles were raised with monitoring; engineering traced one of them (undercodenews) to cluster cyber_attack_dt_20260915155539357_not.impactful., and the other three remain open with PM.</t>
         </is>
       </c>
       <c r="Y112" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z112" s="37" t="n"/>
@@ -15831,12 +15845,12 @@
       </c>
       <c r="I114" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J114" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Deliberate Rule</t>
         </is>
       </c>
       <c r="K114" s="33" t="inlineStr">
@@ -15901,7 +15915,7 @@
       </c>
       <c r="Y114" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z114" s="37" t="n"/>
@@ -16404,7 +16418,7 @@
       </c>
       <c r="J119" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier Selection Miss</t>
         </is>
       </c>
       <c r="K119" s="33" t="inlineStr">
@@ -16414,7 +16428,7 @@
       </c>
       <c r="L119" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M119" s="33" t="inlineStr">
@@ -16429,7 +16443,7 @@
       </c>
       <c r="O119" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Cause per EventWatch Ops: the analyst did not research the region beyond Bangkok when scoping the initial impacted-site list.</t>
+          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Analyst research and site-selection issue. Available reporting described flooding beyond Bangkok, but the initial assessment focused only on Bangkok and did not evaluate the other affected regions. The relevant Delta Electronics site was consequently omitted from the initial WarRoom. Ticket remains open with no formal RCA; status retained as Clarification Provided.</t>
         </is>
       </c>
       <c r="P119" s="33" t="n"/>
@@ -16462,7 +16476,11 @@
           <t>EAO-49</t>
         </is>
       </c>
-      <c r="X119" s="33" t="n"/>
+      <c r="X119" s="33" t="inlineStr">
+        <is>
+          <t>The initial EventWatch assessment focused on Bangkok and did not sufficiently evaluate the broader affected geography identified in the available reporting. The articles indicated that flooding extended beyond Bangkok into other affected regions. However, the analyst did not complete the additional regional research required to assess those locations and identify the relevant Delta Electronics site for inclusion in the initial WarRoom. The relevant site was omitted because the initial assessment remained limited to Bangkok, rather than because of a Product mapping, geocoding, portal-visibility, or source-detection failure. The issue originated in incomplete analyst research and impacted-site selection.</t>
+        </is>
+      </c>
       <c r="Y119" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -16844,7 +16862,7 @@
       </c>
       <c r="J123" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier / Site Not Shared</t>
         </is>
       </c>
       <c r="K123" s="33" t="inlineStr">
@@ -16947,12 +16965,12 @@
       </c>
       <c r="I124" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J124" s="33" t="inlineStr">
         <is>
-          <t>Captured Late</t>
+          <t>Analyst Review Miss</t>
         </is>
       </c>
       <c r="K124" s="33" t="inlineStr">
@@ -16962,7 +16980,7 @@
       </c>
       <c r="L124" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M124" s="33" t="inlineStr">
@@ -17002,18 +17020,18 @@
       </c>
       <c r="V124" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W124" s="33" t="n"/>
       <c r="X124" s="33" t="inlineStr">
         <is>
-          <t>No agreed RCA yet. What the timeline establishes: the searches were conducted on 07-Oct-2026 and reported publicly before EventWatch carried anything, the customer raised the gap on 09-Oct, and the bulletin published at 12:07 AM IST on 10-Oct, after the escalation. The event therefore reached publication but not in time, and whether the delay sits in source coverage, keyword matching or the publishing pipeline is the open question. The customer's source list is part of that same investigation rather than a separate coverage query.</t>
+          <t>EventWatch captured the relevant articles on 07-Oct-2026 and 08-Oct-2026. The event was classified Not Impactful during human-in-the-loop review. The customer inquiry was received on 09-Oct-2026, the event was re-evaluated and a WarRoom was created, and the bulletin published on 10-Oct-2026. The RCA identifies incorrect human assessment as the root cause.</t>
         </is>
       </c>
       <c r="Y124" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z124" s="37" t="n"/>
@@ -19262,17 +19280,17 @@
         <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
-      <c r="E76" s="25" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F76" s="26">
-        <f>SUM(F67:F75)</f>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>Classification &amp; Impact Validation</t>
+        </is>
+      </c>
+      <c r="F76" s="22">
+        <f>COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Standard Automation Focus],E76)</f>
         <v/>
       </c>
-      <c r="G76" s="27">
-        <f>SUM(G67:G75)</f>
+      <c r="G76" s="24">
+        <f>F76/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
         <v/>
       </c>
       <c r="H76" s="3" t="n"/>
@@ -19306,9 +19324,19 @@
         <v/>
       </c>
       <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
+      <c r="E77" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F77" s="26">
+        <f>SUM(F67:F76)</f>
+        <v/>
+      </c>
+      <c r="G77" s="27">
+        <f>SUM(G67:G76)</f>
+        <v/>
+      </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="20" t="inlineStr">
         <is>
@@ -20231,7 +20259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24383,6 +24411,303 @@
       <c r="E155" s="41" t="inlineStr">
         <is>
           <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30.75" customHeight="1">
+      <c r="A156" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B156" s="41" t="inlineStr">
+        <is>
+          <t>Published Late</t>
+        </is>
+      </c>
+      <c r="C156" s="41" t="inlineStr">
+        <is>
+          <t>The event was available to analysts in time for review, but publication or escalation occurred materially late because of delayed analysis, prioritization, research, or operational handling.</t>
+        </is>
+      </c>
+      <c r="D156" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The story reached a person in time; what was late was the decision to raise it. Use Alerting Gap where the item never reached the analyst, and Captured Late where our own first usable capture came late.</t>
+        </is>
+      </c>
+      <c r="E156" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30.75" customHeight="1">
+      <c r="A157" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B157" s="41" t="inlineStr">
+        <is>
+          <t>Methodology Weakness</t>
+        </is>
+      </c>
+      <c r="C157" s="41" t="inlineStr">
+        <is>
+          <t>The available methodology, reporting guidance, or evaluation approach was inadequate and led to the wrong outcome, even though the workflow was performed as designed.</t>
+        </is>
+      </c>
+      <c r="D157" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Nobody departed from the guidance; the guidance itself was deficient and the deficiency was accepted. Use Deliberate Rule where the rule was adequate and the customer simply queried it.</t>
+        </is>
+      </c>
+      <c r="E157" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30.75" customHeight="1">
+      <c r="A158" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B158" s="41" t="inlineStr">
+        <is>
+          <t>Deliberate Rule</t>
+        </is>
+      </c>
+      <c r="C158" s="41" t="inlineStr">
+        <is>
+          <t>The system or team acted according to an approved reporting rule, threshold, or internal convention. The customer questioned the rule, but no miss or defect occurred under the rule then in force.</t>
+        </is>
+      </c>
+      <c r="D158" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. A rule changed afterwards is an enhancement, not a fault, and the record stays here. Use Methodology Weakness where the rule itself was accepted as deficient.</t>
+        </is>
+      </c>
+      <c r="E158" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30.75" customHeight="1">
+      <c r="A159" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B159" s="41" t="inlineStr">
+        <is>
+          <t>Platform Bug</t>
+        </is>
+      </c>
+      <c r="C159" s="41" t="inlineStr">
+        <is>
+          <t>A confirmed software, code, system, or data-processing defect produced incorrect Product behavior and does not fit the more specific categories of Alerting Gap, Clustering / Duplication Defect, Model Classification Defect, or Mapping / Routing Defect.</t>
+        </is>
+      </c>
+      <c r="D159" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The residual Product defect category, used only once the four specific defect categories have been ruled out. Requires a confirmed defect, not a suspected one.</t>
+        </is>
+      </c>
+      <c r="E159" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30.75" customHeight="1">
+      <c r="A160" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B160" s="41" t="inlineStr">
+        <is>
+          <t>Mapping / Routing Defect</t>
+        </is>
+      </c>
+      <c r="C160" s="41" t="inlineStr">
+        <is>
+          <t>Incorrect system data, association, coordinates, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
+        </is>
+      </c>
+      <c r="D160" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers geocoding and address-to-coordinate mismatches, cross-tenant leakage and entity mislinkage. Use Supplier / Site Not Shared where the data was never provided at all.</t>
+        </is>
+      </c>
+      <c r="E160" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30.75" customHeight="1">
+      <c r="A161" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B161" s="41" t="inlineStr">
+        <is>
+          <t>Supplier / Site Not Shared</t>
+        </is>
+      </c>
+      <c r="C161" s="41" t="inlineStr">
+        <is>
+          <t>The affected supplier, company, or site was not present in the customer-provided or customer-maintained data available to EventWatch. The issue is an input-data dependency rather than a Product or analyst failure.</t>
+        </is>
+      </c>
+      <c r="D161" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. There was nothing for the event to match against, so neither the platform nor analyst review failed. The remedy is our process for collecting the customer's facility data.</t>
+        </is>
+      </c>
+      <c r="E161" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30.75" customHeight="1">
+      <c r="A162" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B162" s="41" t="inlineStr">
+        <is>
+          <t>Analyst Review Miss</t>
+        </is>
+      </c>
+      <c r="C162" s="41" t="inlineStr">
+        <is>
+          <t>The relevant story was available for human review, but it was incorrectly rejected, closed, deprioritized, or insufficiently researched, resulting in a missed customer notification.</t>
+        </is>
+      </c>
+      <c r="D162" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. A person had it in front of them and the quality of that look is the failure. Use Model Classification Defect where an automated model made the call, and Published Late where the item was eventually raised but too late.</t>
+        </is>
+      </c>
+      <c r="E162" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="30.75" customHeight="1">
+      <c r="A163" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B163" s="41" t="inlineStr">
+        <is>
+          <t>Supplier Selection Miss</t>
+        </is>
+      </c>
+      <c r="C163" s="41" t="inlineStr">
+        <is>
+          <t>The relevant supplier, company, facility, location, or impact area was available during bulletin or WarRoom preparation but was omitted from the initial impacted selection.</t>
+        </is>
+      </c>
+      <c r="D163" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The event was published and the supplier data was on file; an analyst left it out of the initial selection or geofence. Normally carries Missed_Flag No, since the customer did receive the event.</t>
+        </is>
+      </c>
+      <c r="E163" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30.75" customHeight="1">
+      <c r="A164" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B164" s="41" t="inlineStr">
+        <is>
+          <t>Clustering / Duplication Defect</t>
+        </is>
+      </c>
+      <c r="C164" s="41" t="inlineStr">
+        <is>
+          <t>Product incorrectly grouped, split, duplicated, or associated stories or bulletins across clusters or WarRooms, resulting in incomplete, duplicate, or disrupted event handling.</t>
+        </is>
+      </c>
+      <c r="D164" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. Covers a split update sequence, a duplicated WarRoom and a cluster state that mishandles a correctly captured story.</t>
+        </is>
+      </c>
+      <c r="E164" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30.75" customHeight="1">
+      <c r="A165" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B165" s="41" t="inlineStr">
+        <is>
+          <t>Model Classification Defect</t>
+        </is>
+      </c>
+      <c r="C165" s="41" t="inlineStr">
+        <is>
+          <t>The relevant article or event was captured and entered the Product workflow, but an automated classification model assigned an incorrect event, relevance, or impact outcome, causing the item to be excluded, misrouted, or handled incorrectly.</t>
+        </is>
+      </c>
+      <c r="D165" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The model made the call. A human review that failed to correct the model is a contributing factor recorded in Comments, not a reason to file the record under Analyst Review Miss.</t>
+        </is>
+      </c>
+      <c r="E165" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30.75" customHeight="1">
+      <c r="A166" s="42" t="inlineStr">
+        <is>
+          <t>Automation focus</t>
+        </is>
+      </c>
+      <c r="B166" s="41" t="inlineStr">
+        <is>
+          <t>Classification &amp; Impact Validation</t>
+        </is>
+      </c>
+      <c r="C166" s="41" t="inlineStr">
+        <is>
+          <t>Controls that validate automated event, relevance, and impact classifications and identify cases where model output requires correction before final disposition.</t>
+        </is>
+      </c>
+      <c r="D166" s="41" t="inlineStr">
+        <is>
+          <t>Standardized dashboard category</t>
+        </is>
+      </c>
+      <c r="E166" s="41" t="inlineStr">
+        <is>
+          <t>Standard Automation Focus</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1275,7 +1275,7 @@
                   <v>8</v>
                 </pt>
                 <pt idx="2">
-                  <v>14</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
@@ -1397,7 +1397,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="2">
-                  <v>0</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
@@ -1774,7 +1774,7 @@
                   <v>39</v>
                 </pt>
                 <pt idx="2">
-                  <v>16</v>
+                  <v>15</v>
                 </pt>
                 <pt idx="3">
                   <v>3</v>
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>60</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>39</v>
                 </pt>
                 <pt idx="2">
-                  <v>6</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>27</v>
+                  <v>26</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2993,7 +2993,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>7</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="4">
                   <v>9</v>
@@ -4794,12 +4794,12 @@
       </c>
       <c r="I11" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J11" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Event Identification</t>
         </is>
       </c>
       <c r="K11" s="33" t="inlineStr">
@@ -4824,13 +4824,13 @@
       </c>
       <c r="O11" s="33" t="inlineStr">
         <is>
-          <t>AI classification bias + missed human escalation; WarRoom created after reassessment. NC issued.</t>
+          <t>AI classification bias + missed human escalation; WarRoom created after reassessment. NC issued. Settled by the owner: the bulletin was already published. The analyst selected the wrong event type and reviewer validation did not correct it. This is an analyst-understanding and classification complaint, not a missed bulletin, so Missed_Flag is No.</t>
         </is>
       </c>
       <c r="P11" s="33" t="n"/>
       <c r="Q11" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R11" s="39" t="n">
@@ -4853,7 +4853,7 @@
       <c r="X11" s="33" t="n"/>
       <c r="Y11" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z11" s="37" t="n"/>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="J21" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Model Classification Defect</t>
         </is>
       </c>
       <c r="K21" s="33" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="O21" s="33" t="inlineStr">
         <is>
-          <t>AI classified LPG shortage as Non-Event; human review missed embedded company-impact articles. Dedicated WarRoom created.</t>
+          <t>AI classified LPG shortage as Non-Event; human review missed embedded company-impact articles. Dedicated WarRoom created. Settled by the owner: the Product model incorrectly classified the captured event as Not Impactful, and human review did not correct the classification. Filed under the model defect rather than Review, because the first wrong call was the model's.</t>
         </is>
       </c>
       <c r="P21" s="33" t="n"/>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H24" s="33" t="inlineStr">
@@ -6159,13 +6159,13 @@
       </c>
       <c r="O24" s="33" t="inlineStr">
         <is>
-          <t>SEC notification delay investigation requested; awaiting closure inputs.</t>
+          <t>SEC notification delay investigation requested; awaiting closure inputs. Settled by the owner: the claimed news was not available in the public domain, so EventWatch could not report it. No EventWatch failure was established, so this is an Inquiry and Missed_Flag is No. Kept under Process Clarification rather than adding a Scope or Threshold Clarification sub-type.</t>
         </is>
       </c>
       <c r="P24" s="33" t="n"/>
       <c r="Q24" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R24" s="39" t="n">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Methodology Weakness</t>
+          <t>Model Classification Defect</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input. Settled by the owner: the reports were captured, but Product incorrectly classified the event as Not Impactful. The customer later raised the event, after which it was reported. Filed as a model classification defect rather than a methodology weakness.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="Y74" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z74" s="37" t="n">
@@ -11647,12 +11647,12 @@
       </c>
       <c r="I76" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Creation</t>
+          <t>Mapping / Routing Defect</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="O76" s="33" t="inlineStr">
         <is>
-          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing.</t>
+          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing. Settled by the owner: the bulletin existed, but the applicable customer WarRoom was not created because supplier and site normalization was not applied correctly.</t>
         </is>
       </c>
       <c r="P76" s="33" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="Y76" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z76" s="37" t="n">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="I97" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J97" s="33" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Industry selection</t>
         </is>
       </c>
       <c r="K97" s="33" t="inlineStr">
@@ -13999,13 +13999,13 @@
       </c>
       <c r="O97" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided.</t>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided. Settled by the owner: the bulletin was published, but the analyst selected incomplete industries and review did not correct the selection. This is a publishing-quality complaint, not a missed bulletin, so Missed_Flag is No.</t>
         </is>
       </c>
       <c r="P97" s="33" t="n"/>
       <c r="Q97" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R97" s="39" t="n">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.34951456310679613</v>
+        <v>0.35294117647058826</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18941,7 +18941,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1262135922330097</v>
+        <v>0.12745098039215685</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18983,7 +18983,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06796116504854369</v>
+        <v>0.06862745098039216</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19025,7 +19025,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04854368932038835</v>
+        <v>0.049019607843137254</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19067,7 +19067,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.038834951456310676</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19109,7 +19109,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.02912621359223301</v>
+        <v>0.029411764705882353</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19151,7 +19151,7 @@
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19193,7 +19193,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19235,7 +19235,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19277,7 +19277,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19654,10 +19654,10 @@
         </is>
       </c>
       <c r="J89" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K89" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="76" t="n">
         <v>6</v>
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L93" s="77" t="n">
         <v>124</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1275,13 +1275,13 @@
                   <v>8</v>
                 </pt>
                 <pt idx="2">
-                  <v>13</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
                 </pt>
                 <pt idx="4">
-                  <v>18</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="5">
                   <v>9</v>
@@ -1397,13 +1397,13 @@
                   <v>1</v>
                 </pt>
                 <pt idx="2">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
                 </pt>
                 <pt idx="4">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -1771,10 +1771,10 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>39</v>
+                  <v>38</v>
                 </pt>
                 <pt idx="2">
-                  <v>15</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="3">
                   <v>3</v>
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>59</v>
                 </pt>
                 <pt idx="1">
-                  <v>39</v>
+                  <v>40</v>
                 </pt>
                 <pt idx="2">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
-                  <v>Belden Inc</v>
+                  <v>General Mills</v>
                 </pt>
                 <pt idx="7">
-                  <v>General Mills</v>
+                  <v>META</v>
                 </pt>
                 <pt idx="8">
-                  <v>META</v>
+                  <v>Merck</v>
                 </pt>
                 <pt idx="9">
-                  <v>Merck</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>36</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>26</v>
+                  <v>25</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>32</v>
@@ -2993,7 +2993,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="4">
                   <v>9</v>
@@ -3008,7 +3008,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>10</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="9">
                   <v>1</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G19" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H19" s="33" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G45" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H45" s="33" t="inlineStr">
@@ -14005,7 +14005,7 @@
       <c r="P97" s="33" t="n"/>
       <c r="Q97" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R97" s="39" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G107" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H107" s="33" t="inlineStr">
@@ -15089,7 +15089,7 @@
       <c r="P107" s="33" t="n"/>
       <c r="Q107" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R107" s="39" t="n">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G117" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H117" s="33" t="inlineStr">
@@ -16223,7 +16223,7 @@
       <c r="P117" s="33" t="n"/>
       <c r="Q117" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R117" s="39" t="n">
@@ -18896,11 +18896,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35294117647058826</v>
+        <v>0.35</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18922,10 +18922,10 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K67" s="75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="75" t="n">
         <v>15</v>
@@ -18941,7 +18941,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12745098039215685</v>
+        <v>0.13</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18983,7 +18983,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.07</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19025,7 +19025,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.049019607843137254</v>
+        <v>0.05</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19048,10 +19048,10 @@
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K70" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="76" t="n">
         <v>15</v>
@@ -19067,7 +19067,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0392156862745098</v>
+        <v>0.04</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19109,7 +19109,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.029411764705882353</v>
+        <v>0.03</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19144,14 +19144,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19186,14 +19186,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19228,14 +19228,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19270,14 +19270,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19344,10 +19344,10 @@
         </is>
       </c>
       <c r="J77" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="76" t="n">
         <v>2</v>
@@ -19684,10 +19684,10 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
         <v>8</v>
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L93" s="77" t="n">
         <v>124</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>38</v>
+                  <v>39</v>
                 </pt>
                 <pt idx="2">
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="L120" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M120" s="33" t="inlineStr">
@@ -16598,7 +16598,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z120" s="37" t="n"/>
+      <c r="Z120" s="37" t="n">
+        <v>46309</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="35" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1275,13 +1275,13 @@
                   <v>8</v>
                 </pt>
                 <pt idx="2">
-                  <v>13</v>
+                  <v>12</v>
                 </pt>
                 <pt idx="3">
                   <v>11</v>
                 </pt>
                 <pt idx="4">
-                  <v>18</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="5">
                   <v>9</v>
@@ -1397,13 +1397,13 @@
                   <v>1</v>
                 </pt>
                 <pt idx="2">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="3">
                   <v>2</v>
                 </pt>
                 <pt idx="4">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -1774,10 +1774,10 @@
                   <v>39</v>
                 </pt>
                 <pt idx="2">
-                  <v>15</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,13 +2378,13 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>59</v>
                 </pt>
                 <pt idx="1">
-                  <v>39</v>
+                  <v>40</v>
                 </pt>
                 <pt idx="2">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
-                  <v>Belden Inc</v>
+                  <v>General Mills</v>
                 </pt>
                 <pt idx="7">
-                  <v>General Mills</v>
+                  <v>META</v>
                 </pt>
                 <pt idx="8">
-                  <v>META</v>
+                  <v>Merck</v>
                 </pt>
                 <pt idx="9">
-                  <v>Merck</v>
+                  <v>Schneider Electric</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>36</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>26</v>
+                  <v>25</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>31</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>32</v>
@@ -2993,7 +2993,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>6</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="4">
                   <v>9</v>
@@ -3008,7 +3008,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="8">
-                  <v>10</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="9">
                   <v>1</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G19" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H19" s="33" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="G45" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H45" s="33" t="inlineStr">
@@ -14005,7 +14005,7 @@
       <c r="P97" s="33" t="n"/>
       <c r="Q97" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R97" s="39" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G107" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H107" s="33" t="inlineStr">
@@ -15089,7 +15089,7 @@
       <c r="P107" s="33" t="n"/>
       <c r="Q107" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R107" s="39" t="n">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G117" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H117" s="33" t="inlineStr">
@@ -16223,7 +16223,7 @@
       <c r="P117" s="33" t="n"/>
       <c r="Q117" s="33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R117" s="39" t="n">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="L120" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M120" s="33" t="inlineStr">
@@ -16598,7 +16598,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z120" s="37" t="n"/>
+      <c r="Z120" s="37" t="n">
+        <v>46309</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="35" t="n">
@@ -18896,11 +18898,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35294117647058826</v>
+        <v>0.35</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18922,10 +18924,10 @@
         <v>Bankruptcy</v>
       </c>
       <c r="J67" s="75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K67" s="75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="75" t="n">
         <v>15</v>
@@ -18941,7 +18943,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12745098039215685</v>
+        <v>0.13</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18983,7 +18985,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.07</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19025,7 +19027,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.049019607843137254</v>
+        <v>0.05</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19048,10 +19050,10 @@
         </is>
       </c>
       <c r="J70" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K70" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="76" t="n">
         <v>15</v>
@@ -19067,7 +19069,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0392156862745098</v>
+        <v>0.04</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19109,7 +19111,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.029411764705882353</v>
+        <v>0.03</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19144,14 +19146,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19186,14 +19188,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19228,14 +19230,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19270,14 +19272,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19344,10 +19346,10 @@
         </is>
       </c>
       <c r="J77" s="76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="76" t="n">
         <v>2</v>
@@ -19684,10 +19686,10 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K90" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
         <v>8</v>
@@ -19774,10 +19776,10 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L93" s="77" t="n">
         <v>124</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="9">
-                  <v>4</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>106</v>
+                  <v>108</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>59</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
                   <v>40</v>
@@ -2639,16 +2639,16 @@
                   <v>Ford/GM</v>
                 </pt>
                 <pt idx="6">
+                  <v>Belden Inc</v>
+                </pt>
+                <pt idx="7">
                   <v>General Mills</v>
                 </pt>
-                <pt idx="7">
-                  <v>META</v>
-                </pt>
                 <pt idx="8">
-                  <v>Merck</v>
+                  <v>Irving Oil</v>
                 </pt>
                 <pt idx="9">
-                  <v>Schneider Electric</v>
+                  <v>META</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>25</v>
+                  <v>27</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2987,7 +2987,7 @@
                   <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3324,7 +3324,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z125" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z127" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z125"/>
+  <dimension ref="A1:Z127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="J125" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K125" s="33" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="M125" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Source onboarding and feed-receipt verification for Turkish-language business and regional news covering the Bursa automotive cluster, so a filing at a sub-tier supplier is carried when it is published rather than found when the customer raises it</t>
         </is>
       </c>
       <c r="N125" s="33" t="inlineStr">
@@ -17138,13 +17138,233 @@
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X125" s="33" t="n"/>
+      <c r="X125" s="33" t="inlineStr">
+        <is>
+          <t>Neither of the two Turkish-language sources carrying the Bursa fraud allegations is part of the vendor's monitoring network, established by Ankit Gupta on the ticket on 16-Oct-2026. The vendor has been asked to add them and is working on it. Not a keyword gap: the story never reached the application.</t>
+        </is>
+      </c>
       <c r="Y125" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z125" s="37" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B126" s="37" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C126" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D126" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E126" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="33" t="inlineStr">
+        <is>
+          <t>Gallium Arsenide and Indium Phosphide Semiconductor Supply-Chain Risk - No EventWatch Notification (Belden)</t>
+        </is>
+      </c>
+      <c r="G126" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H126" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I126" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K126" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L126" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M126" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage check for compound-semiconductor materials and substrate supply risk</t>
+        </is>
+      </c>
+      <c r="N126" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O126" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-54 (Open). Belden asked why news on gallium arsenide, indium phosphide and semiconductor supply-chain risk is not shown on the Resilinc platform. CS verified the Belden org and found no notification for the event, then checked the database across all customer orgs and found no evidence that any notification was generated or sent. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported. The reference detail on the ticket is an image that cannot be read from here, so the number of distinct events behind this query is unconfirmed. Whether the affected suppliers are mapped for Belden has not been asked, which is what unwound their earlier EAO-39 TSMC complaint.</t>
+        </is>
+      </c>
+      <c r="P126" s="33" t="n"/>
+      <c r="Q126" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R126" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S126" s="39" t="n"/>
+      <c r="T126" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U126" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V126" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W126" s="33" t="inlineStr">
+        <is>
+          <t>EAO-54</t>
+        </is>
+      </c>
+      <c r="X126" s="33" t="n"/>
+      <c r="Y126" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z126" s="37" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B127" s="37" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C127" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D127" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil</t>
+        </is>
+      </c>
+      <c r="E127" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="33" t="inlineStr">
+        <is>
+          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+        </is>
+      </c>
+      <c r="G127" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H127" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I127" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J127" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K127" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L127" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M127" s="33" t="inlineStr">
+        <is>
+          <t>Coverage check for acquisition announcements carried only in French-language Canadian business press</t>
+        </is>
+      </c>
+      <c r="N127" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O127" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+        </is>
+      </c>
+      <c r="P127" s="33" t="n"/>
+      <c r="Q127" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R127" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S127" s="39" t="n"/>
+      <c r="T127" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U127" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V127" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W127" s="33" t="inlineStr">
+        <is>
+          <t>EAO-55</t>
+        </is>
+      </c>
+      <c r="X127" s="33" t="n"/>
+      <c r="Y127" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z127" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18902,7 +19122,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18943,7 +19163,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13</v>
+        <v>0.12745098039215685</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18985,7 +19205,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07</v>
+        <v>0.06862745098039216</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19027,7 +19247,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.05</v>
+        <v>0.049019607843137254</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19069,7 +19289,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04</v>
+        <v>0.0392156862745098</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19111,7 +19331,7 @@
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03</v>
+        <v>0.029411764705882353</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19146,14 +19366,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19188,14 +19408,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19230,14 +19450,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Irving Oil</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19272,14 +19492,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02</v>
+        <v>0.0196078431372549</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19500,13 +19720,13 @@
         </is>
       </c>
       <c r="J83" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L83" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -19686,13 +19906,13 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19776,13 +19996,13 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K93" s="77" t="n">
         <v>24</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17192,7 +17192,7 @@
       </c>
       <c r="J126" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K126" s="33" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="M126" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage check for compound-semiconductor materials and substrate supply risk</t>
+          <t>Source onboarding and feed-receipt verification for compound-semiconductor trade press and commodity-market wires covering gallium, germanium, indium phosphide and epiwafer supply, so a materials-supply story is carried when it is published rather than found when the customer raises it</t>
         </is>
       </c>
       <c r="N126" s="33" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="O126" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). Belden asked why news on gallium arsenide, indium phosphide and semiconductor supply-chain risk is not shown on the Resilinc platform. CS verified the Belden org and found no notification for the event, then checked the database across all customer orgs and found no evidence that any notification was generated or sent. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported. The reference detail on the ticket is an image that cannot be read from here, so the number of distinct events behind this query is unconfirmed. Whether the affected suppliers are mapped for Belden has not been asked, which is what unwound their earlier EAO-39 TSMC complaint.</t>
+          <t>Staged from Jira EAO-54 (Open). Belden asked why news on gallium arsenide, indium phosphide and semiconductor supply-chain risk is not shown on the Resilinc platform. CS verified the Belden org and found no notification for the event, then checked the database across all customer orgs and found no evidence that any notification was generated or sent. The ticket's reference detail lists three items: Reuters 18-Sep-2026 on gallium and germanium prices under Chinese export curbs, DigiTimes 2-Jul-2026 on GaAs and InP epiwafer price increases hitting the Taiwan supply chain, and DigiTimes 4-May-2026 carrying WIN Semiconductors stating that GaAs and InP supply still meets production demand, which is recorded as a counterpoint to the shortage claim. Settled by the owner: these events are critical and EventWatch could have notified them, and the initial investigation indicates the sources were not captured, so the Sub-type is Source Coverage rather than the staged Keyword Update. One customer email, so one row; the three items are evidence behind a single query rather than separate incidents.</t>
         </is>
       </c>
       <c r="P126" s="33" t="n"/>
@@ -17250,7 +17250,11 @@
           <t>EAO-54</t>
         </is>
       </c>
-      <c r="X126" s="33" t="n"/>
+      <c r="X126" s="33" t="inlineStr">
+        <is>
+          <t>Initial investigation indicates the sources carrying these reports were not captured, so nothing entered the application and no notification could be generated for any customer. Recorded as the initial finding; Root Cause and Sub-type remain provisional until the investigation closes.</t>
+        </is>
+      </c>
       <c r="Y126" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="9">
-                  <v>6</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>108</v>
+                  <v>109</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>62</v>
                 </pt>
                 <pt idx="1">
                   <v>40</v>
@@ -2636,10 +2636,10 @@
                   <v>GM</v>
                 </pt>
                 <pt idx="5">
-                  <v>Ford/GM</v>
+                  <v>Belden Inc</v>
                 </pt>
                 <pt idx="6">
-                  <v>Belden Inc</v>
+                  <v>Ford/GM</v>
                 </pt>
                 <pt idx="7">
                   <v>General Mills</v>
@@ -2681,7 +2681,7 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -2987,7 +2987,7 @@
                   <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>34</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3324,7 +3324,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z127" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z128" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z127"/>
+  <dimension ref="A1:Z128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="F126" s="33" t="inlineStr">
         <is>
-          <t>Gallium Arsenide and Indium Phosphide Semiconductor Supply-Chain Risk - No EventWatch Notification (Belden)</t>
+          <t>Gallium and Germanium Supply Risk Under Chinese Export Curbs - No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G126" s="33" t="inlineStr">
@@ -17192,7 +17192,7 @@
       </c>
       <c r="J126" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K126" s="33" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="M126" s="33" t="inlineStr">
         <is>
-          <t>Source onboarding and feed-receipt verification for compound-semiconductor trade press and commodity-market wires covering gallium, germanium, indium phosphide and epiwafer supply, so a materials-supply story is carried when it is published rather than found when the customer raises it</t>
+          <t>Coverage check for critical-minerals export controls and compound-semiconductor feedstock risk, covering both whether the carrying outlets are monitored and whether the matching terms cover this wording</t>
         </is>
       </c>
       <c r="N126" s="33" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="O126" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). Belden asked why news on gallium arsenide, indium phosphide and semiconductor supply-chain risk is not shown on the Resilinc platform. CS verified the Belden org and found no notification for the event, then checked the database across all customer orgs and found no evidence that any notification was generated or sent. The ticket's reference detail lists three items: Reuters 18-Sep-2026 on gallium and germanium prices under Chinese export curbs, DigiTimes 2-Jul-2026 on GaAs and InP epiwafer price increases hitting the Taiwan supply chain, and DigiTimes 4-May-2026 carrying WIN Semiconductors stating that GaAs and InP supply still meets production demand, which is recorded as a counterpoint to the shortage claim. Settled by the owner: these events are critical and EventWatch could have notified them, and the initial investigation indicates the sources were not captured, so the Sub-type is Source Coverage rather than the staged Keyword Update. One customer email, so one row; the three items are evidence behind a single query rather than separate incidents.</t>
+          <t>Staged from Jira EAO-54 (Open). One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The Sub-type is a staging guess under the standing default: the investigation has not established whether the carrying outlet is monitored, so Source Coverage is not supported yet. Reuters being a major wire makes a keyword gap the more likely of the two, which is the question that closes this row.</t>
         </is>
       </c>
       <c r="P126" s="33" t="n"/>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="X126" s="33" t="inlineStr">
         <is>
-          <t>Initial investigation indicates the sources carrying these reports were not captured, so nothing entered the application and no notification could be generated for any customer. Recorded as the initial finding; Root Cause and Sub-type remain provisional until the investigation closes.</t>
+          <t>Initial investigation established that neither the exact titles nor similar articles for the date window were present in the system, so nothing was available to publish and no notification could be generated for any customer. That establishes non-capture but not its cause: whether the carrying outlets are monitored has not yet been confirmed, so Sub-type remains provisional between a source gap and a keyword gap.</t>
         </is>
       </c>
       <c r="Y126" s="33" t="inlineStr">
@@ -17267,16 +17267,16 @@
         <v>46296</v>
       </c>
       <c r="B127" s="37" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="C127" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D127" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E127" s="39" t="n">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="F127" s="33" t="inlineStr">
         <is>
-          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+          <t>GaAs and InP Epiwafer Price Increases in the Taiwan Supply Chain - No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G127" s="33" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="M127" s="33" t="inlineStr">
         <is>
-          <t>Coverage check for acquisition announcements carried only in French-language Canadian business press</t>
+          <t>Coverage check for compound-semiconductor trade press reporting epiwafer and substrate pricing, covering both whether the carrying outlets are monitored and whether the matching terms cover this wording</t>
         </is>
       </c>
       <c r="N127" s="33" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O127" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>Staged from Jira EAO-54 (Open). The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own. The Sub-type is a staging guess under the standing default: the investigation has not established whether the carrying outlet is monitored, so Source Coverage is not supported yet. DigiTimes being niche trade press makes a source gap more plausible here than on the companion row.</t>
         </is>
       </c>
       <c r="P127" s="33" t="n"/>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="W127" s="33" t="inlineStr">
         <is>
-          <t>EAO-55</t>
+          <t>EAO-54</t>
         </is>
       </c>
       <c r="X127" s="33" t="n"/>
@@ -17369,6 +17369,114 @@
         </is>
       </c>
       <c r="Z127" s="37" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B128" s="37" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C128" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D128" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil</t>
+        </is>
+      </c>
+      <c r="E128" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="33" t="inlineStr">
+        <is>
+          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+        </is>
+      </c>
+      <c r="G128" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H128" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I128" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J128" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K128" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L128" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M128" s="33" t="inlineStr">
+        <is>
+          <t>Coverage check for acquisition announcements carried only in French-language Canadian business press</t>
+        </is>
+      </c>
+      <c r="N128" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O128" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+        </is>
+      </c>
+      <c r="P128" s="33" t="n"/>
+      <c r="Q128" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R128" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S128" s="39" t="n"/>
+      <c r="T128" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U128" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V128" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W128" s="33" t="inlineStr">
+        <is>
+          <t>EAO-55</t>
+        </is>
+      </c>
+      <c r="X128" s="33" t="n"/>
+      <c r="Y128" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z128" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -19126,7 +19234,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3431372549019608</v>
+        <v>0.33980582524271846</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -19167,7 +19275,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.12745098039215685</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -19209,7 +19317,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06862745098039216</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19251,7 +19359,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.049019607843137254</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19293,7 +19401,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.0392156862745098</v>
+        <v>0.038834951456310676</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19328,14 +19436,14 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B72" s="22" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.029411764705882353</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19370,14 +19478,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19419,7 +19527,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19461,7 +19569,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19503,7 +19611,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19910,13 +20018,13 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -20000,13 +20108,13 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
         <v>24</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17207,7 +17207,7 @@
       </c>
       <c r="M126" s="33" t="inlineStr">
         <is>
-          <t>Coverage check for critical-minerals export controls and compound-semiconductor feedstock risk, covering both whether the carrying outlets are monitored and whether the matching terms cover this wording</t>
+          <t>Keyword coverage for critical-minerals export controls and compound-semiconductor feedstock risk, so a story worded around export curbs and niche metals is matched rather than passing through an ingested feed unrecognised</t>
         </is>
       </c>
       <c r="N126" s="33" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="O126" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The Sub-type is a staging guess under the standing default: the investigation has not established whether the carrying outlet is monitored, so Source Coverage is not supported yet. Reuters being a major wire makes a keyword gap the more likely of the two, which is the question that closes this row.</t>
+          <t>Staged from Jira EAO-54 (Open). One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess.</t>
         </is>
       </c>
       <c r="P126" s="33" t="n"/>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="X126" s="33" t="inlineStr">
         <is>
-          <t>Initial investigation established that neither the exact titles nor similar articles for the date window were present in the system, so nothing was available to publish and no notification could be generated for any customer. That establishes non-capture but not its cause: whether the carrying outlets are monitored has not yet been confirmed, so Sub-type remains provisional between a source gap and a keyword gap.</t>
+          <t>Keyword gap, not a source gap. Reuters is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
         </is>
       </c>
       <c r="Y126" s="33" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="M127" s="33" t="inlineStr">
         <is>
-          <t>Coverage check for compound-semiconductor trade press reporting epiwafer and substrate pricing, covering both whether the carrying outlets are monitored and whether the matching terms cover this wording</t>
+          <t>Keyword coverage for compound-semiconductor epiwafer and substrate pricing terminology, so a trade-press story on GaAs and InP price increases is matched rather than passing through an ingested feed unrecognised</t>
         </is>
       </c>
       <c r="N127" s="33" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O127" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own. The Sub-type is a staging guess under the standing default: the investigation has not established whether the carrying outlet is monitored, so Source Coverage is not supported yet. DigiTimes being niche trade press makes a source gap more plausible here than on the companion row.</t>
+          <t>Staged from Jira EAO-54 (Open). The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own.</t>
         </is>
       </c>
       <c r="P127" s="33" t="n"/>
@@ -17362,7 +17362,11 @@
           <t>EAO-54</t>
         </is>
       </c>
-      <c r="X127" s="33" t="n"/>
+      <c r="X127" s="33" t="inlineStr">
+        <is>
+          <t>Keyword gap, not a source gap. DigiTimes is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
+        </is>
+      </c>
       <c r="Y127" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="9">
-                  <v>4</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1777,7 +1777,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>5</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>106</v>
+                  <v>109</v>
                 </pt>
                 <pt idx="3">
                   <v>12</v>
@@ -2378,7 +2378,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>59</v>
+                  <v>62</v>
                 </pt>
                 <pt idx="1">
                   <v>40</v>
@@ -2636,19 +2636,19 @@
                   <v>GM</v>
                 </pt>
                 <pt idx="5">
+                  <v>Belden Inc</v>
+                </pt>
+                <pt idx="6">
                   <v>Ford/GM</v>
                 </pt>
-                <pt idx="6">
+                <pt idx="7">
                   <v>General Mills</v>
                 </pt>
-                <pt idx="7">
-                  <v>META</v>
-                </pt>
                 <pt idx="8">
-                  <v>Merck</v>
+                  <v>Irving Oil</v>
                 </pt>
                 <pt idx="9">
-                  <v>Schneider Electric</v>
+                  <v>META</v>
                 </pt>
                 <pt idx="10">
                   <v>Other customers</v>
@@ -2681,7 +2681,7 @@
                   <v>3</v>
                 </pt>
                 <pt idx="6">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -2693,7 +2693,7 @@
                   <v>2</v>
                 </pt>
                 <pt idx="10">
-                  <v>25</v>
+                  <v>27</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2987,7 +2987,7 @@
                   <v>32</v>
                 </pt>
                 <pt idx="1">
-                  <v>32</v>
+                  <v>35</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -3324,7 +3324,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z125" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z128" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z125"/>
+  <dimension ref="A1:Z128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="J125" s="33" t="inlineStr">
         <is>
-          <t>Keyword Update</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K125" s="33" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="M125" s="33" t="inlineStr">
         <is>
-          <t>Keyword coverage for bankruptcy, insolvency and fraud proceedings in Türkiye's automotive manufacturing cluster, so a filing at a sub-tier supplier is matched when it is published rather than when the customer raises it</t>
+          <t>Source onboarding and feed-receipt verification for Turkish-language business and regional news covering the Bursa automotive cluster, so a filing at a sub-tier supplier is carried when it is published rather than found when the customer raises it</t>
         </is>
       </c>
       <c r="N125" s="33" t="inlineStr">
@@ -17138,13 +17138,349 @@
           <t>EAO-53</t>
         </is>
       </c>
-      <c r="X125" s="33" t="n"/>
+      <c r="X125" s="33" t="inlineStr">
+        <is>
+          <t>Neither of the two Turkish-language sources carrying the Bursa fraud allegations is part of the vendor's monitoring network, established by Ankit Gupta on the ticket on 16-Oct-2026. The vendor has been asked to add them and is working on it. Not a keyword gap: the story never reached the application.</t>
+        </is>
+      </c>
       <c r="Y125" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z125" s="37" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B126" s="37" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C126" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D126" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E126" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="33" t="inlineStr">
+        <is>
+          <t>Gallium and Germanium Supply Risk Under Chinese Export Curbs - No EventWatch Notification (Belden)</t>
+        </is>
+      </c>
+      <c r="G126" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H126" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I126" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K126" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L126" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M126" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for critical-minerals export controls and compound-semiconductor feedstock risk, so a story worded around export curbs and niche metals is matched rather than passing through an ingested feed unrecognised</t>
+        </is>
+      </c>
+      <c r="N126" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O126" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-54 (Open). One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess.</t>
+        </is>
+      </c>
+      <c r="P126" s="33" t="n"/>
+      <c r="Q126" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R126" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S126" s="39" t="n"/>
+      <c r="T126" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U126" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V126" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W126" s="33" t="inlineStr">
+        <is>
+          <t>EAO-54</t>
+        </is>
+      </c>
+      <c r="X126" s="33" t="inlineStr">
+        <is>
+          <t>Keyword gap, not a source gap. Reuters is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
+        </is>
+      </c>
+      <c r="Y126" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z126" s="37" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B127" s="37" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C127" s="33" t="inlineStr">
+        <is>
+          <t>Supply Shortage</t>
+        </is>
+      </c>
+      <c r="D127" s="33" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="E127" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="33" t="inlineStr">
+        <is>
+          <t>GaAs and InP Epiwafer Price Increases in the Taiwan Supply Chain - No EventWatch Notification (Belden)</t>
+        </is>
+      </c>
+      <c r="G127" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H127" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I127" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J127" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K127" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L127" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M127" s="33" t="inlineStr">
+        <is>
+          <t>Keyword coverage for compound-semiconductor epiwafer and substrate pricing terminology, so a trade-press story on GaAs and InP price increases is matched rather than passing through an ingested feed unrecognised</t>
+        </is>
+      </c>
+      <c r="N127" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O127" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-54 (Open). The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own.</t>
+        </is>
+      </c>
+      <c r="P127" s="33" t="n"/>
+      <c r="Q127" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R127" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S127" s="39" t="n"/>
+      <c r="T127" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U127" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V127" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W127" s="33" t="inlineStr">
+        <is>
+          <t>EAO-54</t>
+        </is>
+      </c>
+      <c r="X127" s="33" t="inlineStr">
+        <is>
+          <t>Keyword gap, not a source gap. DigiTimes is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
+        </is>
+      </c>
+      <c r="Y127" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z127" s="37" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B128" s="37" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C128" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D128" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil</t>
+        </is>
+      </c>
+      <c r="E128" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="33" t="inlineStr">
+        <is>
+          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+        </is>
+      </c>
+      <c r="G128" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H128" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I128" s="33" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="J128" s="33" t="inlineStr">
+        <is>
+          <t>Keyword Update</t>
+        </is>
+      </c>
+      <c r="K128" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L128" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M128" s="33" t="inlineStr">
+        <is>
+          <t>Coverage check for acquisition announcements carried only in French-language Canadian business press</t>
+        </is>
+      </c>
+      <c r="N128" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O128" s="33" t="inlineStr">
+        <is>
+          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+        </is>
+      </c>
+      <c r="P128" s="33" t="n"/>
+      <c r="Q128" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R128" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S128" s="39" t="n"/>
+      <c r="T128" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U128" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V128" s="33" t="inlineStr">
+        <is>
+          <t>Dynamic Source Discovery</t>
+        </is>
+      </c>
+      <c r="W128" s="33" t="inlineStr">
+        <is>
+          <t>EAO-55</t>
+        </is>
+      </c>
+      <c r="X128" s="33" t="n"/>
+      <c r="Y128" s="33" t="inlineStr">
+        <is>
+          <t>Product &amp; Platform</t>
+        </is>
+      </c>
+      <c r="Z128" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -18902,7 +19238,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.35</v>
+        <v>0.33980582524271846</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -18943,7 +19279,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.13</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -18985,7 +19321,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.07</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19027,7 +19363,7 @@
         <v>5</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.05</v>
+        <v>0.04854368932038835</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19069,7 +19405,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.04</v>
+        <v>0.038834951456310676</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19104,14 +19440,14 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Ford/GM</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B72" s="22" t="n">
         <v>3</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.03</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19146,14 +19482,14 @@
     <row r="73" ht="23.25" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Ford/GM</t>
         </is>
       </c>
       <c r="B73" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02</v>
+        <v>0.02912621359223301</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19188,14 +19524,14 @@
     <row r="74" ht="23.25" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B74" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19230,14 +19566,14 @@
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Irving Oil</t>
         </is>
       </c>
       <c r="B75" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19272,14 +19608,14 @@
     <row r="76" ht="23.25" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B76" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -19500,13 +19836,13 @@
         </is>
       </c>
       <c r="J83" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" s="76" t="n">
         <v>2</v>
       </c>
       <c r="L83" s="76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -19686,13 +20022,13 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -19776,13 +20112,13 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
         <v>24</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17105,7 +17105,7 @@
       </c>
       <c r="O125" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The only cited source is a Turkish-language report of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Under investigation: no RCA yet, and the Sub-type is a staging guess - source coverage and a keyword gap are both open, as EAO-52 has just shown.</t>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The cited sources are Turkish-language reports of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Settled as a source coverage gap: none of the three outlets is in the vendor's monitoring network and no similar source was captured, so there was no keyword possibility. This is the distinction against EAO-54, where the vendor did monitor the outlets and the matching terms missed the stories. Still open with PM: no RCA has gone back to Ford, and the vendor has not confirmed the sources are added.</t>
         </is>
       </c>
       <c r="P125" s="33" t="n"/>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="X125" s="33" t="inlineStr">
         <is>
-          <t>Neither of the two Turkish-language sources carrying the Bursa fraud allegations is part of the vendor's monitoring network, established by Ankit Gupta on the ticket on 16-Oct-2026. The vendor has been asked to add them and is working on it. Not a keyword gap: the story never reached the application.</t>
+          <t>Source coverage gap, confirmed by Product Management. None of the three outlets carrying the Bursa fraud allegations is in the vendor's monitoring network: ekonomistar.com.tr, which Ford cited, and sondakihaber.com and ifinnapp.com, which were checked on the ticket. No similar source reporting the news was captured either, so the story never reached the application and no keyword could have matched it. The vendor has been asked to add the sources and is working on it. Established by Ankit Gupta on 16-Oct-2026 and confirmed by Product Management.</t>
         </is>
       </c>
       <c r="Y125" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>45</v>
                 </pt>
                 <pt idx="1">
-                  <v>39</v>
+                  <v>40</v>
                 </pt>
                 <pt idx="2">
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
               </numCache>
             </numRef>
@@ -17090,7 +17090,7 @@
       </c>
       <c r="L125" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M125" s="33" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="O125" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The cited sources are Turkish-language reports of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. The ticket asks for an RCA plus interim and permanent corrective actions. Settled as a source coverage gap: none of the three outlets is in the vendor's monitoring network and no similar source was captured, so there was no keyword possibility. This is the distinction against EAO-54, where the vendor did monitor the outlets and the matching terms missed the stories. Still open with PM: no RCA has gone back to Ford, and the vendor has not confirmed the sources are added.</t>
+          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The cited sources are Turkish-language reports of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. Settled as a source coverage gap: none of the three outlets is in the vendor's monitoring network and no similar source was captured, so there was no keyword possibility. This is the distinction against EAO-54, where the vendor did monitor the outlets and the matching terms missed the stories. Closed on the owner's call on 18-Oct-2026: the source-coverage finding is the response going back to Ford, so the row moves off Pending to RCA Shared. Resolution Date is left blank because the Jira ticket is still open at Sent to PM with no resolutiondate, and a guessed date is worse than none. A human carries the two loose ends from here, because a row off Pending is no longer picked up by the daily re-check: the vendor has not confirmed the sources are added, and the ticket has no closing date.</t>
         </is>
       </c>
       <c r="P125" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
                   <v>35</v>
@@ -2996,7 +2996,7 @@
                   <v>5</v>
                 </pt>
                 <pt idx="4">
-                  <v>9</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="5">
                   <v>3</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="J55" s="33" t="inlineStr">
         <is>
-          <t>Prioritization</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K55" s="33" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="M55" s="33" t="inlineStr">
         <is>
-          <t>Mapping validation</t>
+          <t>Escalation timeliness check on a mapped supplier, so a bulletin that has been sitting unpublished is raised before the customer asks for it</t>
         </is>
       </c>
       <c r="N55" s="33" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="O55" s="33" t="inlineStr">
         <is>
-          <t>Supplier mapped but WarRoom delayed ~9 days; internal notes mention erosion of trust. RCA requested.</t>
+          <t>NVR asked why no WarRoom appeared for SRS Distribution's completed acquisition of Mingledorff's. The supplier was mapped; the entire bulletin was published late, nine days after the event of 11-May-2026. Internal notes record erosion of trust. Settled by the owner: this is a publishing delay, not a mapping failure and not a ranking decision, so the Sub-type is Published Late and the focus moves off Entity &amp; Supplier Resolution to WarRoom &amp; Decision Validation, where the other two Published Late rows sit. The earlier Prioritization filing and the Mapping validation remedy both described causes the record does not support.</t>
         </is>
       </c>
       <c r="P55" s="33" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="V55" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="X55" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>62</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
-                  <v>40</v>
+                  <v>41</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
@@ -2987,19 +2987,19 @@
                   <v>33</v>
                 </pt>
                 <pt idx="1">
-                  <v>35</v>
+                  <v>37</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="4">
                   <v>8</v>
                 </pt>
                 <pt idx="5">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="6">
                   <v>3</v>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="J4" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K4" s="33" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O4" s="33" t="inlineStr">
         <is>
-          <t>Feed harvesting gap; WarRoom created after escalation.</t>
+          <t>Feed harvesting gap; WarRoom created after escalation. Settled by the owner on 18-Oct-2026: no analyst can review an event they never saw, so this is a capture gap and not an identification failure. Keyword Update.</t>
         </is>
       </c>
       <c r="P4" s="33" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="V4" s="33" t="inlineStr">
         <is>
-          <t>Other Control Automation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="X4" s="33" t="n"/>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="J10" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K10" s="33" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="O10" s="33" t="inlineStr">
         <is>
-          <t>Snowstorm moved to monitoring incorrectly; decision explained to customer.</t>
+          <t>Snowstorm moved to monitoring incorrectly; decision explained to customer. Settled by the owner on 18-Oct-2026: an analyst moved the snowstorm to monitoring in error, which is a judgement failure. People and Review.</t>
         </is>
       </c>
       <c r="P10" s="33" t="n"/>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="J11" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>WarRoom Creation</t>
         </is>
       </c>
       <c r="K11" s="33" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="O11" s="33" t="inlineStr">
         <is>
-          <t>AI classification bias + missed human escalation; WarRoom created after reassessment. NC issued. Settled by the owner: the bulletin was already published. The analyst selected the wrong event type and reviewer validation did not correct it. This is an analyst-understanding and classification complaint, not a missed bulletin, so Missed_Flag is No.</t>
+          <t>AI classification bias + missed human escalation; WarRoom created after reassessment. NC issued. Settled by the owner: the bulletin was already published. The analyst selected the wrong event type and reviewer validation did not correct it. This is an analyst-understanding and classification complaint, not a missed bulletin, so Missed_Flag is No. Settled by the owner on 18-Oct-2026: notifying the event and creating the WarRoom are two steps issued together, and here the event went out with no WarRoom attached. The WarRoom was created after the customer wrote in, so the sub-type is WarRoom Creation and Missed_Flag stays No.</t>
         </is>
       </c>
       <c r="P11" s="33" t="n"/>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="J26" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Published Late</t>
         </is>
       </c>
       <c r="K26" s="33" t="inlineStr">
@@ -6361,10 +6361,14 @@
       </c>
       <c r="O26" s="33" t="inlineStr">
         <is>
-          <t>Severe weather alert missed; response already provided on 27-Mar-26.</t>
-        </is>
-      </c>
-      <c r="P26" s="33" t="n"/>
+          <t>Severe weather alert missed; response already provided on 27-Mar-26. Settled by the owner on 18-Oct-2026: both the bulletin and the WarRoom went out after the customer email. The guidance was applied correctly while the event was under monitoring, so no decision was wrong; what came late was the escalation once the impact threshold was met. People and Published Late, Missed_Flag stays Yes.</t>
+        </is>
+      </c>
+      <c r="P26" s="33" t="inlineStr">
+        <is>
+          <t>~1 day (Mar 26 to Mar 27)</t>
+        </is>
+      </c>
       <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -6373,7 +6377,9 @@
       <c r="R26" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="S26" s="39" t="n"/>
+      <c r="S26" s="39" t="n">
+        <v>24</v>
+      </c>
       <c r="T26" s="35" t="n">
         <v>46082</v>
       </c>
@@ -6387,7 +6393,11 @@
           <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
-      <c r="X26" s="33" t="n"/>
+      <c r="X26" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch monitored the Midwest weather threat from the point it was first identified. While it was thunderstorm activity and tornado warnings it was correctly held under monitoring, because the guidelines notify those only on confirmed impact such as structural damage, infrastructure disruption, transport interruption or utility outage. Public reports then confirmed structural damage in Hardin County and Kenton, Ohio, and a tornado touchdown, which met the notification criteria. The bulletin and the WarRoom were prepared and issued only after Ford wrote in on 27-Mar-2026, so the escalation at the point the threshold was crossed came late.</t>
+        </is>
+      </c>
       <c r="Y26" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -6980,7 +6990,7 @@
       </c>
       <c r="J32" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K32" s="33" t="inlineStr">
@@ -7005,7 +7015,7 @@
       </c>
       <c r="O32" s="33" t="inlineStr">
         <is>
-          <t>AI correctly classified, but analyst assessed as localized/temporary. NC logged; post-incident review done.</t>
+          <t>AI correctly classified, but analyst assessed as localized/temporary. NC logged; post-incident review done. Settled by the owner on 18-Oct-2026: the model identified the event correctly and the analyst got the impact call wrong, which is People and Review.</t>
         </is>
       </c>
       <c r="P32" s="33" t="n"/>
@@ -7081,7 +7091,7 @@
       </c>
       <c r="J33" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K33" s="33" t="inlineStr">
@@ -7106,7 +7116,7 @@
       </c>
       <c r="O33" s="33" t="inlineStr">
         <is>
-          <t>AI correctly classified, but human review missed company-facility validation. NC logged.</t>
+          <t>AI correctly classified, but human review missed company-facility validation. NC logged. Settled by the owner on 18-Oct-2026: the analyst did not run the company-mapping check before marking the story Not Impactful. The process existed and a person skipped it, so the row is People and Review with the process-adherence finding recorded here, not a Process root cause. Missed_Flag stays Yes.</t>
         </is>
       </c>
       <c r="P33" s="33" t="n"/>
@@ -9250,7 +9260,7 @@
       </c>
       <c r="J54" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Keyword Update</t>
         </is>
       </c>
       <c r="K54" s="33" t="inlineStr">
@@ -9275,7 +9285,7 @@
       </c>
       <c r="O54" s="33" t="inlineStr">
         <is>
-          <t>RCA shared with customer; source coverage + keyword gap identified. Blockade lasted 27+ hours; impacted suppliers in Santa Rosa Jáuregui.</t>
+          <t>RCA shared with customer; source coverage + keyword gap identified. Blockade lasted 27+ hours; impacted suppliers in Santa Rosa Jáuregui. Settled by the owner on 18-Oct-2026: the record's own finding names a keyword gap, so the row is filed Keyword Update rather than Event Identification.</t>
         </is>
       </c>
       <c r="P54" s="33" t="n"/>
@@ -9298,7 +9308,7 @@
       </c>
       <c r="V54" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="X54" s="33" t="n"/>
@@ -10413,12 +10423,12 @@
       </c>
       <c r="I65" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J65" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K65" s="33" t="inlineStr">
@@ -10443,7 +10453,7 @@
       </c>
       <c r="O65" s="33" t="inlineStr">
         <is>
-          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility.</t>
+          <t>RCA document prepared and shared with customer. Customer reported missing EventWatch coverage related to a CO₂ leak involving fatalities at a mapped supplier facility. Settled by the owner on 18-Oct-2026: an analyst overlooked the event, so the root cause moves from Product to People and the row routes to EventWatch Ops.</t>
         </is>
       </c>
       <c r="P65" s="33" t="n"/>
@@ -10481,7 +10491,7 @@
       </c>
       <c r="Y65" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z65" s="37" t="n">
@@ -10978,7 +10988,7 @@
       </c>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Clustering / Duplication Defect</t>
         </is>
       </c>
       <c r="K70" s="33" t="inlineStr">
@@ -11003,7 +11013,7 @@
       </c>
       <c r="O70" s="33" t="inlineStr">
         <is>
-          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation.</t>
+          <t>RCA PDF prepared and approved for customer sharing. Event was captured by feeds but incorrectly clustered with another unrelated factory fire in Germany, preventing separate WarRoom creation. Settled by the owner on 18-Oct-2026: the feeds captured the fire and clustered it with an unrelated German factory fire, which is a Product clustering defect.</t>
         </is>
       </c>
       <c r="P70" s="33" t="n"/>
@@ -12318,7 +12328,7 @@
       </c>
       <c r="J82" s="33" t="inlineStr">
         <is>
-          <t>Event Identification</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K82" s="33" t="inlineStr">
@@ -12343,7 +12353,7 @@
       </c>
       <c r="O82" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found.</t>
+          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found. Settled by the owner on 18-Oct-2026: an analyst did not assess or review the wildfire smoke event correctly. People and Review.</t>
         </is>
       </c>
       <c r="Q82" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>60</v>
                 </pt>
                 <pt idx="1">
-                  <v>41</v>
+                  <v>42</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="J17" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Model Classification Defect</t>
         </is>
       </c>
       <c r="K17" s="33" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O17" s="33" t="inlineStr">
         <is>
-          <t>Event not triggered due to company not mapped as Ford supplier; explanation provided.</t>
+          <t>Event not triggered due to company not mapped as Ford supplier; explanation provided. Settled by the owner on 18-Oct-2026: this is the same failure as the ADM data breach row. The articles were captured and the classification models categorised them Not Impactful, and the human-in-the-loop review did not correct it. Product and Model Classification Defect. The earlier note that the company was not mapped as a Ford supplier is superseded by this finding.</t>
         </is>
       </c>
       <c r="P17" s="33" t="n"/>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="J31" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Platform Bug</t>
         </is>
       </c>
       <c r="K31" s="33" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="O31" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3298 (Open). For Harman on the Murata Manufacturing cyber attack, 45 Murata sites were potentially impacted but impact-confirmation requests went to only 41. The four omitted Tier 2 sites met customer settings and impact-region criteria. Company notification settings were on for everything except 'Site Contacts Shared by Suppliers in our SCV (mapping)'.</t>
+          <t>From Jira CAN-3298 (Open). For Harman on the Murata Manufacturing cyber attack, 45 Murata sites were potentially impacted but impact-confirmation requests went to only 41. The four omitted Tier 2 sites met customer settings and impact-region criteria. Company notification settings were on for everything except 'Site Contacts Shared by Suppliers in our SCV (mapping)'. Settled by the owner on 18-Oct-2026: this is an engineering defect, not a mapping gap. The four omitted sites met the customer settings and the impact-region criteria, so the targets were on file and the system did not send to them. Product and Platform Bug, and it stays a miss.</t>
         </is>
       </c>
       <c r="P31" s="33" t="n"/>
@@ -11657,12 +11657,12 @@
       </c>
       <c r="I76" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J76" s="33" t="inlineStr">
         <is>
-          <t>Mapping / Routing Defect</t>
+          <t>Supplier Selection Miss</t>
         </is>
       </c>
       <c r="K76" s="33" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="O76" s="33" t="inlineStr">
         <is>
-          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing. Settled by the owner: the bulletin existed, but the applicable customer WarRoom was not created because supplier and site normalization was not applied correctly.</t>
+          <t>EventWatch alert published but corresponding WarRoom not created despite supplier normalization. Investigation ongoing. Settled by the owner: the bulletin existed, but the applicable customer WarRoom was not created because supplier and site normalization was not applied correctly. Settled by the owner on 18-Oct-2026: the supplier was mapped under two names and the analyst checked only one of them, so this is an analyst selection miss rather than a normalization defect. Missed_Flag stays Yes: no WarRoom reached the customer.</t>
         </is>
       </c>
       <c r="P76" s="33" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="X76" s="33" t="inlineStr">
         <is>
-          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026.</t>
+          <t>The event met the Price Fluctuation reporting threshold and did qualify for a WarRoom; the failure came later, in customer-specific supplier normalization. The Samsung Electronics sites are normalized under Samsung for the affected customer, and that normalization was not applied during the impacted-site assessment, so the sites were never associated with the event and no customer WarRoom was created. This was not a parent-child modelling issue. Normalization is maintained outside the EventWatch editorial workflow, so the response is strengthened validation controls plus AI-assisted WarRoom generation rather than a guarantee. RCA shared 15-Jul-2026. Settled by the owner on 18-Oct-2026: the normalization account above is superseded. Samsung Electronics is also mapped as Samsung in the portal for this customer, so the supplier was on file under a second name. The analyst checked Samsung Electronics only and did not check Samsung, so the sites were never selected and no customer WarRoom was created. The failure is supplier selection by a person, not a platform normalization defect. People and Supplier Selection Miss, routed to EventWatch Ops.</t>
         </is>
       </c>
       <c r="Y76" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z76" s="37" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2996,7 +2996,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="4">
-                  <v>8</v>
+                  <v>7</v>
                 </pt>
                 <pt idx="5">
                   <v>2</v>
@@ -3011,7 +3011,7 @@
                   <v>8</v>
                 </pt>
                 <pt idx="9">
-                  <v>1</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M17" s="33" t="inlineStr">
         <is>
-          <t>Customer-facing "not mapped" explanation template + What-If guidance</t>
+          <t>A not-impactful decision check on captured incidents at manufacturing sites, so a factory fire is not closed out before an analyst has weighed it; and relevance scoring that stops treating supplier mapping as a dominant decision factor, so an unmapped site is judged on incident severity and downstream supply chain potential instead</t>
         </is>
       </c>
       <c r="N17" s="33" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O17" s="33" t="inlineStr">
         <is>
-          <t>Event not triggered due to company not mapped as Ford supplier; explanation provided. Settled by the owner on 18-Oct-2026: this is the same failure as the ADM data breach row. The articles were captured and the classification models categorised them Not Impactful, and the human-in-the-loop review did not correct it. Product and Model Classification Defect. The earlier note that the company was not mapped as a Ford supplier is superseded by this finding.</t>
+          <t>Event not triggered due to company not mapped as Ford supplier; explanation provided. Settled by the owner on 18-Oct-2026: this is the same failure as the ADM data breach row. The articles were captured and the classification models categorised them Not Impactful, and the human-in-the-loop review did not correct it. Product and Model Classification Defect. The earlier note that the company was not mapped as a Ford supplier is superseded by this finding. Settled by the owner on 18-Oct-2026: the remedy and the focus follow the corrected cause. The mapping-explanation template and Entity and Supplier Resolution described the superseded theory, not the failure.</t>
         </is>
       </c>
       <c r="P17" s="33" t="n"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="V17" s="33" t="inlineStr">
         <is>
-          <t>Entity &amp; Supplier Resolution</t>
+          <t>Classification &amp; Impact Validation</t>
         </is>
       </c>
       <c r="X17" s="33" t="n"/>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="K31" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L31" s="33" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="O31" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3298 (Open). For Harman on the Murata Manufacturing cyber attack, 45 Murata sites were potentially impacted but impact-confirmation requests went to only 41. The four omitted Tier 2 sites met customer settings and impact-region criteria. Company notification settings were on for everything except 'Site Contacts Shared by Suppliers in our SCV (mapping)'. Settled by the owner on 18-Oct-2026: this is an engineering defect, not a mapping gap. The four omitted sites met the customer settings and the impact-region criteria, so the targets were on file and the system did not send to them. Product and Platform Bug, and it stays a miss.</t>
+          <t>From Jira CAN-3298 (Open). For Harman on the Murata Manufacturing cyber attack, 45 Murata sites were potentially impacted but impact-confirmation requests went to only 41. The four omitted Tier 2 sites met customer settings and impact-region criteria. Company notification settings were on for everything except 'Site Contacts Shared by Suppliers in our SCV (mapping)'. Settled by the owner on 18-Oct-2026: this is an engineering defect, not a mapping gap. The four omitted sites met the customer settings and the impact-region criteria, so the targets were on file and the system did not send to them. Product and Platform Bug, and it stays a miss. Settled by the owner on 18-Oct-2026: recorded as a Bug rather than an Improvement, to match the Platform Bug sub-type. The ticket documented no root cause at the time, so the defect is confirmed by the owner rather than by the record.</t>
         </is>
       </c>
       <c r="P31" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1768,7 +1768,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="4"/>
                 <pt idx="0">
-                  <v>45</v>
+                  <v>46</v>
                 </pt>
                 <pt idx="1">
                   <v>40</v>
@@ -1777,7 +1777,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>4</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -16664,7 +16664,7 @@
       </c>
       <c r="L121" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="M121" s="33" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and that the keyword is being added, so the Sub-type is no longer a staging guess; the ticket is still open with PM and the geofencing and WarRoom questions have not been answered separately. Under investigation: no agreed RCA yet.</t>
+          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and added the keywords to two RSS feeds on 14-Oct-2026, so the corrective action is complete and the row leaves Pending. STILL OPEN, and nothing automatic will look at this row again: the written RCA was attached on 14-Oct-2026 and is in internal approval with PM, not yet shared with General Mills, so there is no Resolution Date; the geofencing and WarRoom-creation questions the customer raised have not been answered separately. The Sub-type reads Keyword Update on engineering's own wording and awaits the owner's confirmation.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="X121" s="33" t="inlineStr">
         <is>
-          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. The keyword is being added. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here.</t>
+          <t>Monitoring checked the Not Impacted tab and found no relevant article, then established the cause as a keyword miss: the Carlisle coverage was not matched by the algorithm's keyword set. Engineering added the keywords to two RSS feeds on 14-Oct-2026. Not a source-coverage gap - the row was staged as one before the investigation reported, and is corrected here. A written RCA was attached to the ticket on 14-Oct-2026 and its text is not readable from Jira.</t>
         </is>
       </c>
       <c r="Y121" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17451,7 +17451,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. No investigation has been done and no RCA exists. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. An RCA document was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai for review; the ticket is Approval Requested, so no answer has gone back to Irving Oil yet and this row stays Pending. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,13 +1771,13 @@
                   <v>46</v>
                 </pt>
                 <pt idx="1">
-                  <v>40</v>
+                  <v>41</v>
                 </pt>
                 <pt idx="2">
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
               </numCache>
             </numRef>
@@ -17436,7 +17436,7 @@
       </c>
       <c r="L128" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M128" s="33" t="inlineStr">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. An RCA document was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai for review; the ticket is Approval Requested, so no answer has gone back to Irving Oil yet and this row stays Pending. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3382,7 +3382,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E166" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E167" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -20607,7 +20607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24883,12 +24883,12 @@
       </c>
       <c r="C160" s="41" t="inlineStr">
         <is>
-          <t>Incorrect system data, association, coordinates, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
+          <t>Incorrect system data, association, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
         </is>
       </c>
       <c r="D160" s="41" t="inlineStr">
         <is>
-          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers geocoding and address-to-coordinate mismatches, cross-tenant leakage and entity mislinkage. Use Supplier / Site Not Shared where the data was never provided at all.</t>
+          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers cross-tenant leakage and entity mislinkage. Use Incorrect Geocode where a site's own stored coordinates are wrong, and Supplier / Site Not Shared where the data was never provided at all.</t>
         </is>
       </c>
       <c r="E160" s="41" t="inlineStr">
@@ -25056,6 +25056,33 @@
       <c r="E166" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="30.75" customHeight="1">
+      <c r="A167" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B167" s="41" t="inlineStr">
+        <is>
+          <t>Incorrect Geocode</t>
+        </is>
+      </c>
+      <c r="C167" s="41" t="inlineStr">
+        <is>
+          <t>The supplier site's stored geographic coordinates do not match its actual address, so a correctly drawn geofence selected a site that is not in the affected area.</t>
+        </is>
+      </c>
+      <c r="D167" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The geofence and the automated selection both behaved correctly; the coordinates on the site record did not match the address. Owned by the Data team, who maintain supplier geocoding. Use Mapping / Routing Defect for tenant or entity linkage, and Supplier / Site Not Shared where the site was never provided at all.</t>
+        </is>
+      </c>
+      <c r="E167" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -14728,7 +14728,7 @@
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Mapping / Routing Defect</t>
+          <t>Incorrect Geocode</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Probable geocoding / address-to-coordinate mismatch. The impact polygon and automated selection operated on the coordinates available in the system. Detailed validation of the coordinate source and assignment process was referred to the Data team.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Two things are still open and nobody is chasing them from this row: the DO team's correction of the SMI AMTEK coordinates is unconfirmed, and the Data team has not answered what the source of the Pune site's coordinates was, having been asked on 13-Oct and chased on 19-Oct. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. Customer Support confirmed on 08-Oct-2026 that SMI AMTEK CRANKSHAFT held two sets of geographic coordinates, one of which pinned the site near Chandigarh rather than at its actual location in Dharuhera, Rewari, Haryana. The incorrectly pinned location fell inside the geofence, so the site was associated with the WarRoom automatically. No proximity rule and no buffer zone were applied: inclusion was decided by the coordinates on the site record intersecting the polygon. A ticket was raised with the DO team to correct the coordinates. The source of the coordinates on Eaton's Pune site sits with the Data team and is still unanswered. This supersedes the earlier explanation that the site was included on its proximity to the affected region, which was read off the location the platform displayed and was itself the wrong pin.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -3382,7 +3382,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E166" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefinitionsTable" displayName="DefinitionsTable" ref="A3:E167" headerRowCount="1" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E139"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Section" dataDxfId="4"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="J104" s="33" t="inlineStr">
         <is>
-          <t>Mapping / Routing Defect</t>
+          <t>Incorrect Geocode</t>
         </is>
       </c>
       <c r="K104" s="33" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the probable cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Probable geocoding / address-to-coordinate mismatch. The impact polygon and automated selection operated on the coordinates available in the system. Detailed validation of the coordinate source and assignment process was referred to the Data team.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Two things are still open and nobody is chasing them from this row: the DO team's correction of the SMI AMTEK coordinates is unconfirmed, and the Data team has not answered what the source of the Pune site's coordinates was, having been asked on 13-Oct and chased on 19-Oct. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="X104" s="33" t="inlineStr">
         <is>
-          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. The probable cause is incorrect geocoding placing supplier sites inside the impact area. Reported to Eaton and Ford on that basis.</t>
+          <t>Supplier selection for this event was system-driven: a polygon was drawn around the affected region in Punjab, so no analyst chose the sites by hand and an incorrect manual selection is not possible. Customer Support confirmed on 08-Oct-2026 that SMI AMTEK CRANKSHAFT held two sets of geographic coordinates, one of which pinned the site near Chandigarh rather than at its actual location in Dharuhera, Rewari, Haryana. The incorrectly pinned location fell inside the geofence, so the site was associated with the WarRoom automatically. No proximity rule and no buffer zone were applied: inclusion was decided by the coordinates on the site record intersecting the polygon. A ticket was raised with the DO team to correct the coordinates. The source of the coordinates on Eaton's Pune site sits with the Data team and is still unanswered. This supersedes the earlier explanation that the site was included on its proximity to the affected region, which was read off the location the platform displayed and was itself the wrong pin.</t>
         </is>
       </c>
       <c r="Y104" s="33" t="inlineStr">
@@ -20607,7 +20607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24883,12 +24883,12 @@
       </c>
       <c r="C160" s="41" t="inlineStr">
         <is>
-          <t>Incorrect system data, association, coordinates, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
+          <t>Incorrect system data, association, tenant linkage, entity linkage, or routing caused the wrong customer, supplier, site, or destination to be selected or displayed.</t>
         </is>
       </c>
       <c r="D160" s="41" t="inlineStr">
         <is>
-          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers geocoding and address-to-coordinate mismatches, cross-tenant leakage and entity mislinkage. Use Supplier / Site Not Shared where the data was never provided at all.</t>
+          <t>Detailed cause/handling category. The data the platform acted on was wrong, so correct logic produced a wrong selection. Covers cross-tenant leakage and entity mislinkage. Use Incorrect Geocode where a site's own stored coordinates are wrong, and Supplier / Site Not Shared where the data was never provided at all.</t>
         </is>
       </c>
       <c r="E160" s="41" t="inlineStr">
@@ -25056,6 +25056,33 @@
       <c r="E166" s="41" t="inlineStr">
         <is>
           <t>Standard Automation Focus</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="30.75" customHeight="1">
+      <c r="A167" s="42" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
+        </is>
+      </c>
+      <c r="B167" s="41" t="inlineStr">
+        <is>
+          <t>Incorrect Geocode</t>
+        </is>
+      </c>
+      <c r="C167" s="41" t="inlineStr">
+        <is>
+          <t>The supplier site's stored geographic coordinates do not match its actual address, so a correctly drawn geofence selected a site that is not in the affected area.</t>
+        </is>
+      </c>
+      <c r="D167" s="41" t="inlineStr">
+        <is>
+          <t>Detailed cause/handling category. The geofence and the automated selection both behaved correctly; the coordinates on the site record did not match the address. Owned by the Data team, who maintain supplier geocoding. Use Mapping / Routing Defect for tenant or entity linkage, and Supplier / Site Not Shared where the site was never provided at all.</t>
+        </is>
+      </c>
+      <c r="E167" s="41" t="inlineStr">
+        <is>
+          <t>Sub-type</t>
         </is>
       </c>
     </row>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2996,10 +2996,10 @@
                   <v>4</v>
                 </pt>
                 <pt idx="4">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="5">
-                  <v>2</v>
+                  <v>1</v>
                 </pt>
                 <pt idx="6">
                   <v>3</v>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="V104" s="33" t="inlineStr">
         <is>
-          <t>AI-Assisted Geofencing</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W104" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -14576,7 +14576,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z102" s="37" t="n"/>
+      <c r="Z102" s="37" t="n">
+        <v>46286</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="35" t="n">
@@ -14684,7 +14686,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z103" s="37" t="n"/>
+      <c r="Z103" s="37" t="n">
+        <v>46290</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="35" t="n">
@@ -14912,7 +14916,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z105" s="37" t="n"/>
+      <c r="Z105" s="37" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="35" t="n">
@@ -15024,7 +15030,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z106" s="37" t="n"/>
+      <c r="Z106" s="37" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="35" t="n">
@@ -15136,7 +15144,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z107" s="37" t="n"/>
+      <c r="Z107" s="37" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="35" t="n">
@@ -15248,7 +15258,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z108" s="37" t="n"/>
+      <c r="Z108" s="37" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="35" t="n">
@@ -15360,7 +15372,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z109" s="37" t="n"/>
+      <c r="Z109" s="37" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="35" t="n">
@@ -15816,7 +15830,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z113" s="37" t="n"/>
+      <c r="Z113" s="37" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="35" t="n">
@@ -15928,7 +15944,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z114" s="37" t="n"/>
+      <c r="Z114" s="37" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="35" t="n">
@@ -16046,7 +16064,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z115" s="37" t="n"/>
+      <c r="Z115" s="37" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="35" t="n">
@@ -16158,7 +16178,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z116" s="37" t="n"/>
+      <c r="Z116" s="37" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="35" t="n">
@@ -16496,7 +16518,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z119" s="37" t="n"/>
+      <c r="Z119" s="37" t="n">
+        <v>46316</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="35" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -11803,7 +11803,7 @@
       </c>
       <c r="O77" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-16 (Done). Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
+          <t>Eaton asked why the WarRoom for Super Typhoon Bavi (Taiwan) was activated on 9-Jul after the storm had already peaked, and what triggering criteria were used.</t>
         </is>
       </c>
       <c r="Q77" s="33" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="O78" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-17 (Done). Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
+          <t>Micron reported a forced-labor lawsuit against Jacobs Engineering/CH2M Hill was not captured in EventWatch and requested RCA if it was in scope.</t>
         </is>
       </c>
       <c r="Q78" s="33" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="O79" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-18 (Done). Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
+          <t>Western Digital asked whether EventWatch has published or is monitoring a reported Suspension Baseplate supply risk tied to Fujita Plating/NHK/OSK decommitments; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q79" s="33" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="O80" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-19 (Done). Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
+          <t>Ford requested an explanation of Resilinc's monitoring strategy for power grid failure events after multiple incidents affected suppliers in the US and Europe.</t>
         </is>
       </c>
       <c r="Q80" s="33" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="O81" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-20 (Done). Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
+          <t>Honeywell reported ASSMANN WSW Components GmbH's July 6 insolvency filing (a mapped Tier-1 supplier) was never published as an EventWatch bulletin or WarRoom; RCA requested.</t>
         </is>
       </c>
       <c r="Q81" s="33" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="O82" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-21 (Done). Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found. Settled by the owner on 18-Oct-2026: an analyst did not assess or review the wildfire smoke event correctly. People and Review.</t>
+          <t>Ford reported no EventWatch alert/WarRoom was generated for July 15-17 wildfire smoke air-quality degradation across the US Midwest/Northeast; CS confirmed no matching notification was found. Settled by the owner on 18-Oct-2026: an analyst did not assess or review the wildfire smoke event correctly. People and Review.</t>
         </is>
       </c>
       <c r="Q82" s="33" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="O83" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-22 (Done). Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
+          <t>Eaton reported the July 14-16 ANCPI (Romania land registry) cyberattack had no corresponding WarRoom or news on the portal; RCA requested if it was in scope.</t>
         </is>
       </c>
       <c r="Q83" s="33" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="O85" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>GM reported a fire at UTAS-Nova Automotive Lighting Systems, Danyang, Jiangsu, China (reported July 10) was not found in GM's org. EventWatch searched English and Chinese public sources on 04-Aug-2026 and found no article confirming the fire, and opened a monitoring story pending credible public reporting. Unresolved: the RCA Details on this row name a clustering defect, which is the finding for the Nemak article on the same ticket and not for this event. The cause here has not been settled.</t>
         </is>
       </c>
       <c r="Q85" s="33" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="O86" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-25 (Sent to PM). GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted; investigation findings not yet shared, Short Term Fix Status set to Pending until CS responds.</t>
+          <t>GM reported no event was created specifically for the July 27 Chicago Heights, Illinois tornado (broader Illinois storm alerts existed) and asked whether Trialco was identified as impacted. EventWatch answered on 04-Aug-2026 that the storm was notified with a WarRoom on 27-Jul-2026, titled Severe Thunderstorms Cause Widespread Damage in Parts of Wisconsin, Illinois, and that Trialco's Chicago Heights location sits inside that WarRoom's geofence, with no public reporting of damage at the facility. Unresolved: a bulletin did reach GM, so whether this row is a confirmed miss has not been re-examined since, and the RCA Details name the clustering finding for the Nemak article on the same ticket rather than this event.</t>
         </is>
       </c>
       <c r="Q86" s="33" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="O91" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-28 (Done). Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
+          <t>Eaton asked what criteria triggered impact-confirmation notifications to Eaton suppliers on the Kandla Port cargo congestion bulletin, since the bulletin text focused on rice exports.</t>
         </is>
       </c>
       <c r="Q91" s="33" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="X94" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Keyword miss, confirmed by Engineering on 21-Aug-2026. The articles carrying the Laredo World Trade Bridge closure were not matched by the terms then in use. The keywords have been added and the articles are captured now. Supersedes the earlier shared note that no RCA had been issued, which was written while the ticket was still with Engineering.</t>
         </is>
       </c>
       <c r="Y94" s="33" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="O95" s="33" t="inlineStr">
         <is>
-          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail.</t>
+          <t>EAO-25: Event was not captured by the vendor due to a source coverage gap. Vendor was asked to add the sources to its network. RCA shared based on the investigation trail. Unresolved: EAO-13 records the same Cuautitlan FXI fire of 28-Jun-2026 as captured and then classified Not Impactful by the model, which is the opposite finding. Both tickets are Ford-facing and the contradiction has not been resolved.</t>
         </is>
       </c>
       <c r="P95" s="33" t="n"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="X95" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Source miss, confirmed by Engineering on 21-Aug-2026: the FXI de Cuautitlan fire was not captured by the vendor, and the vendor has been asked to add the outlets carrying it to its network. Supersedes the earlier shared note that no RCA had been issued, which was written while the ticket was still with Engineering.</t>
         </is>
       </c>
       <c r="Y95" s="33" t="inlineStr">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="X96" s="33" t="inlineStr">
         <is>
-          <t>Source articles for the Laredo World Trade Bridge closure, the Nemak Monterrey fire and the FXI Cuautitlan fire were not captured on the portal; Engineering investigation into the feed gap was requested 04-Aug-2026. Ticket is still open with PM, so no RCA has been issued yet.</t>
+          <t>Captured, clustered, and then closed at review. Engineering confirmed on 21-Aug-2026 that the algorithm captured the Nemak Santa Catarina fire, and that the news processing pipeline attached it to the existing factory-fire cluster for Nuevo Leon as an update; an analyst later marked that cluster Not Impactful. Supersedes the earlier shared note that the source articles were not captured, which was true of the FXI fire on the same ticket and not of this one.</t>
         </is>
       </c>
       <c r="Y96" s="33" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="O101" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-32 (Open). Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
+          <t>Liberty Blume requested industry intelligence on counterfeit/grey-market Ciena 400G optical transceivers beyond the supplier scanning report already provided.</t>
         </is>
       </c>
       <c r="Q101" s="33" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="O102" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-33 (In Progress). Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
+          <t>Caterpillar reported no notification for “Taiwan Strait Conflict Risk Assessment and Potential Global Supply Chain Impact”; CS found no matching event in the backend.</t>
         </is>
       </c>
       <c r="Q102" s="33" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="O103" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-34 (Open). Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
+          <t>Ford reported a missed alert for the August 31 update to Western Balkans/Serbia-EU border blockade disruptions; CS found the original January 2026 event but needs to confirm whether it was updated to cover this development. Related to the January 2026 Eaton row above (same underlying WarRoom, different customer/date).</t>
         </is>
       </c>
       <c r="Q103" s="33" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, Open) and EAO-36 (Ford, 08-Sep, Open). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Two things are still open and nobody is chasing them from this row: the DO team's correction of the SMI AMTEK coordinates is unconfirmed, and the Data team has not answered what the source of the Pune site's coordinates was, having been asked on 13-Oct and chased on 19-Oct. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, In Progress) and EAO-36 (Ford, 08-Sep, closed 22-Oct-2026). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Two things are still open and nobody is chasing them from this row: the DO team's correction of the SMI AMTEK coordinates is unconfirmed, and the Data team has not answered what the source of the Pune site's coordinates was, having been asked on 13-Oct and chased on 19-Oct. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14869,7 +14869,7 @@
       </c>
       <c r="O105" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-37 (Open). Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
+          <t>Sandisk was alerted internally to record heavy rain in Yokkaichi city, Japan and could find no news item or WarRoom for it, despite having loaded their own Yokkaichi sites as suppliers. The customer supplied no public source. CS verified the Sandisk org and then the database across all customer orgs and found no evidence the notification was ever generated, so the event did not enter the system at all rather than being filtered out. RCA requested.</t>
         </is>
       </c>
       <c r="P105" s="33" t="inlineStr">
@@ -14987,7 +14987,7 @@
       </c>
       <c r="O106" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-38 (Open). Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
+          <t>Eaton queried WarRoom 37485945, 'Vertiv Acquires UtilityInnovation Group' (event date 08-Sep-2026, closed, severity Low). Two questions: why a Supplier Impact Confirmation Request was issued when the supplier is the acquiring party, which the latest Resilinc event-threshold guidance says does not require supplier notification; and why the event was classified Medium risk. The customer wants to know whether scenarios are being missed. A written explanation covering both was requested rather than an RCA.</t>
         </is>
       </c>
       <c r="P106" s="33" t="n"/>
@@ -15215,7 +15215,7 @@
       </c>
       <c r="O108" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-39 (Open). Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
+          <t>Belden reported receiving no EventWatch notification and seeing no related news for Murata Manufacturing's FY2026 product line optimization, which discontinues specific MLCC part numbers across the GRM, GRJ, GRT, GXM, GXT, GCM, GCJ, GCG and ZRA families; written responses are due by end 2027, final orders by end March 2028 and last shipment 31-Mar-2029. Cause established as an analyst miss at review, not a coverage gap.</t>
         </is>
       </c>
       <c r="P108" s="33" t="n"/>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="O109" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-40 (Open). Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
+          <t>Hydraulic press fire at Precision Resource, Mt. Sterling, Kentucky on 08-Sep-2026, with smoke and water-suppression damage to the pressing and machining areas. The facility is a deep-tier supplier to Ford through two Tier-1s, producing fineblanked powertrain, transmission, seating and safety-critical parts. Reported by The Mt. Sterling Advocate; EventWatch neither detected nor broadcast it. The customer has formally requested an RCA, an Interim Corrective Action and a Permanent Corrective Action covering regional industrial incident detection and deep-tier site monitoring.</t>
         </is>
       </c>
       <c r="P109" s="33" t="n"/>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="X109" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement and posted on 24-Sep-2026; it is with the CSM for review before it goes to the customer, so the record stays Pending.</t>
+          <t>Source coverage gap, confirmed by Engineering on 17-Sep-2026: the incident was carried by a single outlet, a local Kentucky news reporter that was not part of the vendor's source network, and the vendor was asked to add it. Ford then asked whether the vendor being onboarded next quarter would have covered the event; Engineering confirmed on 24-Sep-2026 that the incoming vendor already carries that source, so the same event would have been captured under the new network. The RCA was amended to carry that statement, posted on 24-Sep-2026 and shared with the customer; the ticket closed on 05-Oct-2026.</t>
         </is>
       </c>
       <c r="Y109" s="33" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="O113" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-43 (In Progress). Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
+          <t>Eaton asked why Supplier Impact Confirmation requests are issued to a Tier-1 supplier when that supplier is the acquiring party, as distinct from a merger or business sale where integration impact is understandable. Three questions: what specific risks or impacts the notification assesses, which supply chain disruption scenarios are commonly associated with acquisitions, and what criteria Resilinc uses to decide an acquisition event warrants supplier outreach. No event or WarRoom was named and no service failure is alleged. Follows EAO-38, the same account's query on the Vertiv acquisition. A written explanation was issued on 23-Sep-2026.</t>
         </is>
       </c>
       <c r="P113" s="33" t="n"/>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="O114" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-44 (In Progress). Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
+          <t>Eaton queried the WarRoom 'UPG Enterprises Files for Chapter 11 Bankruptcy in the USA' (event date 23-Sep-2026) created against Mapes &amp; Sprowl. The customer read the source article and points out that although UPG Enterprises and Mapes &amp; Sprowl are corporately linked, the article states the filing is not related to Mapes &amp; Sprowl. Two questions: the rationale for creating the WarRoom against that supplier, and the basis for classifying the event as High severity. Findings and a response were requested rather than a formal RCA. Nitin answered both on the ticket on 24-Sep-2026.</t>
         </is>
       </c>
       <c r="P114" s="33" t="n"/>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="O118" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-48 (Open). Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
+          <t>Ford reported that Resilinc did not flag the South African logistics and port disruption set out in the Exporters Western Cape Cargo Movement Update of 20-Sep-2026. Cause per EventWatch Ops: the story did reach the analyst portal and an analyst overlooked it. An analyst error, not a source-coverage gap.</t>
         </is>
       </c>
       <c r="P118" s="33" t="n"/>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="O119" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-49 (Open). META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Analyst research and site-selection issue. Available reporting described flooding beyond Bangkok, but the initial assessment focused only on Bangkok and did not evaluate the other affected regions. The relevant Delta Electronics site was consequently omitted from the initial WarRoom. Ticket remains open with no formal RCA; status retained as Clarification Provided.</t>
+          <t>META reported that supplier DELTA ELECTRONICS and its Samut Prakan / Bangpoo site were not in the WarRoom at initial creation. TS confirmed the site is present now, added through a later WarRoom update, with the Activity Grid showing the subsequent addition. Analyst research and site-selection issue. Available reporting described flooding beyond Bangkok, but the initial assessment focused only on Bangkok and did not evaluate the other affected regions. The relevant Delta Electronics site was consequently omitted from the initial WarRoom. Ticket remains open with no formal RCA; status retained as Clarification Provided.</t>
         </is>
       </c>
       <c r="P119" s="33" t="n"/>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="O120" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-50 (Open). Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
+          <t>Ford reported a missed alert for a planned strike at AGC Display Glass, Yunlin County, Taiwan on 05-Oct-2026. Monitoring did pick up the 30-Sep-2026 report, but the story was classified Not Impactful at editorial review, so no EventWatch alert or WarRoom was published and nothing reached Ford. Cause per EventWatch Ops: an analyst, not automated logic. The story reached the analyst portal and the analyst moved it to Not Impactful without assessing it carefully.</t>
         </is>
       </c>
       <c r="P120" s="33" t="n"/>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="X120" s="33" t="inlineStr">
         <is>
-          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket is still open and the document text is not in the ticket.</t>
+          <t>Engineering confirmed on the ticket that the feed was received by the application and processed successfully, that a cluster was created for it, and that the cluster was later marked Not Impactful by an analyst. The written RCA was approved internally on 11-Oct-2026 and Customer Success was asked on 12-Oct-2026 to share the PDF with the customer; the ticket closed on 14-Oct-2026 and the document text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y120" s="33" t="inlineStr">
@@ -16703,7 +16703,7 @@
       </c>
       <c r="O121" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-52 (Open). General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and added the keywords to two RSS feeds on 14-Oct-2026, so the corrective action is complete and the row leaves Pending. STILL OPEN, and nothing automatic will look at this row again: the written RCA was attached on 14-Oct-2026 and is in internal approval with PM, not yet shared with General Mills, so there is no Resolution Date; the geofencing and WarRoom-creation questions the customer raised have not been answered separately. The Sub-type reads Keyword Update on engineering's own wording and awaits the owner's confirmation.</t>
+          <t>General Mills reported that a complete municipal water supply disruption and a citywide do-not-use-water order hit their Carlisle, Iowa flour mill on 30-Sep-2026, temporarily disrupting milling operations and requiring 2,500-gallon water tankers as mitigation, and that no WarRoom notification was generated. The customer confirms the Carlisle facility has been in their CDIF/site data since inception, including site ID, address, city and state, and that news coverage named Carlisle, Iowa explicitly. The ticket asks whether the event was captured by monitoring at all, why it was not associated with the facility if it was, and why no WarRoom followed. Engineering confirmed on 12-Oct-2026 that this is a keyword miss and added the keywords to two RSS feeds on 14-Oct-2026, so the corrective action is complete and the row leaves Pending. STILL OPEN, and nothing automatic will look at this row again: the written RCA was attached on 14-Oct-2026 and is in internal approval with PM, not yet shared with General Mills, so there is no Resolution Date; the geofencing and WarRoom-creation questions the customer raised have not been answered separately. The Sub-type reads Keyword Update on engineering's own wording and awaits the owner's confirmation.</t>
         </is>
       </c>
       <c r="P121" s="33" t="n"/>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="O125" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-53 (Open). Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The cited sources are Turkish-language reports of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. Settled as a source coverage gap: none of the three outlets is in the vendor's monitoring network and no similar source was captured, so there was no keyword possibility. This is the distinction against EAO-54, where the vendor did monitor the outlets and the matching terms missed the stories. Closed on the owner's call on 18-Oct-2026: the source-coverage finding is the response going back to Ford, so the row moves off Pending to RCA Shared. Resolution Date is left blank because the Jira ticket is still open at Sent to PM with no resolutiondate, and a guessed date is worse than none. A human carries the two loose ends from here, because a row off Pending is no longer picked up by the daily re-check: the vendor has not confirmed the sources are added, and the ticket has no closing date.</t>
+          <t>Ford reported that no alert was broadcast for the official bankruptcy declaration and reported operational distress at BER Automotive, Bursa, Türkiye, and asked for a manual event and WarRoom to be created immediately. Ford's own mapping links the supplier to its production network through Tier 1 AUO-connected suppliers, with line-stoppage risk once buffer stock is exhausted; they are running BOM mapping, Tier 1 stock audits and alternative sourcing in parallel. The cited sources are Turkish-language reports of alleged billion-lira fraud in the Bursa automotive sector, offered as customer evidence rather than verified fact. Settled as a source coverage gap: none of the three outlets is in the vendor's monitoring network and no similar source was captured, so there was no keyword possibility. This is the distinction against EAO-54, where the vendor did monitor the outlets and the matching terms missed the stories. Closed on the owner's call on 18-Oct-2026: the source-coverage finding is the response going back to Ford, so the row moves off Pending to RCA Shared. Resolution Date is left blank because the Jira ticket is still open at Approval Requested with no resolutiondate, and a guessed date is worse than none. A human carries the two loose ends from here, because a row off Pending is no longer picked up by the daily re-check: the vendor has not confirmed the sources are added, and the ticket has no closing date.</t>
         </is>
       </c>
       <c r="P125" s="33" t="n"/>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="O126" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess.</t>
+          <t>One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess.</t>
         </is>
       </c>
       <c r="P126" s="33" t="n"/>
@@ -17363,7 +17363,7 @@
       </c>
       <c r="O127" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-54 (Open). The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own.</t>
+          <t>The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own.</t>
         </is>
       </c>
       <c r="P127" s="33" t="n"/>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>Staged from Jira EAO-55 (In Progress). Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -11944,7 +11944,7 @@
       </c>
       <c r="X78" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 14-Jul-2026 as a PDF attached to EAO-17; the document text is not in the ticket.</t>
+          <t>Captured by the AI as an event, then failed at editorial assessment. Nitin Rindhe answered Micron's own follow-up on 21-Jul-2026: the reviewer evaluates whether an event meets the EventWatch publication criteria on the nature of the event, the affected company or facility, the potential operational or supply chain impact, geographic scope and the reporting thresholds in the methodology; in this instance the event had been successfully captured and identified by the AI, and was incorrectly assessed at that human validation step as not meeting the publication criteria, so it was not published until it was re-evaluated after Micron's inquiry. The RCA itself went out as a PDF whose text is not in the ticket. Open question for the owner: this description is an analyst review miss and the row is filed Product / Source Coverage, which says the story never arrived. The ticket says it did.</t>
         </is>
       </c>
       <c r="Y78" s="33" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="X90" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-27; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>Assessed as an isolated occurrence rather than in the context of the incidents before it. The corrective action Nitin Rindhe set out on 07-Oct-2026, answering Ford's question about whether the RCA's enhancement had been deployed, is that analysts are now expected to evaluate recurring or evolving geopolitical and border-related events against previous incidents rather than assessing each feed on its own, weighing recurrence and escalation, previously reported disruptions, proximity to critical transportation or logistics infrastructure, and implications for cross-border freight. It is a process-level change to the assessment methodology, not a product deployment. The RCA was reviewed and sent to the customer on 20-Aug-2026 as a PDF whose text is not in the ticket; the ticket closed 25-Aug-2026 and Ford reopened the thread on 05-Oct-2026 to ask about deployment.</t>
         </is>
       </c>
       <c r="Y90" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2987,7 +2987,7 @@
                   <v>33</v>
                 </pt>
                 <pt idx="1">
-                  <v>37</v>
+                  <v>36</v>
                 </pt>
                 <pt idx="2">
                   <v>5</v>
@@ -2996,7 +2996,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="4">
-                  <v>8</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="5">
                   <v>1</v>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="X75" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 13-Jul-2026 as a PDF attached to EAO-14; the document text is not in the ticket.</t>
+          <t>An AI misclassification reinforced during analyst review. The classification models did not sufficiently recognise the potential supply chain relevance of a factory fire involving an industrial manufacturing facility despite the severity of the incident. During manual review the initial AI assessment was accepted, so the event did not progress through the reporting workflow. Taken from the RCA shared with Ford on 13-Jul-2026, which supersedes the earlier note that the document text was unreadable from the ticket. Filed People / Review because the human review is where the assessment could have been corrected and was not.</t>
         </is>
       </c>
       <c r="Y75" s="33" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="X82" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 21-Jul-2026 as a PDF attached to EAO-21; the document text is not in the ticket.</t>
+          <t>The analyst missed it. During the initial AI assessment the event was classified Not Impactful because the news articles primarily emphasised hazardous air quality levels and public health advisories resulting from wildfire smoke, and the broader operational and regional supply chain implications of the widespread air quality degradation were not sufficiently recognised at that stage. The classification was then not identified during the human-in-the-loop review, so the event was not progressed for publication until it was re-evaluated after Ford's notification. Taken from the RCA shared with Ford on 21-Jul-2026. Owner's ruling: this is an analyst miss and does not go to Product.</t>
         </is>
       </c>
       <c r="Y82" s="33" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="X88" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 05-Aug-2026 as a PDF attached to EAO-23; the document text is not in the ticket.</t>
+          <t>The analyst overlooked it. The missed publication occurred during the human review stage, where the significance of China's export control measures and their potential impact on affected suppliers and downstream supply chains was incorrectly assessed. The event was marked Not Impactful and was not published despite meeting the EventWatch reporting criteria. Taken from the RCA shared with Ford on 05-Aug-2026. Owner's ruling: this is an analyst miss and does not go to Product.</t>
         </is>
       </c>
       <c r="Y88" s="33" t="inlineStr">
@@ -13430,7 +13430,7 @@
       </c>
       <c r="J92" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Mapping</t>
         </is>
       </c>
       <c r="K92" s="33" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="M92" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Supplier site mapping validation for named facilities, so a captured article naming a facility absent from the customer's mapped data is surfaced for assessment rather than closed on the absence</t>
         </is>
       </c>
       <c r="N92" s="33" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="V92" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Entity &amp; Supplier Resolution</t>
         </is>
       </c>
       <c r="W92" s="33" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="X92" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer on 20-Aug-2026 as a PDF attached to EAO-26; the document text is not in the ticket. Closed 25-Aug-2026 after no customer follow-up.</t>
+          <t>Not a source coverage gap. No independent public reporting was identified before 24-Jul-2026 and the 24-Jul article was successfully captured when it became available. The gap occurred during the event assessment: the affected Sasol facility was not mapped in the Resilinc database, no mapped supplier sites were identified in the immediate vicinity, and the first available article reported an incident that had occurred three days earlier. Those factors led to the event being classified Not Impactful. Taken from the RCA shared with Ford on 20-Aug-2026, which supersedes the earlier filing of this row as Source Coverage: the article was captured, so coverage was not what failed.</t>
         </is>
       </c>
       <c r="Y92" s="33" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="X118" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed internally on 05-Oct-2026 and shared with the customer as a PDF attached to EAO-48; the document text is not in the ticket. Closed 07-Oct-2026 with no follow-up received.</t>
+          <t>The analyst missed it. The gap occurred during the human-in-the-loop review of the 24-Sep and 25-Sep feeds: because an existing WarRoom already covered congestion at the Durban Gateway Terminal, the subsequent feeds were treated as information relating to an already-reported event and were marked Not Impactful. Taken from the RCA shared with Ford on 05-Oct-2026, which supersedes the earlier note that the document text was unreadable from the ticket.</t>
         </is>
       </c>
       <c r="Y118" s="33" t="inlineStr">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -10486,7 +10486,7 @@
       </c>
       <c r="X65" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 15-Jun-2026 as a PDF attached to EAO-4; the document text is not in the ticket.</t>
+          <t>An analyst overlooked the event. Eaton reported missing EventWatch coverage of a CO2 leak involving fatalities at a mapped supplier facility; settled by the owner on 18-Oct-2026 as an analyst miss, which moved the root cause from Product to People and routed the row to EventWatch Ops. The RCA itself went to the customer on 15-Jun-2026 as a PDF whose text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y65" s="33" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="X69" s="33" t="inlineStr">
         <is>
-          <t>RCA reviewed and sent to the customer as a PDF attached to EAO-10 (29-Jun-2026); the document text is not in the ticket.</t>
+          <t>An analyst impact-assessment failure. The event was captured successfully and was then incorrectly assessed as Not Impactful during analyst review, so it was never escalated. The RCA went to the customer on 29-Jun-2026 as a PDF whose text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y69" s="33" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="X70" s="33" t="inlineStr">
         <is>
-          <t>RCA approved and sent to the customer on 25-Jun-2026 as a PDF attached to EAO-9; the document text is not in the ticket. The WarRoom itself was published before the RCA was issued.</t>
+          <t>A clustering defect. The feeds captured the fire and the platform clustered it with an unrelated factory fire in Germany, which prevented a separate WarRoom being created. Settled by the owner on 18-Oct-2026 as Product rather than an analyst failure. The WarRoom was published before the RCA was issued, and the RCA went to the customer on 25-Jun-2026 as a PDF whose text is not in the ticket.</t>
         </is>
       </c>
       <c r="Y70" s="33" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="O97" s="33" t="inlineStr">
         <is>
-          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided. Settled by the owner: the bulletin was published, but the analyst selected incomplete industries and review did not correct the selection. This is a publishing-quality complaint, not a missed bulletin, so Missed_Flag is No.</t>
+          <t>EAO-30: EventWatch news was published on August 13 but was not visible on the customer portal. Portal visibility investigation completed and clarification provided. Settled by the owner: the bulletin was published, but the analyst selected incomplete industries and review did not correct the selection. Superseded on 15-Oct-2026 under the delivery test: published is not delivered. Nothing reached the Red Cross portal, so Missed_Flag is Yes.</t>
         </is>
       </c>
       <c r="P97" s="33" t="n"/>
@@ -14040,7 +14040,11 @@
           <t>TS-22695</t>
         </is>
       </c>
-      <c r="X97" s="33" t="n"/>
+      <c r="X97" s="33" t="inlineStr">
+        <is>
+          <t>The bulletin was published on 13-Aug-2026 and incorrect industry selection kept it off the Red Cross portal. The analyst selected incomplete industries and review did not correct the selection, so a customer-specific treatment existed only after the Red Cross chased it.</t>
+        </is>
+      </c>
       <c r="Y97" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>
@@ -14757,7 +14761,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, In Progress) and EAO-36 (Ford, 08-Sep, closed 22-Oct-2026). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Two things are still open and nobody is chasing them from this row: the DO team's correction of the SMI AMTEK coordinates is unconfirmed, and the Data team has not answered what the source of the Pune site's coordinates was, having been asked on 13-Oct and chased on 19-Oct. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, In Progress) and EAO-36 (Ford, 08-Sep, closed 22-Oct-2026). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Closed by the owner on 22-Oct-2026: the Data team acknowledged the geocode issue and nothing further is coming back on the source of the Pune site's coordinates, so the row is settled on the finding above rather than held open for an answer. EAO-36 resolved 22-Oct-2026 and EAO-35 was still at In Progress when the owner closed it. One thing is recorded as unconfirmed rather than chased: the DO team's correction of the SMI AMTEK coordinates. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -14800,7 +14804,9 @@
           <t>Product &amp; Platform</t>
         </is>
       </c>
-      <c r="Z104" s="37" t="n"/>
+      <c r="Z104" s="37" t="n">
+        <v>46317</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="35" t="n">

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>60</v>
+                  <v>61</v>
                 </pt>
                 <pt idx="1">
-                  <v>42</v>
+                  <v>41</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>32</v>
                 </pt>
                 <pt idx="1">
                   <v>36</v>
@@ -3002,7 +3002,7 @@
                   <v>1</v>
                 </pt>
                 <pt idx="6">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="7">
                   <v>2</v>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="M94" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Keyword coverage review on the feed harvesting algorithm for border and crossing closures, so a closure reported in the public domain is captured without a customer inquiry prompting it</t>
         </is>
       </c>
       <c r="N94" s="33" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="X94" s="33" t="inlineStr">
         <is>
-          <t>Keyword miss, confirmed by Engineering on 21-Aug-2026. The articles carrying the Laredo World Trade Bridge closure were not matched by the terms then in use. The keywords have been added and the articles are captured now. Supersedes the earlier shared note that no RCA had been issued, which was written while the ticket was still with Engineering.</t>
+          <t>A keyword gap in the feed harvesting algorithm. Product Management's investigation identified the gap, which stopped the relevant articles about the bridge closure being captured and processed by EventWatch, so the event never entered the AI classification or human-in-the-loop review workflow. Corrective actions: the event was assessed against the EventWatch reporting criteria after the customer inquiry and a bulletin was published; Product Management investigated the feed capture failure and identified the keyword gap; and the missing keyword was added to the feed harvesting algorithm. Taken from the RCA shared with the customer.</t>
         </is>
       </c>
       <c r="Y94" s="33" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="M95" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>Vendor source network gap tracking, so an outlet found to be carrying an incident outside the monitoring network is submitted for inclusion and the submission tracked to confirmation</t>
         </is>
       </c>
       <c r="N95" s="33" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="X95" s="33" t="inlineStr">
         <is>
-          <t>Source miss, confirmed by Engineering on 21-Aug-2026: the FXI de Cuautitlan fire was not captured by the vendor, and the vendor has been asked to add the outlets carrying it to its network. Supersedes the earlier shared note that no RCA had been issued, which was written while the ticket was still with Engineering.</t>
+          <t>An upstream source coverage gap, not an AI classification or human review error. Product Management confirmed that the sources reporting the incident were not part of the news vendor's monitoring network, so the relevant articles were never captured by EventWatch and never proceeded to AI classification or human-in-the-loop review. Corrective actions: the incident was reassessed against the reporting criteria after the customer inquiry and a bulletin was published; Product Management investigated the capture failure with the vendor; and the relevant sources were submitted to the vendor with a request to include them in its monitoring network. Taken from the RCA shared with the customer. Unresolved: EAO-13's own RCA describes the same Cuautitlan FXI fire as captured by EventWatch and then misjudged by the classification models, which is the opposite finding. Both RCAs went to Ford.</t>
         </is>
       </c>
       <c r="Y95" s="33" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="I96" s="33" t="inlineStr">
         <is>
-          <t>People</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="J96" s="33" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Clustering / Duplication Defect</t>
         </is>
       </c>
       <c r="K96" s="33" t="inlineStr">
@@ -13889,7 +13889,7 @@
       </c>
       <c r="M96" s="33" t="inlineStr">
         <is>
-          <t>Not Impactful Decision Validation</t>
+          <t>Cluster separation validation for distinct industrial incidents, so a new fire at a different facility is not absorbed as an update to an existing cluster</t>
         </is>
       </c>
       <c r="N96" s="33" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="V96" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Cluster Integrity &amp; Duplicate Prevention</t>
         </is>
       </c>
       <c r="W96" s="33" t="inlineStr">
@@ -13932,12 +13932,12 @@
       </c>
       <c r="X96" s="33" t="inlineStr">
         <is>
-          <t>Captured, clustered, and then closed at review. Engineering confirmed on 21-Aug-2026 that the algorithm captured the Nemak Santa Catarina fire, and that the news processing pipeline attached it to the existing factory-fire cluster for Nuevo Leon as an update; an analyst later marked that cluster Not Impactful. Supersedes the earlier shared note that the source articles were not captured, which was true of the FXI fire on the same ticket and not of this one.</t>
+          <t>Incorrect AI event clustering, not corrected at human review. The news processing pipeline captured the articles about the 30-Jul-2026 fire at Nemak's Santa Catarina plant, so there was no feed harvesting or source coverage issue. The AI classification models associated the articles with an existing event cluster instead of identifying the fire as a distinct industrial incident requiring independent assessment, and the reporting team accepted that classification at human-in-the-loop review and marked the feeds Not Impactful without recognising they were a separate fire. The RCA states the root cause as a combination of incorrect AI event clustering and insufficient validation during human review. A bulletin was published after the customer inquiry. Taken from the RCA shared with the customer, which supersedes the earlier filing of this row as People / Review: the failure originated in the clustering, and the Caterpillar Isselguss row (EAO-9) is the owner's precedent for filing that shape as a Product clustering defect rather than an analyst failure.</t>
         </is>
       </c>
       <c r="Y96" s="33" t="inlineStr">
         <is>
-          <t>EventWatch Ops - Nitin Rindhe</t>
+          <t>Product &amp; Platform</t>
         </is>
       </c>
       <c r="Z96" s="37" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1290,13 +1290,13 @@
                   <v>7</v>
                 </pt>
                 <pt idx="7">
-                  <v>14</v>
+                  <v>13</v>
                 </pt>
                 <pt idx="8">
                   <v>14</v>
                 </pt>
                 <pt idx="9">
-                  <v>7</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1412,7 +1412,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="7">
-                  <v>4</v>
+                  <v>5</v>
                 </pt>
                 <pt idx="8">
                   <v>4</v>
@@ -1771,13 +1771,13 @@
                   <v>46</v>
                 </pt>
                 <pt idx="1">
-                  <v>41</v>
+                  <v>40</v>
                 </pt>
                 <pt idx="2">
                   <v>14</v>
                 </pt>
                 <pt idx="3">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2091,7 +2091,7 @@
                   <v>109</v>
                 </pt>
                 <pt idx="3">
-                  <v>12</v>
+                  <v>13</v>
                 </pt>
               </numCache>
             </numRef>
@@ -2378,10 +2378,10 @@
                 <formatCode>General</formatCode>
                 <ptCount val="3"/>
                 <pt idx="0">
-                  <v>61</v>
+                  <v>59</v>
                 </pt>
                 <pt idx="1">
-                  <v>41</v>
+                  <v>43</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
@@ -2633,10 +2633,10 @@
                   <v>Collins Aerospace</v>
                 </pt>
                 <pt idx="4">
-                  <v>GM</v>
+                  <v>Belden Inc</v>
                 </pt>
                 <pt idx="5">
-                  <v>Belden Inc</v>
+                  <v>GM</v>
                 </pt>
                 <pt idx="6">
                   <v>Ford/GM</v>
@@ -2663,7 +2663,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="11"/>
                 <pt idx="0">
-                  <v>35</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="1">
                   <v>13</v>
@@ -2678,7 +2678,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="5">
-                  <v>3</v>
+                  <v>4</v>
                 </pt>
                 <pt idx="6">
                   <v>3</v>
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>32</v>
+                  <v>33</v>
                 </pt>
                 <pt idx="1">
                   <v>36</v>
@@ -2996,7 +2996,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="4">
-                  <v>9</v>
+                  <v>8</v>
                 </pt>
                 <pt idx="5">
                   <v>1</v>
@@ -3324,7 +3324,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z128" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z129" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z128"/>
+  <dimension ref="A1:Z129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>Model Classification Defect</t>
+          <t>Source Coverage</t>
         </is>
       </c>
       <c r="K74" s="33" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="M74" s="33" t="inlineStr">
         <is>
-          <t>Relevance scoring that stops treating supplier mapping as a dominant decision factor for major industrial incidents, weighting incident severity, manufacturing activity, facility type, industry relevance and downstream supply chain potential instead, so an unmapped manufacturing site is not closed out before an analyst has weighed it</t>
+          <t>Vendor source network coverage for Mexican regional and industrial trade press, so a factory fire carried only by outlets outside the monitoring network is captured without a customer inquiry prompting it</t>
         </is>
       </c>
       <c r="N74" s="33" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="O74" s="33" t="inlineStr">
         <is>
-          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input. Settled by the owner: the reports were captured, but Product incorrectly classified the event as Not Impactful. The customer later raised the event, after which it was reported. Filed as a model classification defect rather than a methodology weakness.</t>
+          <t>Customer reported a fire at FXI, a Tier 2 supplier, causing a Force Majeure at Sage Automotive Interiors, with no matching EventWatch notification. EventWatch captured the reports, but the event was classified Not Impactful under an inadequate relevance-assessment methodology. The available approach did not give sufficient weight to the severity and potential downstream significance of a major industrial fire when direct supply-chain impact had not yet been confirmed. Resilinc accepted this as a methodology weakness and committed to enhancing the relevance-scoring and review approach. The earlier explanation linking the classification to the company being unmapped is superseded; supplier mapping was not a dominant classification input. Settled by the owner: the reports were captured, but Product incorrectly classified the event as Not Impactful. The customer later raised the event, after which it was reported. Filed as a model classification defect rather than a methodology weakness. Superseded on 22-Oct-2026: the owner settled the EAO-13 against EAO-25 contradiction over this one fire in favour of EAO-25's RCA, so the row is filed Source Coverage and the methodology-weakness account above is the explanation that was sent to Ford, not the cause the tracker now carries.</t>
         </is>
       </c>
       <c r="P74" s="33" t="n"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="V74" s="33" t="inlineStr">
         <is>
-          <t>WarRoom &amp; Decision Validation</t>
+          <t>Dynamic Source Discovery</t>
         </is>
       </c>
       <c r="W74" s="33" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="X74" s="33" t="inlineStr">
         <is>
-          <t>A methodology weakness that Resilinc accepted, rather than an analyst execution error. EventWatch captured multiple public reports of the June 28, 2026 fire at the foam-manufacturing facility in Cuautitlan Izcalli, Mexico. The AI classification models categorized the event as Not Impactful based on the relevance assessment, including the absence of confirmed downstream supply-chain impact in the available reporting. The reporting team reviewed the captured articles through the human-in-the-loop process and concurred with the classification, so the event was not published. The investigation concluded that the weakness was in the relevance-assessment methodology itself. Significant industrial incidents required greater evaluation based on incident severity, manufacturing activity, facility type, industry relevance, and potential downstream impact, even when the available reporting did not yet confirm a direct supply-chain disruption. Resilinc accepted this methodology weakness, issued an ICA on 17-Jul-2026 adding a manual review for major industrial incidents initially classified Not Impactful, and committed to a PCA enhancing the AI relevance-scoring models. An earlier version of this entry listed the company's absence from the supplier database as a ground for the Not Impactful classification. That explanation is superseded. Supplier mapping was not a dominant input to the Event/Non-Event or Impactful/Not-Impactful classification decision.</t>
+          <t>An upstream source coverage gap. Superseded on 22-Oct-2026 by the owner, who settled this row against EAO-25's RCA for the same Cuautitlan FXI fire: Product Management confirmed that the sources reporting the incident were not part of the news vendor's monitoring network, so the articles were never captured by EventWatch and never proceeded to AI classification or human-in-the-loop review. The relevant sources were submitted to the vendor with a request to include them. This replaces the finding EAO-13's own RCA carried and that this row was filed on until today, which described the fire as captured by EventWatch and then classified Not Impactful by the AI models under a relevance-assessment methodology Resilinc accepted as deficient. The two RCAs went to Ford and they disagree; the owner has ruled that EAO-25's finding is the one the tracker carries.</t>
         </is>
       </c>
       <c r="Y74" s="33" t="inlineStr">
@@ -11883,12 +11883,12 @@
       </c>
       <c r="I78" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J78" s="33" t="inlineStr">
         <is>
-          <t>Source Coverage</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="K78" s="33" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="M78" s="33" t="inlineStr">
         <is>
-          <t>Legal/labor-litigation source coverage and entity-linking for supplier-adjacent lawsuits</t>
+          <t>Not Impactful decision validation for legal actions involving a monitored supplier, so a significant legal development is checked against the reporting criteria before it is closed at review</t>
         </is>
       </c>
       <c r="N78" s="33" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="V78" s="33" t="inlineStr">
         <is>
-          <t>Dynamic Source Discovery</t>
+          <t>WarRoom &amp; Decision Validation</t>
         </is>
       </c>
       <c r="W78" s="33" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="X78" s="33" t="inlineStr">
         <is>
-          <t>Captured by the AI as an event, then failed at editorial assessment. Nitin Rindhe answered Micron's own follow-up on 21-Jul-2026: the reviewer evaluates whether an event meets the EventWatch publication criteria on the nature of the event, the affected company or facility, the potential operational or supply chain impact, geographic scope and the reporting thresholds in the methodology; in this instance the event had been successfully captured and identified by the AI, and was incorrectly assessed at that human validation step as not meeting the publication criteria, so it was not published until it was re-evaluated after Micron's inquiry. The RCA itself went out as a PDF whose text is not in the ticket. Open question for the owner: this description is an analyst review miss and the row is filed Product / Source Coverage, which says the story never arrived. The ticket says it did.</t>
+          <t>The root cause occurred during the analyst review stage, where the litigation was mistakenly assessed as Not Impactful. The event was excluded from publication despite meeting the EventWatch reporting criteria for significant legal developments involving a monitored supplier. Taken from the RCA shared with Micron, which supersedes the earlier filing of this row as Product / Source Coverage: the event was captured, and what failed was the review.</t>
         </is>
       </c>
       <c r="Y78" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z78" s="37" t="n">
@@ -13415,22 +13415,22 @@
       </c>
       <c r="G92" s="33" t="inlineStr">
         <is>
-          <t>Complaint</t>
+          <t>Inquiry</t>
         </is>
       </c>
       <c r="H92" s="33" t="inlineStr">
         <is>
-          <t>Missed Event</t>
+          <t>Supplier Impact Mapping Clarification</t>
         </is>
       </c>
       <c r="I92" s="33" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="J92" s="33" t="inlineStr">
         <is>
-          <t>Mapping</t>
+          <t>Supplier / Site Not Shared</t>
         </is>
       </c>
       <c r="K92" s="33" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="M92" s="33" t="inlineStr">
         <is>
-          <t>Supplier site mapping validation for named facilities, so a captured article naming a facility absent from the customer's mapped data is surfaced for assessment rather than closed on the absence</t>
+          <t>A site-data completeness review with the customer, so a facility of a named supplier that is absent from the customer-provided data is identified before an event tests it</t>
         </is>
       </c>
       <c r="N92" s="33" t="inlineStr">
@@ -13461,7 +13461,7 @@
       <c r="P92" s="33" t="n"/>
       <c r="Q92" s="33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R92" s="39" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="U92" s="33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="V92" s="33" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="X92" s="33" t="inlineStr">
         <is>
-          <t>Not a source coverage gap. No independent public reporting was identified before 24-Jul-2026 and the 24-Jul article was successfully captured when it became available. The gap occurred during the event assessment: the affected Sasol facility was not mapped in the Resilinc database, no mapped supplier sites were identified in the immediate vicinity, and the first available article reported an incident that had occurred three days earlier. Those factors led to the event being classified Not Impactful. Taken from the RCA shared with Ford on 20-Aug-2026, which supersedes the earlier filing of this row as Source Coverage: the article was captured, so coverage was not what failed.</t>
+          <t>The affected Sasol facility was never in the customer-provided data, so no notification was owed. No independent public reporting was identified before 24-Jul-2026 and the 24-Jul article was successfully captured when it became available; the facility was not mapped in the Resilinc database, no mapped supplier sites were in the immediate vicinity, and the first available article reported an incident three days old, which together led to the event being classified Not Impactful. Settled by the owner on 22-Oct-2026 under the NVR Kinston rule: where the site was never shared with Resilinc, nothing in the platform and nothing an analyst did failed, and the remedy is how site data is gathered from the customer rather than a platform change. Issue Type is Inquiry, Root Cause Process, and Missed_Flag No. This supersedes both the original Source Coverage filing and the Product / Mapping reading of 22-Oct-2026.</t>
         </is>
       </c>
       <c r="Y92" s="33" t="inlineStr">
         <is>
-          <t>Product &amp; Platform</t>
+          <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
       <c r="Z92" s="37" t="n">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="X95" s="33" t="inlineStr">
         <is>
-          <t>An upstream source coverage gap, not an AI classification or human review error. Product Management confirmed that the sources reporting the incident were not part of the news vendor's monitoring network, so the relevant articles were never captured by EventWatch and never proceeded to AI classification or human-in-the-loop review. Corrective actions: the incident was reassessed against the reporting criteria after the customer inquiry and a bulletin was published; Product Management investigated the capture failure with the vendor; and the relevant sources were submitted to the vendor with a request to include them in its monitoring network. Taken from the RCA shared with the customer. Unresolved: EAO-13's own RCA describes the same Cuautitlan FXI fire as captured by EventWatch and then misjudged by the classification models, which is the opposite finding. Both RCAs went to Ford.</t>
+          <t>An upstream source coverage gap, not an AI classification or human review error. Product Management confirmed that the sources reporting the incident were not part of the news vendor's monitoring network, so the relevant articles were never captured by EventWatch and never proceeded to AI classification or human-in-the-loop review. Corrective actions: the incident was reassessed against the reporting criteria after the customer inquiry and a bulletin was published; Product Management investigated the capture failure with the vendor; and the relevant sources were submitted to the vendor with a request to include them in its monitoring network. Taken from the RCA shared with the customer. Settled on 22-Oct-2026: the owner ruled this finding over EAO-13's, which described the same fire as captured and then misjudged by the models, and EAO-13's row moved to Source Coverage to match.</t>
         </is>
       </c>
       <c r="Y95" s="33" t="inlineStr">
@@ -17419,16 +17419,16 @@
         <v>46296</v>
       </c>
       <c r="B128" s="37" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="C128" s="33" t="inlineStr">
         <is>
-          <t>Merger &amp; Acquisition</t>
+          <t>Supply Shortage</t>
         </is>
       </c>
       <c r="D128" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="E128" s="39" t="n">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="F128" s="33" t="inlineStr">
         <is>
-          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+          <t>WIN Semiconductors GaAs and InP Supply Adequacy Report - No EventWatch Notification (Belden)</t>
         </is>
       </c>
       <c r="G128" s="33" t="inlineStr">
@@ -17466,12 +17466,12 @@
       </c>
       <c r="L128" s="33" t="inlineStr">
         <is>
-          <t>RCA Shared</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="M128" s="33" t="inlineStr">
         <is>
-          <t>Coverage check for acquisition announcements carried only in French-language Canadian business press</t>
+          <t>Keyword coverage for compound-semiconductor substrate supply and production-demand reporting, so a DigiTimes assessment of GaAs and InP availability is captured whether it reports a shortage or adequate supply</t>
         </is>
       </c>
       <c r="N128" s="33" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>The third of three events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; the companion rows cover the gallium and germanium export-curb risk and the GaAs and InP epiwafer price increases. This row covers the DigiTimes report of 04-May-2026 that WIN Semiconductors said GaAs and InP supply still meets production demand despite higher GaAs substrate costs, which is the supply-adequacy counterpoint in the same thread and one of the five article URLs Nitin Rindhe put to Engineering on 21-Oct-2026. Split onto its own row on the owner's instruction of 22-Oct-2026 that the ticket carries three reportable events. Not captured, per the owner. DigiTimes is in the monitoring network, which is what rules out a source gap and leaves a keyword gap, the same reading the two companion rows carry. STILL OPEN: EAO-54 is at Sent to PM with one comment and no engineering reply, so this row stays Pending and nothing automatic will settle it.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="W128" s="33" t="inlineStr">
         <is>
-          <t>EAO-55</t>
+          <t>EAO-54</t>
         </is>
       </c>
       <c r="X128" s="33" t="n"/>
@@ -17521,6 +17521,118 @@
         </is>
       </c>
       <c r="Z128" s="37" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B129" s="37" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C129" s="33" t="inlineStr">
+        <is>
+          <t>Merger &amp; Acquisition</t>
+        </is>
+      </c>
+      <c r="D129" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil</t>
+        </is>
+      </c>
+      <c r="E129" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="33" t="inlineStr">
+        <is>
+          <t>WSP Acquisition of GCM Corpo - No EventWatch Notification (Irving Oil)</t>
+        </is>
+      </c>
+      <c r="G129" s="33" t="inlineStr">
+        <is>
+          <t>Complaint</t>
+        </is>
+      </c>
+      <c r="H129" s="33" t="inlineStr">
+        <is>
+          <t>Missed Event</t>
+        </is>
+      </c>
+      <c r="I129" s="33" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="J129" s="33" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="K129" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L129" s="33" t="inlineStr">
+        <is>
+          <t>RCA Shared</t>
+        </is>
+      </c>
+      <c r="M129" s="33" t="inlineStr">
+        <is>
+          <t>M&amp;A reportability validation at review, so an industry-relevant transaction is assessed for industry and product relevance before a Not Impactful call is made on the absence of customer-specific supplier mapping</t>
+        </is>
+      </c>
+      <c r="N129" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O129" s="33" t="inlineStr">
+        <is>
+          <t>Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+        </is>
+      </c>
+      <c r="P129" s="33" t="n"/>
+      <c r="Q129" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R129" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S129" s="39" t="n"/>
+      <c r="T129" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U129" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V129" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W129" s="33" t="inlineStr">
+        <is>
+          <t>EAO-55</t>
+        </is>
+      </c>
+      <c r="X129" s="33" t="inlineStr">
+        <is>
+          <t>An incorrect application of the M&amp;A reporting criteria during human-in-the-loop review. The feed harvesting algorithms captured the relevant articles on 01-Oct-2026 and the AI classification models correctly identified the feeds as an Event and routed them for review; the reporting team then treated the absence of customer-specific supplier mapping as sufficient grounds to classify the acquisition Not Impactful. Under the EventWatch Merger and Acquisition reporting guidelines, industry-relevant transactions involving unmapped companies may still qualify for publication as informational news alerts even where no customer-specific WarRoom is required. Corrective actions: the event was reassessed after the customer inquiry and a bulletin was published; the original Not Impactful classification was reviewed to identify the gap; and the incident was reviewed with the reporting team, emphasising the distinction between event reportability and customer-specific supplier mapping. Preventive measures: the M&amp;A reporting guidelines were reinforced, the reporting team will assess M&amp;A events for relevance to EventWatch-covered industries before a final Not Impactful determination based on supplier mapping, and this incident becomes a reference scenario for distinguishing informational M&amp;A events from those needing a customer-specific WarRoom. Taken from the RCA shared with Irving Oil, which supersedes the earlier filing of this row as Product / Keyword Update: the articles were captured and the models routed them correctly, so what failed was the review.</t>
+        </is>
+      </c>
+      <c r="Y129" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z129" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -19274,11 +19386,11 @@
       </c>
       <c r="B67" s="21" t="n" cm="1">
         <f t="array" ref="B67:B76">COUNTIFS(ComplaintTracker[Issue Type],"Complaint",ComplaintTracker[Customer],_xlfn.ANCHORARRAY(A67))</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.33980582524271846</v>
+        <v>0.3300970873786408</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -19438,7 +19550,7 @@
     <row r="71" ht="23.25" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>Belden Inc</t>
         </is>
       </c>
       <c r="B71" s="22" t="n">
@@ -19480,14 +19592,14 @@
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B72" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.02912621359223301</v>
+        <v>0.038834951456310676</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19678,10 +19790,10 @@
         </is>
       </c>
       <c r="J76" s="76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K76" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="76" t="n">
         <v>16</v>
@@ -20062,13 +20174,13 @@
         </is>
       </c>
       <c r="J90" s="76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
@@ -20155,10 +20267,10 @@
         <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17481,7 +17481,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>The third of three events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; the companion rows cover the gallium and germanium export-curb risk and the GaAs and InP epiwafer price increases. This row covers the DigiTimes report of 04-May-2026 that WIN Semiconductors said GaAs and InP supply still meets production demand despite higher GaAs substrate costs, which is the supply-adequacy counterpoint in the same thread and one of the five article URLs Nitin Rindhe put to Engineering on 21-Oct-2026. Split onto its own row on the owner's instruction of 22-Oct-2026 that the ticket carries three reportable events. Not captured, per the owner. DigiTimes is in the monitoring network, which is what rules out a source gap and leaves a keyword gap, the same reading the two companion rows carry. STILL OPEN: EAO-54 is at Sent to PM with one comment and no engineering reply, so this row stays Pending and nothing automatic will settle it.</t>
+          <t>The third of three events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; the companion rows cover the gallium and germanium export-curb risk and the GaAs and InP epiwafer price increases. This row covers the DigiTimes report of 04-May-2026 that WIN Semiconductors said GaAs and InP supply still meets production demand despite higher GaAs substrate costs, which is the supply-adequacy counterpoint in the same thread and one of the five article URLs Nitin Rindhe put to Engineering on 21-Oct-2026. Split onto its own row on the owner's instruction of 22-Oct-2026 that the ticket carries three reportable events. Not captured, per the owner. The owner confirmed on 22-Oct-2026 that all three articles were owed to Belden, which settles this row as a miss rather than an article we had no obligation to surface: the supply-adequacy report is part of the picture Belden was owed on GaAs and InP availability, not a counterpoint outside scope. DigiTimes is in the monitoring network, which is what rules out a source gap and leaves a keyword gap, the same reading the two companion rows carry. STILL OPEN: EAO-54 is at Sent to PM with one comment and no engineering reply, so this row stays Pending and nothing automatic will settle it.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17292,7 +17292,7 @@
       </c>
       <c r="X126" s="33" t="inlineStr">
         <is>
-          <t>Keyword gap, not a source gap. Reuters is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
+          <t>Keyword gap, not a source gap. Reuters is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026. Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. Of the three articles behind this row, the Asia Times report of 04-Sep-2026 and the MarketScreener report of 18-Sep-2026 were captured by the vendor and Engineering is checking why they did not reach our system, naming a keyword miss or RSS leakage as the two candidates. The FT Mercati report of 18-Sep-2026 was NOT captured by the vendor and a request has been raised with them. OPEN QUESTION for the owner, not applied here: one of the three articles is a source gap by Engineering's own account, which the Keyword Update filing on this row does not cover. Note also that this RCA names Reuters as the carrying outlet while the ticket's own evidence URLs are Asia Times, MarketScreener and FT Mercati.</t>
         </is>
       </c>
       <c r="Y126" s="33" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="X127" s="33" t="inlineStr">
         <is>
-          <t>Keyword gap, not a source gap. DigiTimes is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026.</t>
+          <t>Keyword gap, not a source gap. DigiTimes is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026. Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. The DigiTimes report of 02-Jul-2026 behind this row cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window. STILL OPEN and nothing automatic will settle it: the keyword-gap reading rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored, and no capture evidence for this article can now be produced either way.</t>
         </is>
       </c>
       <c r="Y127" s="33" t="inlineStr">
@@ -17514,7 +17514,11 @@
           <t>EAO-54</t>
         </is>
       </c>
-      <c r="X128" s="33" t="n"/>
+      <c r="X128" s="33" t="inlineStr">
+        <is>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. The DigiTimes report of 04-May-2026 behind this row cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window. STILL OPEN and nothing automatic will settle it: the keyword-gap reading rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored, and no capture evidence for this article can now be produced either way.</t>
+        </is>
+      </c>
       <c r="Y128" s="33" t="inlineStr">
         <is>
           <t>Product &amp; Platform</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1418,7 +1418,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="9">
-                  <v>2</v>
+                  <v>3</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -2088,7 +2088,7 @@
                   <v>6</v>
                 </pt>
                 <pt idx="2">
-                  <v>109</v>
+                  <v>110</v>
                 </pt>
                 <pt idx="3">
                   <v>13</v>
@@ -3324,7 +3324,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z129" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ComplaintTracker" displayName="ComplaintTracker" ref="A1:Z130" headerRowCount="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="A1:Z104"/>
   <tableColumns count="26">
     <tableColumn id="1" name="Month" dataDxfId="28">
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z129"/>
+  <dimension ref="A1:Z130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.7109375" customWidth="1" style="1" min="1" max="1"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="X125" s="33" t="inlineStr">
         <is>
-          <t>Source coverage gap, confirmed by Product Management. None of the three outlets carrying the Bursa fraud allegations is in the vendor's monitoring network: ekonomistar.com.tr, which Ford cited, and sondakihaber.com and ifinnapp.com, which were checked on the ticket. No similar source reporting the news was captured either, so the story never reached the application and no keyword could have matched it. The vendor has been asked to add the sources and is working on it. Established by Ankit Gupta on 16-Oct-2026 and confirmed by Product Management.</t>
+          <t>An upstream source coverage gap. Product Management's investigation confirmed that the sources reporting the incident were outside the news vendor's existing monitoring network, so the relevant articles were unavailable for automated classification and human-in-the-loop review, which resulted in the missed notification. The outlets checked were ekonomistar.com.tr, which Ford cited, and sondakihaber.com and ifinnapp.com, which were raised on the ticket. Taken from the RCA shared with Ford.</t>
         </is>
       </c>
       <c r="Y125" s="33" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="X126" s="33" t="inlineStr">
         <is>
-          <t>Keyword gap, not a source gap. Reuters is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026. Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. Of the three articles behind this row, the Asia Times report of 04-Sep-2026 and the MarketScreener report of 18-Sep-2026 were captured by the vendor and Engineering is checking why they did not reach our system, naming a keyword miss or RSS leakage as the two candidates. The FT Mercati report of 18-Sep-2026 was NOT captured by the vendor and a request has been raised with them. OPEN QUESTION for the owner, not applied here: one of the three articles is a source gap by Engineering's own account, which the Keyword Update filing on this row does not cover. Note also that this RCA names Reuters as the carrying outlet while the ticket's own evidence URLs are Asia Times, MarketScreener and FT Mercati.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. Three of the five URLs belong to this row, and the findings differ by outlet. The Asia Times report of 04-Sep-2026 and the MarketScreener report of 18-Sep-2026 WERE captured by the vendor, and Engineering is still checking why they did not reach our system, naming a keyword miss or RSS leakage as the two candidates. The FT Mercati report of 18-Sep-2026 was NOT captured by the vendor, which is a source miss on that outlet, and a request has been raised with them to add it. The row stays Keyword Update because a source miss on FT Mercati is not what stopped delivery: two other outlets carrying the same story did reach the vendor, so Belden would have been notified had those come through. That is the only concluded finding on this row, and the cause of the two that did arrive is still open. OPEN FOR THE OWNER: filing this row as Source Coverage instead is a one-field change if the FT Mercati finding is to be the one the row carries. Note also that this row previously named Reuters as the carrying outlet; the ticket's own evidence URLs are Asia Times, MarketScreener and FT Mercati.</t>
         </is>
       </c>
       <c r="Y126" s="33" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="X127" s="33" t="inlineStr">
         <is>
-          <t>Keyword gap, not a source gap. DigiTimes is in the monitoring network and its feed was received, so the article was available to the application; neither the exact title nor a similar article for that date window was matched, so nothing was created and no notification could be generated. Confirmed by the owner on 18-Oct-2026. Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. The DigiTimes report of 02-Jul-2026 behind this row cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window. STILL OPEN and nothing automatic will settle it: the keyword-gap reading rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored, and no capture evidence for this article can now be produced either way.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. The DigiTimes report of 02-Jul-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. STILL OPEN and nothing automatic will settle it.</t>
         </is>
       </c>
       <c r="Y127" s="33" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="X128" s="33" t="inlineStr">
         <is>
-          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, an interim finding rather than a concluded RCA: the ticket is still at Sent to PM with no resolution date. The DigiTimes report of 04-May-2026 behind this row cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window. STILL OPEN and nothing automatic will settle it: the keyword-gap reading rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored, and no capture evidence for this article can now be produced either way.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. The DigiTimes report of 04-May-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. STILL OPEN and nothing automatic will settle it.</t>
         </is>
       </c>
       <c r="Y128" s="33" t="inlineStr">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="X129" s="33" t="inlineStr">
         <is>
-          <t>An incorrect application of the M&amp;A reporting criteria during human-in-the-loop review. The feed harvesting algorithms captured the relevant articles on 01-Oct-2026 and the AI classification models correctly identified the feeds as an Event and routed them for review; the reporting team then treated the absence of customer-specific supplier mapping as sufficient grounds to classify the acquisition Not Impactful. Under the EventWatch Merger and Acquisition reporting guidelines, industry-relevant transactions involving unmapped companies may still qualify for publication as informational news alerts even where no customer-specific WarRoom is required. Corrective actions: the event was reassessed after the customer inquiry and a bulletin was published; the original Not Impactful classification was reviewed to identify the gap; and the incident was reviewed with the reporting team, emphasising the distinction between event reportability and customer-specific supplier mapping. Preventive measures: the M&amp;A reporting guidelines were reinforced, the reporting team will assess M&amp;A events for relevance to EventWatch-covered industries before a final Not Impactful determination based on supplier mapping, and this incident becomes a reference scenario for distinguishing informational M&amp;A events from those needing a customer-specific WarRoom. Taken from the RCA shared with Irving Oil, which supersedes the earlier filing of this row as Product / Keyword Update: the articles were captured and the models routed them correctly, so what failed was the review.</t>
+          <t>Analyst error, per the owner. An incorrect application of the M&amp;A reporting criteria during human-in-the-loop review: the reporting team incorrectly treated the absence of customer-specific supplier mapping as sufficient grounds to classify the acquisition Not Impactful. Under the EventWatch Merger and Acquisition reporting guidelines, industry-relevant transactions involving unmapped companies may still qualify for publication as informational news alerts, even where no customer-specific WarRoom is required. The feed harvesting algorithms captured the relevant articles on 01-Oct-2026 and the AI classification models correctly identified the feeds as an Event and routed them for review, so neither capture nor classification failed. Taken from the RCA shared with Irving Oil on 23-Oct-2026.</t>
         </is>
       </c>
       <c r="Y129" s="33" t="inlineStr">
@@ -17637,6 +17637,114 @@
         </is>
       </c>
       <c r="Z129" s="37" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="35" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B130" s="37" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C130" s="33" t="inlineStr">
+        <is>
+          <t>Hurricane/Typhoon</t>
+        </is>
+      </c>
+      <c r="D130" s="33" t="inlineStr">
+        <is>
+          <t>Collins Aerospace</t>
+        </is>
+      </c>
+      <c r="E130" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="33" t="inlineStr">
+        <is>
+          <t>Tropical Depression Nine Supplier Impact Notification Sent Before Landfall (Collins Aerospace)</t>
+        </is>
+      </c>
+      <c r="G130" s="33" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="H130" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+        </is>
+      </c>
+      <c r="I130" s="33" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="J130" s="33" t="inlineStr">
+        <is>
+          <t>Process Clarification</t>
+        </is>
+      </c>
+      <c r="K130" s="33" t="inlineStr">
+        <is>
+          <t>Improvement</t>
+        </is>
+      </c>
+      <c r="L130" s="33" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M130" s="33" t="inlineStr">
+        <is>
+          <t>Supplier Impact Notification trigger-timing validation against the WarRoom guideline, so a forecast-stage weather event does not issue impact-confirmation requests before the criterion the guideline names is met</t>
+        </is>
+      </c>
+      <c r="N130" s="33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O130" s="33" t="inlineStr">
+        <is>
+          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification.</t>
+        </is>
+      </c>
+      <c r="P130" s="33" t="n"/>
+      <c r="Q130" s="33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R130" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="S130" s="39" t="n"/>
+      <c r="T130" s="35" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="U130" s="33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="V130" s="33" t="inlineStr">
+        <is>
+          <t>WarRoom &amp; Decision Validation</t>
+        </is>
+      </c>
+      <c r="W130" s="33" t="inlineStr">
+        <is>
+          <t>EAO-56</t>
+        </is>
+      </c>
+      <c r="X130" s="33" t="n"/>
+      <c r="Y130" s="33" t="inlineStr">
+        <is>
+          <t>EventWatch Ops - Nitin Rindhe</t>
+        </is>
+      </c>
+      <c r="Z130" s="37" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="U2:U81">
@@ -19899,10 +20007,10 @@
         <v>0</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" ht="23.25" customHeight="1">
@@ -20271,10 +20379,10 @@
         <v>103</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L93" s="77" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M93" s="3" t="n"/>
       <c r="N93" s="3" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1774,10 +1774,10 @@
                   <v>40</v>
                 </pt>
                 <pt idx="2">
-                  <v>14</v>
+                  <v>17</v>
                 </pt>
                 <pt idx="3">
-                  <v>3</v>
+                  <v>0</v>
                 </pt>
               </numCache>
             </numRef>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="L126" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M126" s="33" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="O126" s="33" t="inlineStr">
         <is>
-          <t>One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess.</t>
+          <t>One of two events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; see the companion row for the epiwafer price increases. This row covers the Reuters report of 18-Sep-2026 on continued high prices and supply shortages for gallium and germanium under Chinese export curbs, with AI, fibre-optic and infrared-imaging demand adding pressure. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that Reuters is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap rather than leaving it a staging guess. Closed by the owner on 26-Oct-2026: these are not open tickets any more. Short Term Fix Status moves off Pending to Clarification Provided -- Engineering's findings are the answer that went back, and no RCA document was attached to this ticket. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: Engineering has not reported whether the two captured articles were a keyword miss or RSS leakage, and the vendor request to add the FT Mercati source is unconfirmed.</t>
         </is>
       </c>
       <c r="P126" s="33" t="n"/>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="L127" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M127" s="33" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="O127" s="33" t="inlineStr">
         <is>
-          <t>The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own.</t>
+          <t>The second of two events Belden raised in a single ticket; see the companion row for the gallium and germanium export-curb risk. This row covers the DigiTimes report of 02-Jul-2026 that compound-semiconductor epitaxy makers are raising GaAs and InP epiwafer prices amid rising input costs, supply-chain shortages and inflation. CS verified the Belden org and found no notification, then checked the database across all customer orgs and found no evidence any notification was generated or sent. Settled by the owner: the event is critical and EventWatch could have notified it within that date range, and neither the exact title nor a similar article was found in the system for that window. The owner has since confirmed that DigiTimes is in the monitoring network, which rules out a source gap and establishes the Sub-type as a keyword gap. Recorded as a counterpoint on the same subject: DigiTimes of 04-May-2026 carried WIN Semiconductors stating that GaAs and InP supply still meets production demand despite higher substrate costs. That statement is not itself a reportable disruption, so it takes no row of its own. Closed by the owner on 26-Oct-2026: these are not open tickets any more. Short Term Fix Status moves off Pending to Clarification Provided -- Engineering's findings are the answer that went back, and no RCA document was attached to this ticket. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: the cause can never be established, the article being outside the vendor's 100-day retention window.</t>
         </is>
       </c>
       <c r="P127" s="33" t="n"/>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L128" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M128" s="33" t="inlineStr">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="O128" s="33" t="inlineStr">
         <is>
-          <t>The third of three events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; the companion rows cover the gallium and germanium export-curb risk and the GaAs and InP epiwafer price increases. This row covers the DigiTimes report of 04-May-2026 that WIN Semiconductors said GaAs and InP supply still meets production demand despite higher GaAs substrate costs, which is the supply-adequacy counterpoint in the same thread and one of the five article URLs Nitin Rindhe put to Engineering on 21-Oct-2026. Split onto its own row on the owner's instruction of 22-Oct-2026 that the ticket carries three reportable events. Not captured, per the owner. The owner confirmed on 22-Oct-2026 that all three articles were owed to Belden, which settles this row as a miss rather than an article we had no obligation to surface: the supply-adequacy report is part of the picture Belden was owed on GaAs and InP availability, not a counterpoint outside scope. DigiTimes is in the monitoring network, which is what rules out a source gap and leaves a keyword gap, the same reading the two companion rows carry. STILL OPEN: EAO-54 is at Sent to PM with one comment and no engineering reply, so this row stays Pending and nothing automatic will settle it.</t>
+          <t>The third of three events Belden raised in a single ticket about gallium arsenide, indium phosphide and semiconductor supply-chain risk; the companion rows cover the gallium and germanium export-curb risk and the GaAs and InP epiwafer price increases. This row covers the DigiTimes report of 04-May-2026 that WIN Semiconductors said GaAs and InP supply still meets production demand despite higher GaAs substrate costs, which is the supply-adequacy counterpoint in the same thread and one of the five article URLs Nitin Rindhe put to Engineering on 21-Oct-2026. Split onto its own row on the owner's instruction of 22-Oct-2026 that the ticket carries three reportable events. Not captured, per the owner. The owner confirmed on 22-Oct-2026 that all three articles were owed to Belden, which settles this row as a miss rather than an article we had no obligation to surface: the supply-adequacy report is part of the picture Belden was owed on GaAs and InP availability, not a counterpoint outside scope. DigiTimes is in the monitoring network, which is what rules out a source gap and leaves a keyword gap, the same reading the two companion rows carry. EAO-54 was at Sent to PM with one comment and no engineering reply when this row was written. Closed by the owner on 26-Oct-2026: these are not open tickets any more. Short Term Fix Status moves off Pending to Clarification Provided -- Engineering's findings are the answer that went back, and no RCA document was attached to this ticket. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: the cause can never be established, the article being outside the vendor's 100-day retention window.</t>
         </is>
       </c>
       <c r="P128" s="33" t="n"/>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="L130" s="33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Clarification Provided</t>
         </is>
       </c>
       <c r="M130" s="33" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="O130" s="33" t="inlineStr">
         <is>
-          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification.</t>
+          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification. Closed by the owner on 26-Oct-2026: these are not open tickets any more. Short Term Fix Status moves off Pending to Clarification Provided -- Engineering's findings are the answer that went back, and no RCA document was attached to this ticket. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: EAO-56 carries no engineering comment at all, so the Process Clarification reading has never been tested against what the trigger actually did.</t>
         </is>
       </c>
       <c r="P130" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -17593,7 +17593,7 @@
       </c>
       <c r="O129" s="33" t="inlineStr">
         <is>
-          <t>Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. The ticket itself carries no resolution date, so Resolution Date stays blank. The RCA is an attachment and its text is not readable from the ticket, so RCA Details stays blank rather than carrying a paraphrase of a document nobody here can open. The cause named in that document is not known, so the Sub-type below is still the staging guess it was. The Sub-type is a staging guess: the ticket does not say the feed was not received, so Source Coverage is not supported on the evidence available. If the investigation names language as the cause, the Standard Automation Focus becomes Multilingual Keyword Expansion.</t>
+          <t>Irving Oil reported that no event was published for WSP's acquisition of GCM Corpo. Customer Support checked the backend and found no event matching that title in the database. The supporting article is a French-language release in Le Devoir. RCA - WSP Global to Acquire GCM Corpo.docx was attached to the ticket by Nitin Rindhe on 21-Oct-2026 and sent to Prithviraj Bajpai. On the owner's rule that attaching the RCA completes the record, this row is RCA Shared. Prithviraj Bajpai confirmed on 23-Oct-2026 that the RCA went to the customer, and Nitin Rindhe closed the ticket on 26-Oct-2026 with no follow-up received. Resolution Date is the ticket's own resolutiondate of 26-Oct-2026, which supersedes the earlier note on this row that the ticket carried none. The RCA document itself is an attachment nobody here can open; its text reached this row on 26-Oct-2026 because the owner pasted it, which also supersedes the earlier note that RCA Details stays blank and that the Sub-type is a staging guess. The owner's ruling is analyst error, and People / Review is settled rather than staged.</t>
         </is>
       </c>
       <c r="P129" s="33" t="n"/>
@@ -17636,7 +17636,9 @@
           <t>EventWatch Ops - Nitin Rindhe</t>
         </is>
       </c>
-      <c r="Z129" s="37" t="n"/>
+      <c r="Z129" s="37" t="n">
+        <v>46321</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="35" t="n">
@@ -17690,7 +17692,7 @@
       </c>
       <c r="L130" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M130" s="33" t="inlineStr">
@@ -17705,7 +17707,7 @@
       </c>
       <c r="O130" s="33" t="inlineStr">
         <is>
-          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification. Closed by the owner on 26-Oct-2026: these are not open tickets any more. Short Term Fix Status moves off Pending to Clarification Provided -- Engineering's findings are the answer that went back, and no RCA document was attached to this ticket. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: EAO-56 carries no engineering comment at all, so the Process Clarification reading has never been tested against what the trigger actually did.</t>
+          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification. Closed by the owner on 26-Oct-2026: these are not open tickets any more. An RCA document was then attached to the ticket by Nitin Rindhe on 26-Oct-2026 and passed to Kishor Patil, who asked Steven Brandt to review it before it goes to the customer, so the status moves from Clarification Provided to RCA Shared on the owner's rule that attaching the RCA completes the record -- the same reading the Irving Oil row carries. That supersedes the note on this row that no RCA document was attached. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: the RCA is an attachment nobody here can open and the ticket's comments are routing notes rather than findings, so the Process Clarification reading has still never been tested against what the trigger actually did. The ticket carries no resolutiondate, so Resolution Date stays blank.</t>
         </is>
       </c>
       <c r="P130" s="33" t="n"/>
@@ -17738,7 +17740,11 @@
           <t>EAO-56</t>
         </is>
       </c>
-      <c r="X130" s="33" t="n"/>
+      <c r="X130" s="33" t="inlineStr">
+        <is>
+          <t>An RCA document was attached to EAO-56 on 26-Oct-2026 by Nitin Rindhe and is with the CSM for review before it goes to Collins Aerospace. Its text is an attachment that is not readable from the ticket, and the ticket's own comments are routing notes rather than findings, so the cause it names is not known here. The row's Root Cause and Sub-type remain the staging reading taken when it was appended: whether the Supplier Impact Notification fired against its own guideline has not been established.</t>
+        </is>
+      </c>
       <c r="Y130" s="33" t="inlineStr">
         <is>
           <t>EventWatch Ops - Nitin Rindhe</t>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1296,7 +1296,7 @@
                   <v>14</v>
                 </pt>
                 <pt idx="9">
-                  <v>8</v>
+                  <v>9</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1418,7 +1418,7 @@
                   <v>4</v>
                 </pt>
                 <pt idx="9">
-                  <v>3</v>
+                  <v>2</v>
                 </pt>
                 <pt idx="10">
                   <v>0</v>
@@ -1771,7 +1771,7 @@
                   <v>46</v>
                 </pt>
                 <pt idx="1">
-                  <v>40</v>
+                  <v>41</v>
                 </pt>
                 <pt idx="2">
                   <v>17</v>
@@ -2381,7 +2381,7 @@
                   <v>59</v>
                 </pt>
                 <pt idx="1">
-                  <v>43</v>
+                  <v>44</v>
                 </pt>
                 <pt idx="2">
                   <v>1</v>
@@ -2672,7 +2672,7 @@
                   <v>7</v>
                 </pt>
                 <pt idx="3">
-                  <v>5</v>
+                  <v>6</v>
                 </pt>
                 <pt idx="4">
                   <v>4</v>
@@ -2984,7 +2984,7 @@
                 <formatCode>General</formatCode>
                 <ptCount val="10"/>
                 <pt idx="0">
-                  <v>33</v>
+                  <v>34</v>
                 </pt>
                 <pt idx="1">
                   <v>36</v>
@@ -17667,22 +17667,22 @@
       </c>
       <c r="G130" s="33" t="inlineStr">
         <is>
-          <t>Inquiry</t>
+          <t>Complaint</t>
         </is>
       </c>
       <c r="H130" s="33" t="inlineStr">
         <is>
-          <t>WarRoom Timing/Trigger Criteria Clarification</t>
+          <t>Incorrect Action</t>
         </is>
       </c>
       <c r="I130" s="33" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>People</t>
         </is>
       </c>
       <c r="J130" s="33" t="inlineStr">
         <is>
-          <t>Process Clarification</t>
+          <t>Policy/Logic</t>
         </is>
       </c>
       <c r="K130" s="33" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="M130" s="33" t="inlineStr">
         <is>
-          <t>Supplier Impact Notification trigger-timing validation against the WarRoom guideline, so a forecast-stage weather event does not issue impact-confirmation requests before the criterion the guideline names is met</t>
+          <t>Landfall verification before supplier outreach on tropical systems, so a Supplier Impact Confirmation request for a hurricane, typhoon or tropical storm cannot be issued until the storm's landfall status is checked against the reporting guideline</t>
         </is>
       </c>
       <c r="N130" s="33" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="O130" s="33" t="inlineStr">
         <is>
-          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as an Inquiry on the owner's instruction of 26-Oct-2026: the customer is asking which criterion the trigger applies, and nothing has gone back to them yet. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. STILL OPEN and nothing automatic will settle it beyond the Pending re-check: EAO-56 is at Open with no engineering comment, so Root Cause and Sub-type here are staging guesses. If the guideline says what the customer says it says and the trigger fired against it, this becomes a Platform Bug rather than a clarification. Closed by the owner on 26-Oct-2026: these are not open tickets any more. An RCA document was then attached to the ticket by Nitin Rindhe on 26-Oct-2026 and passed to Kishor Patil, who asked Steven Brandt to review it before it goes to the customer, so the status moves from Clarification Provided to RCA Shared on the owner's rule that attaching the RCA completes the record -- the same reading the Irving Oil row carries. That supersedes the note on this row that no RCA document was attached. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. Outstanding and carried by a human from here: the RCA is an attachment nobody here can open and the ticket's comments are routing notes rather than findings, so the Process Clarification reading has still never been tested against what the trigger actually did. The ticket carries no resolutiondate, so Resolution Date stays blank.</t>
+          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as a Complaint on the owner's instruction of 27-Oct-2026: the RCA establishes that a guideline was broken, which is the test for a complaint rather than a question about how something works. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. Settled by the owner on 27-Oct-2026 against the RCA document, which the owner pasted in because its text is not readable from the ticket: this is analyst error and not an inquiry. The reporting team assessed the storm's intensification correctly and the WarRoom was right; the error was issuing the Supplier Impact Notification before landfall, contrary to a guideline that was itself sound. That supersedes the Inquiry and Process Clarification staging reading taken when this row was appended, and the Platform Bug alternative named beside it: no software defect is involved. Closed by the owner on 26-Oct-2026: these are not open tickets any more. An RCA document was then attached to the ticket by Nitin Rindhe on 26-Oct-2026 and passed to Kishor Patil, who asked Steven Brandt to review it before it goes to the customer, so the status moves from Clarification Provided to RCA Shared on the owner's rule that attaching the RCA completes the record -- the same reading the Irving Oil row carries. That supersedes the note on this row that no RCA document was attached. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. The ticket carries no resolutiondate, so Resolution Date stays blank. Outstanding and carried by a human from here: an internal Nonconformity was raised to document the assessment error and track its corrective and preventive actions, and nothing here tracks that NC.</t>
         </is>
       </c>
       <c r="P130" s="33" t="n"/>
@@ -17742,7 +17742,7 @@
       </c>
       <c r="X130" s="33" t="inlineStr">
         <is>
-          <t>An RCA document was attached to EAO-56 on 26-Oct-2026 by Nitin Rindhe and is with the CSM for review before it goes to Collins Aerospace. Its text is an attachment that is not readable from the ticket, and the ticket's own comments are routing notes rather than findings, so the cause it names is not known here. The row's Root Cause and Sub-type remain the staging reading taken when it was appended: whether the Supplier Impact Notification fired against its own guideline has not been established.</t>
+          <t>An assessment error during human-in-the-loop review in determining the appropriate timing of supplier outreach. The reporting team correctly assessed the storm's intensification and created the WarRoom; an error in judgment then resulted in the premature issuance of the Supplier Impact Notification. Under the existing guidelines, customer impact notifications may be issued when the forecasted storm path becomes known, while Supplier Impact Confirmation requests should be initiated upon landfall. Corrective actions: the 07-Oct notification decision was reviewed and the Supplier Impact Notification confirmed as issued prematurely, contrary to the established pre-landfall reporting guidelines; an internal Nonconformity was raised to formally document the assessment error and track the corrective and preventive actions; and the distinction between pre-landfall Customer Impact Notifications and post-landfall Supplier Impact Confirmation requests was reinforced with the reporting team. Preventive measures: the reporting team has been reminded that storm formation, naming, intensification or changes in the forecasted path do not independently justify issuing Supplier Impact Confirmation requests before landfall; analysts are to verify a storm's landfall status against credible meteorological sources and the applicable EventWatch reporting guidelines before issuing supplier impact requests for hurricanes, typhoons or tropical storms; and this incident is used as a reference scenario in reporting-team quality reviews. Taken from the RCA attached to EAO-56 on 26-Oct-2026.</t>
         </is>
       </c>
       <c r="Y130" s="33" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C67" s="23" t="n" cm="1">
         <f t="array" ref="C67:C76">_xlfn.ANCHORARRAY(B67)/COUNTIF(ComplaintTracker[Issue Type],"Complaint")</f>
-        <v>0.3300970873786408</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="D67" s="3" t="n"/>
       <c r="E67" s="18" t="inlineStr">
@@ -19549,7 +19549,7 @@
         <v>13</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.1262135922330097</v>
+        <v>0.125</v>
       </c>
       <c r="D68" s="3" t="n"/>
       <c r="E68" s="20" t="inlineStr">
@@ -19591,7 +19591,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="24" t="n">
-        <v>0.06796116504854369</v>
+        <v>0.0673076923076923</v>
       </c>
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="20" t="inlineStr">
@@ -19630,10 +19630,10 @@
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.04854368932038835</v>
+        <v>0.057692307692307696</v>
       </c>
       <c r="D70" s="3" t="n"/>
       <c r="E70" s="20" t="inlineStr">
@@ -19675,7 +19675,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="24" t="n">
-        <v>0.038834951456310676</v>
+        <v>0.038461538461538464</v>
       </c>
       <c r="D71" s="3" t="n"/>
       <c r="E71" s="20" t="inlineStr">
@@ -19717,7 +19717,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.038834951456310676</v>
+        <v>0.038461538461538464</v>
       </c>
       <c r="D72" s="3" t="n"/>
       <c r="E72" s="20" t="inlineStr">
@@ -19759,7 +19759,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="24" t="n">
-        <v>0.02912621359223301</v>
+        <v>0.028846153846153848</v>
       </c>
       <c r="D73" s="3" t="n"/>
       <c r="E73" s="20" t="inlineStr">
@@ -19801,7 +19801,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.019230769230769232</v>
       </c>
       <c r="D74" s="3" t="n"/>
       <c r="E74" s="20" t="inlineStr">
@@ -19843,7 +19843,7 @@
         <v>2</v>
       </c>
       <c r="C75" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.019230769230769232</v>
       </c>
       <c r="D75" s="3" t="n"/>
       <c r="E75" s="20" t="inlineStr">
@@ -19885,7 +19885,7 @@
         <v>2</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.019417475728155338</v>
+        <v>0.019230769230769232</v>
       </c>
       <c r="D76" s="3" t="n"/>
       <c r="E76" s="20" t="inlineStr">
@@ -20010,10 +20010,10 @@
         </is>
       </c>
       <c r="J79" s="76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" s="76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L79" s="76" t="n">
         <v>3</v>
@@ -20382,10 +20382,10 @@
         </is>
       </c>
       <c r="J93" s="77" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K93" s="77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L93" s="77" t="n">
         <v>129</v>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -1771,10 +1771,10 @@
                   <v>46</v>
                 </pt>
                 <pt idx="1">
-                  <v>41</v>
+                  <v>44</v>
                 </pt>
                 <pt idx="2">
-                  <v>17</v>
+                  <v>14</v>
                 </pt>
                 <pt idx="3">
                   <v>0</v>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="O104" s="33" t="inlineStr">
         <is>
-          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, In Progress) and EAO-36 (Ford, 08-Sep, closed 22-Oct-2026). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Closed by the owner on 22-Oct-2026: the Data team acknowledged the geocode issue and nothing further is coming back on the source of the Pune site's coordinates, so the row is settled on the finding above rather than held open for an answer. EAO-36 resolved 22-Oct-2026 and EAO-35 was still at In Progress when the owner closed it. One thing is recorded as unconfirmed rather than chased: the DO team's correction of the SMI AMTEK coordinates. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
+          <t>One incident reported by two customers on consecutive days, merged from Jira EAO-35 (Eaton, 07-Sep, In Progress) and EAO-36 (Ford, 08-Sep, closed 22-Oct-2026). Eaton queried why four Tier 1 suppliers including a logistics partner were mapped to a Punjab risk event when their CDIF lists only Kumar Exports in Punjab, with Bhavani Industries (Maharashtra) and MT Autocraft (Himachal Pradesh) also attached and Tier 2 mappings reaching LOROM Industrial (Taipei) and DB Schenker (Barcelona). Ford separately reported that a Punjab power-cut WarRoom sent an impact-confirmation request to SMI AMTEK CRANKSHAFT in Dharuhera, Haryana, and that SNAP shows no active direct Tier 1 suppliers in Punjab at all, generating wasted supplier outreach. The geofence polygon over the affected region was correct and supplier selection is system-driven, so the cause is incorrect geocoding of supplier site coordinates rather than an operator or polygon error. Ford requested RCA, immediate corrective action and preventive corrective action. Number of Customers is 2; see the customer exposure table for the per-customer split. Confirmed on 08-Oct-2026 as a geocode mismatch, not a probable one: the SMI AMTEK site carried two sets of coordinates and one of them pinned it near Chandigarh. The impact polygon and the automated selection operated correctly on the coordinates available in the system. Sub-type moved from Mapping / Routing Defect to Incorrect Geocode on 22-Oct-2026, that value having been added for this failure. Closed by the owner on 22-Oct-2026: the Data team acknowledged the geocode issue and nothing further is coming back on the source of the Pune site's coordinates, so the row is settled on the finding above rather than held open for an answer. EAO-36 resolved 22-Oct-2026 and EAO-35 was still at In Progress when the owner closed it. The DO team's correction of the SMI AMTEK coordinates was recorded as unconfirmed. Closed by the owner on 27-Oct-2026: the RCA has been shared, which ends this record, and the correction is not held open against it. The proximity explanation given to the customer on 11-Sep-2026 is superseded by the finding above.</t>
         </is>
       </c>
       <c r="P104" s="33" t="n"/>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="L126" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M126" s="33" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="X126" s="33" t="inlineStr">
         <is>
-          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. Three of the five URLs belong to this row, and the findings differ by outlet. The Asia Times report of 04-Sep-2026 and the MarketScreener report of 18-Sep-2026 WERE captured by the vendor, and Engineering is still checking why they did not reach our system, naming a keyword miss or RSS leakage as the two candidates. The FT Mercati report of 18-Sep-2026 was NOT captured by the vendor, which is a source miss on that outlet, and a request has been raised with them to add it. The row stays Keyword Update because a source miss on FT Mercati is not what stopped delivery: two other outlets carrying the same story did reach the vendor, so Belden would have been notified had those come through. That is the only concluded finding on this row, and the cause of the two that did arrive is still open. OPEN FOR THE OWNER: filing this row as Source Coverage instead is a one-field change if the FT Mercati finding is to be the one the row carries. Note also that this row previously named Reuters as the carrying outlet; the ticket's own evidence URLs are Asia Times, MarketScreener and FT Mercati.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. Closed by the owner on 27-Oct-2026: the PM has addressed the investigation and one shared RCA is being issued across the three events on this ticket, which is what settles these rows on the owner's rule that attaching the RCA completes the record. The Jira ticket is at Sent to PM and carries no resolutiondate, so Resolution Date stays blank rather than being guessed. Three of the five URLs belong to this row, and the findings differ by outlet. The Asia Times report of 04-Sep-2026 and the MarketScreener report of 18-Sep-2026 WERE captured by the vendor, and Engineering is still checking why they did not reach our system, naming a keyword miss or RSS leakage as the two candidates. The FT Mercati report of 18-Sep-2026 was NOT captured by the vendor, which is a source miss on that outlet, and a request has been raised with them to add it. The row stays Keyword Update because a source miss on FT Mercati is not what stopped delivery: two other outlets carrying the same story did reach the vendor, so Belden would have been notified had those come through. That is the only concluded finding on this row, and the cause of the two that did arrive is still open. That open question is closed with the row: it stays Keyword Update, and the FT Mercati source miss is recorded above rather than becoming the cause the row carries. Note also that this row previously named Reuters as the carrying outlet; the ticket's own evidence URLs are Asia Times, MarketScreener and FT Mercati.</t>
         </is>
       </c>
       <c r="Y126" s="33" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="L127" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M127" s="33" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="X127" s="33" t="inlineStr">
         <is>
-          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. The DigiTimes report of 02-Jul-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. STILL OPEN and nothing automatic will settle it.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. Closed by the owner on 27-Oct-2026: the PM has addressed the investigation and one shared RCA is being issued across the three events on this ticket, which is what settles these rows on the owner's rule that attaching the RCA completes the record. The Jira ticket is at Sent to PM and carries no resolutiondate, so Resolution Date stays blank rather than being guessed. The DigiTimes report of 02-Jul-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. That is as far as the evidence goes, and the row is settled on it rather than held open for capture evidence the retention window cannot produce.</t>
         </is>
       </c>
       <c r="Y127" s="33" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="L128" s="33" t="inlineStr">
         <is>
-          <t>Clarification Provided</t>
+          <t>RCA Shared</t>
         </is>
       </c>
       <c r="M128" s="33" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="X128" s="33" t="inlineStr">
         <is>
-          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. The ticket is still at Sent to PM with no resolution date. The DigiTimes report of 04-May-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. STILL OPEN and nothing automatic will settle it.</t>
+          <t>Engineering update of 22-Oct-2026 from Ankit Gupta, matched to the article URLs Nitin Rindhe put to him on 21-Oct-2026. Closed by the owner on 27-Oct-2026: the PM has addressed the investigation and one shared RCA is being issued across the three events on this ticket, which is what settles these rows on the owner's rule that attaching the RCA completes the record. The Jira ticket is at Sent to PM and carries no resolutiondate, so Resolution Date stays blank rather than being guessed. The DigiTimes report of 04-May-2026 is the URL behind this row, and it cannot be investigated: Engineering states the vendor does not store data beyond 100 days, so the article is outside the retention window and no capture evidence can be produced either way. It is therefore not among the articles confirmed as not captured, and the row keeps the Keyword Update staging guess, which rests on the owner's 18-Oct-2026 confirmation that DigiTimes is monitored. That is as far as the evidence goes, and the row is settled on it rather than held open for capture evidence the retention window cannot produce.</t>
         </is>
       </c>
       <c r="Y128" s="33" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="O130" s="33" t="inlineStr">
         <is>
-          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as a Complaint on the owner's instruction of 27-Oct-2026: the RCA establishes that a guideline was broken, which is the test for a complaint rather than a question about how something works. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. Settled by the owner on 27-Oct-2026 against the RCA document, which the owner pasted in because its text is not readable from the ticket: this is analyst error and not an inquiry. The reporting team assessed the storm's intensification correctly and the WarRoom was right; the error was issuing the Supplier Impact Notification before landfall, contrary to a guideline that was itself sound. That supersedes the Inquiry and Process Clarification staging reading taken when this row was appended, and the Platform Bug alternative named beside it: no software defect is involved. Closed by the owner on 26-Oct-2026: these are not open tickets any more. An RCA document was then attached to the ticket by Nitin Rindhe on 26-Oct-2026 and passed to Kishor Patil, who asked Steven Brandt to review it before it goes to the customer, so the status moves from Clarification Provided to RCA Shared on the owner's rule that attaching the RCA completes the record -- the same reading the Irving Oil row carries. That supersedes the note on this row that no RCA document was attached. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. The ticket carries no resolutiondate, so Resolution Date stays blank. Outstanding and carried by a human from here: an internal Nonconformity was raised to document the assessment error and track its corrective and preventive actions, and nothing here tracks that NC.</t>
+          <t>Collins Aerospace asked why a Supplier Impact Notification was sent on 07-Oct-2026 for the WarRoom Tropical Depression Nine Forms in the Southwestern Gulf, when the storm had not yet made landfall and the WarRoom guideline they cite calls for the notification at landfall. Customer Support confirmed in the Collins Aerospace org that the notification was sent on 07-Oct-2026, the same date the WarRoom was created, and set out the timeline: the depression formed 06-Oct, became Tropical Storm Isaias on 07-Oct, became a hurricane at 22:30 CDT on 07-Oct, and made landfall near Destin, Florida at about 20:30 CDT on 09-Oct. The customer states this is not the first occurrence. Logged as a Complaint on the owner's instruction of 27-Oct-2026: the RCA establishes that a guideline was broken, which is the test for a complaint rather than a question about how something works. Missed_Flag is No because the WarRoom was created and the notification did reach Collins Aerospace; the question is its timing, not its delivery. Settled by the owner on 27-Oct-2026 against the RCA document, which the owner pasted in because its text is not readable from the ticket: this is analyst error and not an inquiry. The reporting team assessed the storm's intensification correctly and the WarRoom was right; the error was issuing the Supplier Impact Notification before landfall, contrary to a guideline that was itself sound. That supersedes the Inquiry and Process Clarification staging reading taken when this row was appended, and the Platform Bug alternative named beside it: no software defect is involved. Closed by the owner on 26-Oct-2026: these are not open tickets any more. An RCA document was then attached to the ticket by Nitin Rindhe on 26-Oct-2026 and passed to Kishor Patil, who asked Steven Brandt to review it before it goes to the customer, so the status moves from Clarification Provided to RCA Shared on the owner's rule that attaching the RCA completes the record -- the same reading the Irving Oil row carries. That supersedes the note on this row that no RCA document was attached. Resolution Date stays blank because the Jira ticket carries no resolutiondate and a guessed one is worse than none. NOTHING AUTOMATIC WILL LOOK AT THIS ROW AGAIN: the daily re-check scans Pending rows only. The ticket carries no resolutiondate, so Resolution Date stays blank. An internal Nonconformity was raised to document the assessment error and track its corrective and preventive actions. Closed by the owner on 27-Oct-2026: the RCA has been shared, which ends this record -- the NC runs in the quality system and is not a loose end the tracker carries.</t>
         </is>
       </c>
       <c r="P130" s="33" t="n"/>

--- a/EventWatch_Customer_Complaints_2026.xlsx
+++ b/EventWatch_Customer_Complaints_2026.xlsx
@@ -10321,7 +10321,7 @@
       </c>
       <c r="K64" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L64" s="33" t="inlineStr">
@@ -10341,7 +10341,7 @@
       </c>
       <c r="O64" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected.</t>
+          <t>From Jira CAN-3377 (Resolved). The 'Credit Suisse to be Acquired by UBS Group' alert and all 14 of its updates were absent from Ford's EventWatch News Dashboard, and keyword searches there returned No Data Available. The same alert was returned normally by Global Search, so the content existed and only the dashboard view was affected. Improvement VS Bug moved from Improvement to Bug on the owner's call of 27-Oct-2026: the defect is confirmed and a fix was shipped, so the field was reading the opposite of what the record establishes.</t>
         </is>
       </c>
       <c r="P64" s="33" t="n"/>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="K87" s="33" t="inlineStr">
         <is>
-          <t>Improvement</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="L87" s="33" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt. Whitespace / data-hygiene matching defect fixed under TENAR-45367.</t>
+          <t>From Jira CAN-3433 (Resolved). For Hitachi, a single Disruption Agent prompt asking for both Tier 1 and Tier 2 suppliers potentially impacted by the 6.8 magnitude Kumamoto earthquake returned Tier 1 only; Tier 2 required a second prompt. Whitespace / data-hygiene matching defect fixed under TENAR-45367. Improvement VS Bug moved from Improvement to Bug on the owner's call of 27-Oct-2026: the defect is confirmed and a fix was shipped, so the field was reading the opposite of what the record establishes.</t>
         </is>
       </c>
       <c r="P87" s="33" t="n"/>
